--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AFE47E-64B3-4E1F-95F6-E0C8DBCF8168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF909C17-5CC9-46E9-86D9-B19855C126E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -2059,7 +2059,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2104,8 +2104,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2121,6 +2129,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2153,7 +2167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2184,6 +2198,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3476,6 +3491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L661"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3532,7 +3548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>143</v>
       </c>
@@ -3564,7 +3580,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>144</v>
       </c>
@@ -3596,7 +3612,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>145</v>
       </c>
@@ -3628,7 +3644,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>146</v>
       </c>
@@ -3660,7 +3676,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>147</v>
       </c>
@@ -3692,7 +3708,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>148</v>
       </c>
@@ -3724,7 +3740,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>149</v>
       </c>
@@ -3756,7 +3772,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>150</v>
       </c>
@@ -3788,7 +3804,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>151</v>
       </c>
@@ -3820,7 +3836,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>152</v>
       </c>
@@ -3852,7 +3868,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>153</v>
       </c>
@@ -3884,7 +3900,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>154</v>
       </c>
@@ -3916,7 +3932,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>155</v>
       </c>
@@ -3948,7 +3964,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>156</v>
       </c>
@@ -3980,7 +3996,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>157</v>
       </c>
@@ -4012,7 +4028,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>158</v>
       </c>
@@ -4044,7 +4060,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>159</v>
       </c>
@@ -4076,7 +4092,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>160</v>
       </c>
@@ -4108,7 +4124,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>161</v>
       </c>
@@ -4140,7 +4156,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>162</v>
       </c>
@@ -4172,7 +4188,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>163</v>
       </c>
@@ -4204,7 +4220,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>164</v>
       </c>
@@ -4236,7 +4252,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>165</v>
       </c>
@@ -4268,7 +4284,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>166</v>
       </c>
@@ -4300,7 +4316,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>167</v>
       </c>
@@ -4332,7 +4348,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>168</v>
       </c>
@@ -4364,7 +4380,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>169</v>
       </c>
@@ -4396,7 +4412,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>170</v>
       </c>
@@ -4428,7 +4444,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>171</v>
       </c>
@@ -4492,7 +4508,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>173</v>
       </c>
@@ -4524,7 +4540,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>174</v>
       </c>
@@ -4556,7 +4572,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>175</v>
       </c>
@@ -4588,7 +4604,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>176</v>
       </c>
@@ -4620,7 +4636,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>177</v>
       </c>
@@ -4652,7 +4668,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>178</v>
       </c>
@@ -4684,7 +4700,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>179</v>
       </c>
@@ -4716,7 +4732,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>180</v>
       </c>
@@ -4748,7 +4764,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>181</v>
       </c>
@@ -4780,7 +4796,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>182</v>
       </c>
@@ -4812,7 +4828,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>183</v>
       </c>
@@ -4844,7 +4860,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>184</v>
       </c>
@@ -4876,7 +4892,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>185</v>
       </c>
@@ -4908,7 +4924,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>186</v>
       </c>
@@ -4940,7 +4956,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>187</v>
       </c>
@@ -4972,7 +4988,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>188</v>
       </c>
@@ -5004,7 +5020,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>266</v>
       </c>
@@ -5036,7 +5052,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>189</v>
       </c>
@@ -5068,7 +5084,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>190</v>
       </c>
@@ -5100,7 +5116,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>191</v>
       </c>
@@ -5132,7 +5148,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>192</v>
       </c>
@@ -5164,7 +5180,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>193</v>
       </c>
@@ -5196,7 +5212,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>194</v>
       </c>
@@ -5228,7 +5244,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>195</v>
       </c>
@@ -5260,7 +5276,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>196</v>
       </c>
@@ -5292,7 +5308,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>197</v>
       </c>
@@ -5324,7 +5340,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>198</v>
       </c>
@@ -5356,7 +5372,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>199</v>
       </c>
@@ -5388,7 +5404,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>200</v>
       </c>
@@ -5420,7 +5436,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>201</v>
       </c>
@@ -5452,7 +5468,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>202</v>
       </c>
@@ -5484,7 +5500,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>203</v>
       </c>
@@ -5516,7 +5532,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>204</v>
       </c>
@@ -5548,7 +5564,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>205</v>
       </c>
@@ -5580,7 +5596,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>206</v>
       </c>
@@ -5612,7 +5628,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>207</v>
       </c>
@@ -5644,7 +5660,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>208</v>
       </c>
@@ -5676,7 +5692,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>209</v>
       </c>
@@ -5708,7 +5724,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>210</v>
       </c>
@@ -5740,7 +5756,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>211</v>
       </c>
@@ -5772,7 +5788,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>218</v>
       </c>
@@ -5804,7 +5820,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>212</v>
       </c>
@@ -5836,7 +5852,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>213</v>
       </c>
@@ -5868,7 +5884,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>214</v>
       </c>
@@ -5900,7 +5916,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>215</v>
       </c>
@@ -5932,7 +5948,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>216</v>
       </c>
@@ -5964,7 +5980,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>217</v>
       </c>
@@ -5996,7 +6012,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>218</v>
       </c>
@@ -6028,7 +6044,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>219</v>
       </c>
@@ -6060,7 +6076,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>220</v>
       </c>
@@ -6092,7 +6108,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>221</v>
       </c>
@@ -6124,7 +6140,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>222</v>
       </c>
@@ -6156,7 +6172,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>223</v>
       </c>
@@ -6188,7 +6204,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>224</v>
       </c>
@@ -6220,7 +6236,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>225</v>
       </c>
@@ -6252,7 +6268,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>226</v>
       </c>
@@ -6284,7 +6300,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>227</v>
       </c>
@@ -6316,7 +6332,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>228</v>
       </c>
@@ -6348,7 +6364,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>229</v>
       </c>
@@ -6380,7 +6396,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>230</v>
       </c>
@@ -6412,7 +6428,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>231</v>
       </c>
@@ -6444,7 +6460,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>232</v>
       </c>
@@ -6476,7 +6492,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>233</v>
       </c>
@@ -6508,7 +6524,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>234</v>
       </c>
@@ -6540,7 +6556,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>235</v>
       </c>
@@ -6572,7 +6588,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>236</v>
       </c>
@@ -6604,7 +6620,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>237</v>
       </c>
@@ -6636,7 +6652,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>238</v>
       </c>
@@ -6668,7 +6684,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>239</v>
       </c>
@@ -6700,7 +6716,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>240</v>
       </c>
@@ -6732,7 +6748,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>241</v>
       </c>
@@ -6764,7 +6780,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>242</v>
       </c>
@@ -6796,7 +6812,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>243</v>
       </c>
@@ -6828,7 +6844,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>244</v>
       </c>
@@ -6860,7 +6876,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>245</v>
       </c>
@@ -6892,7 +6908,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>246</v>
       </c>
@@ -6924,7 +6940,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>247</v>
       </c>
@@ -6956,7 +6972,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>248</v>
       </c>
@@ -6988,7 +7004,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>249</v>
       </c>
@@ -7020,7 +7036,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>250</v>
       </c>
@@ -7052,7 +7068,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>251</v>
       </c>
@@ -7084,7 +7100,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>252</v>
       </c>
@@ -7116,7 +7132,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>206</v>
       </c>
@@ -7148,7 +7164,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>269</v>
       </c>
@@ -7177,7 +7193,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>253</v>
       </c>
@@ -7209,7 +7225,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>254</v>
       </c>
@@ -7241,7 +7257,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>255</v>
       </c>
@@ -7273,7 +7289,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>256</v>
       </c>
@@ -7305,7 +7321,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>257</v>
       </c>
@@ -7337,7 +7353,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>258</v>
       </c>
@@ -7369,7 +7385,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>259</v>
       </c>
@@ -7401,7 +7417,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>260</v>
       </c>
@@ -7433,7 +7449,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>261</v>
       </c>
@@ -7465,7 +7481,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>262</v>
       </c>
@@ -7497,7 +7513,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>221</v>
       </c>
@@ -7529,7 +7545,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>263</v>
       </c>
@@ -7561,7 +7577,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>264</v>
       </c>
@@ -7593,7 +7609,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>265</v>
       </c>
@@ -7625,7 +7641,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>212</v>
       </c>
@@ -7657,7 +7673,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>270</v>
       </c>
@@ -7686,7 +7702,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>271</v>
       </c>
@@ -7715,7 +7731,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>182</v>
       </c>
@@ -7747,7 +7763,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>266</v>
       </c>
@@ -7779,7 +7795,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>189</v>
       </c>
@@ -7811,7 +7827,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>217</v>
       </c>
@@ -7843,7 +7859,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>143</v>
       </c>
@@ -7875,7 +7891,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>145</v>
       </c>
@@ -7907,7 +7923,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>147</v>
       </c>
@@ -7939,7 +7955,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>148</v>
       </c>
@@ -7971,7 +7987,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>152</v>
       </c>
@@ -8003,7 +8019,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>153</v>
       </c>
@@ -8035,7 +8051,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>154</v>
       </c>
@@ -8067,7 +8083,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>158</v>
       </c>
@@ -8099,7 +8115,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>160</v>
       </c>
@@ -8131,7 +8147,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>161</v>
       </c>
@@ -8163,7 +8179,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>163</v>
       </c>
@@ -8227,7 +8243,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>174</v>
       </c>
@@ -8259,7 +8275,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>267</v>
       </c>
@@ -8291,7 +8307,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>177</v>
       </c>
@@ -8323,7 +8339,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>178</v>
       </c>
@@ -8355,7 +8371,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>268</v>
       </c>
@@ -8387,7 +8403,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>180</v>
       </c>
@@ -8419,7 +8435,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>182</v>
       </c>
@@ -8451,7 +8467,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>183</v>
       </c>
@@ -8483,7 +8499,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>184</v>
       </c>
@@ -8515,7 +8531,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>185</v>
       </c>
@@ -8547,7 +8563,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>187</v>
       </c>
@@ -8579,7 +8595,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>188</v>
       </c>
@@ -8611,7 +8627,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>266</v>
       </c>
@@ -8643,7 +8659,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>189</v>
       </c>
@@ -8675,7 +8691,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>190</v>
       </c>
@@ -8707,7 +8723,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
         <v>191</v>
       </c>
@@ -8739,7 +8755,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
         <v>192</v>
       </c>
@@ -8771,7 +8787,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>196</v>
       </c>
@@ -8803,7 +8819,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
         <v>199</v>
       </c>
@@ -8835,7 +8851,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>200</v>
       </c>
@@ -8867,7 +8883,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>201</v>
       </c>
@@ -8899,7 +8915,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>202</v>
       </c>
@@ -8931,7 +8947,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
         <v>206</v>
       </c>
@@ -8963,7 +8979,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
         <v>211</v>
       </c>
@@ -8995,7 +9011,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
         <v>218</v>
       </c>
@@ -9059,7 +9075,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
         <v>196</v>
       </c>
@@ -9091,7 +9107,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
         <v>143</v>
       </c>
@@ -9123,7 +9139,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
         <v>144</v>
       </c>
@@ -9155,7 +9171,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
         <v>145</v>
       </c>
@@ -9187,7 +9203,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
         <v>146</v>
       </c>
@@ -9219,7 +9235,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
         <v>147</v>
       </c>
@@ -9251,7 +9267,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
         <v>148</v>
       </c>
@@ -9283,7 +9299,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
         <v>149</v>
       </c>
@@ -9315,7 +9331,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
         <v>150</v>
       </c>
@@ -9347,7 +9363,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
         <v>152</v>
       </c>
@@ -9379,7 +9395,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4" t="s">
         <v>153</v>
       </c>
@@ -9411,7 +9427,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
         <v>154</v>
       </c>
@@ -9443,7 +9459,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
         <v>157</v>
       </c>
@@ -9475,7 +9491,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
         <v>158</v>
       </c>
@@ -9507,7 +9523,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
         <v>160</v>
       </c>
@@ -9539,7 +9555,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
         <v>161</v>
       </c>
@@ -9571,7 +9587,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
         <v>162</v>
       </c>
@@ -9603,7 +9619,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
         <v>163</v>
       </c>
@@ -9635,7 +9651,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
         <v>164</v>
       </c>
@@ -9667,7 +9683,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
         <v>167</v>
       </c>
@@ -9699,7 +9715,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
         <v>168</v>
       </c>
@@ -9731,7 +9747,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4" t="s">
         <v>170</v>
       </c>
@@ -9795,7 +9811,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4" t="s">
         <v>173</v>
       </c>
@@ -9827,7 +9843,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
         <v>174</v>
       </c>
@@ -9859,7 +9875,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4" t="s">
         <v>175</v>
       </c>
@@ -9891,7 +9907,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4" t="s">
         <v>176</v>
       </c>
@@ -9923,7 +9939,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
         <v>267</v>
       </c>
@@ -9955,7 +9971,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
         <v>177</v>
       </c>
@@ -9987,7 +10003,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
         <v>178</v>
       </c>
@@ -10019,7 +10035,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
         <v>268</v>
       </c>
@@ -10051,7 +10067,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
         <v>180</v>
       </c>
@@ -10083,7 +10099,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
         <v>181</v>
       </c>
@@ -10115,7 +10131,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
         <v>182</v>
       </c>
@@ -10147,7 +10163,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
         <v>183</v>
       </c>
@@ -10179,7 +10195,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
         <v>184</v>
       </c>
@@ -10211,7 +10227,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
         <v>185</v>
       </c>
@@ -10243,7 +10259,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
         <v>186</v>
       </c>
@@ -10275,7 +10291,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
         <v>187</v>
       </c>
@@ -10307,7 +10323,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
         <v>188</v>
       </c>
@@ -10339,7 +10355,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
         <v>266</v>
       </c>
@@ -10371,7 +10387,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
         <v>190</v>
       </c>
@@ -10403,7 +10419,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
         <v>191</v>
       </c>
@@ -10435,7 +10451,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
         <v>192</v>
       </c>
@@ -10467,7 +10483,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
         <v>194</v>
       </c>
@@ -10499,7 +10515,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
         <v>195</v>
       </c>
@@ -10531,7 +10547,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
         <v>196</v>
       </c>
@@ -10563,7 +10579,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
         <v>197</v>
       </c>
@@ -10595,7 +10611,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
         <v>198</v>
       </c>
@@ -10627,7 +10643,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
         <v>199</v>
       </c>
@@ -10659,7 +10675,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
         <v>200</v>
       </c>
@@ -10691,7 +10707,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
         <v>201</v>
       </c>
@@ -10723,7 +10739,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
         <v>202</v>
       </c>
@@ -10755,7 +10771,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
         <v>203</v>
       </c>
@@ -10787,7 +10803,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
         <v>204</v>
       </c>
@@ -10819,7 +10835,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
         <v>205</v>
       </c>
@@ -10851,7 +10867,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
         <v>206</v>
       </c>
@@ -10883,7 +10899,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
         <v>207</v>
       </c>
@@ -10915,7 +10931,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
         <v>208</v>
       </c>
@@ -10947,7 +10963,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
         <v>209</v>
       </c>
@@ -10979,7 +10995,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
         <v>210</v>
       </c>
@@ -11011,7 +11027,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
         <v>211</v>
       </c>
@@ -11043,7 +11059,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
         <v>218</v>
       </c>
@@ -11075,7 +11091,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
         <v>212</v>
       </c>
@@ -11107,7 +11123,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
         <v>216</v>
       </c>
@@ -11139,7 +11155,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
         <v>218</v>
       </c>
@@ -11171,7 +11187,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
         <v>221</v>
       </c>
@@ -11203,7 +11219,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
         <v>222</v>
       </c>
@@ -11235,7 +11251,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
         <v>223</v>
       </c>
@@ -11267,7 +11283,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
         <v>247</v>
       </c>
@@ -11299,7 +11315,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
         <v>257</v>
       </c>
@@ -11331,7 +11347,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
         <v>150</v>
       </c>
@@ -11363,7 +11379,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
         <v>235</v>
       </c>
@@ -11395,7 +11411,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
         <v>217</v>
       </c>
@@ -11427,7 +11443,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
         <v>248</v>
       </c>
@@ -11459,7 +11475,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
         <v>190</v>
       </c>
@@ -11491,7 +11507,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
         <v>264</v>
       </c>
@@ -11523,7 +11539,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
         <v>186</v>
       </c>
@@ -11555,7 +11571,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
         <v>180</v>
       </c>
@@ -11587,7 +11603,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>153</v>
       </c>
@@ -11619,7 +11635,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>148</v>
       </c>
@@ -11651,7 +11667,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>177</v>
       </c>
@@ -11683,7 +11699,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
         <v>189</v>
       </c>
@@ -11713,7 +11729,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
         <v>242</v>
       </c>
@@ -11745,7 +11761,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
         <v>159</v>
       </c>
@@ -11777,7 +11793,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="260" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
         <v>155</v>
       </c>
@@ -11807,7 +11823,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="261" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
         <v>225</v>
       </c>
@@ -11839,7 +11855,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
         <v>230</v>
       </c>
@@ -11871,7 +11887,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
         <v>218</v>
       </c>
@@ -11903,7 +11919,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
         <v>179</v>
       </c>
@@ -11935,7 +11951,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
         <v>191</v>
       </c>
@@ -11967,7 +11983,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
         <v>218</v>
       </c>
@@ -11997,7 +12013,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="267" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
         <v>189</v>
       </c>
@@ -12029,7 +12045,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
         <v>183</v>
       </c>
@@ -12061,7 +12077,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
         <v>207</v>
       </c>
@@ -12093,7 +12109,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
         <v>259</v>
       </c>
@@ -12125,7 +12141,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="271" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
         <v>221</v>
       </c>
@@ -12157,7 +12173,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="272" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
         <v>157</v>
       </c>
@@ -12189,7 +12205,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4" t="s">
         <v>233</v>
       </c>
@@ -12221,7 +12237,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="274" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4" t="s">
         <v>160</v>
       </c>
@@ -12253,7 +12269,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="4" t="s">
         <v>154</v>
       </c>
@@ -12285,7 +12301,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="276" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
         <v>147</v>
       </c>
@@ -12317,7 +12333,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="277" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
         <v>266</v>
       </c>
@@ -12347,7 +12363,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="278" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
         <v>185</v>
       </c>
@@ -12379,7 +12395,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="279" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
         <v>198</v>
       </c>
@@ -12411,7 +12427,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
         <v>168</v>
       </c>
@@ -12462,7 +12478,7 @@
       <c r="F281" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="I281">
+      <c r="I281" s="12">
         <v>390</v>
       </c>
       <c r="J281" s="1" t="s">
@@ -12475,7 +12491,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="282" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>143</v>
       </c>
@@ -12507,7 +12523,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>262</v>
       </c>
@@ -12537,7 +12553,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="284" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>163</v>
       </c>
@@ -12569,7 +12585,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>149</v>
       </c>
@@ -12601,7 +12617,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
         <v>162</v>
       </c>
@@ -12633,7 +12649,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="287" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
         <v>212</v>
       </c>
@@ -12665,7 +12681,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>266</v>
       </c>
@@ -12697,7 +12713,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
         <v>166</v>
       </c>
@@ -12729,7 +12745,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>156</v>
       </c>
@@ -12761,7 +12777,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="291" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>145</v>
       </c>
@@ -12793,7 +12809,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="292" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>161</v>
       </c>
@@ -12825,7 +12841,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="293" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>204</v>
       </c>
@@ -12857,7 +12873,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="294" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>213</v>
       </c>
@@ -12889,7 +12905,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="295" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>255</v>
       </c>
@@ -12921,7 +12937,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="296" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>146</v>
       </c>
@@ -12953,7 +12969,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>220</v>
       </c>
@@ -12985,7 +13001,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>192</v>
       </c>
@@ -13017,7 +13033,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>227</v>
       </c>
@@ -13049,7 +13065,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="300" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
         <v>187</v>
       </c>
@@ -13081,7 +13097,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="301" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
         <v>206</v>
       </c>
@@ -13113,7 +13129,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="302" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
         <v>265</v>
       </c>
@@ -13145,7 +13161,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="303" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
         <v>152</v>
       </c>
@@ -13177,7 +13193,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="304" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>229</v>
       </c>
@@ -13209,7 +13225,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="305" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>222</v>
       </c>
@@ -13241,7 +13257,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="306" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>158</v>
       </c>
@@ -13273,7 +13289,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="307" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>216</v>
       </c>
@@ -13305,7 +13321,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="308" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>246</v>
       </c>
@@ -13337,7 +13353,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="309" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
         <v>253</v>
       </c>
@@ -13369,7 +13385,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
         <v>249</v>
       </c>
@@ -13401,7 +13417,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="311" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
         <v>201</v>
       </c>
@@ -13433,7 +13449,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="312" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
         <v>276</v>
       </c>
@@ -13465,7 +13481,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
         <v>252</v>
       </c>
@@ -13497,7 +13513,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
         <v>226</v>
       </c>
@@ -13529,7 +13545,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="315" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
         <v>151</v>
       </c>
@@ -13561,7 +13577,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="316" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
         <v>232</v>
       </c>
@@ -13593,7 +13609,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="317" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
         <v>215</v>
       </c>
@@ -13625,7 +13641,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="318" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
         <v>237</v>
       </c>
@@ -13657,7 +13673,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="319" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
         <v>174</v>
       </c>
@@ -13689,7 +13705,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="320" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
         <v>236</v>
       </c>
@@ -13721,7 +13737,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
         <v>263</v>
       </c>
@@ -13753,7 +13769,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="322" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="4" t="s">
         <v>176</v>
       </c>
@@ -13785,7 +13801,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="323" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="4" t="s">
         <v>182</v>
       </c>
@@ -13817,7 +13833,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="324" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="4" t="s">
         <v>164</v>
       </c>
@@ -13849,7 +13865,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="325" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="4" t="s">
         <v>194</v>
       </c>
@@ -13881,7 +13897,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="326" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="4" t="s">
         <v>243</v>
       </c>
@@ -13913,7 +13929,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="327" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="4" t="s">
         <v>170</v>
       </c>
@@ -13945,7 +13961,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="328" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="4" t="s">
         <v>211</v>
       </c>
@@ -13977,7 +13993,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="329" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="4" t="s">
         <v>234</v>
       </c>
@@ -14009,7 +14025,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="330" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="4" t="s">
         <v>224</v>
       </c>
@@ -14041,7 +14057,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="331" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="4" t="s">
         <v>244</v>
       </c>
@@ -14073,7 +14089,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="332" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="4" t="s">
         <v>219</v>
       </c>
@@ -14105,7 +14121,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="4" t="s">
         <v>171</v>
       </c>
@@ -14137,7 +14153,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="4" t="s">
         <v>167</v>
       </c>
@@ -14167,7 +14183,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="4" t="s">
         <v>245</v>
       </c>
@@ -14199,7 +14215,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="4" t="s">
         <v>277</v>
       </c>
@@ -14229,7 +14245,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="337" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="4" t="s">
         <v>241</v>
       </c>
@@ -14261,7 +14277,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="338" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="4" t="s">
         <v>260</v>
       </c>
@@ -14291,7 +14307,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="339" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="4" t="s">
         <v>238</v>
       </c>
@@ -14323,7 +14339,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="340" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4" t="s">
         <v>144</v>
       </c>
@@ -14355,7 +14371,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="341" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="4" t="s">
         <v>202</v>
       </c>
@@ -14387,7 +14403,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="342" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4" t="s">
         <v>208</v>
       </c>
@@ -14419,7 +14435,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="343" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="4" t="s">
         <v>250</v>
       </c>
@@ -14451,7 +14467,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="344" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="4" t="s">
         <v>278</v>
       </c>
@@ -14483,7 +14499,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="345" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="4" t="s">
         <v>188</v>
       </c>
@@ -14515,7 +14531,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="346" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="4" t="s">
         <v>239</v>
       </c>
@@ -14547,7 +14563,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="347" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="4" t="s">
         <v>258</v>
       </c>
@@ -14577,7 +14593,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="348" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="4" t="s">
         <v>181</v>
       </c>
@@ -14609,7 +14625,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="349" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="4" t="s">
         <v>214</v>
       </c>
@@ -14641,7 +14657,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="350" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="4" t="s">
         <v>203</v>
       </c>
@@ -14673,7 +14689,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="351" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="4" t="s">
         <v>231</v>
       </c>
@@ -14705,7 +14721,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="352" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="4" t="s">
         <v>184</v>
       </c>
@@ -14737,7 +14753,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="353" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="4" t="s">
         <v>256</v>
       </c>
@@ -14769,7 +14785,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="354" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="4" t="s">
         <v>209</v>
       </c>
@@ -14801,7 +14817,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="355" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="4" t="s">
         <v>196</v>
       </c>
@@ -14833,7 +14849,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="356" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="4" t="s">
         <v>197</v>
       </c>
@@ -14865,7 +14881,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="357" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="4" t="s">
         <v>175</v>
       </c>
@@ -14897,7 +14913,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="358" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
         <v>195</v>
       </c>
@@ -14929,7 +14945,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="359" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
         <v>228</v>
       </c>
@@ -14961,7 +14977,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="360" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
         <v>200</v>
       </c>
@@ -14993,7 +15009,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="361" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
         <v>261</v>
       </c>
@@ -15023,7 +15039,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="362" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
         <v>205</v>
       </c>
@@ -15055,7 +15071,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="363" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
         <v>254</v>
       </c>
@@ -15087,7 +15103,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="364" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
         <v>199</v>
       </c>
@@ -15119,7 +15135,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="365" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
         <v>240</v>
       </c>
@@ -15151,7 +15167,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="366" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
         <v>210</v>
       </c>
@@ -15183,7 +15199,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="367" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
         <v>223</v>
       </c>
@@ -15215,7 +15231,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="368" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
         <v>161</v>
       </c>
@@ -15247,7 +15263,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="369" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
         <v>191</v>
       </c>
@@ -15279,7 +15295,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="370" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
         <v>205</v>
       </c>
@@ -15311,7 +15327,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="371" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
         <v>143</v>
       </c>
@@ -15343,7 +15359,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="372" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
         <v>152</v>
       </c>
@@ -15375,7 +15391,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="373" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
         <v>208</v>
       </c>
@@ -15407,7 +15423,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="374" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
         <v>207</v>
       </c>
@@ -15439,7 +15455,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="375" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
         <v>199</v>
       </c>
@@ -15471,7 +15487,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="376" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
         <v>211</v>
       </c>
@@ -15503,7 +15519,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="377" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>198</v>
       </c>
@@ -15535,7 +15551,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>209</v>
       </c>
@@ -15567,7 +15583,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="379" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>194</v>
       </c>
@@ -15609,7 +15625,7 @@
       <c r="C380" t="s">
         <v>275</v>
       </c>
-      <c r="D380" s="7" t="s">
+      <c r="D380" s="1" t="s">
         <v>306</v>
       </c>
       <c r="E380" s="1" t="s">
@@ -15631,7 +15647,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="381" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>162</v>
       </c>
@@ -15663,7 +15679,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="382" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>145</v>
       </c>
@@ -15695,7 +15711,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="383" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
         <v>148</v>
       </c>
@@ -15727,7 +15743,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="384" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
         <v>210</v>
       </c>
@@ -15759,7 +15775,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="385" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
         <v>153</v>
       </c>
@@ -15791,7 +15807,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="386" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
         <v>266</v>
       </c>
@@ -15823,7 +15839,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="387" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
         <v>212</v>
       </c>
@@ -15855,7 +15871,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="388" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -15884,7 +15900,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="389" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
         <v>181</v>
       </c>
@@ -15916,7 +15932,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="390" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
         <v>185</v>
       </c>
@@ -15948,7 +15964,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="391" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
         <v>206</v>
       </c>
@@ -15980,7 +15996,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="392" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
         <v>158</v>
       </c>
@@ -16012,7 +16028,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="393" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
         <v>146</v>
       </c>
@@ -16044,7 +16060,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="394" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
         <v>151</v>
       </c>
@@ -16076,7 +16092,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="395" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
         <v>197</v>
       </c>
@@ -16108,7 +16124,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="396" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
         <v>180</v>
       </c>
@@ -16140,7 +16156,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="397" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>190</v>
       </c>
@@ -16172,7 +16188,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="398" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>178</v>
       </c>
@@ -16204,7 +16220,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="399" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
         <v>188</v>
       </c>
@@ -16236,7 +16252,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="400" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
         <v>156</v>
       </c>
@@ -16268,7 +16284,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="401" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>186</v>
       </c>
@@ -16300,7 +16316,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="402" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>192</v>
       </c>
@@ -16332,7 +16348,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="403" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>195</v>
       </c>
@@ -16364,7 +16380,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="404" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>204</v>
       </c>
@@ -16396,7 +16412,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="405" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
         <v>160</v>
       </c>
@@ -16428,7 +16444,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="406" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>187</v>
       </c>
@@ -16460,7 +16476,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="407" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>164</v>
       </c>
@@ -16492,7 +16508,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="408" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>154</v>
       </c>
@@ -16524,7 +16540,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="409" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>218</v>
       </c>
@@ -16556,7 +16572,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="410" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>163</v>
       </c>
@@ -16588,7 +16604,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="411" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>168</v>
       </c>
@@ -16620,7 +16636,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="412" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>150</v>
       </c>
@@ -16652,7 +16668,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="413" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
         <v>268</v>
       </c>
@@ -16684,7 +16700,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="414" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
         <v>184</v>
       </c>
@@ -16716,7 +16732,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="415" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
         <v>144</v>
       </c>
@@ -16748,7 +16764,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="416" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
         <v>182</v>
       </c>
@@ -16780,7 +16796,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="417" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
         <v>196</v>
       </c>
@@ -16812,7 +16828,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="418" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
         <v>169</v>
       </c>
@@ -16844,7 +16860,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="419" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
         <v>157</v>
       </c>
@@ -16876,7 +16892,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="420" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
         <v>149</v>
       </c>
@@ -16908,7 +16924,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="421" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
         <v>200</v>
       </c>
@@ -16940,7 +16956,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="422" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
         <v>202</v>
       </c>
@@ -16972,7 +16988,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="423" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
         <v>155</v>
       </c>
@@ -17004,7 +17020,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
         <v>175</v>
       </c>
@@ -17036,7 +17052,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="425" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
         <v>176</v>
       </c>
@@ -17068,7 +17084,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="426" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
         <v>591</v>
       </c>
@@ -17100,7 +17116,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
         <v>167</v>
       </c>
@@ -17132,7 +17148,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
         <v>189</v>
       </c>
@@ -17164,7 +17180,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="429" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
         <v>593</v>
       </c>
@@ -17196,7 +17212,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="430" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
         <v>595</v>
       </c>
@@ -17228,7 +17244,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="431" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
         <v>159</v>
       </c>
@@ -17260,7 +17276,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="432" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
         <v>267</v>
       </c>
@@ -17292,7 +17308,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="433" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
         <v>170</v>
       </c>
@@ -17324,7 +17340,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="434" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
         <v>173</v>
       </c>
@@ -17356,7 +17372,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="435" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
         <v>597</v>
       </c>
@@ -17388,7 +17404,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="436" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
         <v>599</v>
       </c>
@@ -17420,7 +17436,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="437" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
         <v>177</v>
       </c>
@@ -17452,7 +17468,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="438" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
         <v>601</v>
       </c>
@@ -17484,7 +17500,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="439" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
         <v>276</v>
       </c>
@@ -17516,7 +17532,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="440" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
         <v>603</v>
       </c>
@@ -17548,7 +17564,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="441" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
         <v>605</v>
       </c>
@@ -17580,7 +17596,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="442" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
         <v>607</v>
       </c>
@@ -17612,7 +17628,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="443" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
         <v>609</v>
       </c>
@@ -17644,7 +17660,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="444" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
         <v>611</v>
       </c>
@@ -17676,7 +17692,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="445" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
         <v>165</v>
       </c>
@@ -17708,7 +17724,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="446" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
         <v>613</v>
       </c>
@@ -17740,7 +17756,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="447" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
         <v>615</v>
       </c>
@@ -17772,7 +17788,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="448" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
         <v>617</v>
       </c>
@@ -17804,7 +17820,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="449" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
         <v>619</v>
       </c>
@@ -17836,7 +17852,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
         <v>201</v>
       </c>
@@ -17868,7 +17884,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="451" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
         <v>277</v>
       </c>
@@ -17900,7 +17916,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="452" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
         <v>621</v>
       </c>
@@ -17932,7 +17948,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="453" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
         <v>623</v>
       </c>
@@ -17964,7 +17980,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="454" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
         <v>625</v>
       </c>
@@ -17996,7 +18012,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="455" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
         <v>627</v>
       </c>
@@ -18028,7 +18044,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="456" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
         <v>629</v>
       </c>
@@ -18060,7 +18076,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
         <v>147</v>
       </c>
@@ -18092,7 +18108,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="458" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
         <v>631</v>
       </c>
@@ -18124,7 +18140,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="459" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
         <v>633</v>
       </c>
@@ -18156,7 +18172,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="460" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
         <v>635</v>
       </c>
@@ -18188,7 +18204,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="461" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
         <v>166</v>
       </c>
@@ -18220,7 +18236,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="462" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
         <v>637</v>
       </c>
@@ -18252,7 +18268,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="463" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
         <v>639</v>
       </c>
@@ -18284,7 +18300,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="464" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
         <v>641</v>
       </c>
@@ -18316,7 +18332,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="465" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
         <v>643</v>
       </c>
@@ -18348,7 +18364,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="466" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
         <v>645</v>
       </c>
@@ -18380,7 +18396,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="467" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -18409,7 +18425,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="468" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -18438,7 +18454,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="469" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -18467,7 +18483,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="470" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -18496,7 +18512,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="471" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -18525,7 +18541,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="472" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
         <v>171</v>
       </c>
@@ -18557,7 +18573,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="473" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
         <v>647</v>
       </c>
@@ -18589,7 +18605,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="474" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
         <v>179</v>
       </c>
@@ -18621,7 +18637,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="475" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
         <v>649</v>
       </c>
@@ -18653,7 +18669,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="476" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
         <v>651</v>
       </c>
@@ -18685,7 +18701,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="477" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
         <v>653</v>
       </c>
@@ -18717,7 +18733,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="478" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -18746,7 +18762,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="479" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
         <v>183</v>
       </c>
@@ -18778,7 +18794,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="480" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
         <v>203</v>
       </c>
@@ -18810,7 +18826,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="481" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
         <v>216</v>
       </c>
@@ -18842,7 +18858,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="482" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
         <v>219</v>
       </c>
@@ -18874,7 +18890,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="483" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
         <v>217</v>
       </c>
@@ -18906,7 +18922,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="484" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
         <v>223</v>
       </c>
@@ -18938,7 +18954,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="485" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
         <v>221</v>
       </c>
@@ -18970,7 +18986,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="486" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
         <v>222</v>
       </c>
@@ -19002,7 +19018,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="487" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="4" t="s">
         <v>238</v>
       </c>
@@ -19034,7 +19050,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="488" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="4" t="s">
         <v>239</v>
       </c>
@@ -19066,7 +19082,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="489" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="4" t="s">
         <v>240</v>
       </c>
@@ -19098,7 +19114,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="490" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="4" t="s">
         <v>241</v>
       </c>
@@ -19130,7 +19146,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="491" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
         <v>220</v>
       </c>
@@ -19162,7 +19178,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="492" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
         <v>242</v>
       </c>
@@ -19194,7 +19210,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="493" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
         <v>254</v>
       </c>
@@ -19226,7 +19242,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="494" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="4" t="s">
         <v>257</v>
       </c>
@@ -19258,7 +19274,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="495" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -19287,7 +19303,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="496" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="4" t="s">
         <v>259</v>
       </c>
@@ -19319,7 +19335,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="497" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="4" t="s">
         <v>260</v>
       </c>
@@ -19351,7 +19367,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="498" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="4" t="s">
         <v>261</v>
       </c>
@@ -19383,7 +19399,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="499" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="4" t="s">
         <v>262</v>
       </c>
@@ -19415,7 +19431,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="500" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="4" t="s">
         <v>263</v>
       </c>
@@ -19447,7 +19463,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="501" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="4" t="s">
         <v>265</v>
       </c>
@@ -19479,7 +19495,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="502" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -19508,7 +19524,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="503" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="4" t="s">
         <v>255</v>
       </c>
@@ -19540,7 +19556,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="504" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="4" t="s">
         <v>253</v>
       </c>
@@ -19572,7 +19588,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="505" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="4" t="s">
         <v>214</v>
       </c>
@@ -19604,7 +19620,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="506" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="4" t="s">
         <v>655</v>
       </c>
@@ -19636,7 +19652,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="507" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="4" t="s">
         <v>269</v>
       </c>
@@ -19668,7 +19684,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="508" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
         <v>270</v>
       </c>
@@ -19700,7 +19716,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="509" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -19729,7 +19745,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="510" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="4" t="s">
         <v>150</v>
       </c>
@@ -19761,7 +19777,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="511" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="4" t="s">
         <v>146</v>
       </c>
@@ -19793,7 +19809,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="512" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="4" t="s">
         <v>158</v>
       </c>
@@ -19825,7 +19841,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="513" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="4" t="s">
         <v>210</v>
       </c>
@@ -19857,7 +19873,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="514" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="4" t="s">
         <v>207</v>
       </c>
@@ -19889,7 +19905,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="515" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="4" t="s">
         <v>157</v>
       </c>
@@ -19921,7 +19937,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="516" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="4" t="s">
         <v>194</v>
       </c>
@@ -19953,7 +19969,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="517" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="4" t="s">
         <v>156</v>
       </c>
@@ -19985,7 +20001,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="518" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="4" t="s">
         <v>170</v>
       </c>
@@ -20017,7 +20033,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="519" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="4" t="s">
         <v>217</v>
       </c>
@@ -20049,7 +20065,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="520" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="4" t="s">
         <v>188</v>
       </c>
@@ -20081,7 +20097,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="521" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="4" t="s">
         <v>197</v>
       </c>
@@ -20113,7 +20129,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="522" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -20142,7 +20158,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="523" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="4" t="s">
         <v>147</v>
       </c>
@@ -20174,7 +20190,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="524" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="4" t="s">
         <v>220</v>
       </c>
@@ -20206,7 +20222,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="525" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="4" t="s">
         <v>205</v>
       </c>
@@ -20238,7 +20254,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="526" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="4" t="s">
         <v>187</v>
       </c>
@@ -20270,7 +20286,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="527" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="4" t="s">
         <v>204</v>
       </c>
@@ -20302,7 +20318,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="528" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="4" t="s">
         <v>200</v>
       </c>
@@ -20334,7 +20350,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="529" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="4" t="s">
         <v>143</v>
       </c>
@@ -20366,7 +20382,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="530" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="4" t="s">
         <v>198</v>
       </c>
@@ -20398,7 +20414,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="531" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="4" t="s">
         <v>219</v>
       </c>
@@ -20430,7 +20446,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="532" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="4" t="s">
         <v>160</v>
       </c>
@@ -20462,7 +20478,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="533" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="4" t="s">
         <v>171</v>
       </c>
@@ -20494,7 +20510,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="534" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="4" t="s">
         <v>196</v>
       </c>
@@ -20526,7 +20542,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="535" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="4" t="s">
         <v>208</v>
       </c>
@@ -20558,7 +20574,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="536" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="4" t="s">
         <v>221</v>
       </c>
@@ -20590,7 +20606,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="537" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="4" t="s">
         <v>239</v>
       </c>
@@ -20622,7 +20638,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="538" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="4" t="s">
         <v>153</v>
       </c>
@@ -20654,7 +20670,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="539" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="4" t="s">
         <v>161</v>
       </c>
@@ -20686,7 +20702,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="540" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -20715,7 +20731,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="541" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="4" t="s">
         <v>192</v>
       </c>
@@ -20747,7 +20763,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="542" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="4" t="s">
         <v>195</v>
       </c>
@@ -20779,7 +20795,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="543" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A543" s="4" t="s">
         <v>202</v>
       </c>
@@ -20811,7 +20827,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="544" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A544" s="4" t="s">
         <v>218</v>
       </c>
@@ -20843,7 +20859,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="545" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="4" t="s">
         <v>241</v>
       </c>
@@ -20875,7 +20891,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="546" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A546" s="4" t="s">
         <v>149</v>
       </c>
@@ -20907,7 +20923,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="547" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A547" s="4" t="s">
         <v>151</v>
       </c>
@@ -20939,7 +20955,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="548" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A548" s="4" t="s">
         <v>180</v>
       </c>
@@ -20971,7 +20987,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="549" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A549" s="4" t="s">
         <v>184</v>
       </c>
@@ -21003,7 +21019,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="550" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A550" s="4" t="s">
         <v>186</v>
       </c>
@@ -21035,7 +21051,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="551" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -21064,7 +21080,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="552" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
         <v>199</v>
       </c>
@@ -21096,7 +21112,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="553" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A553" s="4" t="s">
         <v>206</v>
       </c>
@@ -21128,7 +21144,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="554" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A554" s="4" t="s">
         <v>214</v>
       </c>
@@ -21160,7 +21176,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="555" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A555" s="4" t="s">
         <v>163</v>
       </c>
@@ -21192,7 +21208,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="556" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="4" t="s">
         <v>191</v>
       </c>
@@ -21224,7 +21240,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="557" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A557" s="4" t="s">
         <v>203</v>
       </c>
@@ -21256,7 +21272,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="558" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A558" s="4" t="s">
         <v>209</v>
       </c>
@@ -21288,7 +21304,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="559" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A559" s="4" t="s">
         <v>223</v>
       </c>
@@ -21320,7 +21336,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="560" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="4" t="s">
         <v>242</v>
       </c>
@@ -21352,7 +21368,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="561" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A561" s="4" t="s">
         <v>255</v>
       </c>
@@ -21384,7 +21400,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="562" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A562" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -21413,7 +21429,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="563" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A563" s="4" t="s">
         <v>253</v>
       </c>
@@ -21445,7 +21461,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="564" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564" s="4" t="s">
         <v>254</v>
       </c>
@@ -21477,7 +21493,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="565" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565" s="4" t="s">
         <v>259</v>
       </c>
@@ -21509,7 +21525,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="566" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566" s="4" t="s">
         <v>260</v>
       </c>
@@ -21541,7 +21557,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="567" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567" s="4" t="s">
         <v>201</v>
       </c>
@@ -21573,7 +21589,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="568" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568" s="4" t="s">
         <v>265</v>
       </c>
@@ -21605,7 +21621,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="569" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="4" t="s">
         <v>216</v>
       </c>
@@ -21637,7 +21653,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="570" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="4" t="s">
         <v>270</v>
       </c>
@@ -21669,7 +21685,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="571" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -21698,7 +21714,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="572" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -21727,7 +21743,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="573" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -21756,7 +21772,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="574" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="4" t="s">
         <v>187</v>
       </c>
@@ -21788,7 +21804,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="575" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="4" t="s">
         <v>198</v>
       </c>
@@ -21820,7 +21836,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="576" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="4" t="s">
         <v>143</v>
       </c>
@@ -21852,7 +21868,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="577" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -21881,7 +21897,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="578" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="4" t="s">
         <v>205</v>
       </c>
@@ -21913,7 +21929,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="579" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="4" t="s">
         <v>199</v>
       </c>
@@ -21945,7 +21961,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="580" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="4" t="s">
         <v>200</v>
       </c>
@@ -21977,7 +21993,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="581" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A581" s="4" t="s">
         <v>145</v>
       </c>
@@ -22009,7 +22025,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="582" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A582" s="4" t="s">
         <v>146</v>
       </c>
@@ -22041,7 +22057,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="583" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A583" s="4" t="s">
         <v>147</v>
       </c>
@@ -22073,7 +22089,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="584" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A584" s="4" t="s">
         <v>150</v>
       </c>
@@ -22105,7 +22121,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="585" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A585" s="4" t="s">
         <v>154</v>
       </c>
@@ -22137,7 +22153,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="586" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A586" s="4" t="s">
         <v>155</v>
       </c>
@@ -22169,7 +22185,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="587" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A587" s="4" t="s">
         <v>156</v>
       </c>
@@ -22201,7 +22217,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="588" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A588" s="4" t="s">
         <v>157</v>
       </c>
@@ -22233,7 +22249,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="589" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A589" s="4" t="s">
         <v>158</v>
       </c>
@@ -22265,7 +22281,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="590" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A590" s="4" t="s">
         <v>159</v>
       </c>
@@ -22297,7 +22313,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="591" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A591" s="4" t="s">
         <v>160</v>
       </c>
@@ -22329,7 +22345,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="592" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A592" s="4" t="s">
         <v>170</v>
       </c>
@@ -22371,7 +22387,7 @@
       <c r="C593" t="s">
         <v>275</v>
       </c>
-      <c r="D593" s="6" t="s">
+      <c r="D593" s="1" t="s">
         <v>306</v>
       </c>
       <c r="E593" s="1" t="s">
@@ -22393,7 +22409,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="594" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A594" s="4" t="s">
         <v>185</v>
       </c>
@@ -22425,7 +22441,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="595" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A595" s="4" t="s">
         <v>187</v>
       </c>
@@ -22457,7 +22473,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="596" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A596" s="4" t="s">
         <v>188</v>
       </c>
@@ -22489,7 +22505,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="597" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A597" s="4" t="s">
         <v>194</v>
       </c>
@@ -22521,7 +22537,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="598" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A598" s="4" t="s">
         <v>196</v>
       </c>
@@ -22553,7 +22569,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="599" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A599" s="4" t="s">
         <v>197</v>
       </c>
@@ -22585,7 +22601,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="600" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A600" s="4" t="s">
         <v>198</v>
       </c>
@@ -22617,7 +22633,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="601" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A601" s="4" t="s">
         <v>200</v>
       </c>
@@ -22649,7 +22665,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="602" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A602" s="4" t="s">
         <v>201</v>
       </c>
@@ -22681,7 +22697,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="603" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A603" s="4" t="s">
         <v>204</v>
       </c>
@@ -22713,7 +22729,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="604" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A604" s="4" t="s">
         <v>205</v>
       </c>
@@ -22745,7 +22761,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="605" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A605" s="4" t="s">
         <v>207</v>
       </c>
@@ -22777,7 +22793,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="606" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A606" s="4" t="s">
         <v>208</v>
       </c>
@@ -22809,7 +22825,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="607" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A607" s="4" t="s">
         <v>209</v>
       </c>
@@ -22841,7 +22857,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="608" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A608" s="4" t="s">
         <v>210</v>
       </c>
@@ -22873,7 +22889,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="609" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A609" s="4" t="s">
         <v>218</v>
       </c>
@@ -22905,7 +22921,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="610" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A610" s="4" t="s">
         <v>212</v>
       </c>
@@ -22937,7 +22953,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="611" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A611" s="4" t="s">
         <v>217</v>
       </c>
@@ -22969,7 +22985,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="612" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A612" s="4" t="s">
         <v>219</v>
       </c>
@@ -23001,7 +23017,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="613" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A613" s="4" t="s">
         <v>220</v>
       </c>
@@ -23033,7 +23049,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="614" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A614" s="4" t="s">
         <v>222</v>
       </c>
@@ -23065,7 +23081,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="615" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A615" s="4" t="s">
         <v>238</v>
       </c>
@@ -23097,7 +23113,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="616" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A616" s="4" t="s">
         <v>239</v>
       </c>
@@ -23129,7 +23145,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="617" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A617" s="4" t="s">
         <v>240</v>
       </c>
@@ -23161,7 +23177,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="618" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A618" s="4" t="s">
         <v>241</v>
       </c>
@@ -23193,7 +23209,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="619" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A619" s="4" t="s">
         <v>212</v>
       </c>
@@ -23225,7 +23241,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="620" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A620" s="4" t="s">
         <v>261</v>
       </c>
@@ -23257,7 +23273,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="621" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A621" s="4" t="s">
         <v>262</v>
       </c>
@@ -23289,7 +23305,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="622" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A622" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -23318,7 +23334,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="623" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A623" s="4" t="s">
         <v>657</v>
       </c>
@@ -23350,7 +23366,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="624" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A624" s="4" t="s">
         <v>658</v>
       </c>
@@ -23382,7 +23398,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="625" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A625" s="4" t="s">
         <v>659</v>
       </c>
@@ -23414,7 +23430,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="626" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A626" s="4" t="s">
         <v>660</v>
       </c>
@@ -23446,7 +23462,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="627" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A627" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -23475,7 +23491,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="628" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A628" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -23504,7 +23520,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="629" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A629" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -23533,7 +23549,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="630" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A630" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -23562,7 +23578,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="631" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A631" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -23591,7 +23607,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="632" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A632" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -23620,7 +23636,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="633" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A633" s="4" t="s">
         <v>262</v>
       </c>
@@ -23652,7 +23668,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="634" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A634" s="4" t="s">
         <v>261</v>
       </c>
@@ -23684,7 +23700,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="635" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A635" s="4" t="s">
         <v>661</v>
       </c>
@@ -23716,7 +23732,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="636" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A636" s="4" t="s">
         <v>161</v>
       </c>
@@ -23748,7 +23764,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="637" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A637" s="4" t="s">
         <v>205</v>
       </c>
@@ -23780,7 +23796,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="638" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A638" s="4" t="s">
         <v>143</v>
       </c>
@@ -23812,7 +23828,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="639" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A639" s="4" t="s">
         <v>207</v>
       </c>
@@ -23844,7 +23860,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="640" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A640" s="4" t="s">
         <v>198</v>
       </c>
@@ -23886,7 +23902,7 @@
       <c r="C641" t="s">
         <v>275</v>
       </c>
-      <c r="D641" s="7" t="s">
+      <c r="D641" s="1" t="s">
         <v>306</v>
       </c>
       <c r="E641" s="1" t="s">
@@ -23908,7 +23924,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="642" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A642" s="4" t="s">
         <v>153</v>
       </c>
@@ -23940,7 +23956,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="643" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A643" s="4" t="s">
         <v>212</v>
       </c>
@@ -23972,7 +23988,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="644" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A644" s="4" t="s">
         <v>195</v>
       </c>
@@ -24004,7 +24020,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="645" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A645" s="4" t="s">
         <v>154</v>
       </c>
@@ -24036,7 +24052,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="646" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A646" s="4" t="s">
         <v>196</v>
       </c>
@@ -24068,7 +24084,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="647" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A647" s="4" t="s">
         <v>155</v>
       </c>
@@ -24100,7 +24116,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="648" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A648" s="4" t="s">
         <v>220</v>
       </c>
@@ -24132,7 +24148,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="649" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A649" s="4" t="s">
         <v>661</v>
       </c>
@@ -24164,7 +24180,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="650" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A650" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -24193,7 +24209,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="651" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A651" s="4" t="e">
         <v>#N/A</v>
       </c>
@@ -24222,7 +24238,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="652" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A652" s="4" t="s">
         <v>662</v>
       </c>
@@ -24254,7 +24270,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="653" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A653" s="4" t="s">
         <v>663</v>
       </c>
@@ -24286,7 +24302,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="654" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A654" s="4" t="s">
         <v>664</v>
       </c>
@@ -24318,7 +24334,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="655" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A655" s="4" t="s">
         <v>665</v>
       </c>
@@ -24350,7 +24366,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="656" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A656" s="4" t="s">
         <v>666</v>
       </c>
@@ -24382,7 +24398,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="657" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A657" s="4" t="s">
         <v>667</v>
       </c>
@@ -24414,7 +24430,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="658" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A658" s="4" t="s">
         <v>668</v>
       </c>
@@ -24446,7 +24462,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="659" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A659" s="4" t="s">
         <v>669</v>
       </c>
@@ -24478,7 +24494,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="660" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A660" s="4" t="s">
         <v>670</v>
       </c>
@@ -24510,7 +24526,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="661" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A661" s="4" t="s">
         <v>671</v>
       </c>
@@ -24543,7 +24559,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L661" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
+  <autoFilter ref="A1:L661" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="AI-04 Red"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="92" priority="488"/>
@@ -24562,7 +24584,7 @@
     <cfRule type="duplicateValues" dxfId="83" priority="268" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="82" priority="267"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D397:D427 D388:D395 D373:D386">
+  <conditionalFormatting sqref="D397:D427 D388:D395 D373:D379 D381:D386">
     <cfRule type="duplicateValues" dxfId="81" priority="285" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="80" priority="284"/>
     <cfRule type="duplicateValues" dxfId="79" priority="283" stopIfTrue="1"/>
@@ -24664,7 +24686,7 @@
   <conditionalFormatting sqref="D644:D646">
     <cfRule type="duplicateValues" dxfId="18" priority="41" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D644:D647 D639:D642">
+  <conditionalFormatting sqref="D644:D647 D639:D640 D642">
     <cfRule type="duplicateValues" dxfId="17" priority="49"/>
     <cfRule type="duplicateValues" dxfId="16" priority="50" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="15" priority="48" stopIfTrue="1"/>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 10\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E7F037-1E8F-492C-A123-043F34FFA367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 12\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0ED3DE6-631E-44A1-B07B-9A2D1C3E2711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 13\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79781DC1-9204-43B0-B728-487456D18F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -2604,6 +2604,66 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -2646,6 +2706,234 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2860,8 +3148,48 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2958,334 +3286,6 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -29033,141 +29033,141 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="D368">
     <cfRule type="duplicateValues" dxfId="97" priority="228"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="229"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="230" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="231" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="232" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="232" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="231" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="230" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D377">
-    <cfRule type="duplicateValues" dxfId="92" priority="233"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="234"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="235" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="235" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="237" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="89" priority="236" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="237" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D378:D408 D369:D376 D354:D367">
-    <cfRule type="duplicateValues" dxfId="87" priority="249"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="250" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="251"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="252" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="252" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="250" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="249"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D384:D403">
     <cfRule type="duplicateValues" dxfId="83" priority="248" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D458">
-    <cfRule type="duplicateValues" dxfId="82" priority="218"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="219"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="220" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="221" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="222" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="220" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="222" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="221" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D459:D461 D436:D457 D409:D411">
     <cfRule type="duplicateValues" dxfId="77" priority="283"/>
     <cfRule type="duplicateValues" dxfId="76" priority="284" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D459:D461">
-    <cfRule type="duplicateValues" dxfId="75" priority="285"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="286" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="286" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="285"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D463:D472">
-    <cfRule type="duplicateValues" dxfId="73" priority="894"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="895"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="896"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="897"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="898"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="899"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="900" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="901" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="901" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="900" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="899"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="898"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="896"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="894"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="895"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="897"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D474:D485">
-    <cfRule type="duplicateValues" dxfId="65" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="118" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="119" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="118" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="119" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D573:D613">
     <cfRule type="duplicateValues" dxfId="57" priority="846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D615:D616">
-    <cfRule type="duplicateValues" dxfId="56" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="99" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="101" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="99" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="101" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D617">
-    <cfRule type="duplicateValues" dxfId="52" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="95" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="96" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="97" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="95" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="97" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="96" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D618">
-    <cfRule type="duplicateValues" dxfId="47" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="88"/>
     <cfRule type="duplicateValues" dxfId="45" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="91" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="92" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="91" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="92" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D619:D625">
-    <cfRule type="duplicateValues" dxfId="39" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="84" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="77"/>
     <cfRule type="duplicateValues" dxfId="33" priority="83" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="84" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D632">
-    <cfRule type="duplicateValues" dxfId="31" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="68" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="69" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="69" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="68" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="27" priority="70" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D633:D643 D629:D631">
-    <cfRule type="duplicateValues" dxfId="26" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="72" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="74" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="74" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="72" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D638:D642">
     <cfRule type="duplicateValues" dxfId="22" priority="65" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D645:D647">
-    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
     <cfRule type="duplicateValues" dxfId="20" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="15" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="16" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="15" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D648:D671">
-    <cfRule type="duplicateValues" dxfId="13" priority="902"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="903"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="904"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="905"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="906"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="907"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="908" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="909" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="909" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="902"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="903"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="904"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="905"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="906"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="907"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="908" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
     <cfRule type="duplicateValues" dxfId="5" priority="788"/>
     <cfRule type="duplicateValues" dxfId="4" priority="789" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="3" priority="785"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="786" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="786" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="785"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
     <cfRule type="duplicateValues" dxfId="1" priority="783"/>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 15\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECB13C4-4BEC-4A59-AE50-F43438949D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -2391,56 +2391,6 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -2522,124 +2472,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3102,6 +2934,8 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3112,6 +2946,174 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3218,12 +3220,10 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -3233,7 +3233,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -3243,7 +3243,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -3253,7 +3253,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -3263,7 +3263,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -26810,165 +26810,159 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A555">
+    <cfRule type="duplicateValues" dxfId="105" priority="1070"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="1069"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A589:A594 A542:A587">
-    <cfRule type="duplicateValues" dxfId="105" priority="1001"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="1001"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A595:A600">
+    <cfRule type="duplicateValues" dxfId="102" priority="1061"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A603:A606">
+    <cfRule type="duplicateValues" dxfId="101" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="104" priority="904"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="904"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D542:D550">
+    <cfRule type="duplicateValues" dxfId="99" priority="1078" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D542:D551">
+    <cfRule type="duplicateValues" dxfId="98" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="1082" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="1081"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="1080" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D552:D554">
+    <cfRule type="duplicateValues" dxfId="94" priority="1124"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="1128" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="1127" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="1126" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="1125"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D556:D558">
+    <cfRule type="duplicateValues" dxfId="89" priority="1122" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="1121" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="1120"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="1119"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="1123" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D559:D562">
+    <cfRule type="duplicateValues" dxfId="84" priority="1089" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="1088"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="1086"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="1085"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="1084"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="1083"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="1090" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D563:D586">
+    <cfRule type="duplicateValues" dxfId="76" priority="1098" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="1097" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="1096"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="1095"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="1094"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="1093"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="1092"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="1091"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D588">
+    <cfRule type="duplicateValues" dxfId="68" priority="1100"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="1099"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1101"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="1102"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="1103"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="1105" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="1106" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D601:D602">
+    <cfRule type="duplicateValues" dxfId="60" priority="1114" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="1112"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="1113" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1111"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1110"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1109"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1108"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1107"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D604">
+    <cfRule type="duplicateValues" dxfId="52" priority="46" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="48" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="44" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D605:D606">
+    <cfRule type="duplicateValues" dxfId="47" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="43" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="42" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D607:D626">
+    <cfRule type="duplicateValues" dxfId="39" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="35" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="34" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D632">
+    <cfRule type="duplicateValues" dxfId="31" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="22" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="21" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="20" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D633:D642 D629:D631">
+    <cfRule type="duplicateValues" dxfId="26" priority="26" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D638:D641">
+    <cfRule type="duplicateValues" dxfId="22" priority="17" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D644:D646">
+    <cfRule type="duplicateValues" dxfId="21" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D647:D656">
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:H1">
+    <cfRule type="duplicateValues" dxfId="5" priority="1115"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1116" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="103" priority="902"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="903" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="903" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="902"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="101" priority="900"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="901" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A595:A600">
-    <cfRule type="duplicateValues" dxfId="99" priority="1061"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A555">
-    <cfRule type="duplicateValues" dxfId="98" priority="1069"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="1070"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D604">
-    <cfRule type="duplicateValues" dxfId="96" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="46" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D604">
-    <cfRule type="duplicateValues" dxfId="94" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="48" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D604">
-    <cfRule type="duplicateValues" dxfId="92" priority="44" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D605:D606">
-    <cfRule type="duplicateValues" dxfId="91" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="42" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="43" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D607:D626">
-    <cfRule type="duplicateValues" dxfId="83" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="34" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="35" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A603:A606">
-    <cfRule type="duplicateValues" dxfId="75" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D633:D642 D629:D631">
-    <cfRule type="duplicateValues" dxfId="74" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="24" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D633:D642 D629:D631">
-    <cfRule type="duplicateValues" dxfId="72" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="26" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D632">
-    <cfRule type="duplicateValues" dxfId="70" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="20" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="21" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="22" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D638:D641">
-    <cfRule type="duplicateValues" dxfId="65" priority="17" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D644:D646">
-    <cfRule type="duplicateValues" dxfId="64" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="15" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="16" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D647:D656">
-    <cfRule type="duplicateValues" dxfId="56" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="8" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D542:D550">
-    <cfRule type="duplicateValues" dxfId="48" priority="1078" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D542:D551">
-    <cfRule type="duplicateValues" dxfId="47" priority="1079"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="1080" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="1081"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="1082" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D559:D562">
-    <cfRule type="duplicateValues" dxfId="43" priority="1083"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="1084"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="1085"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="1086"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="1087"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="1088"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="1089" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="1090" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D563:D586">
-    <cfRule type="duplicateValues" dxfId="35" priority="1091"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="1092"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="1093"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="1094"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="1095"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="1096"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="1097" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="1098" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D588">
-    <cfRule type="duplicateValues" dxfId="27" priority="1099"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="1100"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="1101"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="1102"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="1103"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="1104"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="1105" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="1106" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D601:D602">
-    <cfRule type="duplicateValues" dxfId="19" priority="1107"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="1108"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1109"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="1110"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="1111"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1112"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="1113" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="1114" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="11" priority="1115"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="1116" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D556:D558">
-    <cfRule type="duplicateValues" dxfId="9" priority="1119"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="1120"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1121" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1122" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1123" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D552:D554">
-    <cfRule type="duplicateValues" dxfId="4" priority="1124"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1125"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1126" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1127" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="1128" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="901" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="900"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 17\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83FA14C-B0F8-43B4-8B4C-047FCAF41D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -2384,160 +2384,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2672,6 +2518,70 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2706,6 +2616,96 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -26061,114 +26061,114 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A444">
+    <cfRule type="duplicateValues" dxfId="64" priority="1676"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A468:A479 A336:A455">
+    <cfRule type="duplicateValues" dxfId="63" priority="1629"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A520:A550">
+    <cfRule type="duplicateValues" dxfId="62" priority="1628"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A520:A551">
+    <cfRule type="duplicateValues" dxfId="61" priority="1625"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A552">
-    <cfRule type="duplicateValues" dxfId="64" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A553">
+    <cfRule type="duplicateValues" dxfId="59" priority="1603"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="1602"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1604"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A554:A560">
+    <cfRule type="duplicateValues" dxfId="56" priority="1606"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="63" priority="1597"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D355">
-    <cfRule type="duplicateValues" dxfId="62" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="254" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="255" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="256" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="255" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="256" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="254" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D364">
-    <cfRule type="duplicateValues" dxfId="57" priority="257"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="259" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="260" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="261" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="260" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="259" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="261" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D365:D395 D356:D363 D341:D354">
-    <cfRule type="duplicateValues" dxfId="52" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="274" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="274" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D365:D395">
-    <cfRule type="duplicateValues" dxfId="50" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="276" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="276" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D371:D390">
-    <cfRule type="duplicateValues" dxfId="48" priority="272" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="272" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D440">
-    <cfRule type="duplicateValues" dxfId="47" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="244" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="245" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="246" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="246" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="244" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="245" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D442 D423:D439 D396:D398">
-    <cfRule type="duplicateValues" dxfId="42" priority="307"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="308" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="308" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D442">
-    <cfRule type="duplicateValues" dxfId="40" priority="309"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="310" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="310" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D445:D454">
+    <cfRule type="duplicateValues" dxfId="29" priority="1668"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1670"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1669"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1671"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1672"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1673"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1674" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1675" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D456:D463 D465:D466">
-    <cfRule type="duplicateValues" dxfId="38" priority="1443"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="1444"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="1445"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="1446"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="1447"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="1448"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="1449" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="1450" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1447"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1443"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1444"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1445"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1449" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1446"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1448"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1450" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D475:D479">
-    <cfRule type="duplicateValues" dxfId="30" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="126" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="127" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="127" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="126" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="22" priority="1595"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="1596" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1595"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1596" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="20" priority="1225"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="1226" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1226" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="18" priority="1223"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1224" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A553">
-    <cfRule type="duplicateValues" dxfId="16" priority="1602"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="1603"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1604"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A554:A560">
-    <cfRule type="duplicateValues" dxfId="13" priority="1605"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="1606"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A520:A551">
-    <cfRule type="duplicateValues" dxfId="11" priority="1625"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A520:A550">
-    <cfRule type="duplicateValues" dxfId="10" priority="1628"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A468:A479 A336:A455">
-    <cfRule type="duplicateValues" dxfId="9" priority="1629"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D445:D454">
-    <cfRule type="duplicateValues" dxfId="8" priority="1668"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1669"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1670"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1671"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1672"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1673"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1674" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1675" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A444">
-    <cfRule type="duplicateValues" dxfId="0" priority="1676"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1223"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1224" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83FA14C-B0F8-43B4-8B4C-047FCAF41D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810A5F8E-1495-465D-B307-29E1894A8818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -2327,7 +2327,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2335,7 +2335,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2372,26 +2371,6 @@
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
   <dxfs count="65">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2518,6 +2497,38 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -2540,18 +2551,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -11236,7 +11235,7 @@
         <v>1998</v>
       </c>
       <c r="I207">
-        <v>662</v>
+        <v>637</v>
       </c>
       <c r="J207" s="1" t="s">
         <v>464</v>
@@ -11274,7 +11273,7 @@
         <v>4107</v>
       </c>
       <c r="I208">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="J208" s="1" t="s">
         <v>464</v>
@@ -11349,8 +11348,8 @@
       <c r="H210" s="1">
         <v>1362</v>
       </c>
-      <c r="I210" s="3">
-        <v>1038</v>
+      <c r="I210">
+        <v>948</v>
       </c>
       <c r="J210" s="1" t="s">
         <v>464</v>
@@ -11388,7 +11387,7 @@
         <v>2006</v>
       </c>
       <c r="I211">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J211" s="1" t="s">
         <v>464</v>
@@ -11426,7 +11425,7 @@
         <v>1008</v>
       </c>
       <c r="I212">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="J212" s="1" t="s">
         <v>464</v>
@@ -11464,7 +11463,7 @@
         <v>1310</v>
       </c>
       <c r="I213">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J213" s="1" t="s">
         <v>464</v>
@@ -11502,7 +11501,7 @@
         <v>241</v>
       </c>
       <c r="I214">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="J214" s="1" t="s">
         <v>464</v>
@@ -11578,7 +11577,7 @@
         <v>1345</v>
       </c>
       <c r="I216">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J216" s="1" t="s">
         <v>464</v>
@@ -11616,7 +11615,7 @@
         <v>1865</v>
       </c>
       <c r="I217">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="J217" s="1" t="s">
         <v>464</v>
@@ -11654,7 +11653,7 @@
         <v>1130</v>
       </c>
       <c r="I218">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J218" s="1" t="s">
         <v>464</v>
@@ -11692,7 +11691,7 @@
         <v>1805</v>
       </c>
       <c r="I219">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J219" s="1" t="s">
         <v>464</v>
@@ -11730,7 +11729,7 @@
         <v>157</v>
       </c>
       <c r="I220">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J220" s="1" t="s">
         <v>464</v>
@@ -11768,7 +11767,7 @@
         <v>2005</v>
       </c>
       <c r="I221">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J221" s="1" t="s">
         <v>464</v>
@@ -11806,7 +11805,7 @@
         <v>3521</v>
       </c>
       <c r="I222">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="J222" s="1" t="s">
         <v>464</v>
@@ -11844,7 +11843,7 @@
         <v>3843</v>
       </c>
       <c r="I223">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J223" s="1" t="s">
         <v>464</v>
@@ -11882,7 +11881,7 @@
         <v>3342</v>
       </c>
       <c r="I224">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J224" s="1" t="s">
         <v>464</v>
@@ -11920,7 +11919,7 @@
         <v>963</v>
       </c>
       <c r="I225">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J225" s="1" t="s">
         <v>464</v>
@@ -11996,7 +11995,7 @@
         <v>2743</v>
       </c>
       <c r="I227">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J227" s="1" t="s">
         <v>464</v>
@@ -12034,7 +12033,7 @@
         <v>803</v>
       </c>
       <c r="I228">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J228" s="1" t="s">
         <v>464</v>
@@ -12072,7 +12071,7 @@
         <v>2139</v>
       </c>
       <c r="I229">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>464</v>
@@ -12148,7 +12147,7 @@
         <v>1675</v>
       </c>
       <c r="I231">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J231" s="1" t="s">
         <v>464</v>
@@ -12186,7 +12185,7 @@
         <v>807</v>
       </c>
       <c r="I232">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J232" s="1" t="s">
         <v>464</v>
@@ -12224,7 +12223,7 @@
         <v>2572</v>
       </c>
       <c r="I233">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J233" s="1" t="s">
         <v>464</v>
@@ -12262,7 +12261,7 @@
         <v>1760</v>
       </c>
       <c r="I234">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J234" s="1" t="s">
         <v>464</v>
@@ -12300,7 +12299,7 @@
         <v>1925</v>
       </c>
       <c r="I235">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J235" s="1" t="s">
         <v>464</v>
@@ -12338,7 +12337,7 @@
         <v>259</v>
       </c>
       <c r="I236">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="J236" s="1" t="s">
         <v>464</v>
@@ -12376,7 +12375,7 @@
         <v>2268</v>
       </c>
       <c r="I237">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J237" s="1" t="s">
         <v>464</v>
@@ -12490,7 +12489,7 @@
         <v>301</v>
       </c>
       <c r="I240">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J240" s="1" t="s">
         <v>464</v>
@@ -12528,7 +12527,7 @@
         <v>121</v>
       </c>
       <c r="I241">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J241" s="1" t="s">
         <v>464</v>
@@ -12603,7 +12602,9 @@
       <c r="H243" s="1">
         <v>1070</v>
       </c>
-      <c r="I243"/>
+      <c r="I243">
+        <v>0</v>
+      </c>
       <c r="J243" s="1" t="s">
         <v>464</v>
       </c>
@@ -12678,7 +12679,7 @@
         <v>685</v>
       </c>
       <c r="I245">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J245" s="1" t="s">
         <v>464</v>
@@ -12716,7 +12717,7 @@
         <v>2716</v>
       </c>
       <c r="I246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J246" s="1" t="s">
         <v>464</v>
@@ -12754,7 +12755,7 @@
         <v>3024</v>
       </c>
       <c r="I247">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J247" s="1" t="s">
         <v>464</v>
@@ -12830,7 +12831,7 @@
         <v>482</v>
       </c>
       <c r="I249">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J249" s="1" t="s">
         <v>464</v>
@@ -12906,7 +12907,7 @@
         <v>3140</v>
       </c>
       <c r="I251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J251" s="1" t="s">
         <v>464</v>
@@ -12982,7 +12983,7 @@
         <v>2133</v>
       </c>
       <c r="I253">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J253" s="1" t="s">
         <v>464</v>
@@ -13020,7 +13021,7 @@
         <v>2586</v>
       </c>
       <c r="I254">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J254" s="1" t="s">
         <v>464</v>
@@ -13058,7 +13059,7 @@
         <v>166</v>
       </c>
       <c r="I255">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J255" s="1" t="s">
         <v>464</v>
@@ -13172,7 +13173,7 @@
         <v>1997</v>
       </c>
       <c r="I258">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J258" s="1" t="s">
         <v>464</v>
@@ -13247,7 +13248,9 @@
       <c r="H260" s="1">
         <v>2587</v>
       </c>
-      <c r="I260"/>
+      <c r="I260">
+        <v>0</v>
+      </c>
       <c r="J260" s="1" t="s">
         <v>464</v>
       </c>
@@ -13284,7 +13287,7 @@
         <v>2683</v>
       </c>
       <c r="I261">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="J261" s="1" t="s">
         <v>464</v>
@@ -13360,7 +13363,7 @@
         <v>609</v>
       </c>
       <c r="I263">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J263" s="1" t="s">
         <v>464</v>
@@ -13398,7 +13401,7 @@
         <v>1956</v>
       </c>
       <c r="I264">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J264" s="1" t="s">
         <v>464</v>
@@ -13436,7 +13439,7 @@
         <v>2211</v>
       </c>
       <c r="I265">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J265" s="1" t="s">
         <v>464</v>
@@ -13473,7 +13476,9 @@
       <c r="H266" s="1">
         <v>1997</v>
       </c>
-      <c r="I266"/>
+      <c r="I266">
+        <v>0</v>
+      </c>
       <c r="J266" s="1" t="s">
         <v>464</v>
       </c>
@@ -13548,7 +13553,7 @@
         <v>441</v>
       </c>
       <c r="I268">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J268" s="1" t="s">
         <v>464</v>
@@ -13586,7 +13591,7 @@
         <v>3527</v>
       </c>
       <c r="I269">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J269" s="1" t="s">
         <v>464</v>
@@ -13700,7 +13705,7 @@
         <v>1731</v>
       </c>
       <c r="I272">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="J272" s="1" t="s">
         <v>464</v>
@@ -13737,7 +13742,9 @@
       <c r="H273" s="1">
         <v>1991</v>
       </c>
-      <c r="I273"/>
+      <c r="I273">
+        <v>0</v>
+      </c>
       <c r="J273" s="1" t="s">
         <v>464</v>
       </c>
@@ -13774,7 +13781,7 @@
         <v>2888</v>
       </c>
       <c r="I274">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J274" s="1" t="s">
         <v>464</v>
@@ -13812,7 +13819,7 @@
         <v>1205</v>
       </c>
       <c r="I275">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J275" s="1" t="s">
         <v>464</v>
@@ -13850,7 +13857,7 @@
         <v>13405</v>
       </c>
       <c r="I276">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J276" s="1" t="s">
         <v>464</v>
@@ -13925,7 +13932,9 @@
       <c r="H278" s="1">
         <v>3121</v>
       </c>
-      <c r="I278"/>
+      <c r="I278">
+        <v>0</v>
+      </c>
       <c r="J278" s="1" t="s">
         <v>464</v>
       </c>
@@ -14152,7 +14161,7 @@
         <v>1731</v>
       </c>
       <c r="I284">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J284" s="1" t="s">
         <v>464</v>
@@ -14190,7 +14199,7 @@
         <v>5837</v>
       </c>
       <c r="I285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J285" s="1" t="s">
         <v>464</v>
@@ -14266,7 +14275,7 @@
         <v>1203</v>
       </c>
       <c r="I287">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J287" s="1" t="s">
         <v>464</v>
@@ -14304,7 +14313,7 @@
         <v>1984</v>
       </c>
       <c r="I288">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J288" s="1" t="s">
         <v>464</v>
@@ -14380,7 +14389,7 @@
         <v>2526</v>
       </c>
       <c r="I290">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J290" s="1" t="s">
         <v>464</v>
@@ -14418,7 +14427,7 @@
         <v>1109</v>
       </c>
       <c r="I291">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="J291" s="1" t="s">
         <v>464</v>
@@ -14570,7 +14579,7 @@
         <v>872</v>
       </c>
       <c r="I295">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J295" s="1" t="s">
         <v>464</v>
@@ -14684,7 +14693,7 @@
         <v>552</v>
       </c>
       <c r="I298">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J298" s="1" t="s">
         <v>464</v>
@@ -14722,7 +14731,7 @@
         <v>1829</v>
       </c>
       <c r="I299">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J299" s="1" t="s">
         <v>464</v>
@@ -14760,7 +14769,7 @@
         <v>3149</v>
       </c>
       <c r="I300">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J300" s="1" t="s">
         <v>464</v>
@@ -14798,7 +14807,7 @@
         <v>805</v>
       </c>
       <c r="I301">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J301" s="1" t="s">
         <v>464</v>
@@ -14987,7 +14996,9 @@
       <c r="H306" s="1">
         <v>2458</v>
       </c>
-      <c r="I306"/>
+      <c r="I306">
+        <v>0</v>
+      </c>
       <c r="J306" s="1" t="s">
         <v>464</v>
       </c>
@@ -15023,7 +15034,9 @@
       <c r="H307" s="1">
         <v>3096</v>
       </c>
-      <c r="I307"/>
+      <c r="I307">
+        <v>0</v>
+      </c>
       <c r="J307" s="1" t="s">
         <v>464</v>
       </c>
@@ -15097,7 +15110,9 @@
       <c r="H309" s="1">
         <v>2587</v>
       </c>
-      <c r="I309"/>
+      <c r="I309">
+        <v>0</v>
+      </c>
       <c r="J309" s="1" t="s">
         <v>464</v>
       </c>
@@ -15248,7 +15263,7 @@
         <v>1809</v>
       </c>
       <c r="I313">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J313" s="1" t="s">
         <v>464</v>
@@ -15286,7 +15301,7 @@
         <v>1070</v>
       </c>
       <c r="I314">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J314" s="1" t="s">
         <v>464</v>
@@ -15362,7 +15377,7 @@
         <v>626</v>
       </c>
       <c r="I316">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J316" s="1" t="s">
         <v>464</v>
@@ -15514,7 +15529,7 @@
         <v>477</v>
       </c>
       <c r="I320">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="J320" s="1" t="s">
         <v>464</v>
@@ -15590,7 +15605,7 @@
         <v>7723</v>
       </c>
       <c r="I322">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J322" s="1" t="s">
         <v>464</v>
@@ -15628,7 +15643,7 @@
         <v>2745</v>
       </c>
       <c r="I323">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J323" s="1" t="s">
         <v>464</v>
@@ -15742,7 +15757,7 @@
         <v>566</v>
       </c>
       <c r="I326">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="J326" s="1" t="s">
         <v>464</v>
@@ -15780,7 +15795,7 @@
         <v>567</v>
       </c>
       <c r="I327">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="J327" s="1" t="s">
         <v>464</v>
@@ -15856,7 +15871,7 @@
         <v>3910</v>
       </c>
       <c r="I329">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J329" s="1" t="s">
         <v>464</v>
@@ -15894,7 +15909,7 @@
         <v>1384</v>
       </c>
       <c r="I330">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="J330" s="1" t="s">
         <v>464</v>
@@ -16008,7 +16023,7 @@
         <v>782</v>
       </c>
       <c r="I333">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="J333" s="1" t="s">
         <v>464</v>
@@ -16097,16 +16112,16 @@
       </c>
     </row>
     <row r="336" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A336" s="4" t="s">
+      <c r="A336" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B336" s="4" t="s">
+      <c r="B336" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C336" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D336" s="9" t="s">
+      <c r="C336" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D336" s="8" t="s">
         <v>335</v>
       </c>
       <c r="E336" s="1" t="s">
@@ -16121,7 +16136,7 @@
       <c r="H336" s="1">
         <v>259</v>
       </c>
-      <c r="I336" s="7">
+      <c r="I336" s="6">
         <v>24</v>
       </c>
       <c r="J336" s="1" t="s">
@@ -16135,16 +16150,16 @@
       </c>
     </row>
     <row r="337" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A337" s="4" t="s">
+      <c r="A337" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B337" s="4" t="s">
+      <c r="B337" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C337" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D337" s="9" t="s">
+      <c r="C337" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D337" s="8" t="s">
         <v>535</v>
       </c>
       <c r="E337" s="1" t="s">
@@ -16159,7 +16174,7 @@
       <c r="H337" s="1">
         <v>482</v>
       </c>
-      <c r="I337" s="7">
+      <c r="I337" s="6">
         <v>502</v>
       </c>
       <c r="J337" s="1" t="s">
@@ -16173,16 +16188,16 @@
       </c>
     </row>
     <row r="338" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A338" s="4" t="s">
+      <c r="A338" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B338" s="4" t="s">
+      <c r="B338" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C338" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D338" s="9" t="s">
+      <c r="C338" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D338" s="8" t="s">
         <v>380</v>
       </c>
       <c r="E338" s="1" t="s">
@@ -16197,7 +16212,7 @@
       <c r="H338" s="1">
         <v>1865</v>
       </c>
-      <c r="I338" s="7">
+      <c r="I338" s="6">
         <v>894</v>
       </c>
       <c r="J338" s="1" t="s">
@@ -16211,16 +16226,16 @@
       </c>
     </row>
     <row r="339" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A339" s="4" t="s">
+      <c r="A339" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B339" s="4" t="s">
+      <c r="B339" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C339" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D339" s="9" t="s">
+      <c r="C339" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D339" s="8" t="s">
         <v>317</v>
       </c>
       <c r="E339" s="1" t="s">
@@ -16235,7 +16250,7 @@
       <c r="H339" s="1">
         <v>1362</v>
       </c>
-      <c r="I339" s="7">
+      <c r="I339" s="6">
         <v>1124</v>
       </c>
       <c r="J339" s="1" t="s">
@@ -16249,16 +16264,16 @@
       </c>
     </row>
     <row r="340" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A340" s="4" t="s">
+      <c r="A340" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B340" s="4" t="s">
+      <c r="B340" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C340" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D340" s="9" t="s">
+      <c r="C340" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D340" s="8" t="s">
         <v>326</v>
       </c>
       <c r="E340" s="1" t="s">
@@ -16273,7 +16288,7 @@
       <c r="H340" s="1">
         <v>166</v>
       </c>
-      <c r="I340" s="7">
+      <c r="I340" s="6">
         <v>342</v>
       </c>
       <c r="J340" s="1" t="s">
@@ -16287,16 +16302,16 @@
       </c>
     </row>
     <row r="341" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A341" s="4" t="s">
+      <c r="A341" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B341" s="4" t="s">
+      <c r="B341" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C341" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D341" s="9" t="s">
+      <c r="C341" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D341" s="8" t="s">
         <v>383</v>
       </c>
       <c r="E341" s="1" t="s">
@@ -16311,7 +16326,7 @@
       <c r="H341" s="1">
         <v>803</v>
       </c>
-      <c r="I341" s="7">
+      <c r="I341" s="6">
         <v>637</v>
       </c>
       <c r="J341" s="1" t="s">
@@ -16325,16 +16340,16 @@
       </c>
     </row>
     <row r="342" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A342" s="4" t="s">
+      <c r="A342" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B342" s="4" t="s">
+      <c r="B342" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C342" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D342" s="9" t="s">
+      <c r="C342" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D342" s="8" t="s">
         <v>382</v>
       </c>
       <c r="E342" s="1" t="s">
@@ -16349,7 +16364,7 @@
       <c r="H342" s="1">
         <v>2006</v>
       </c>
-      <c r="I342" s="7">
+      <c r="I342" s="6">
         <v>357</v>
       </c>
       <c r="J342" s="1" t="s">
@@ -16363,16 +16378,16 @@
       </c>
     </row>
     <row r="343" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A343" s="4" t="s">
+      <c r="A343" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B343" s="4" t="s">
+      <c r="B343" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C343" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D343" s="9" t="s">
+      <c r="C343" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D343" s="8" t="s">
         <v>374</v>
       </c>
       <c r="E343" s="1" t="s">
@@ -16387,7 +16402,7 @@
       <c r="H343" s="1">
         <v>698</v>
       </c>
-      <c r="I343" s="7">
+      <c r="I343" s="6">
         <v>66</v>
       </c>
       <c r="J343" s="1" t="s">
@@ -16401,16 +16416,16 @@
       </c>
     </row>
     <row r="344" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A344" s="4" t="s">
+      <c r="A344" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B344" s="4" t="s">
+      <c r="B344" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C344" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D344" s="9" t="s">
+      <c r="C344" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D344" s="8" t="s">
         <v>386</v>
       </c>
       <c r="E344" s="1" t="s">
@@ -16425,7 +16440,7 @@
       <c r="H344" s="1">
         <v>3342</v>
       </c>
-      <c r="I344" s="7">
+      <c r="I344" s="6">
         <v>63</v>
       </c>
       <c r="J344" s="1" t="s">
@@ -16439,16 +16454,16 @@
       </c>
     </row>
     <row r="345" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A345" s="4" t="s">
+      <c r="A345" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B345" s="4" t="s">
+      <c r="B345" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C345" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D345" s="9" t="s">
+      <c r="C345" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D345" s="8" t="s">
         <v>373</v>
       </c>
       <c r="E345" s="1" t="s">
@@ -16463,7 +16478,7 @@
       <c r="H345" s="1">
         <v>1023</v>
       </c>
-      <c r="I345" s="7">
+      <c r="I345" s="6">
         <v>115</v>
       </c>
       <c r="J345" s="1" t="s">
@@ -16477,16 +16492,16 @@
       </c>
     </row>
     <row r="346" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A346" s="4" t="s">
+      <c r="A346" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B346" s="4" t="s">
+      <c r="B346" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C346" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D346" s="9" t="s">
+      <c r="C346" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D346" s="8" t="s">
         <v>384</v>
       </c>
       <c r="E346" s="1" t="s">
@@ -16501,7 +16516,7 @@
       <c r="H346" s="1">
         <v>2139</v>
       </c>
-      <c r="I346" s="7">
+      <c r="I346" s="6">
         <v>193</v>
       </c>
       <c r="J346" s="1" t="s">
@@ -16515,16 +16530,16 @@
       </c>
     </row>
     <row r="347" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A347" s="4" t="s">
+      <c r="A347" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B347" s="4" t="s">
+      <c r="B347" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C347" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D347" s="9" t="s">
+      <c r="C347" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D347" s="8" t="s">
         <v>369</v>
       </c>
       <c r="E347" s="1" t="s">
@@ -16539,7 +16554,7 @@
       <c r="H347" s="1">
         <v>1384</v>
       </c>
-      <c r="I347" s="7">
+      <c r="I347" s="6">
         <v>1357</v>
       </c>
       <c r="J347" s="1" t="s">
@@ -16553,16 +16568,16 @@
       </c>
     </row>
     <row r="348" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A348" s="4" t="s">
+      <c r="A348" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B348" s="4" t="s">
+      <c r="B348" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C348" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D348" s="9" t="s">
+      <c r="C348" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D348" s="8" t="s">
         <v>345</v>
       </c>
       <c r="E348" s="1" t="s">
@@ -16577,7 +16592,7 @@
       <c r="H348" s="1">
         <v>1998</v>
       </c>
-      <c r="I348" s="7">
+      <c r="I348" s="6">
         <v>761</v>
       </c>
       <c r="J348" s="1" t="s">
@@ -16591,16 +16606,16 @@
       </c>
     </row>
     <row r="349" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A349" s="4" t="s">
+      <c r="A349" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B349" s="4" t="s">
+      <c r="B349" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C349" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D349" s="9" t="s">
+      <c r="C349" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D349" s="8" t="s">
         <v>336</v>
       </c>
       <c r="E349" s="1" t="s">
@@ -16615,7 +16630,7 @@
       <c r="H349" s="1">
         <v>552</v>
       </c>
-      <c r="I349" s="7">
+      <c r="I349" s="6">
         <v>144</v>
       </c>
       <c r="J349" s="1" t="s">
@@ -16629,16 +16644,16 @@
       </c>
     </row>
     <row r="350" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A350" s="4" t="s">
+      <c r="A350" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B350" s="4" t="s">
+      <c r="B350" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C350" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D350" s="9" t="s">
+      <c r="C350" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D350" s="8" t="s">
         <v>319</v>
       </c>
       <c r="E350" s="1" t="s">
@@ -16653,7 +16668,7 @@
       <c r="H350" s="1">
         <v>609</v>
       </c>
-      <c r="I350" s="7">
+      <c r="I350" s="6">
         <v>151</v>
       </c>
       <c r="J350" s="1" t="s">
@@ -16667,16 +16682,16 @@
       </c>
     </row>
     <row r="351" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A351" s="4" t="s">
+      <c r="A351" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B351" s="4" t="s">
+      <c r="B351" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C351" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D351" s="9" t="s">
+      <c r="C351" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D351" s="8" t="s">
         <v>322</v>
       </c>
       <c r="E351" s="1" t="s">
@@ -16691,7 +16706,7 @@
       <c r="H351" s="1">
         <v>1130</v>
       </c>
-      <c r="I351" s="7">
+      <c r="I351" s="6">
         <v>393</v>
       </c>
       <c r="J351" s="1" t="s">
@@ -16705,16 +16720,16 @@
       </c>
     </row>
     <row r="352" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A352" s="4" t="s">
+      <c r="A352" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B352" s="4" t="s">
+      <c r="B352" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C352" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D352" s="9" t="s">
+      <c r="C352" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D352" s="8" t="s">
         <v>385</v>
       </c>
       <c r="E352" s="1" t="s">
@@ -16729,7 +16744,7 @@
       <c r="H352" s="1">
         <v>1805</v>
       </c>
-      <c r="I352" s="7">
+      <c r="I352" s="6">
         <v>286</v>
       </c>
       <c r="J352" s="1" t="s">
@@ -16743,16 +16758,16 @@
       </c>
     </row>
     <row r="353" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A353" s="4" t="s">
+      <c r="A353" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B353" s="4" t="s">
+      <c r="B353" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C353" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D353" s="9" t="s">
+      <c r="C353" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D353" s="8" t="s">
         <v>327</v>
       </c>
       <c r="E353" s="1" t="s">
@@ -16767,7 +16782,7 @@
       <c r="H353" s="1">
         <v>805</v>
       </c>
-      <c r="I353" s="7">
+      <c r="I353" s="6">
         <v>374</v>
       </c>
       <c r="J353" s="1" t="s">
@@ -16781,16 +16796,16 @@
       </c>
     </row>
     <row r="354" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A354" s="4" t="s">
+      <c r="A354" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B354" s="4" t="s">
+      <c r="B354" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C354" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D354" s="9" t="s">
+      <c r="C354" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D354" s="8" t="s">
         <v>363</v>
       </c>
       <c r="E354" s="1" t="s">
@@ -16805,7 +16820,7 @@
       <c r="H354" s="1">
         <v>963</v>
       </c>
-      <c r="I354" s="7">
+      <c r="I354" s="6">
         <v>182</v>
       </c>
       <c r="J354" s="1" t="s">
@@ -16819,16 +16834,16 @@
       </c>
     </row>
     <row r="355" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A355" s="4" t="s">
+      <c r="A355" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B355" s="4" t="s">
+      <c r="B355" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C355" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D355" s="9" t="s">
+      <c r="C355" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D355" s="8" t="s">
         <v>388</v>
       </c>
       <c r="E355" s="1" t="s">
@@ -16843,7 +16858,7 @@
       <c r="H355" s="1">
         <v>4107</v>
       </c>
-      <c r="I355" s="7">
+      <c r="I355" s="6">
         <v>231</v>
       </c>
       <c r="J355" s="1" t="s">
@@ -16857,22 +16872,22 @@
       </c>
     </row>
     <row r="356" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A356" s="4" t="s">
+      <c r="A356" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B356" s="4" t="s">
+      <c r="B356" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C356" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D356" s="9" t="s">
+      <c r="C356" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D356" s="8" t="s">
         <v>347</v>
       </c>
       <c r="E356" s="1">
         <v>4</v>
       </c>
-      <c r="I356" s="7">
+      <c r="I356" s="6">
         <v>398</v>
       </c>
       <c r="J356" s="1" t="s">
@@ -16886,16 +16901,16 @@
       </c>
     </row>
     <row r="357" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A357" s="4" t="s">
+      <c r="A357" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B357" s="4" t="s">
+      <c r="B357" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C357" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D357" s="9" t="s">
+      <c r="C357" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D357" s="8" t="s">
         <v>355</v>
       </c>
       <c r="E357" s="1" t="s">
@@ -16910,7 +16925,7 @@
       <c r="H357" s="1">
         <v>678</v>
       </c>
-      <c r="I357" s="7">
+      <c r="I357" s="6">
         <v>423</v>
       </c>
       <c r="J357" s="1" t="s">
@@ -16924,16 +16939,16 @@
       </c>
     </row>
     <row r="358" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A358" s="4" t="s">
+      <c r="A358" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B358" s="4" t="s">
+      <c r="B358" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C358" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D358" s="9" t="s">
+      <c r="C358" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D358" s="8" t="s">
         <v>359</v>
       </c>
       <c r="E358" s="1" t="s">
@@ -16948,7 +16963,7 @@
       <c r="H358" s="1">
         <v>1731</v>
       </c>
-      <c r="I358" s="7">
+      <c r="I358" s="6">
         <v>40</v>
       </c>
       <c r="J358" s="1" t="s">
@@ -16962,16 +16977,16 @@
       </c>
     </row>
     <row r="359" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A359" s="4" t="s">
+      <c r="A359" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B359" s="4" t="s">
+      <c r="B359" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C359" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D359" s="9" t="s">
+      <c r="C359" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D359" s="8" t="s">
         <v>381</v>
       </c>
       <c r="E359" s="1" t="s">
@@ -16986,7 +17001,7 @@
       <c r="H359" s="1">
         <v>1997</v>
       </c>
-      <c r="I359" s="7">
+      <c r="I359" s="6">
         <v>174</v>
       </c>
       <c r="J359" s="1" t="s">
@@ -17000,16 +17015,16 @@
       </c>
     </row>
     <row r="360" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A360" s="4" t="s">
+      <c r="A360" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B360" s="4" t="s">
+      <c r="B360" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C360" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D360" s="9" t="s">
+      <c r="C360" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D360" s="8" t="s">
         <v>332</v>
       </c>
       <c r="E360" s="1" t="s">
@@ -17024,7 +17039,7 @@
       <c r="H360" s="1">
         <v>2133</v>
       </c>
-      <c r="I360" s="7">
+      <c r="I360" s="6">
         <v>117</v>
       </c>
       <c r="J360" s="1" t="s">
@@ -17038,16 +17053,16 @@
       </c>
     </row>
     <row r="361" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A361" s="4" t="s">
+      <c r="A361" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B361" s="4" t="s">
+      <c r="B361" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C361" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D361" s="9" t="s">
+      <c r="C361" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D361" s="8" t="s">
         <v>320</v>
       </c>
       <c r="E361" s="1" t="s">
@@ -17062,7 +17077,7 @@
       <c r="H361" s="1">
         <v>1569</v>
       </c>
-      <c r="I361" s="7">
+      <c r="I361" s="6">
         <v>47</v>
       </c>
       <c r="J361" s="1" t="s">
@@ -17076,16 +17091,16 @@
       </c>
     </row>
     <row r="362" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A362" s="4" t="s">
+      <c r="A362" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B362" s="4" t="s">
+      <c r="B362" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C362" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D362" s="9" t="s">
+      <c r="C362" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D362" s="8" t="s">
         <v>325</v>
       </c>
       <c r="E362" s="1" t="s">
@@ -17100,7 +17115,7 @@
       <c r="H362" s="1">
         <v>1893</v>
       </c>
-      <c r="I362" s="7">
+      <c r="I362" s="6">
         <v>9</v>
       </c>
       <c r="J362" s="1" t="s">
@@ -17114,16 +17129,16 @@
       </c>
     </row>
     <row r="363" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A363" s="4" t="s">
+      <c r="A363" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B363" s="4" t="s">
+      <c r="B363" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C363" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D363" s="9" t="s">
+      <c r="C363" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D363" s="8" t="s">
         <v>372</v>
       </c>
       <c r="E363" s="1" t="s">
@@ -17138,7 +17153,7 @@
       <c r="H363" s="1">
         <v>2526</v>
       </c>
-      <c r="I363" s="7">
+      <c r="I363" s="6">
         <v>157</v>
       </c>
       <c r="J363" s="1" t="s">
@@ -17152,16 +17167,16 @@
       </c>
     </row>
     <row r="364" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A364" s="4" t="s">
+      <c r="A364" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B364" s="4" t="s">
+      <c r="B364" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C364" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D364" s="9" t="s">
+      <c r="C364" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D364" s="8" t="s">
         <v>354</v>
       </c>
       <c r="E364" s="1" t="s">
@@ -17176,7 +17191,7 @@
       <c r="H364" s="1">
         <v>2005</v>
       </c>
-      <c r="I364" s="7">
+      <c r="I364" s="6">
         <v>105</v>
       </c>
       <c r="J364" s="1" t="s">
@@ -17190,16 +17205,16 @@
       </c>
     </row>
     <row r="365" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A365" s="4" t="s">
+      <c r="A365" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B365" s="4" t="s">
+      <c r="B365" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C365" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D365" s="9" t="s">
+      <c r="C365" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D365" s="8" t="s">
         <v>365</v>
       </c>
       <c r="E365" s="1" t="s">
@@ -17214,7 +17229,7 @@
       <c r="H365" s="1">
         <v>1203</v>
       </c>
-      <c r="I365" s="7">
+      <c r="I365" s="6">
         <v>287</v>
       </c>
       <c r="J365" s="1" t="s">
@@ -17228,16 +17243,16 @@
       </c>
     </row>
     <row r="366" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A366" s="4" t="s">
+      <c r="A366" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B366" s="4" t="s">
+      <c r="B366" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C366" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D366" s="9" t="s">
+      <c r="C366" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D366" s="8" t="s">
         <v>351</v>
       </c>
       <c r="E366" s="1" t="s">
@@ -17252,7 +17267,7 @@
       <c r="H366" s="1">
         <v>247</v>
       </c>
-      <c r="I366" s="7">
+      <c r="I366" s="6">
         <v>68</v>
       </c>
       <c r="J366" s="1" t="s">
@@ -17266,16 +17281,16 @@
       </c>
     </row>
     <row r="367" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A367" s="4" t="s">
+      <c r="A367" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B367" s="4" t="s">
+      <c r="B367" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C367" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D367" s="9" t="s">
+      <c r="C367" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D367" s="8" t="s">
         <v>362</v>
       </c>
       <c r="E367" s="1" t="s">
@@ -17290,7 +17305,7 @@
       <c r="H367" s="1">
         <v>2707</v>
       </c>
-      <c r="I367" s="7">
+      <c r="I367" s="6">
         <v>89</v>
       </c>
       <c r="J367" s="1" t="s">
@@ -17304,16 +17319,16 @@
       </c>
     </row>
     <row r="368" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A368" s="4" t="s">
+      <c r="A368" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B368" s="4" t="s">
+      <c r="B368" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C368" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D368" s="9" t="s">
+      <c r="C368" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D368" s="8" t="s">
         <v>330</v>
       </c>
       <c r="E368" s="1" t="s">
@@ -17328,7 +17343,7 @@
       <c r="H368" s="1">
         <v>2572</v>
       </c>
-      <c r="I368" s="7">
+      <c r="I368" s="6">
         <v>499</v>
       </c>
       <c r="J368" s="1" t="s">
@@ -17342,16 +17357,16 @@
       </c>
     </row>
     <row r="369" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A369" s="4" t="s">
+      <c r="A369" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B369" s="4" t="s">
+      <c r="B369" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C369" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D369" s="9" t="s">
+      <c r="C369" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D369" s="8" t="s">
         <v>360</v>
       </c>
       <c r="E369" s="1" t="s">
@@ -17366,7 +17381,7 @@
       <c r="H369" s="1">
         <v>1731</v>
       </c>
-      <c r="I369" s="7">
+      <c r="I369" s="6">
         <v>222</v>
       </c>
       <c r="J369" s="1" t="s">
@@ -17380,16 +17395,16 @@
       </c>
     </row>
     <row r="370" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A370" s="4" t="s">
+      <c r="A370" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B370" s="4" t="s">
+      <c r="B370" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C370" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D370" s="9" t="s">
+      <c r="C370" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D370" s="8" t="s">
         <v>367</v>
       </c>
       <c r="E370" s="1" t="s">
@@ -17404,7 +17419,7 @@
       <c r="H370" s="1">
         <v>301</v>
       </c>
-      <c r="I370" s="7">
+      <c r="I370" s="6">
         <v>747</v>
       </c>
       <c r="J370" s="1" t="s">
@@ -17418,16 +17433,16 @@
       </c>
     </row>
     <row r="371" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A371" s="4" t="s">
+      <c r="A371" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B371" s="4" t="s">
+      <c r="B371" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C371" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D371" s="9" t="s">
+      <c r="C371" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D371" s="8" t="s">
         <v>370</v>
       </c>
       <c r="E371" s="1" t="s">
@@ -17442,7 +17457,7 @@
       <c r="H371" s="1">
         <v>782</v>
       </c>
-      <c r="I371" s="7">
+      <c r="I371" s="6">
         <v>59</v>
       </c>
       <c r="J371" s="1" t="s">
@@ -17456,16 +17471,16 @@
       </c>
     </row>
     <row r="372" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A372" s="4" t="s">
+      <c r="A372" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B372" s="4" t="s">
+      <c r="B372" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C372" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D372" s="9" t="s">
+      <c r="C372" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D372" s="8" t="s">
         <v>379</v>
       </c>
       <c r="E372" s="1" t="s">
@@ -17480,7 +17495,7 @@
       <c r="H372" s="1">
         <v>1925</v>
       </c>
-      <c r="I372" s="7">
+      <c r="I372" s="6">
         <v>231</v>
       </c>
       <c r="J372" s="1" t="s">
@@ -17494,16 +17509,16 @@
       </c>
     </row>
     <row r="373" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A373" s="4" t="s">
+      <c r="A373" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B373" s="4" t="s">
+      <c r="B373" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C373" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D373" s="9" t="s">
+      <c r="C373" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D373" s="8" t="s">
         <v>334</v>
       </c>
       <c r="E373" s="1" t="s">
@@ -17518,7 +17533,7 @@
       <c r="H373" s="1">
         <v>2745</v>
       </c>
-      <c r="I373" s="7">
+      <c r="I373" s="6">
         <v>0</v>
       </c>
       <c r="J373" s="1" t="s">
@@ -17532,16 +17547,16 @@
       </c>
     </row>
     <row r="374" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A374" s="4" t="s">
+      <c r="A374" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B374" s="4" t="s">
+      <c r="B374" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C374" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D374" s="9" t="s">
+      <c r="C374" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D374" s="8" t="s">
         <v>361</v>
       </c>
       <c r="E374" s="1" t="s">
@@ -17556,7 +17571,7 @@
       <c r="H374" s="1">
         <v>2683</v>
       </c>
-      <c r="I374" s="7">
+      <c r="I374" s="6">
         <v>242</v>
       </c>
       <c r="J374" s="1" t="s">
@@ -17570,16 +17585,16 @@
       </c>
     </row>
     <row r="375" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A375" s="4" t="s">
+      <c r="A375" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B375" s="4" t="s">
+      <c r="B375" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C375" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D375" s="9" t="s">
+      <c r="C375" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D375" s="8" t="s">
         <v>339</v>
       </c>
       <c r="E375" s="1" t="s">
@@ -17594,7 +17609,7 @@
       <c r="H375" s="1">
         <v>1140</v>
       </c>
-      <c r="I375" s="7">
+      <c r="I375" s="6">
         <v>6</v>
       </c>
       <c r="J375" s="1" t="s">
@@ -17608,16 +17623,16 @@
       </c>
     </row>
     <row r="376" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A376" s="4" t="s">
+      <c r="A376" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B376" s="4" t="s">
+      <c r="B376" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C376" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D376" s="9" t="s">
+      <c r="C376" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D376" s="8" t="s">
         <v>328</v>
       </c>
       <c r="E376" s="1" t="s">
@@ -17632,7 +17647,7 @@
       <c r="H376" s="1">
         <v>4552</v>
       </c>
-      <c r="I376" s="7">
+      <c r="I376" s="6">
         <v>10</v>
       </c>
       <c r="J376" s="1" t="s">
@@ -17646,16 +17661,16 @@
       </c>
     </row>
     <row r="377" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A377" s="4" t="s">
+      <c r="A377" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B377" s="4" t="s">
+      <c r="B377" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C377" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D377" s="9" t="s">
+      <c r="C377" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D377" s="8" t="s">
         <v>387</v>
       </c>
       <c r="E377" s="1" t="s">
@@ -17670,7 +17685,7 @@
       <c r="H377" s="1">
         <v>2587</v>
       </c>
-      <c r="I377" s="7">
+      <c r="I377" s="6">
         <v>8</v>
       </c>
       <c r="J377" s="1" t="s">
@@ -17684,16 +17699,16 @@
       </c>
     </row>
     <row r="378" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A378" s="4" t="s">
+      <c r="A378" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B378" s="4" t="s">
+      <c r="B378" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C378" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D378" s="9" t="s">
+      <c r="C378" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D378" s="8" t="s">
         <v>337</v>
       </c>
       <c r="E378" s="1" t="s">
@@ -17708,7 +17723,7 @@
       <c r="H378" s="1">
         <v>492</v>
       </c>
-      <c r="I378" s="7">
+      <c r="I378" s="6">
         <v>17</v>
       </c>
       <c r="J378" s="1" t="s">
@@ -17722,16 +17737,16 @@
       </c>
     </row>
     <row r="379" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A379" s="4" t="s">
+      <c r="A379" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B379" s="4" t="s">
+      <c r="B379" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C379" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D379" s="9" t="s">
+      <c r="C379" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D379" s="8" t="s">
         <v>341</v>
       </c>
       <c r="E379" s="1" t="s">
@@ -17746,7 +17761,7 @@
       <c r="H379" s="1">
         <v>764</v>
       </c>
-      <c r="I379" s="7">
+      <c r="I379" s="6">
         <v>0</v>
       </c>
       <c r="J379" s="1" t="s">
@@ -17760,16 +17775,16 @@
       </c>
     </row>
     <row r="380" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="4" t="s">
+      <c r="A380" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B380" s="4" t="s">
+      <c r="B380" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C380" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D380" s="9" t="s">
+      <c r="C380" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D380" s="8" t="s">
         <v>324</v>
       </c>
       <c r="E380" s="1" t="s">
@@ -17784,7 +17799,7 @@
       <c r="H380" s="1">
         <v>1675</v>
       </c>
-      <c r="I380" s="7">
+      <c r="I380" s="6">
         <v>19</v>
       </c>
       <c r="J380" s="1" t="s">
@@ -17798,16 +17813,16 @@
       </c>
     </row>
     <row r="381" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A381" s="4" t="s">
+      <c r="A381" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B381" s="4" t="s">
+      <c r="B381" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C381" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D381" s="9" t="s">
+      <c r="C381" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D381" s="8" t="s">
         <v>352</v>
       </c>
       <c r="E381" s="1" t="s">
@@ -17822,7 +17837,7 @@
       <c r="H381" s="1">
         <v>420</v>
       </c>
-      <c r="I381" s="7">
+      <c r="I381" s="6">
         <v>43</v>
       </c>
       <c r="J381" s="1" t="s">
@@ -17836,16 +17851,16 @@
       </c>
     </row>
     <row r="382" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A382" s="4" t="s">
+      <c r="A382" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B382" s="4" t="s">
+      <c r="B382" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C382" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D382" s="9" t="s">
+      <c r="C382" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D382" s="8" t="s">
         <v>358</v>
       </c>
       <c r="E382" s="1" t="s">
@@ -17860,7 +17875,7 @@
       <c r="H382" s="1">
         <v>1022</v>
       </c>
-      <c r="I382" s="7">
+      <c r="I382" s="6">
         <v>409</v>
       </c>
       <c r="J382" s="1" t="s">
@@ -17874,16 +17889,16 @@
       </c>
     </row>
     <row r="383" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A383" s="4" t="s">
+      <c r="A383" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B383" s="4" t="s">
+      <c r="B383" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C383" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D383" s="9" t="s">
+      <c r="C383" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D383" s="8" t="s">
         <v>318</v>
       </c>
       <c r="E383" s="1" t="s">
@@ -17898,7 +17913,7 @@
       <c r="H383" s="1">
         <v>1956</v>
       </c>
-      <c r="I383" s="7">
+      <c r="I383" s="6">
         <v>68</v>
       </c>
       <c r="J383" s="1" t="s">
@@ -17912,16 +17927,16 @@
       </c>
     </row>
     <row r="384" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A384" s="4" t="s">
+      <c r="A384" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B384" s="4" t="s">
+      <c r="B384" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C384" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D384" s="9" t="s">
+      <c r="C384" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D384" s="8" t="s">
         <v>356</v>
       </c>
       <c r="E384" s="1" t="s">
@@ -17936,7 +17951,7 @@
       <c r="H384" s="1">
         <v>3024</v>
       </c>
-      <c r="I384" s="7">
+      <c r="I384" s="6">
         <v>0</v>
       </c>
       <c r="J384" s="1" t="s">
@@ -17950,16 +17965,16 @@
       </c>
     </row>
     <row r="385" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A385" s="4" t="s">
+      <c r="A385" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B385" s="4" t="s">
+      <c r="B385" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C385" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D385" s="9" t="s">
+      <c r="C385" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D385" s="8" t="s">
         <v>371</v>
       </c>
       <c r="E385" s="1" t="s">
@@ -17974,7 +17989,7 @@
       <c r="H385" s="1">
         <v>626</v>
       </c>
-      <c r="I385" s="7">
+      <c r="I385" s="6">
         <v>119</v>
       </c>
       <c r="J385" s="1" t="s">
@@ -17988,16 +18003,16 @@
       </c>
     </row>
     <row r="386" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A386" s="4" t="s">
+      <c r="A386" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B386" s="4" t="s">
+      <c r="B386" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C386" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D386" s="9" t="s">
+      <c r="C386" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D386" s="8" t="s">
         <v>342</v>
       </c>
       <c r="E386" s="1" t="s">
@@ -18012,7 +18027,7 @@
       <c r="H386" s="1">
         <v>6617</v>
       </c>
-      <c r="I386" s="7">
+      <c r="I386" s="6">
         <v>18</v>
       </c>
       <c r="J386" s="1" t="s">
@@ -18026,16 +18041,16 @@
       </c>
     </row>
     <row r="387" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A387" s="4" t="s">
+      <c r="A387" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B387" s="4" t="s">
+      <c r="B387" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C387" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D387" s="9" t="s">
+      <c r="C387" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D387" s="8" t="s">
         <v>331</v>
       </c>
       <c r="E387" s="1" t="s">
@@ -18050,7 +18065,7 @@
       <c r="H387" s="1">
         <v>1205</v>
       </c>
-      <c r="I387" s="7">
+      <c r="I387" s="6">
         <v>309</v>
       </c>
       <c r="J387" s="1" t="s">
@@ -18064,16 +18079,16 @@
       </c>
     </row>
     <row r="388" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A388" s="4" t="s">
+      <c r="A388" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B388" s="4" t="s">
+      <c r="B388" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C388" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D388" s="9" t="s">
+      <c r="C388" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D388" s="8" t="s">
         <v>323</v>
       </c>
       <c r="E388" s="1" t="s">
@@ -18088,7 +18103,7 @@
       <c r="H388" s="1">
         <v>1345</v>
       </c>
-      <c r="I388" s="7">
+      <c r="I388" s="6">
         <v>1005</v>
       </c>
       <c r="J388" s="1" t="s">
@@ -18102,16 +18117,16 @@
       </c>
     </row>
     <row r="389" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A389" s="4" t="s">
+      <c r="A389" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B389" s="4" t="s">
+      <c r="B389" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C389" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D389" s="9" t="s">
+      <c r="C389" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D389" s="8" t="s">
         <v>375</v>
       </c>
       <c r="E389" s="1" t="s">
@@ -18126,7 +18141,7 @@
       <c r="H389" s="1">
         <v>566</v>
       </c>
-      <c r="I389" s="7">
+      <c r="I389" s="6">
         <v>1660</v>
       </c>
       <c r="J389" s="1" t="s">
@@ -18140,16 +18155,16 @@
       </c>
     </row>
     <row r="390" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A390" s="4" t="s">
+      <c r="A390" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B390" s="4" t="s">
+      <c r="B390" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C390" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D390" s="9" t="s">
+      <c r="C390" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D390" s="8" t="s">
         <v>377</v>
       </c>
       <c r="E390" s="1" t="s">
@@ -18164,7 +18179,7 @@
       <c r="H390" s="1">
         <v>2743</v>
       </c>
-      <c r="I390" s="7">
+      <c r="I390" s="6">
         <v>97</v>
       </c>
       <c r="J390" s="1" t="s">
@@ -18178,16 +18193,16 @@
       </c>
     </row>
     <row r="391" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A391" s="4" t="s">
+      <c r="A391" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B391" s="4" t="s">
+      <c r="B391" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C391" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D391" s="9" t="s">
+      <c r="C391" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D391" s="8" t="s">
         <v>329</v>
       </c>
       <c r="E391" s="1" t="s">
@@ -18202,7 +18217,7 @@
       <c r="H391" s="1">
         <v>2636</v>
       </c>
-      <c r="I391" s="7">
+      <c r="I391" s="6">
         <v>2</v>
       </c>
       <c r="J391" s="1" t="s">
@@ -18216,16 +18231,16 @@
       </c>
     </row>
     <row r="392" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A392" s="4" t="s">
+      <c r="A392" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B392" s="4" t="s">
+      <c r="B392" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C392" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D392" s="9" t="s">
+      <c r="C392" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D392" s="8" t="s">
         <v>348</v>
       </c>
       <c r="E392" s="1" t="s">
@@ -18240,7 +18255,7 @@
       <c r="H392" s="1">
         <v>2949</v>
       </c>
-      <c r="I392" s="7">
+      <c r="I392" s="6">
         <v>19</v>
       </c>
       <c r="J392" s="1" t="s">
@@ -18254,16 +18269,16 @@
       </c>
     </row>
     <row r="393" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A393" s="4" t="s">
+      <c r="A393" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B393" s="4" t="s">
+      <c r="B393" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C393" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D393" s="9" t="s">
+      <c r="C393" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D393" s="8" t="s">
         <v>452</v>
       </c>
       <c r="E393" s="1" t="s">
@@ -18278,7 +18293,7 @@
       <c r="H393" s="1">
         <v>3538</v>
       </c>
-      <c r="I393" s="7">
+      <c r="I393" s="6">
         <v>3</v>
       </c>
       <c r="J393" s="1" t="s">
@@ -18292,16 +18307,16 @@
       </c>
     </row>
     <row r="394" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A394" s="4" t="s">
+      <c r="A394" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="B394" s="4" t="s">
+      <c r="B394" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="C394" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D394" s="9" t="s">
+      <c r="C394" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D394" s="8" t="s">
         <v>537</v>
       </c>
       <c r="E394" s="1" t="s">
@@ -18316,7 +18331,7 @@
       <c r="H394" s="1">
         <v>3910</v>
       </c>
-      <c r="I394" s="7">
+      <c r="I394" s="6">
         <v>7</v>
       </c>
       <c r="J394" s="1" t="s">
@@ -18330,16 +18345,16 @@
       </c>
     </row>
     <row r="395" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A395" s="4" t="s">
+      <c r="A395" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B395" s="4" t="s">
+      <c r="B395" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C395" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D395" s="9" t="s">
+      <c r="C395" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D395" s="8" t="s">
         <v>340</v>
       </c>
       <c r="E395" s="1" t="s">
@@ -18354,7 +18369,7 @@
       <c r="H395" s="1">
         <v>1991</v>
       </c>
-      <c r="I395" s="7">
+      <c r="I395" s="6">
         <v>0</v>
       </c>
       <c r="J395" s="1" t="s">
@@ -18368,16 +18383,16 @@
       </c>
     </row>
     <row r="396" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A396" s="4" t="s">
+      <c r="A396" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B396" s="4" t="s">
+      <c r="B396" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C396" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D396" s="9" t="s">
+      <c r="C396" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D396" s="8" t="s">
         <v>364</v>
       </c>
       <c r="E396" s="1" t="s">
@@ -18392,7 +18407,7 @@
       <c r="H396" s="1">
         <v>1384</v>
       </c>
-      <c r="I396" s="7">
+      <c r="I396" s="6">
         <v>102</v>
       </c>
       <c r="J396" s="1" t="s">
@@ -18406,16 +18421,16 @@
       </c>
     </row>
     <row r="397" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A397" s="4" t="s">
+      <c r="A397" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="B397" s="4" t="s">
+      <c r="B397" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="C397" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D397" s="9" t="s">
+      <c r="C397" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D397" s="8" t="s">
         <v>538</v>
       </c>
       <c r="E397" s="1" t="s">
@@ -18430,7 +18445,7 @@
       <c r="H397" s="1">
         <v>9175</v>
       </c>
-      <c r="I397" s="7">
+      <c r="I397" s="6">
         <v>0</v>
       </c>
       <c r="J397" s="1" t="s">
@@ -18444,16 +18459,16 @@
       </c>
     </row>
     <row r="398" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A398" s="4" t="s">
+      <c r="A398" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B398" s="4" t="s">
+      <c r="B398" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C398" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D398" s="9" t="s">
+      <c r="C398" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D398" s="8" t="s">
         <v>338</v>
       </c>
       <c r="E398" s="1" t="s">
@@ -18468,7 +18483,7 @@
       <c r="H398" s="1">
         <v>346</v>
       </c>
-      <c r="I398" s="7">
+      <c r="I398" s="6">
         <v>0</v>
       </c>
       <c r="J398" s="1" t="s">
@@ -18482,16 +18497,16 @@
       </c>
     </row>
     <row r="399" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A399" s="4" t="s">
+      <c r="A399" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B399" s="4" t="s">
+      <c r="B399" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C399" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D399" s="9" t="s">
+      <c r="C399" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D399" s="8" t="s">
         <v>333</v>
       </c>
       <c r="E399" s="1" t="s">
@@ -18506,7 +18521,7 @@
       <c r="H399" s="1">
         <v>3843</v>
       </c>
-      <c r="I399" s="7">
+      <c r="I399" s="6">
         <v>284</v>
       </c>
       <c r="J399" s="1" t="s">
@@ -18520,16 +18535,16 @@
       </c>
     </row>
     <row r="400" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A400" s="4" t="s">
+      <c r="A400" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B400" s="4" t="s">
+      <c r="B400" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C400" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D400" s="9" t="s">
+      <c r="C400" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D400" s="8" t="s">
         <v>349</v>
       </c>
       <c r="E400" s="1" t="s">
@@ -18544,7 +18559,7 @@
       <c r="H400" s="1">
         <v>2418</v>
       </c>
-      <c r="I400" s="7">
+      <c r="I400" s="6">
         <v>6</v>
       </c>
       <c r="J400" s="1" t="s">
@@ -18558,16 +18573,16 @@
       </c>
     </row>
     <row r="401" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A401" s="4" t="s">
+      <c r="A401" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B401" s="4" t="s">
+      <c r="B401" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C401" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D401" s="9" t="s">
+      <c r="C401" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D401" s="8" t="s">
         <v>343</v>
       </c>
       <c r="E401" s="1" t="s">
@@ -18582,7 +18597,7 @@
       <c r="H401" s="1">
         <v>807</v>
       </c>
-      <c r="I401" s="7">
+      <c r="I401" s="6">
         <v>551</v>
       </c>
       <c r="J401" s="1" t="s">
@@ -18596,16 +18611,16 @@
       </c>
     </row>
     <row r="402" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A402" s="4" t="s">
+      <c r="A402" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B402" s="4" t="s">
+      <c r="B402" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C402" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D402" s="9" t="s">
+      <c r="C402" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D402" s="8" t="s">
         <v>346</v>
       </c>
       <c r="E402" s="1" t="s">
@@ -18620,7 +18635,7 @@
       <c r="H402" s="1">
         <v>3248</v>
       </c>
-      <c r="I402" s="7">
+      <c r="I402" s="6">
         <v>10</v>
       </c>
       <c r="J402" s="1" t="s">
@@ -18634,16 +18649,16 @@
       </c>
     </row>
     <row r="403" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A403" s="4" t="s">
+      <c r="A403" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="B403" s="4" t="s">
+      <c r="B403" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="C403" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D403" s="9" t="s">
+      <c r="C403" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D403" s="8" t="s">
         <v>539</v>
       </c>
       <c r="E403" s="1" t="s">
@@ -18658,7 +18673,7 @@
       <c r="H403" s="1">
         <v>1229</v>
       </c>
-      <c r="I403" s="7">
+      <c r="I403" s="6">
         <v>8</v>
       </c>
       <c r="J403" s="1" t="s">
@@ -18672,16 +18687,16 @@
       </c>
     </row>
     <row r="404" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A404" s="4" t="s">
+      <c r="A404" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="B404" s="4" t="s">
+      <c r="B404" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="C404" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D404" s="9" t="s">
+      <c r="C404" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D404" s="8" t="s">
         <v>540</v>
       </c>
       <c r="E404" s="1" t="s">
@@ -18696,7 +18711,7 @@
       <c r="H404" s="1">
         <v>507</v>
       </c>
-      <c r="I404" s="7">
+      <c r="I404" s="6">
         <v>3</v>
       </c>
       <c r="J404" s="1" t="s">
@@ -18710,16 +18725,16 @@
       </c>
     </row>
     <row r="405" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A405" s="4" t="s">
+      <c r="A405" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B405" s="4" t="s">
+      <c r="B405" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C405" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D405" s="9" t="s">
+      <c r="C405" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D405" s="8" t="s">
         <v>350</v>
       </c>
       <c r="E405" s="1" t="s">
@@ -18734,7 +18749,7 @@
       <c r="H405" s="1">
         <v>10849</v>
       </c>
-      <c r="I405" s="7">
+      <c r="I405" s="6">
         <v>9</v>
       </c>
       <c r="J405" s="1" t="s">
@@ -18748,16 +18763,16 @@
       </c>
     </row>
     <row r="406" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A406" s="4" t="s">
+      <c r="A406" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B406" s="4" t="s">
+      <c r="B406" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C406" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D406" s="9" t="s">
+      <c r="C406" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D406" s="8" t="s">
         <v>541</v>
       </c>
       <c r="E406" s="1" t="s">
@@ -18772,7 +18787,7 @@
       <c r="H406" s="1">
         <v>3677</v>
       </c>
-      <c r="I406" s="7">
+      <c r="I406" s="6">
         <v>7</v>
       </c>
       <c r="J406" s="1" t="s">
@@ -18786,16 +18801,16 @@
       </c>
     </row>
     <row r="407" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A407" s="4" t="s">
+      <c r="A407" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="B407" s="4" t="s">
+      <c r="B407" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C407" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D407" s="9" t="s">
+      <c r="C407" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D407" s="8" t="s">
         <v>463</v>
       </c>
       <c r="E407" s="1" t="s">
@@ -18810,7 +18825,7 @@
       <c r="H407" s="1">
         <v>2458</v>
       </c>
-      <c r="I407" s="7">
+      <c r="I407" s="6">
         <v>4</v>
       </c>
       <c r="J407" s="1" t="s">
@@ -18824,16 +18839,16 @@
       </c>
     </row>
     <row r="408" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="4" t="s">
+      <c r="A408" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="B408" s="4" t="s">
+      <c r="B408" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="C408" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D408" s="9" t="s">
+      <c r="C408" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D408" s="8" t="s">
         <v>542</v>
       </c>
       <c r="E408" s="1" t="s">
@@ -18848,7 +18863,7 @@
       <c r="H408" s="1">
         <v>1564</v>
       </c>
-      <c r="I408" s="7">
+      <c r="I408" s="6">
         <v>6</v>
       </c>
       <c r="J408" s="1" t="s">
@@ -18862,16 +18877,16 @@
       </c>
     </row>
     <row r="409" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A409" s="4" t="s">
+      <c r="A409" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B409" s="4" t="s">
+      <c r="B409" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="C409" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D409" s="9" t="s">
+      <c r="C409" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D409" s="8" t="s">
         <v>543</v>
       </c>
       <c r="E409" s="1" t="s">
@@ -18886,7 +18901,7 @@
       <c r="H409" s="1">
         <v>337</v>
       </c>
-      <c r="I409" s="7">
+      <c r="I409" s="6">
         <v>5</v>
       </c>
       <c r="J409" s="1" t="s">
@@ -18900,16 +18915,16 @@
       </c>
     </row>
     <row r="410" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A410" s="4" t="s">
+      <c r="A410" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="B410" s="4" t="s">
+      <c r="B410" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="C410" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D410" s="9" t="s">
+      <c r="C410" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D410" s="8" t="s">
         <v>544</v>
       </c>
       <c r="E410" s="1" t="s">
@@ -18924,7 +18939,7 @@
       <c r="H410" s="1">
         <v>1313</v>
       </c>
-      <c r="I410" s="7">
+      <c r="I410" s="6">
         <v>4</v>
       </c>
       <c r="J410" s="1" t="s">
@@ -18938,16 +18953,16 @@
       </c>
     </row>
     <row r="411" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A411" s="4" t="s">
+      <c r="A411" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="B411" s="4" t="s">
+      <c r="B411" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="C411" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D411" s="9" t="s">
+      <c r="C411" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D411" s="8" t="s">
         <v>545</v>
       </c>
       <c r="E411" s="1" t="s">
@@ -18962,7 +18977,7 @@
       <c r="H411" s="1">
         <v>1048</v>
       </c>
-      <c r="I411" s="7">
+      <c r="I411" s="6">
         <v>3</v>
       </c>
       <c r="J411" s="1" t="s">
@@ -18976,16 +18991,16 @@
       </c>
     </row>
     <row r="412" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A412" s="4" t="s">
+      <c r="A412" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="B412" s="4" t="s">
+      <c r="B412" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="C412" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D412" s="9" t="s">
+      <c r="C412" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D412" s="8" t="s">
         <v>546</v>
       </c>
       <c r="E412" s="1" t="s">
@@ -19000,7 +19015,7 @@
       <c r="H412" s="1">
         <v>1439</v>
       </c>
-      <c r="I412" s="7">
+      <c r="I412" s="6">
         <v>7</v>
       </c>
       <c r="J412" s="1" t="s">
@@ -19014,16 +19029,16 @@
       </c>
     </row>
     <row r="413" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A413" s="4" t="s">
+      <c r="A413" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="B413" s="4" t="s">
+      <c r="B413" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="C413" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D413" s="9" t="s">
+      <c r="C413" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D413" s="8" t="s">
         <v>547</v>
       </c>
       <c r="E413" s="1" t="s">
@@ -19038,7 +19053,7 @@
       <c r="H413" s="1">
         <v>784</v>
       </c>
-      <c r="I413" s="7">
+      <c r="I413" s="6">
         <v>3</v>
       </c>
       <c r="J413" s="1" t="s">
@@ -19052,16 +19067,16 @@
       </c>
     </row>
     <row r="414" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A414" s="4" t="s">
+      <c r="A414" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="B414" s="4" t="s">
+      <c r="B414" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="C414" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D414" s="9" t="s">
+      <c r="C414" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D414" s="8" t="s">
         <v>548</v>
       </c>
       <c r="E414" s="1" t="s">
@@ -19076,7 +19091,7 @@
       <c r="H414" s="1">
         <v>1599</v>
       </c>
-      <c r="I414" s="7">
+      <c r="I414" s="6">
         <v>4</v>
       </c>
       <c r="J414" s="1" t="s">
@@ -19090,16 +19105,16 @@
       </c>
     </row>
     <row r="415" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A415" s="4" t="s">
+      <c r="A415" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="B415" s="4" t="s">
+      <c r="B415" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="C415" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D415" s="9" t="s">
+      <c r="C415" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D415" s="8" t="s">
         <v>549</v>
       </c>
       <c r="E415" s="1" t="s">
@@ -19114,7 +19129,7 @@
       <c r="H415" s="1">
         <v>3168</v>
       </c>
-      <c r="I415" s="7">
+      <c r="I415" s="6">
         <v>1</v>
       </c>
       <c r="J415" s="1" t="s">
@@ -19128,16 +19143,16 @@
       </c>
     </row>
     <row r="416" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A416" s="4" t="s">
+      <c r="A416" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="B416" s="4" t="s">
+      <c r="B416" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="C416" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D416" s="9" t="s">
+      <c r="C416" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D416" s="8" t="s">
         <v>550</v>
       </c>
       <c r="E416" s="1" t="s">
@@ -19152,7 +19167,7 @@
       <c r="H416" s="1">
         <v>1599</v>
       </c>
-      <c r="I416" s="7">
+      <c r="I416" s="6">
         <v>1</v>
       </c>
       <c r="J416" s="1" t="s">
@@ -19166,16 +19181,16 @@
       </c>
     </row>
     <row r="417" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A417" s="4" t="s">
+      <c r="A417" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="B417" s="4" t="s">
+      <c r="B417" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="C417" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D417" s="9" t="s">
+      <c r="C417" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D417" s="8" t="s">
         <v>551</v>
       </c>
       <c r="E417" s="1" t="s">
@@ -19190,7 +19205,7 @@
       <c r="H417" s="1">
         <v>3465</v>
       </c>
-      <c r="I417" s="7">
+      <c r="I417" s="6">
         <v>3</v>
       </c>
       <c r="J417" s="1" t="s">
@@ -19204,16 +19219,16 @@
       </c>
     </row>
     <row r="418" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A418" s="4" t="s">
+      <c r="A418" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B418" s="4" t="s">
+      <c r="B418" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C418" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D418" s="9" t="s">
+      <c r="C418" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D418" s="8" t="s">
         <v>376</v>
       </c>
       <c r="E418" s="1" t="s">
@@ -19228,7 +19243,7 @@
       <c r="H418" s="1">
         <v>3946</v>
       </c>
-      <c r="I418" s="7">
+      <c r="I418" s="6">
         <v>19</v>
       </c>
       <c r="J418" s="1" t="s">
@@ -19242,16 +19257,16 @@
       </c>
     </row>
     <row r="419" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A419" s="4" t="s">
+      <c r="A419" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="B419" s="4" t="s">
+      <c r="B419" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="C419" s="8" t="s">
+      <c r="C419" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="D419" s="9" t="s">
+      <c r="D419" s="8" t="s">
         <v>552</v>
       </c>
       <c r="E419" s="1" t="s">
@@ -19266,7 +19281,7 @@
       <c r="H419" s="1">
         <v>1516</v>
       </c>
-      <c r="I419" s="7">
+      <c r="I419" s="6">
         <v>0</v>
       </c>
       <c r="J419" s="1" t="s">
@@ -19280,16 +19295,16 @@
       </c>
     </row>
     <row r="420" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A420" s="4" t="s">
+      <c r="A420" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="B420" s="4" t="s">
+      <c r="B420" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="C420" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D420" s="9" t="s">
+      <c r="C420" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D420" s="8" t="s">
         <v>553</v>
       </c>
       <c r="E420" s="1" t="s">
@@ -19304,7 +19319,7 @@
       <c r="H420" s="1">
         <v>7925</v>
       </c>
-      <c r="I420" s="7">
+      <c r="I420" s="6">
         <v>3</v>
       </c>
       <c r="J420" s="1" t="s">
@@ -19318,16 +19333,16 @@
       </c>
     </row>
     <row r="421" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="4" t="s">
+      <c r="A421" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="B421" s="4" t="s">
+      <c r="B421" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="C421" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D421" s="9" t="s">
+      <c r="C421" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D421" s="8" t="s">
         <v>554</v>
       </c>
       <c r="E421" s="1" t="s">
@@ -19342,7 +19357,7 @@
       <c r="H421" s="1">
         <v>1322</v>
       </c>
-      <c r="I421" s="7">
+      <c r="I421" s="6">
         <v>0</v>
       </c>
       <c r="J421" s="1" t="s">
@@ -19356,16 +19371,16 @@
       </c>
     </row>
     <row r="422" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A422" s="4" t="s">
+      <c r="A422" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="B422" s="4" t="s">
+      <c r="B422" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="C422" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D422" s="9" t="s">
+      <c r="C422" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D422" s="8" t="s">
         <v>555</v>
       </c>
       <c r="E422" s="1" t="s">
@@ -19380,7 +19395,7 @@
       <c r="H422" s="1">
         <v>1360</v>
       </c>
-      <c r="I422" s="7">
+      <c r="I422" s="6">
         <v>1</v>
       </c>
       <c r="J422" s="1" t="s">
@@ -19394,16 +19409,16 @@
       </c>
     </row>
     <row r="423" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="4" t="s">
+      <c r="A423" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="B423" s="4" t="s">
+      <c r="B423" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="C423" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D423" s="9" t="s">
+      <c r="C423" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D423" s="8" t="s">
         <v>556</v>
       </c>
       <c r="E423" s="1" t="s">
@@ -19418,7 +19433,7 @@
       <c r="H423" s="1">
         <v>243</v>
       </c>
-      <c r="I423" s="7">
+      <c r="I423" s="6">
         <v>2</v>
       </c>
       <c r="J423" s="1" t="s">
@@ -19432,16 +19447,16 @@
       </c>
     </row>
     <row r="424" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A424" s="4" t="s">
+      <c r="A424" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="B424" s="4" t="s">
+      <c r="B424" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="C424" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D424" s="9" t="s">
+      <c r="C424" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D424" s="8" t="s">
         <v>557</v>
       </c>
       <c r="E424" s="1" t="s">
@@ -19456,7 +19471,7 @@
       <c r="H424" s="1">
         <v>3095</v>
       </c>
-      <c r="I424" s="7">
+      <c r="I424" s="6">
         <v>1</v>
       </c>
       <c r="J424" s="1" t="s">
@@ -19470,16 +19485,16 @@
       </c>
     </row>
     <row r="425" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A425" s="4" t="s">
+      <c r="A425" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B425" s="4" t="s">
+      <c r="B425" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C425" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D425" s="9" t="s">
+      <c r="C425" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D425" s="8" t="s">
         <v>321</v>
       </c>
       <c r="E425" s="1" t="s">
@@ -19494,7 +19509,7 @@
       <c r="H425" s="1">
         <v>1310</v>
       </c>
-      <c r="I425" s="7">
+      <c r="I425" s="6">
         <v>1802</v>
       </c>
       <c r="J425" s="1" t="s">
@@ -19508,16 +19523,16 @@
       </c>
     </row>
     <row r="426" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A426" s="4" t="s">
+      <c r="A426" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="B426" s="4" t="s">
+      <c r="B426" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="C426" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D426" s="9" t="s">
+      <c r="C426" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D426" s="8" t="s">
         <v>558</v>
       </c>
       <c r="E426" s="1" t="s">
@@ -19532,7 +19547,7 @@
       <c r="H426" s="1">
         <v>911</v>
       </c>
-      <c r="I426" s="7">
+      <c r="I426" s="6">
         <v>0</v>
       </c>
       <c r="J426" s="1" t="s">
@@ -19546,16 +19561,16 @@
       </c>
     </row>
     <row r="427" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A427" s="4" t="s">
+      <c r="A427" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="B427" s="4" t="s">
+      <c r="B427" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="C427" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D427" s="9" t="s">
+      <c r="C427" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D427" s="8" t="s">
         <v>559</v>
       </c>
       <c r="E427" s="1" t="s">
@@ -19570,7 +19585,7 @@
       <c r="H427" s="1">
         <v>266</v>
       </c>
-      <c r="I427" s="7">
+      <c r="I427" s="6">
         <v>0</v>
       </c>
       <c r="J427" s="1" t="s">
@@ -19584,16 +19599,16 @@
       </c>
     </row>
     <row r="428" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A428" s="4" t="s">
+      <c r="A428" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="B428" s="4" t="s">
+      <c r="B428" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="C428" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D428" s="9" t="s">
+      <c r="C428" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D428" s="8" t="s">
         <v>560</v>
       </c>
       <c r="E428" s="1" t="s">
@@ -19608,7 +19623,7 @@
       <c r="H428" s="1">
         <v>1365</v>
       </c>
-      <c r="I428" s="7">
+      <c r="I428" s="6">
         <v>0</v>
       </c>
       <c r="J428" s="1" t="s">
@@ -19622,16 +19637,16 @@
       </c>
     </row>
     <row r="429" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A429" s="4" t="s">
+      <c r="A429" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="B429" s="4" t="s">
+      <c r="B429" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="C429" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D429" s="9" t="s">
+      <c r="C429" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D429" s="8" t="s">
         <v>461</v>
       </c>
       <c r="E429" s="1" t="s">
@@ -19646,7 +19661,7 @@
       <c r="H429" s="1">
         <v>1547</v>
       </c>
-      <c r="I429" s="7">
+      <c r="I429" s="6">
         <v>3</v>
       </c>
       <c r="J429" s="1" t="s">
@@ -19660,16 +19675,16 @@
       </c>
     </row>
     <row r="430" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A430" s="4" t="s">
+      <c r="A430" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="B430" s="4" t="s">
+      <c r="B430" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="C430" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D430" s="9" t="s">
+      <c r="C430" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D430" s="8" t="s">
         <v>561</v>
       </c>
       <c r="E430" s="1" t="s">
@@ -19684,7 +19699,7 @@
       <c r="H430" s="1">
         <v>1795</v>
       </c>
-      <c r="I430" s="7">
+      <c r="I430" s="6">
         <v>1</v>
       </c>
       <c r="J430" s="1" t="s">
@@ -19698,16 +19713,16 @@
       </c>
     </row>
     <row r="431" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A431" s="4" t="s">
+      <c r="A431" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="B431" s="4" t="s">
+      <c r="B431" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="C431" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D431" s="9" t="s">
+      <c r="C431" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D431" s="8" t="s">
         <v>562</v>
       </c>
       <c r="E431" s="1" t="s">
@@ -19722,7 +19737,7 @@
       <c r="H431" s="1">
         <v>1543</v>
       </c>
-      <c r="I431" s="7">
+      <c r="I431" s="6">
         <v>1</v>
       </c>
       <c r="J431" s="1" t="s">
@@ -19736,16 +19751,16 @@
       </c>
     </row>
     <row r="432" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A432" s="4" t="s">
+      <c r="A432" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="B432" s="4" t="s">
+      <c r="B432" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="C432" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D432" s="9" t="s">
+      <c r="C432" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D432" s="8" t="s">
         <v>563</v>
       </c>
       <c r="E432" s="1" t="s">
@@ -19760,7 +19775,7 @@
       <c r="H432" s="1">
         <v>1772</v>
       </c>
-      <c r="I432" s="7">
+      <c r="I432" s="6">
         <v>3</v>
       </c>
       <c r="J432" s="1" t="s">
@@ -19774,16 +19789,16 @@
       </c>
     </row>
     <row r="433" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A433" s="4" t="s">
+      <c r="A433" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="B433" s="4" t="s">
+      <c r="B433" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="C433" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D433" s="9" t="s">
+      <c r="C433" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D433" s="8" t="s">
         <v>564</v>
       </c>
       <c r="E433" s="1" t="s">
@@ -19798,7 +19813,7 @@
       <c r="H433" s="1">
         <v>1108</v>
       </c>
-      <c r="I433" s="7">
+      <c r="I433" s="6">
         <v>0</v>
       </c>
       <c r="J433" s="1" t="s">
@@ -19812,16 +19827,16 @@
       </c>
     </row>
     <row r="434" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A434" s="4" t="s">
+      <c r="A434" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="B434" s="4" t="s">
+      <c r="B434" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="C434" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D434" s="9" t="s">
+      <c r="C434" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D434" s="8" t="s">
         <v>565</v>
       </c>
       <c r="E434" s="1" t="s">
@@ -19836,7 +19851,7 @@
       <c r="H434" s="1">
         <v>1193</v>
       </c>
-      <c r="I434" s="7">
+      <c r="I434" s="6">
         <v>1</v>
       </c>
       <c r="J434" s="1" t="s">
@@ -19850,16 +19865,16 @@
       </c>
     </row>
     <row r="435" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A435" s="4" t="s">
+      <c r="A435" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B435" s="4" t="s">
+      <c r="B435" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C435" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D435" s="9" t="s">
+      <c r="C435" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D435" s="8" t="s">
         <v>344</v>
       </c>
       <c r="E435" s="1" t="s">
@@ -19874,7 +19889,7 @@
       <c r="H435" s="1">
         <v>2888</v>
       </c>
-      <c r="I435" s="7">
+      <c r="I435" s="6">
         <v>221</v>
       </c>
       <c r="J435" s="1" t="s">
@@ -19888,16 +19903,16 @@
       </c>
     </row>
     <row r="436" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A436" s="4" t="s">
+      <c r="A436" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="B436" s="4" t="s">
+      <c r="B436" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="C436" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D436" s="9" t="s">
+      <c r="C436" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D436" s="8" t="s">
         <v>566</v>
       </c>
       <c r="E436" s="1" t="s">
@@ -19912,7 +19927,7 @@
       <c r="H436" s="1">
         <v>1769</v>
       </c>
-      <c r="I436" s="7">
+      <c r="I436" s="6">
         <v>0</v>
       </c>
       <c r="J436" s="1" t="s">
@@ -19926,16 +19941,16 @@
       </c>
     </row>
     <row r="437" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A437" s="4" t="s">
+      <c r="A437" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B437" s="4" t="s">
+      <c r="B437" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C437" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D437" s="9" t="s">
+      <c r="C437" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D437" s="8" t="s">
         <v>353</v>
       </c>
       <c r="E437" s="1" t="s">
@@ -19950,7 +19965,7 @@
       <c r="H437" s="1">
         <v>2863</v>
       </c>
-      <c r="I437" s="7">
+      <c r="I437" s="6">
         <v>7</v>
       </c>
       <c r="J437" s="1" t="s">
@@ -19964,16 +19979,16 @@
       </c>
     </row>
     <row r="438" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A438" s="4" t="s">
+      <c r="A438" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="B438" s="4" t="s">
+      <c r="B438" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="C438" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D438" s="9" t="s">
+      <c r="C438" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D438" s="8" t="s">
         <v>567</v>
       </c>
       <c r="E438" s="1" t="s">
@@ -19988,7 +20003,7 @@
       <c r="H438" s="1">
         <v>1714</v>
       </c>
-      <c r="I438" s="7">
+      <c r="I438" s="6">
         <v>4</v>
       </c>
       <c r="J438" s="1" t="s">
@@ -20002,16 +20017,16 @@
       </c>
     </row>
     <row r="439" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A439" s="4" t="s">
+      <c r="A439" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="B439" s="4" t="s">
+      <c r="B439" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="C439" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D439" s="9" t="s">
+      <c r="C439" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D439" s="8" t="s">
         <v>568</v>
       </c>
       <c r="E439" s="1" t="s">
@@ -20026,7 +20041,7 @@
       <c r="H439" s="1">
         <v>2064</v>
       </c>
-      <c r="I439" s="7">
+      <c r="I439" s="6">
         <v>3</v>
       </c>
       <c r="J439" s="1" t="s">
@@ -20040,16 +20055,16 @@
       </c>
     </row>
     <row r="440" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A440" s="4" t="s">
+      <c r="A440" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="B440" s="4" t="s">
+      <c r="B440" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="C440" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D440" s="9" t="s">
+      <c r="C440" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D440" s="8" t="s">
         <v>569</v>
       </c>
       <c r="E440" s="1" t="s">
@@ -20064,7 +20079,7 @@
       <c r="H440" s="1">
         <v>4812</v>
       </c>
-      <c r="I440" s="7">
+      <c r="I440" s="6">
         <v>0</v>
       </c>
       <c r="J440" s="1" t="s">
@@ -20078,22 +20093,22 @@
       </c>
     </row>
     <row r="441" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A441" s="4" t="s">
+      <c r="A441" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="B441" s="4" t="s">
+      <c r="B441" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="C441" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D441" s="6" t="s">
+      <c r="C441" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D441" s="5" t="s">
         <v>701</v>
       </c>
       <c r="E441" s="1">
         <v>4</v>
       </c>
-      <c r="I441" s="7">
+      <c r="I441" s="6">
         <v>1</v>
       </c>
       <c r="J441" s="1" t="s">
@@ -20107,16 +20122,16 @@
       </c>
     </row>
     <row r="442" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A442" s="4" t="s">
+      <c r="A442" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B442" s="4" t="s">
+      <c r="B442" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C442" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D442" s="9" t="s">
+      <c r="C442" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D442" s="8" t="s">
         <v>357</v>
       </c>
       <c r="E442" s="1" t="s">
@@ -20131,7 +20146,7 @@
       <c r="H442" s="1">
         <v>1809</v>
       </c>
-      <c r="I442" s="7">
+      <c r="I442" s="6">
         <v>109</v>
       </c>
       <c r="J442" s="1" t="s">
@@ -20145,22 +20160,22 @@
       </c>
     </row>
     <row r="443" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A443" s="4" t="s">
+      <c r="A443" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B443" s="4" t="s">
+      <c r="B443" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C443" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D443" s="6" t="s">
+      <c r="C443" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D443" s="5" t="s">
         <v>378</v>
       </c>
       <c r="E443" s="1">
         <v>4</v>
       </c>
-      <c r="I443" s="7">
+      <c r="I443" s="6">
         <v>200</v>
       </c>
       <c r="J443" s="1" t="s">
@@ -20174,16 +20189,16 @@
       </c>
     </row>
     <row r="444" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A444" s="4" t="s">
+      <c r="A444" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B444" s="4" t="s">
+      <c r="B444" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C444" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D444" s="9" t="s">
+      <c r="C444" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D444" s="8" t="s">
         <v>392</v>
       </c>
       <c r="E444" s="1" t="s">
@@ -20198,7 +20213,7 @@
       <c r="H444" s="1">
         <v>241</v>
       </c>
-      <c r="I444" s="7">
+      <c r="I444" s="6">
         <v>229</v>
       </c>
       <c r="J444" s="1" t="s">
@@ -20212,16 +20227,16 @@
       </c>
     </row>
     <row r="445" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A445" s="4" t="s">
+      <c r="A445" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B445" s="4" t="s">
+      <c r="B445" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C445" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D445" s="9" t="s">
+      <c r="C445" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D445" s="8" t="s">
         <v>394</v>
       </c>
       <c r="E445" s="1" t="s">
@@ -20236,7 +20251,7 @@
       <c r="H445" s="1">
         <v>1562</v>
       </c>
-      <c r="I445" s="7">
+      <c r="I445" s="6">
         <v>615</v>
       </c>
       <c r="J445" s="1" t="s">
@@ -20250,16 +20265,16 @@
       </c>
     </row>
     <row r="446" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A446" s="4" t="s">
+      <c r="A446" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B446" s="4" t="s">
+      <c r="B446" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C446" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D446" s="9" t="s">
+      <c r="C446" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D446" s="8" t="s">
         <v>393</v>
       </c>
       <c r="E446" s="1" t="s">
@@ -20274,7 +20289,7 @@
       <c r="H446" s="1">
         <v>685</v>
       </c>
-      <c r="I446" s="7">
+      <c r="I446" s="6">
         <v>2325</v>
       </c>
       <c r="J446" s="1" t="s">
@@ -20288,16 +20303,16 @@
       </c>
     </row>
     <row r="447" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A447" s="4" t="s">
+      <c r="A447" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B447" s="4" t="s">
+      <c r="B447" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C447" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D447" s="9" t="s">
+      <c r="C447" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D447" s="8" t="s">
         <v>398</v>
       </c>
       <c r="E447" s="1" t="s">
@@ -20312,7 +20327,7 @@
       <c r="H447" s="1">
         <v>121</v>
       </c>
-      <c r="I447" s="7">
+      <c r="I447" s="6">
         <v>727</v>
       </c>
       <c r="J447" s="1" t="s">
@@ -20326,16 +20341,16 @@
       </c>
     </row>
     <row r="448" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A448" s="4" t="s">
+      <c r="A448" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B448" s="4" t="s">
+      <c r="B448" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C448" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D448" s="9" t="s">
+      <c r="C448" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D448" s="8" t="s">
         <v>396</v>
       </c>
       <c r="E448" s="1" t="s">
@@ -20350,7 +20365,7 @@
       <c r="H448" s="1">
         <v>1070</v>
       </c>
-      <c r="I448" s="7">
+      <c r="I448" s="6">
         <v>384</v>
       </c>
       <c r="J448" s="1" t="s">
@@ -20364,16 +20379,16 @@
       </c>
     </row>
     <row r="449" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A449" s="4" t="s">
+      <c r="A449" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B449" s="4" t="s">
+      <c r="B449" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C449" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D449" s="9" t="s">
+      <c r="C449" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D449" s="8" t="s">
         <v>397</v>
       </c>
       <c r="E449" s="1" t="s">
@@ -20388,7 +20403,7 @@
       <c r="H449" s="1">
         <v>1760</v>
       </c>
-      <c r="I449" s="7">
+      <c r="I449" s="6">
         <v>931</v>
       </c>
       <c r="J449" s="1" t="s">
@@ -20402,16 +20417,16 @@
       </c>
     </row>
     <row r="450" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A450" s="4" t="s">
+      <c r="A450" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B450" s="4" t="s">
+      <c r="B450" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C450" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D450" s="9" t="s">
+      <c r="C450" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D450" s="8" t="s">
         <v>413</v>
       </c>
       <c r="E450" s="1" t="s">
@@ -20426,7 +20441,7 @@
       <c r="H450" s="1">
         <v>441</v>
       </c>
-      <c r="I450" s="7">
+      <c r="I450" s="6">
         <v>0</v>
       </c>
       <c r="J450" s="1" t="s">
@@ -20440,16 +20455,16 @@
       </c>
     </row>
     <row r="451" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A451" s="4" t="s">
+      <c r="A451" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B451" s="4" t="s">
+      <c r="B451" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C451" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D451" s="9" t="s">
+      <c r="C451" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D451" s="8" t="s">
         <v>414</v>
       </c>
       <c r="E451" s="1" t="s">
@@ -20464,7 +20479,7 @@
       <c r="H451" s="1">
         <v>567</v>
       </c>
-      <c r="I451" s="7">
+      <c r="I451" s="6">
         <v>313</v>
       </c>
       <c r="J451" s="1" t="s">
@@ -20478,16 +20493,16 @@
       </c>
     </row>
     <row r="452" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A452" s="4" t="s">
+      <c r="A452" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B452" s="4" t="s">
+      <c r="B452" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C452" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D452" s="9" t="s">
+      <c r="C452" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D452" s="8" t="s">
         <v>415</v>
       </c>
       <c r="E452" s="1" t="s">
@@ -20502,7 +20517,7 @@
       <c r="H452" s="1">
         <v>1008</v>
       </c>
-      <c r="I452" s="7">
+      <c r="I452" s="6">
         <v>501</v>
       </c>
       <c r="J452" s="1" t="s">
@@ -20516,16 +20531,16 @@
       </c>
     </row>
     <row r="453" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A453" s="4" t="s">
+      <c r="A453" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B453" s="4" t="s">
+      <c r="B453" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C453" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D453" s="9" t="s">
+      <c r="C453" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D453" s="8" t="s">
         <v>416</v>
       </c>
       <c r="E453" s="1" t="s">
@@ -20540,7 +20555,7 @@
       <c r="H453" s="1">
         <v>1008</v>
       </c>
-      <c r="I453" s="7">
+      <c r="I453" s="6">
         <v>173</v>
       </c>
       <c r="J453" s="1" t="s">
@@ -20554,16 +20569,16 @@
       </c>
     </row>
     <row r="454" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A454" s="4" t="s">
+      <c r="A454" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B454" s="4" t="s">
+      <c r="B454" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="C454" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D454" s="9" t="s">
+      <c r="C454" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D454" s="8" t="s">
         <v>395</v>
       </c>
       <c r="E454" s="1" t="s">
@@ -20578,7 +20593,7 @@
       <c r="H454" s="1">
         <v>1109</v>
       </c>
-      <c r="I454" s="7">
+      <c r="I454" s="6">
         <v>2079</v>
       </c>
       <c r="J454" s="1" t="s">
@@ -20592,16 +20607,16 @@
       </c>
     </row>
     <row r="455" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A455" s="4" t="s">
+      <c r="A455" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B455" s="4" t="s">
+      <c r="B455" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C455" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D455" s="7" t="s">
+      <c r="C455" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D455" s="6" t="s">
         <v>417</v>
       </c>
       <c r="E455" s="1" t="s">
@@ -20616,7 +20631,7 @@
       <c r="H455" s="1">
         <v>1805</v>
       </c>
-      <c r="I455" s="7">
+      <c r="I455" s="6">
         <v>310</v>
       </c>
       <c r="J455" s="1" t="s">
@@ -20630,16 +20645,16 @@
       </c>
     </row>
     <row r="456" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A456" s="5" t="s">
+      <c r="A456" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B456" s="7" t="s">
+      <c r="B456" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="C456" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D456" s="5" t="s">
+      <c r="C456" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D456" s="4" t="s">
         <v>429</v>
       </c>
       <c r="E456" s="1" t="s">
@@ -20654,7 +20669,7 @@
       <c r="H456" s="1">
         <v>857</v>
       </c>
-      <c r="I456" s="7">
+      <c r="I456" s="6">
         <v>293</v>
       </c>
       <c r="J456" s="1" t="s">
@@ -20668,16 +20683,16 @@
       </c>
     </row>
     <row r="457" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A457" s="5" t="s">
+      <c r="A457" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B457" s="7" t="s">
+      <c r="B457" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="C457" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D457" s="5" t="s">
+      <c r="C457" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D457" s="4" t="s">
         <v>432</v>
       </c>
       <c r="E457" s="1" t="s">
@@ -20692,7 +20707,7 @@
       <c r="H457" s="1">
         <v>1612</v>
       </c>
-      <c r="I457" s="7">
+      <c r="I457" s="6">
         <v>1</v>
       </c>
       <c r="J457" s="1" t="s">
@@ -20706,16 +20721,16 @@
       </c>
     </row>
     <row r="458" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A458" s="5" t="s">
+      <c r="A458" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B458" s="7" t="s">
+      <c r="B458" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="C458" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D458" s="5" t="s">
+      <c r="C458" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D458" s="4" t="s">
         <v>434</v>
       </c>
       <c r="E458" s="1" t="s">
@@ -20730,7 +20745,7 @@
       <c r="H458" s="1">
         <v>12335</v>
       </c>
-      <c r="I458" s="7">
+      <c r="I458" s="6">
         <v>0</v>
       </c>
       <c r="J458" s="1" t="s">
@@ -20744,16 +20759,16 @@
       </c>
     </row>
     <row r="459" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A459" s="5" t="s">
+      <c r="A459" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B459" s="7" t="s">
+      <c r="B459" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="C459" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D459" s="5" t="s">
+      <c r="C459" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D459" s="4" t="s">
         <v>435</v>
       </c>
       <c r="E459" s="1" t="s">
@@ -20768,7 +20783,7 @@
       <c r="H459" s="1">
         <v>13405</v>
       </c>
-      <c r="I459" s="7">
+      <c r="I459" s="6">
         <v>0</v>
       </c>
       <c r="J459" s="1" t="s">
@@ -20782,16 +20797,16 @@
       </c>
     </row>
     <row r="460" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A460" s="5" t="s">
+      <c r="A460" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B460" s="7" t="s">
+      <c r="B460" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="C460" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D460" s="5" t="s">
+      <c r="C460" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D460" s="4" t="s">
         <v>436</v>
       </c>
       <c r="E460" s="1" t="s">
@@ -20806,7 +20821,7 @@
       <c r="H460" s="1">
         <v>4783</v>
       </c>
-      <c r="I460" s="7">
+      <c r="I460" s="6">
         <v>2</v>
       </c>
       <c r="J460" s="1" t="s">
@@ -20820,16 +20835,16 @@
       </c>
     </row>
     <row r="461" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A461" s="5" t="s">
+      <c r="A461" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B461" s="7" t="s">
+      <c r="B461" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="C461" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D461" s="5" t="s">
+      <c r="C461" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D461" s="4" t="s">
         <v>437</v>
       </c>
       <c r="E461" s="1" t="s">
@@ -20844,7 +20859,7 @@
       <c r="H461" s="1">
         <v>5916</v>
       </c>
-      <c r="I461" s="7">
+      <c r="I461" s="6">
         <v>1</v>
       </c>
       <c r="J461" s="1" t="s">
@@ -20858,16 +20873,16 @@
       </c>
     </row>
     <row r="462" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A462" s="5" t="s">
+      <c r="A462" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B462" s="7" t="s">
+      <c r="B462" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="C462" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D462" s="5" t="s">
+      <c r="C462" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D462" s="4" t="s">
         <v>438</v>
       </c>
       <c r="E462" s="1" t="s">
@@ -20882,7 +20897,7 @@
       <c r="H462" s="1">
         <v>3121</v>
       </c>
-      <c r="I462" s="7">
+      <c r="I462" s="6">
         <v>0</v>
       </c>
       <c r="J462" s="1" t="s">
@@ -20896,16 +20911,16 @@
       </c>
     </row>
     <row r="463" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A463" s="5" t="s">
+      <c r="A463" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B463" s="7" t="s">
+      <c r="B463" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="C463" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D463" s="5" t="s">
+      <c r="C463" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D463" s="4" t="s">
         <v>440</v>
       </c>
       <c r="E463" s="1" t="s">
@@ -20920,7 +20935,7 @@
       <c r="H463" s="1">
         <v>4248</v>
       </c>
-      <c r="I463" s="7">
+      <c r="I463" s="6">
         <v>0</v>
       </c>
       <c r="J463" s="1" t="s">
@@ -20934,22 +20949,22 @@
       </c>
     </row>
     <row r="464" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A464" s="5" t="s">
+      <c r="A464" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B464" s="7" t="s">
+      <c r="B464" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C464" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D464" s="6" t="s">
+      <c r="C464" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D464" s="5" t="s">
         <v>431</v>
       </c>
       <c r="E464" s="1">
         <v>4</v>
       </c>
-      <c r="I464" s="7">
+      <c r="I464" s="6">
         <v>348</v>
       </c>
       <c r="J464" s="1" t="s">
@@ -20963,16 +20978,16 @@
       </c>
     </row>
     <row r="465" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A465" s="5" t="s">
+      <c r="A465" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B465" s="7" t="s">
+      <c r="B465" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="C465" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D465" s="5" t="s">
+      <c r="C465" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D465" s="4" t="s">
         <v>570</v>
       </c>
       <c r="E465" s="1" t="s">
@@ -20987,7 +21002,7 @@
       <c r="H465" s="1">
         <v>477</v>
       </c>
-      <c r="I465" s="7">
+      <c r="I465" s="6">
         <v>651</v>
       </c>
       <c r="J465" s="1" t="s">
@@ -21001,16 +21016,16 @@
       </c>
     </row>
     <row r="466" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A466" s="5" t="s">
+      <c r="A466" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B466" s="7" t="s">
+      <c r="B466" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="C466" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D466" s="5" t="s">
+      <c r="C466" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D466" s="4" t="s">
         <v>428</v>
       </c>
       <c r="E466" s="1" t="s">
@@ -21025,7 +21040,7 @@
       <c r="H466" s="1">
         <v>1482</v>
       </c>
-      <c r="I466" s="7">
+      <c r="I466" s="6">
         <v>292</v>
       </c>
       <c r="J466" s="1" t="s">
@@ -21039,16 +21054,16 @@
       </c>
     </row>
     <row r="467" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A467" s="5" t="s">
+      <c r="A467" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B467" s="7" t="s">
+      <c r="B467" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="C467" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D467" s="7" t="s">
+      <c r="C467" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D467" s="6" t="s">
         <v>571</v>
       </c>
       <c r="E467" s="1" t="s">
@@ -21063,7 +21078,7 @@
       <c r="H467" s="1">
         <v>3149</v>
       </c>
-      <c r="I467" s="7">
+      <c r="I467" s="6">
         <v>684</v>
       </c>
       <c r="J467" s="1" t="s">
@@ -21077,16 +21092,16 @@
       </c>
     </row>
     <row r="468" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A468" s="5" t="s">
+      <c r="A468" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B468" s="7" t="s">
+      <c r="B468" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="C468" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D468" s="7" t="s">
+      <c r="C468" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D468" s="6" t="s">
         <v>445</v>
       </c>
       <c r="E468" s="1" t="s">
@@ -21101,7 +21116,7 @@
       <c r="H468" s="1">
         <v>11599</v>
       </c>
-      <c r="I468" s="7">
+      <c r="I468" s="6">
         <v>0</v>
       </c>
       <c r="J468" s="1" t="s">
@@ -21115,16 +21130,16 @@
       </c>
     </row>
     <row r="469" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A469" s="5" t="s">
+      <c r="A469" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B469" s="7" t="s">
+      <c r="B469" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="C469" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D469" s="7" t="s">
+      <c r="C469" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D469" s="6" t="s">
         <v>427</v>
       </c>
       <c r="E469" s="1" t="s">
@@ -21139,7 +21154,7 @@
       <c r="H469" s="1">
         <v>186</v>
       </c>
-      <c r="I469" s="7">
+      <c r="I469" s="6">
         <v>800</v>
       </c>
       <c r="J469" s="1" t="s">
@@ -21153,16 +21168,16 @@
       </c>
     </row>
     <row r="470" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A470" s="5" t="s">
+      <c r="A470" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B470" s="7" t="s">
+      <c r="B470" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="C470" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D470" s="7" t="s">
+      <c r="C470" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D470" s="6" t="s">
         <v>446</v>
       </c>
       <c r="E470" s="1" t="s">
@@ -21177,7 +21192,7 @@
       <c r="H470" s="1">
         <v>3527</v>
       </c>
-      <c r="I470" s="7">
+      <c r="I470" s="6">
         <v>10</v>
       </c>
       <c r="J470" s="1" t="s">
@@ -21191,16 +21206,16 @@
       </c>
     </row>
     <row r="471" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A471" s="5" t="s">
+      <c r="A471" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B471" s="7" t="s">
+      <c r="B471" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="C471" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D471" s="10" t="s">
+      <c r="C471" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D471" s="9" t="s">
         <v>441</v>
       </c>
       <c r="E471" s="1" t="s">
@@ -21215,7 +21230,7 @@
       <c r="H471" s="1">
         <v>2140</v>
       </c>
-      <c r="I471" s="7">
+      <c r="I471" s="6">
         <v>257</v>
       </c>
       <c r="J471" s="1" t="s">
@@ -21229,16 +21244,16 @@
       </c>
     </row>
     <row r="472" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A472" s="5" t="s">
+      <c r="A472" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B472" s="7" t="s">
+      <c r="B472" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="C472" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D472" s="10" t="s">
+      <c r="C472" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D472" s="9" t="s">
         <v>442</v>
       </c>
       <c r="E472" s="1" t="s">
@@ -21253,7 +21268,7 @@
       <c r="H472" s="1">
         <v>2211</v>
       </c>
-      <c r="I472" s="7">
+      <c r="I472" s="6">
         <v>59</v>
       </c>
       <c r="J472" s="1" t="s">
@@ -21267,16 +21282,16 @@
       </c>
     </row>
     <row r="473" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A473" s="5" t="s">
+      <c r="A473" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B473" s="7" t="s">
+      <c r="B473" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="C473" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D473" s="10" t="s">
+      <c r="C473" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D473" s="9" t="s">
         <v>443</v>
       </c>
       <c r="E473" s="1" t="s">
@@ -21291,7 +21306,7 @@
       <c r="H473" s="1">
         <v>2716</v>
       </c>
-      <c r="I473" s="7">
+      <c r="I473" s="6">
         <v>20</v>
       </c>
       <c r="J473" s="1" t="s">
@@ -21305,16 +21320,16 @@
       </c>
     </row>
     <row r="474" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A474" s="5" t="s">
+      <c r="A474" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B474" s="7" t="s">
+      <c r="B474" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="C474" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D474" s="10" t="s">
+      <c r="C474" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D474" s="9" t="s">
         <v>444</v>
       </c>
       <c r="E474" s="1" t="s">
@@ -21329,7 +21344,7 @@
       <c r="H474" s="1">
         <v>3140</v>
       </c>
-      <c r="I474" s="7">
+      <c r="I474" s="6">
         <v>4</v>
       </c>
       <c r="J474" s="1" t="s">
@@ -21343,16 +21358,16 @@
       </c>
     </row>
     <row r="475" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A475" s="5" t="s">
+      <c r="A475" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B475" s="7" t="s">
+      <c r="B475" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="C475" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D475" s="5" t="s">
+      <c r="C475" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D475" s="4" t="s">
         <v>447</v>
       </c>
       <c r="E475" s="1">
@@ -21367,7 +21382,7 @@
       <c r="H475" s="1">
         <v>0</v>
       </c>
-      <c r="I475" s="7">
+      <c r="I475" s="6">
         <v>3</v>
       </c>
       <c r="J475" s="1" t="s">
@@ -21381,16 +21396,16 @@
       </c>
     </row>
     <row r="476" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A476" s="5" t="s">
+      <c r="A476" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="B476" s="7" t="s">
+      <c r="B476" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="C476" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D476" s="5" t="s">
+      <c r="C476" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D476" s="4" t="s">
         <v>572</v>
       </c>
       <c r="E476" s="1">
@@ -21405,7 +21420,7 @@
       <c r="H476" s="1">
         <v>0</v>
       </c>
-      <c r="I476" s="7">
+      <c r="I476" s="6">
         <v>3</v>
       </c>
       <c r="J476" s="1" t="s">
@@ -21419,16 +21434,16 @@
       </c>
     </row>
     <row r="477" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A477" s="5" t="s">
+      <c r="A477" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B477" s="7" t="s">
+      <c r="B477" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="C477" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D477" s="5" t="s">
+      <c r="C477" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D477" s="4" t="s">
         <v>448</v>
       </c>
       <c r="E477" s="1">
@@ -21443,7 +21458,7 @@
       <c r="H477" s="1">
         <v>0</v>
       </c>
-      <c r="I477" s="7">
+      <c r="I477" s="6">
         <v>2</v>
       </c>
       <c r="J477" s="1" t="s">
@@ -21457,16 +21472,16 @@
       </c>
     </row>
     <row r="478" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A478" s="5" t="s">
+      <c r="A478" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B478" s="7" t="s">
+      <c r="B478" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="C478" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D478" s="5" t="s">
+      <c r="C478" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D478" s="4" t="s">
         <v>449</v>
       </c>
       <c r="E478" s="1">
@@ -21481,7 +21496,7 @@
       <c r="H478" s="1">
         <v>0</v>
       </c>
-      <c r="I478" s="7">
+      <c r="I478" s="6">
         <v>3</v>
       </c>
       <c r="J478" s="1" t="s">
@@ -21495,16 +21510,16 @@
       </c>
     </row>
     <row r="479" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A479" s="5" t="s">
+      <c r="A479" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B479" s="7" t="s">
+      <c r="B479" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="C479" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D479" s="5" t="s">
+      <c r="C479" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D479" s="4" t="s">
         <v>421</v>
       </c>
       <c r="E479" s="1" t="s">
@@ -21519,7 +21534,7 @@
       <c r="H479" s="1">
         <v>3521</v>
       </c>
-      <c r="I479" s="7">
+      <c r="I479" s="6">
         <v>471</v>
       </c>
       <c r="J479" s="1" t="s">
@@ -21533,16 +21548,16 @@
       </c>
     </row>
     <row r="480" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A480" s="11" t="s">
+      <c r="A480" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B480" s="7" t="s">
+      <c r="B480" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C480" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D480" s="7" t="s">
+      <c r="C480" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D480" s="6" t="s">
         <v>319</v>
       </c>
       <c r="E480" s="1" t="s">
@@ -21557,7 +21572,7 @@
       <c r="H480" s="1">
         <v>609</v>
       </c>
-      <c r="I480" s="11">
+      <c r="I480" s="10">
         <v>28</v>
       </c>
       <c r="J480" s="1" t="s">
@@ -21571,16 +21586,16 @@
       </c>
     </row>
     <row r="481" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A481" s="11" t="s">
+      <c r="A481" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B481" s="7" t="s">
+      <c r="B481" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="C481" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D481" s="7" t="s">
+      <c r="C481" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D481" s="6" t="s">
         <v>393</v>
       </c>
       <c r="E481" s="1" t="s">
@@ -21595,7 +21610,7 @@
       <c r="H481" s="1">
         <v>685</v>
       </c>
-      <c r="I481" s="11">
+      <c r="I481" s="10">
         <v>92</v>
       </c>
       <c r="J481" s="1" t="s">
@@ -21609,16 +21624,16 @@
       </c>
     </row>
     <row r="482" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A482" s="11" t="s">
+      <c r="A482" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B482" s="7" t="s">
+      <c r="B482" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C482" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D482" s="7" t="s">
+      <c r="C482" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D482" s="6" t="s">
         <v>388</v>
       </c>
       <c r="E482" s="1" t="s">
@@ -21633,7 +21648,7 @@
       <c r="H482" s="1">
         <v>4107</v>
       </c>
-      <c r="I482" s="11">
+      <c r="I482" s="10">
         <v>49</v>
       </c>
       <c r="J482" s="1" t="s">
@@ -21647,16 +21662,16 @@
       </c>
     </row>
     <row r="483" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A483" s="11" t="s">
+      <c r="A483" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B483" s="7" t="s">
+      <c r="B483" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="C483" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D483" s="7" t="s">
+      <c r="C483" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D483" s="6" t="s">
         <v>321</v>
       </c>
       <c r="E483" s="1" t="s">
@@ -21671,7 +21686,7 @@
       <c r="H483" s="1">
         <v>1310</v>
       </c>
-      <c r="I483" s="11">
+      <c r="I483" s="10">
         <v>59</v>
       </c>
       <c r="J483" s="1" t="s">
@@ -21685,16 +21700,16 @@
       </c>
     </row>
     <row r="484" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A484" s="11" t="s">
+      <c r="A484" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B484" s="7" t="s">
+      <c r="B484" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="C484" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D484" s="7" t="s">
+      <c r="C484" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D484" s="6" t="s">
         <v>395</v>
       </c>
       <c r="E484" s="1" t="s">
@@ -21709,7 +21724,7 @@
       <c r="H484" s="1">
         <v>1109</v>
       </c>
-      <c r="I484" s="11">
+      <c r="I484" s="10">
         <v>105</v>
       </c>
       <c r="J484" s="1" t="s">
@@ -21723,16 +21738,16 @@
       </c>
     </row>
     <row r="485" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A485" s="11" t="s">
+      <c r="A485" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B485" s="7" t="s">
+      <c r="B485" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C485" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D485" s="7" t="s">
+      <c r="C485" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D485" s="6" t="s">
         <v>380</v>
       </c>
       <c r="E485" s="1" t="s">
@@ -21747,7 +21762,7 @@
       <c r="H485" s="1">
         <v>1865</v>
       </c>
-      <c r="I485" s="11">
+      <c r="I485" s="10">
         <v>30</v>
       </c>
       <c r="J485" s="1" t="s">
@@ -21761,16 +21776,16 @@
       </c>
     </row>
     <row r="486" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A486" s="11" t="s">
+      <c r="A486" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B486" s="7" t="s">
+      <c r="B486" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="C486" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D486" s="7" t="s">
+      <c r="C486" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D486" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E486" s="1" t="s">
@@ -21785,7 +21800,7 @@
       <c r="H486" s="1">
         <v>1760</v>
       </c>
-      <c r="I486" s="11">
+      <c r="I486" s="10">
         <v>30</v>
       </c>
       <c r="J486" s="1" t="s">
@@ -21799,16 +21814,16 @@
       </c>
     </row>
     <row r="487" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A487" s="11" t="s">
+      <c r="A487" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B487" s="7" t="s">
+      <c r="B487" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="C487" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D487" s="7" t="s">
+      <c r="C487" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D487" s="6" t="s">
         <v>361</v>
       </c>
       <c r="E487" s="1" t="s">
@@ -21823,7 +21838,7 @@
       <c r="H487" s="1">
         <v>2683</v>
       </c>
-      <c r="I487" s="11">
+      <c r="I487" s="10">
         <v>41</v>
       </c>
       <c r="J487" s="1" t="s">
@@ -21837,16 +21852,16 @@
       </c>
     </row>
     <row r="488" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A488" s="11" t="s">
+      <c r="A488" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B488" s="7" t="s">
+      <c r="B488" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="C488" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D488" s="7" t="s">
+      <c r="C488" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D488" s="6" t="s">
         <v>379</v>
       </c>
       <c r="E488" s="1" t="s">
@@ -21861,7 +21876,7 @@
       <c r="H488" s="1">
         <v>1925</v>
       </c>
-      <c r="I488" s="11">
+      <c r="I488" s="10">
         <v>47</v>
       </c>
       <c r="J488" s="1" t="s">
@@ -21875,16 +21890,16 @@
       </c>
     </row>
     <row r="489" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A489" s="11" t="s">
+      <c r="A489" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B489" s="7" t="s">
+      <c r="B489" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="C489" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D489" s="7" t="s">
+      <c r="C489" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D489" s="6" t="s">
         <v>375</v>
       </c>
       <c r="E489" s="1" t="s">
@@ -21899,7 +21914,7 @@
       <c r="H489" s="1">
         <v>566</v>
       </c>
-      <c r="I489" s="11">
+      <c r="I489" s="10">
         <v>88</v>
       </c>
       <c r="J489" s="1" t="s">
@@ -21913,16 +21928,16 @@
       </c>
     </row>
     <row r="490" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A490" s="11" t="s">
+      <c r="A490" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B490" s="7" t="s">
+      <c r="B490" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C490" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D490" s="7" t="s">
+      <c r="C490" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D490" s="6" t="s">
         <v>317</v>
       </c>
       <c r="E490" s="1" t="s">
@@ -21937,7 +21952,7 @@
       <c r="H490" s="1">
         <v>1362</v>
       </c>
-      <c r="I490" s="11">
+      <c r="I490" s="10">
         <v>130</v>
       </c>
       <c r="J490" s="1" t="s">
@@ -21951,16 +21966,16 @@
       </c>
     </row>
     <row r="491" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A491" s="11" t="s">
+      <c r="A491" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B491" s="7" t="s">
+      <c r="B491" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C491" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D491" s="7" t="s">
+      <c r="C491" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D491" s="6" t="s">
         <v>373</v>
       </c>
       <c r="E491" s="1" t="s">
@@ -21975,7 +21990,7 @@
       <c r="H491" s="1">
         <v>1023</v>
       </c>
-      <c r="I491" s="11">
+      <c r="I491" s="10">
         <v>19</v>
       </c>
       <c r="J491" s="1" t="s">
@@ -21989,16 +22004,16 @@
       </c>
     </row>
     <row r="492" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A492" s="11" t="s">
+      <c r="A492" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B492" s="7" t="s">
+      <c r="B492" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="C492" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D492" s="7" t="s">
+      <c r="C492" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D492" s="6" t="s">
         <v>394</v>
       </c>
       <c r="E492" s="1" t="s">
@@ -22013,7 +22028,7 @@
       <c r="H492" s="1">
         <v>1562</v>
       </c>
-      <c r="I492" s="11">
+      <c r="I492" s="10">
         <v>58</v>
       </c>
       <c r="J492" s="1" t="s">
@@ -22027,16 +22042,16 @@
       </c>
     </row>
     <row r="493" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A493" s="11" t="s">
+      <c r="A493" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B493" s="7" t="s">
+      <c r="B493" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="C493" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D493" s="7" t="s">
+      <c r="C493" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D493" s="6" t="s">
         <v>383</v>
       </c>
       <c r="E493" s="1" t="s">
@@ -22051,7 +22066,7 @@
       <c r="H493" s="1">
         <v>803</v>
       </c>
-      <c r="I493" s="11">
+      <c r="I493" s="10">
         <v>105</v>
       </c>
       <c r="J493" s="1" t="s">
@@ -22065,16 +22080,16 @@
       </c>
     </row>
     <row r="494" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A494" s="11" t="s">
+      <c r="A494" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B494" s="7" t="s">
+      <c r="B494" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C494" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D494" s="7" t="s">
+      <c r="C494" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D494" s="6" t="s">
         <v>327</v>
       </c>
       <c r="E494" s="1" t="s">
@@ -22089,7 +22104,7 @@
       <c r="H494" s="1">
         <v>805</v>
       </c>
-      <c r="I494" s="11">
+      <c r="I494" s="10">
         <v>20</v>
       </c>
       <c r="J494" s="1" t="s">
@@ -22103,16 +22118,16 @@
       </c>
     </row>
     <row r="495" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A495" s="11" t="s">
+      <c r="A495" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B495" s="7" t="s">
+      <c r="B495" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C495" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D495" s="7" t="s">
+      <c r="C495" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D495" s="6" t="s">
         <v>335</v>
       </c>
       <c r="E495" s="1" t="s">
@@ -22127,7 +22142,7 @@
       <c r="H495" s="1">
         <v>259</v>
       </c>
-      <c r="I495" s="11">
+      <c r="I495" s="10">
         <v>50</v>
       </c>
       <c r="J495" s="1" t="s">
@@ -22141,16 +22156,16 @@
       </c>
     </row>
     <row r="496" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A496" s="11" t="s">
+      <c r="A496" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B496" s="7" t="s">
+      <c r="B496" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="C496" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D496" s="7" t="s">
+      <c r="C496" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D496" s="6" t="s">
         <v>416</v>
       </c>
       <c r="E496" s="1" t="s">
@@ -22165,7 +22180,7 @@
       <c r="H496" s="1">
         <v>1008</v>
       </c>
-      <c r="I496" s="11">
+      <c r="I496" s="10">
         <v>29</v>
       </c>
       <c r="J496" s="1" t="s">
@@ -22179,22 +22194,22 @@
       </c>
     </row>
     <row r="497" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A497" s="11" t="s">
+      <c r="A497" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B497" s="7" t="s">
+      <c r="B497" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C497" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D497" s="6" t="s">
+      <c r="C497" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D497" s="5" t="s">
         <v>431</v>
       </c>
       <c r="E497" s="1">
         <v>4</v>
       </c>
-      <c r="I497" s="11">
+      <c r="I497" s="10">
         <v>1</v>
       </c>
       <c r="J497" s="1" t="s">
@@ -22208,16 +22223,16 @@
       </c>
     </row>
     <row r="498" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A498" s="11" t="s">
+      <c r="A498" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B498" s="7" t="s">
+      <c r="B498" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="C498" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D498" s="7" t="s">
+      <c r="C498" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D498" s="6" t="s">
         <v>434</v>
       </c>
       <c r="E498" s="1" t="s">
@@ -22232,7 +22247,7 @@
       <c r="H498" s="1">
         <v>12335</v>
       </c>
-      <c r="I498" s="11">
+      <c r="I498" s="10">
         <v>2</v>
       </c>
       <c r="J498" s="1" t="s">
@@ -22246,16 +22261,16 @@
       </c>
     </row>
     <row r="499" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A499" s="11" t="s">
+      <c r="A499" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B499" s="7" t="s">
+      <c r="B499" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="C499" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D499" s="7" t="s">
+      <c r="C499" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D499" s="6" t="s">
         <v>376</v>
       </c>
       <c r="E499" s="1" t="s">
@@ -22270,7 +22285,7 @@
       <c r="H499" s="1">
         <v>3946</v>
       </c>
-      <c r="I499" s="11">
+      <c r="I499" s="10">
         <v>10</v>
       </c>
       <c r="J499" s="1" t="s">
@@ -22284,16 +22299,16 @@
       </c>
     </row>
     <row r="500" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A500" s="11" t="s">
+      <c r="A500" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B500" s="7" t="s">
+      <c r="B500" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="C500" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D500" s="7" t="s">
+      <c r="C500" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D500" s="6" t="s">
         <v>440</v>
       </c>
       <c r="E500" s="1" t="s">
@@ -22308,7 +22323,7 @@
       <c r="H500" s="1">
         <v>4248</v>
       </c>
-      <c r="I500" s="11">
+      <c r="I500" s="10">
         <v>10</v>
       </c>
       <c r="J500" s="1" t="s">
@@ -22322,16 +22337,16 @@
       </c>
     </row>
     <row r="501" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A501" s="11" t="s">
+      <c r="A501" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B501" s="7" t="s">
+      <c r="B501" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="C501" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D501" s="7" t="s">
+      <c r="C501" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D501" s="6" t="s">
         <v>446</v>
       </c>
       <c r="E501" s="1" t="s">
@@ -22346,7 +22361,7 @@
       <c r="H501" s="1">
         <v>3527</v>
       </c>
-      <c r="I501" s="11">
+      <c r="I501" s="10">
         <v>19</v>
       </c>
       <c r="J501" s="1" t="s">
@@ -22360,16 +22375,16 @@
       </c>
     </row>
     <row r="502" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A502" s="11" t="s">
+      <c r="A502" s="10" t="s">
         <v>531</v>
       </c>
-      <c r="B502" s="7" t="s">
+      <c r="B502" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="C502" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D502" s="7" t="s">
+      <c r="C502" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D502" s="6" t="s">
         <v>576</v>
       </c>
       <c r="E502" s="1" t="s">
@@ -22384,7 +22399,7 @@
       <c r="H502" s="1">
         <v>8889</v>
       </c>
-      <c r="I502" s="11">
+      <c r="I502" s="10">
         <v>4</v>
       </c>
       <c r="J502" s="1" t="s">
@@ -22398,22 +22413,22 @@
       </c>
     </row>
     <row r="503" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A503" s="11" t="s">
+      <c r="A503" s="10" t="s">
         <v>575</v>
       </c>
-      <c r="B503" s="7" t="s">
+      <c r="B503" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="C503" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D503" s="7" t="s">
+      <c r="C503" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D503" s="6" t="s">
         <v>577</v>
       </c>
       <c r="E503" s="1">
         <v>4</v>
       </c>
-      <c r="I503" s="11">
+      <c r="I503" s="10">
         <v>1</v>
       </c>
       <c r="J503" s="1" t="s">
@@ -22427,16 +22442,16 @@
       </c>
     </row>
     <row r="504" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A504" s="11" t="s">
+      <c r="A504" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B504" s="7" t="s">
+      <c r="B504" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="C504" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D504" s="7" t="s">
+      <c r="C504" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D504" s="6" t="s">
         <v>445</v>
       </c>
       <c r="E504" s="1" t="s">
@@ -22451,7 +22466,7 @@
       <c r="H504" s="1">
         <v>11599</v>
       </c>
-      <c r="I504" s="11">
+      <c r="I504" s="10">
         <v>30</v>
       </c>
       <c r="J504" s="1" t="s">
@@ -22465,16 +22480,16 @@
       </c>
     </row>
     <row r="505" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A505" s="11" t="s">
+      <c r="A505" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B505" s="7" t="s">
+      <c r="B505" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="C505" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D505" s="7" t="s">
+      <c r="C505" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D505" s="6" t="s">
         <v>427</v>
       </c>
       <c r="E505" s="1" t="s">
@@ -22489,7 +22504,7 @@
       <c r="H505" s="1">
         <v>186</v>
       </c>
-      <c r="I505" s="11">
+      <c r="I505" s="10">
         <v>50</v>
       </c>
       <c r="J505" s="1" t="s">
@@ -22503,16 +22518,16 @@
       </c>
     </row>
     <row r="506" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A506" s="11" t="s">
+      <c r="A506" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B506" s="7" t="s">
+      <c r="B506" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="C506" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D506" s="7" t="s">
+      <c r="C506" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D506" s="6" t="s">
         <v>437</v>
       </c>
       <c r="E506" s="1" t="s">
@@ -22527,7 +22542,7 @@
       <c r="H506" s="1">
         <v>5916</v>
       </c>
-      <c r="I506" s="11">
+      <c r="I506" s="10">
         <v>5</v>
       </c>
       <c r="J506" s="1" t="s">
@@ -22541,16 +22556,16 @@
       </c>
     </row>
     <row r="507" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A507" s="11" t="s">
+      <c r="A507" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B507" s="7" t="s">
+      <c r="B507" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="C507" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D507" s="7" t="s">
+      <c r="C507" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D507" s="6" t="s">
         <v>436</v>
       </c>
       <c r="E507" s="1" t="s">
@@ -22565,7 +22580,7 @@
       <c r="H507" s="1">
         <v>4783</v>
       </c>
-      <c r="I507" s="11">
+      <c r="I507" s="10">
         <v>15</v>
       </c>
       <c r="J507" s="1" t="s">
@@ -22579,16 +22594,16 @@
       </c>
     </row>
     <row r="508" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A508" s="5" t="s">
+      <c r="A508" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B508" s="7" t="s">
+      <c r="B508" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="C508" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D508" s="8" t="s">
+      <c r="C508" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D508" s="7" t="s">
         <v>447</v>
       </c>
       <c r="E508" s="1">
@@ -22603,7 +22618,7 @@
       <c r="H508" s="1">
         <v>0</v>
       </c>
-      <c r="I508" s="11">
+      <c r="I508" s="10">
         <v>5</v>
       </c>
       <c r="J508" s="1" t="s">
@@ -22617,16 +22632,16 @@
       </c>
     </row>
     <row r="509" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A509" s="5" t="s">
+      <c r="A509" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="B509" s="7" t="s">
+      <c r="B509" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="C509" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D509" s="8" t="s">
+      <c r="C509" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D509" s="7" t="s">
         <v>572</v>
       </c>
       <c r="E509" s="1">
@@ -22641,7 +22656,7 @@
       <c r="H509" s="1">
         <v>0</v>
       </c>
-      <c r="I509" s="11">
+      <c r="I509" s="10">
         <v>5</v>
       </c>
       <c r="J509" s="1" t="s">
@@ -22655,16 +22670,16 @@
       </c>
     </row>
     <row r="510" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A510" s="5" t="s">
+      <c r="A510" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B510" s="7" t="s">
+      <c r="B510" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="C510" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D510" s="8" t="s">
+      <c r="C510" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D510" s="7" t="s">
         <v>448</v>
       </c>
       <c r="E510" s="1">
@@ -22679,7 +22694,7 @@
       <c r="H510" s="1">
         <v>0</v>
       </c>
-      <c r="I510" s="11">
+      <c r="I510" s="10">
         <v>5</v>
       </c>
       <c r="J510" s="1" t="s">
@@ -22693,16 +22708,16 @@
       </c>
     </row>
     <row r="511" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A511" s="5" t="s">
+      <c r="A511" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B511" s="7" t="s">
+      <c r="B511" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="C511" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D511" s="8" t="s">
+      <c r="C511" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D511" s="7" t="s">
         <v>449</v>
       </c>
       <c r="E511" s="1">
@@ -22717,7 +22732,7 @@
       <c r="H511" s="1">
         <v>0</v>
       </c>
-      <c r="I511" s="11">
+      <c r="I511" s="10">
         <v>5</v>
       </c>
       <c r="J511" s="1" t="s">
@@ -22731,16 +22746,16 @@
       </c>
     </row>
     <row r="512" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A512" s="5" t="s">
+      <c r="A512" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B512" s="7" t="s">
+      <c r="B512" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="C512" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D512" s="8" t="s">
+      <c r="C512" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D512" s="7" t="s">
         <v>421</v>
       </c>
       <c r="E512" s="1" t="s">
@@ -22755,7 +22770,7 @@
       <c r="H512" s="1">
         <v>3521</v>
       </c>
-      <c r="I512" s="11">
+      <c r="I512" s="10">
         <v>50</v>
       </c>
       <c r="J512" s="1" t="s">
@@ -22769,16 +22784,16 @@
       </c>
     </row>
     <row r="513" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A513" s="7" t="s">
+      <c r="A513" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B513" s="7" t="s">
+      <c r="B513" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="C513" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D513" s="7" t="s">
+      <c r="C513" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D513" s="6" t="s">
         <v>361</v>
       </c>
       <c r="E513" s="1" t="s">
@@ -22793,13 +22808,13 @@
       <c r="H513" s="1">
         <v>2683</v>
       </c>
-      <c r="I513" s="7">
+      <c r="I513" s="6">
         <v>63</v>
       </c>
-      <c r="J513" s="12" t="s">
+      <c r="J513" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="K513" s="13" t="s">
+      <c r="K513" s="12" t="s">
         <v>454</v>
       </c>
       <c r="L513" s="1" t="s">
@@ -22807,16 +22822,16 @@
       </c>
     </row>
     <row r="514" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A514" s="7" t="s">
+      <c r="A514" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B514" s="7" t="s">
+      <c r="B514" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C514" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D514" s="7" t="s">
+      <c r="C514" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D514" s="6" t="s">
         <v>373</v>
       </c>
       <c r="E514" s="1" t="s">
@@ -22831,13 +22846,13 @@
       <c r="H514" s="1">
         <v>1023</v>
       </c>
-      <c r="I514" s="7">
+      <c r="I514" s="6">
         <v>93</v>
       </c>
-      <c r="J514" s="12" t="s">
+      <c r="J514" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="K514" s="13" t="s">
+      <c r="K514" s="12" t="s">
         <v>454</v>
       </c>
       <c r="L514" s="1" t="s">
@@ -22845,16 +22860,16 @@
       </c>
     </row>
     <row r="515" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A515" s="7" t="s">
+      <c r="A515" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B515" s="7" t="s">
+      <c r="B515" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C515" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D515" s="7" t="s">
+      <c r="C515" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D515" s="6" t="s">
         <v>317</v>
       </c>
       <c r="E515" s="1" t="s">
@@ -22869,13 +22884,13 @@
       <c r="H515" s="1">
         <v>1362</v>
       </c>
-      <c r="I515" s="7">
+      <c r="I515" s="6">
         <v>29</v>
       </c>
-      <c r="J515" s="12" t="s">
+      <c r="J515" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="K515" s="13" t="s">
+      <c r="K515" s="12" t="s">
         <v>454</v>
       </c>
       <c r="L515" s="1" t="s">
@@ -22883,28 +22898,28 @@
       </c>
     </row>
     <row r="516" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A516" s="7" t="s">
+      <c r="A516" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B516" s="7" t="s">
+      <c r="B516" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C516" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D516" s="7" t="s">
+      <c r="C516" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D516" s="6" t="s">
         <v>345</v>
       </c>
       <c r="E516" s="1">
         <v>4</v>
       </c>
-      <c r="I516" s="7">
+      <c r="I516" s="6">
         <v>55</v>
       </c>
-      <c r="J516" s="12" t="s">
+      <c r="J516" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="K516" s="13" t="s">
+      <c r="K516" s="12" t="s">
         <v>454</v>
       </c>
       <c r="L516" s="1" t="s">
@@ -22912,16 +22927,16 @@
       </c>
     </row>
     <row r="517" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A517" s="7" t="s">
+      <c r="A517" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B517" s="7" t="s">
+      <c r="B517" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C517" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D517" s="7" t="s">
+      <c r="C517" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D517" s="6" t="s">
         <v>380</v>
       </c>
       <c r="E517" s="1" t="s">
@@ -22936,13 +22951,13 @@
       <c r="H517" s="1">
         <v>1865</v>
       </c>
-      <c r="I517" s="7">
+      <c r="I517" s="6">
         <v>48</v>
       </c>
-      <c r="J517" s="12" t="s">
+      <c r="J517" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="K517" s="13" t="s">
+      <c r="K517" s="12" t="s">
         <v>454</v>
       </c>
       <c r="L517" s="1" t="s">
@@ -22950,16 +22965,16 @@
       </c>
     </row>
     <row r="518" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A518" s="7" t="s">
+      <c r="A518" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B518" s="7" t="s">
+      <c r="B518" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C518" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D518" s="7" t="s">
+      <c r="C518" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D518" s="6" t="s">
         <v>374</v>
       </c>
       <c r="E518" s="1" t="s">
@@ -22974,13 +22989,13 @@
       <c r="H518" s="1">
         <v>698</v>
       </c>
-      <c r="I518" s="7">
+      <c r="I518" s="6">
         <v>67</v>
       </c>
-      <c r="J518" s="12" t="s">
+      <c r="J518" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="K518" s="13" t="s">
+      <c r="K518" s="12" t="s">
         <v>454</v>
       </c>
       <c r="L518" s="1" t="s">
@@ -22988,16 +23003,16 @@
       </c>
     </row>
     <row r="519" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A519" s="7" t="s">
+      <c r="A519" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B519" s="7" t="s">
+      <c r="B519" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="C519" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D519" s="7" t="s">
+      <c r="C519" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D519" s="6" t="s">
         <v>375</v>
       </c>
       <c r="E519" s="1" t="s">
@@ -23012,13 +23027,13 @@
       <c r="H519" s="1">
         <v>566</v>
       </c>
-      <c r="I519" s="7">
+      <c r="I519" s="6">
         <v>3</v>
       </c>
-      <c r="J519" s="12" t="s">
+      <c r="J519" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="K519" s="13" t="s">
+      <c r="K519" s="12" t="s">
         <v>454</v>
       </c>
       <c r="L519" s="1" t="s">
@@ -23026,16 +23041,16 @@
       </c>
     </row>
     <row r="520" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A520" s="7" t="s">
+      <c r="A520" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B520" s="7" t="s">
+      <c r="B520" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="C520" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D520" s="7" t="s">
+      <c r="C520" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D520" s="6" t="s">
         <v>317</v>
       </c>
       <c r="E520" s="1" t="s">
@@ -23050,13 +23065,13 @@
       <c r="H520" s="1">
         <v>1362</v>
       </c>
-      <c r="I520" s="7">
+      <c r="I520" s="6">
         <v>2</v>
       </c>
-      <c r="J520" s="12" t="s">
+      <c r="J520" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K520" s="13" t="s">
+      <c r="K520" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L520" s="1" t="s">
@@ -23064,16 +23079,16 @@
       </c>
     </row>
     <row r="521" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A521" s="7" t="s">
+      <c r="A521" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B521" s="7" t="s">
+      <c r="B521" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="C521" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D521" s="7" t="s">
+      <c r="C521" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D521" s="6" t="s">
         <v>319</v>
       </c>
       <c r="E521" s="1" t="s">
@@ -23088,13 +23103,13 @@
       <c r="H521" s="1">
         <v>609</v>
       </c>
-      <c r="I521" s="7">
+      <c r="I521" s="6">
         <v>1</v>
       </c>
-      <c r="J521" s="12" t="s">
+      <c r="J521" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K521" s="13" t="s">
+      <c r="K521" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L521" s="1" t="s">
@@ -23102,16 +23117,16 @@
       </c>
     </row>
     <row r="522" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A522" s="7" t="s">
+      <c r="A522" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B522" s="7" t="s">
+      <c r="B522" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="C522" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D522" s="7" t="s">
+      <c r="C522" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D522" s="6" t="s">
         <v>320</v>
       </c>
       <c r="E522" s="1" t="s">
@@ -23126,13 +23141,13 @@
       <c r="H522" s="1">
         <v>1569</v>
       </c>
-      <c r="I522" s="7">
+      <c r="I522" s="6">
         <v>1</v>
       </c>
-      <c r="J522" s="12" t="s">
+      <c r="J522" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K522" s="13" t="s">
+      <c r="K522" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L522" s="1" t="s">
@@ -23140,16 +23155,16 @@
       </c>
     </row>
     <row r="523" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A523" s="7" t="s">
+      <c r="A523" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B523" s="7" t="s">
+      <c r="B523" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="C523" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D523" s="7" t="s">
+      <c r="C523" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D523" s="6" t="s">
         <v>321</v>
       </c>
       <c r="E523" s="1" t="s">
@@ -23164,13 +23179,13 @@
       <c r="H523" s="1">
         <v>1310</v>
       </c>
-      <c r="I523" s="7">
+      <c r="I523" s="6">
         <v>2</v>
       </c>
-      <c r="J523" s="12" t="s">
+      <c r="J523" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K523" s="13" t="s">
+      <c r="K523" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L523" s="1" t="s">
@@ -23178,16 +23193,16 @@
       </c>
     </row>
     <row r="524" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A524" s="7" t="s">
+      <c r="A524" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B524" s="7" t="s">
+      <c r="B524" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="C524" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D524" s="7" t="s">
+      <c r="C524" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D524" s="6" t="s">
         <v>324</v>
       </c>
       <c r="E524" s="1" t="s">
@@ -23202,13 +23217,13 @@
       <c r="H524" s="1">
         <v>1675</v>
       </c>
-      <c r="I524" s="7">
+      <c r="I524" s="6">
         <v>1</v>
       </c>
-      <c r="J524" s="12" t="s">
+      <c r="J524" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K524" s="13" t="s">
+      <c r="K524" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L524" s="1" t="s">
@@ -23216,16 +23231,16 @@
       </c>
     </row>
     <row r="525" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A525" s="7" t="s">
+      <c r="A525" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B525" s="7" t="s">
+      <c r="B525" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C525" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D525" s="7" t="s">
+      <c r="C525" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D525" s="6" t="s">
         <v>328</v>
       </c>
       <c r="E525" s="1" t="s">
@@ -23240,13 +23255,13 @@
       <c r="H525" s="1">
         <v>4552</v>
       </c>
-      <c r="I525" s="7">
+      <c r="I525" s="6">
         <v>1</v>
       </c>
-      <c r="J525" s="12" t="s">
+      <c r="J525" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K525" s="13" t="s">
+      <c r="K525" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L525" s="1" t="s">
@@ -23254,16 +23269,16 @@
       </c>
     </row>
     <row r="526" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A526" s="7" t="s">
+      <c r="A526" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B526" s="7" t="s">
+      <c r="B526" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="C526" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D526" s="7" t="s">
+      <c r="C526" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D526" s="6" t="s">
         <v>329</v>
       </c>
       <c r="E526" s="1" t="s">
@@ -23278,13 +23293,13 @@
       <c r="H526" s="1">
         <v>2636</v>
       </c>
-      <c r="I526" s="7">
+      <c r="I526" s="6">
         <v>1</v>
       </c>
-      <c r="J526" s="12" t="s">
+      <c r="J526" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K526" s="13" t="s">
+      <c r="K526" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L526" s="1" t="s">
@@ -23292,16 +23307,16 @@
       </c>
     </row>
     <row r="527" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A527" s="7" t="s">
+      <c r="A527" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B527" s="7" t="s">
+      <c r="B527" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="C527" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D527" s="7" t="s">
+      <c r="C527" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D527" s="6" t="s">
         <v>330</v>
       </c>
       <c r="E527" s="1" t="s">
@@ -23316,13 +23331,13 @@
       <c r="H527" s="1">
         <v>2572</v>
       </c>
-      <c r="I527" s="7">
+      <c r="I527" s="6">
         <v>1</v>
       </c>
-      <c r="J527" s="12" t="s">
+      <c r="J527" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K527" s="13" t="s">
+      <c r="K527" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L527" s="1" t="s">
@@ -23330,16 +23345,16 @@
       </c>
     </row>
     <row r="528" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A528" s="7" t="s">
+      <c r="A528" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B528" s="7" t="s">
+      <c r="B528" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="C528" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D528" s="7" t="s">
+      <c r="C528" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D528" s="6" t="s">
         <v>331</v>
       </c>
       <c r="E528" s="1" t="s">
@@ -23354,13 +23369,13 @@
       <c r="H528" s="1">
         <v>1205</v>
       </c>
-      <c r="I528" s="7">
+      <c r="I528" s="6">
         <v>1</v>
       </c>
-      <c r="J528" s="12" t="s">
+      <c r="J528" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K528" s="13" t="s">
+      <c r="K528" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L528" s="1" t="s">
@@ -23368,16 +23383,16 @@
       </c>
     </row>
     <row r="529" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A529" s="7" t="s">
+      <c r="A529" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B529" s="7" t="s">
+      <c r="B529" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="C529" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D529" s="7" t="s">
+      <c r="C529" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D529" s="6" t="s">
         <v>332</v>
       </c>
       <c r="E529" s="1" t="s">
@@ -23392,13 +23407,13 @@
       <c r="H529" s="1">
         <v>2133</v>
       </c>
-      <c r="I529" s="7">
+      <c r="I529" s="6">
         <v>2</v>
       </c>
-      <c r="J529" s="12" t="s">
+      <c r="J529" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K529" s="13" t="s">
+      <c r="K529" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L529" s="1" t="s">
@@ -23406,16 +23421,16 @@
       </c>
     </row>
     <row r="530" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A530" s="7" t="s">
+      <c r="A530" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B530" s="7" t="s">
+      <c r="B530" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="C530" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D530" s="7" t="s">
+      <c r="C530" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D530" s="6" t="s">
         <v>333</v>
       </c>
       <c r="E530" s="1" t="s">
@@ -23430,13 +23445,13 @@
       <c r="H530" s="1">
         <v>3843</v>
       </c>
-      <c r="I530" s="7">
+      <c r="I530" s="6">
         <v>1</v>
       </c>
-      <c r="J530" s="12" t="s">
+      <c r="J530" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K530" s="13" t="s">
+      <c r="K530" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L530" s="1" t="s">
@@ -23444,16 +23459,16 @@
       </c>
     </row>
     <row r="531" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A531" s="7" t="s">
+      <c r="A531" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B531" s="7" t="s">
+      <c r="B531" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="C531" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D531" s="7" t="s">
+      <c r="C531" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D531" s="6" t="s">
         <v>334</v>
       </c>
       <c r="E531" s="1" t="s">
@@ -23468,13 +23483,13 @@
       <c r="H531" s="1">
         <v>2745</v>
       </c>
-      <c r="I531" s="7">
+      <c r="I531" s="6">
         <v>1</v>
       </c>
-      <c r="J531" s="12" t="s">
+      <c r="J531" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K531" s="13" t="s">
+      <c r="K531" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L531" s="1" t="s">
@@ -23482,16 +23497,16 @@
       </c>
     </row>
     <row r="532" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A532" s="7" t="s">
+      <c r="A532" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B532" s="7" t="s">
+      <c r="B532" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="C532" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D532" s="7" t="s">
+      <c r="C532" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D532" s="6" t="s">
         <v>343</v>
       </c>
       <c r="E532" s="1" t="s">
@@ -23506,13 +23521,13 @@
       <c r="H532" s="1">
         <v>807</v>
       </c>
-      <c r="I532" s="7">
+      <c r="I532" s="6">
         <v>1</v>
       </c>
-      <c r="J532" s="12" t="s">
+      <c r="J532" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K532" s="13" t="s">
+      <c r="K532" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L532" s="1" t="s">
@@ -23520,16 +23535,16 @@
       </c>
     </row>
     <row r="533" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A533" s="7" t="s">
+      <c r="A533" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B533" s="7" t="s">
+      <c r="B533" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="C533" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D533" s="7" t="s">
+      <c r="C533" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D533" s="6" t="s">
         <v>345</v>
       </c>
       <c r="E533" s="1" t="s">
@@ -23544,13 +23559,13 @@
       <c r="H533" s="1">
         <v>1998</v>
       </c>
-      <c r="I533" s="7">
+      <c r="I533" s="6">
         <v>2</v>
       </c>
-      <c r="J533" s="12" t="s">
+      <c r="J533" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K533" s="13" t="s">
+      <c r="K533" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L533" s="1" t="s">
@@ -23558,16 +23573,16 @@
       </c>
     </row>
     <row r="534" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A534" s="7" t="s">
+      <c r="A534" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B534" s="7" t="s">
+      <c r="B534" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="C534" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D534" s="7" t="s">
+      <c r="C534" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D534" s="6" t="s">
         <v>359</v>
       </c>
       <c r="E534" s="1" t="s">
@@ -23582,13 +23597,13 @@
       <c r="H534" s="1">
         <v>1731</v>
       </c>
-      <c r="I534" s="7">
+      <c r="I534" s="6">
         <v>1</v>
       </c>
-      <c r="J534" s="12" t="s">
+      <c r="J534" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K534" s="13" t="s">
+      <c r="K534" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L534" s="1" t="s">
@@ -23596,16 +23611,16 @@
       </c>
     </row>
     <row r="535" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A535" s="7" t="s">
+      <c r="A535" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B535" s="7" t="s">
+      <c r="B535" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="C535" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D535" s="7" t="s">
+      <c r="C535" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D535" s="6" t="s">
         <v>361</v>
       </c>
       <c r="E535" s="1" t="s">
@@ -23620,13 +23635,13 @@
       <c r="H535" s="1">
         <v>2683</v>
       </c>
-      <c r="I535" s="7">
+      <c r="I535" s="6">
         <v>2</v>
       </c>
-      <c r="J535" s="12" t="s">
+      <c r="J535" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K535" s="13" t="s">
+      <c r="K535" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L535" s="1" t="s">
@@ -23634,16 +23649,16 @@
       </c>
     </row>
     <row r="536" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A536" s="7" t="s">
+      <c r="A536" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B536" s="7" t="s">
+      <c r="B536" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="C536" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D536" s="7" t="s">
+      <c r="C536" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D536" s="6" t="s">
         <v>362</v>
       </c>
       <c r="E536" s="1" t="s">
@@ -23658,13 +23673,13 @@
       <c r="H536" s="1">
         <v>2707</v>
       </c>
-      <c r="I536" s="7">
+      <c r="I536" s="6">
         <v>1</v>
       </c>
-      <c r="J536" s="12" t="s">
+      <c r="J536" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K536" s="13" t="s">
+      <c r="K536" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L536" s="1" t="s">
@@ -23672,16 +23687,16 @@
       </c>
     </row>
     <row r="537" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A537" s="7" t="s">
+      <c r="A537" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B537" s="7" t="s">
+      <c r="B537" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="C537" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D537" s="7" t="s">
+      <c r="C537" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D537" s="6" t="s">
         <v>369</v>
       </c>
       <c r="E537" s="1" t="s">
@@ -23696,13 +23711,13 @@
       <c r="H537" s="1">
         <v>1384</v>
       </c>
-      <c r="I537" s="7">
+      <c r="I537" s="6">
         <v>1</v>
       </c>
-      <c r="J537" s="12" t="s">
+      <c r="J537" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K537" s="13" t="s">
+      <c r="K537" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L537" s="1" t="s">
@@ -23710,16 +23725,16 @@
       </c>
     </row>
     <row r="538" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A538" s="7" t="s">
+      <c r="A538" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B538" s="7" t="s">
+      <c r="B538" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C538" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D538" s="7" t="s">
+      <c r="C538" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D538" s="6" t="s">
         <v>371</v>
       </c>
       <c r="E538" s="1" t="s">
@@ -23734,13 +23749,13 @@
       <c r="H538" s="1">
         <v>626</v>
       </c>
-      <c r="I538" s="7">
+      <c r="I538" s="6">
         <v>1</v>
       </c>
-      <c r="J538" s="12" t="s">
+      <c r="J538" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K538" s="13" t="s">
+      <c r="K538" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L538" s="1" t="s">
@@ -23748,16 +23763,16 @@
       </c>
     </row>
     <row r="539" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A539" s="7" t="s">
+      <c r="A539" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B539" s="7" t="s">
+      <c r="B539" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C539" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D539" s="7" t="s">
+      <c r="C539" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D539" s="6" t="s">
         <v>372</v>
       </c>
       <c r="E539" s="1" t="s">
@@ -23772,13 +23787,13 @@
       <c r="H539" s="1">
         <v>2526</v>
       </c>
-      <c r="I539" s="7">
+      <c r="I539" s="6">
         <v>2</v>
       </c>
-      <c r="J539" s="12" t="s">
+      <c r="J539" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K539" s="13" t="s">
+      <c r="K539" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L539" s="1" t="s">
@@ -23786,16 +23801,16 @@
       </c>
     </row>
     <row r="540" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A540" s="7" t="s">
+      <c r="A540" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B540" s="7" t="s">
+      <c r="B540" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="C540" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D540" s="7" t="s">
+      <c r="C540" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D540" s="6" t="s">
         <v>373</v>
       </c>
       <c r="E540" s="1" t="s">
@@ -23810,13 +23825,13 @@
       <c r="H540" s="1">
         <v>1023</v>
       </c>
-      <c r="I540" s="7">
+      <c r="I540" s="6">
         <v>1</v>
       </c>
-      <c r="J540" s="12" t="s">
+      <c r="J540" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K540" s="13" t="s">
+      <c r="K540" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L540" s="1" t="s">
@@ -23824,16 +23839,16 @@
       </c>
     </row>
     <row r="541" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A541" s="7" t="s">
+      <c r="A541" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B541" s="7" t="s">
+      <c r="B541" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="C541" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D541" s="7" t="s">
+      <c r="C541" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D541" s="6" t="s">
         <v>375</v>
       </c>
       <c r="E541" s="1" t="s">
@@ -23848,13 +23863,13 @@
       <c r="H541" s="1">
         <v>566</v>
       </c>
-      <c r="I541" s="7">
+      <c r="I541" s="6">
         <v>2</v>
       </c>
-      <c r="J541" s="12" t="s">
+      <c r="J541" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K541" s="13" t="s">
+      <c r="K541" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L541" s="1" t="s">
@@ -23862,16 +23877,16 @@
       </c>
     </row>
     <row r="542" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A542" s="7" t="s">
+      <c r="A542" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B542" s="7" t="s">
+      <c r="B542" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="C542" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D542" s="7" t="s">
+      <c r="C542" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D542" s="6" t="s">
         <v>376</v>
       </c>
       <c r="E542" s="1" t="s">
@@ -23886,13 +23901,13 @@
       <c r="H542" s="1">
         <v>3946</v>
       </c>
-      <c r="I542" s="7">
+      <c r="I542" s="6">
         <v>1</v>
       </c>
-      <c r="J542" s="12" t="s">
+      <c r="J542" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K542" s="13" t="s">
+      <c r="K542" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L542" s="1" t="s">
@@ -23900,16 +23915,16 @@
       </c>
     </row>
     <row r="543" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A543" s="7" t="s">
+      <c r="A543" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B543" s="7" t="s">
+      <c r="B543" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="C543" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D543" s="7" t="s">
+      <c r="C543" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D543" s="6" t="s">
         <v>379</v>
       </c>
       <c r="E543" s="1" t="s">
@@ -23924,13 +23939,13 @@
       <c r="H543" s="1">
         <v>1925</v>
       </c>
-      <c r="I543" s="7">
+      <c r="I543" s="6">
         <v>1</v>
       </c>
-      <c r="J543" s="12" t="s">
+      <c r="J543" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K543" s="13" t="s">
+      <c r="K543" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L543" s="1" t="s">
@@ -23938,16 +23953,16 @@
       </c>
     </row>
     <row r="544" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A544" s="7" t="s">
+      <c r="A544" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B544" s="7" t="s">
+      <c r="B544" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C544" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D544" s="7" t="s">
+      <c r="C544" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D544" s="6" t="s">
         <v>380</v>
       </c>
       <c r="E544" s="1" t="s">
@@ -23962,13 +23977,13 @@
       <c r="H544" s="1">
         <v>1865</v>
       </c>
-      <c r="I544" s="7">
+      <c r="I544" s="6">
         <v>1</v>
       </c>
-      <c r="J544" s="12" t="s">
+      <c r="J544" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K544" s="13" t="s">
+      <c r="K544" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L544" s="1" t="s">
@@ -23976,16 +23991,16 @@
       </c>
     </row>
     <row r="545" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A545" s="7" t="s">
+      <c r="A545" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B545" s="7" t="s">
+      <c r="B545" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="C545" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D545" s="7" t="s">
+      <c r="C545" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D545" s="6" t="s">
         <v>382</v>
       </c>
       <c r="E545" s="1" t="s">
@@ -24000,13 +24015,13 @@
       <c r="H545" s="1">
         <v>2006</v>
       </c>
-      <c r="I545" s="7">
+      <c r="I545" s="6">
         <v>1</v>
       </c>
-      <c r="J545" s="12" t="s">
+      <c r="J545" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K545" s="13" t="s">
+      <c r="K545" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L545" s="1" t="s">
@@ -24014,16 +24029,16 @@
       </c>
     </row>
     <row r="546" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A546" s="7" t="s">
+      <c r="A546" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B546" s="7" t="s">
+      <c r="B546" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="C546" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D546" s="7" t="s">
+      <c r="C546" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D546" s="6" t="s">
         <v>383</v>
       </c>
       <c r="E546" s="1" t="s">
@@ -24038,13 +24053,13 @@
       <c r="H546" s="1">
         <v>803</v>
       </c>
-      <c r="I546" s="7">
+      <c r="I546" s="6">
         <v>1</v>
       </c>
-      <c r="J546" s="12" t="s">
+      <c r="J546" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K546" s="13" t="s">
+      <c r="K546" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L546" s="1" t="s">
@@ -24052,16 +24067,16 @@
       </c>
     </row>
     <row r="547" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A547" s="7" t="s">
+      <c r="A547" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B547" s="7" t="s">
+      <c r="B547" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C547" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D547" s="7" t="s">
+      <c r="C547" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D547" s="6" t="s">
         <v>384</v>
       </c>
       <c r="E547" s="1" t="s">
@@ -24076,13 +24091,13 @@
       <c r="H547" s="1">
         <v>2139</v>
       </c>
-      <c r="I547" s="7">
+      <c r="I547" s="6">
         <v>1</v>
       </c>
-      <c r="J547" s="12" t="s">
+      <c r="J547" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K547" s="13" t="s">
+      <c r="K547" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L547" s="1" t="s">
@@ -24090,16 +24105,16 @@
       </c>
     </row>
     <row r="548" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A548" s="7" t="s">
+      <c r="A548" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B548" s="7" t="s">
+      <c r="B548" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="C548" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D548" s="7" t="s">
+      <c r="C548" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D548" s="6" t="s">
         <v>385</v>
       </c>
       <c r="E548" s="1" t="s">
@@ -24114,13 +24129,13 @@
       <c r="H548" s="1">
         <v>1805</v>
       </c>
-      <c r="I548" s="7">
+      <c r="I548" s="6">
         <v>1</v>
       </c>
-      <c r="J548" s="12" t="s">
+      <c r="J548" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K548" s="13" t="s">
+      <c r="K548" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L548" s="1" t="s">
@@ -24128,16 +24143,16 @@
       </c>
     </row>
     <row r="549" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A549" s="7" t="s">
+      <c r="A549" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B549" s="7" t="s">
+      <c r="B549" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="C549" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D549" s="7" t="s">
+      <c r="C549" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D549" s="6" t="s">
         <v>387</v>
       </c>
       <c r="E549" s="1" t="s">
@@ -24152,13 +24167,13 @@
       <c r="H549" s="1">
         <v>2587</v>
       </c>
-      <c r="I549" s="7">
+      <c r="I549" s="6">
         <v>1</v>
       </c>
-      <c r="J549" s="12" t="s">
+      <c r="J549" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K549" s="13" t="s">
+      <c r="K549" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L549" s="1" t="s">
@@ -24166,16 +24181,16 @@
       </c>
     </row>
     <row r="550" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A550" s="7" t="s">
+      <c r="A550" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B550" s="7" t="s">
+      <c r="B550" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C550" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D550" s="7" t="s">
+      <c r="C550" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D550" s="6" t="s">
         <v>388</v>
       </c>
       <c r="E550" s="1" t="s">
@@ -24190,13 +24205,13 @@
       <c r="H550" s="1">
         <v>4107</v>
       </c>
-      <c r="I550" s="7">
+      <c r="I550" s="6">
         <v>2</v>
       </c>
-      <c r="J550" s="12" t="s">
+      <c r="J550" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K550" s="13" t="s">
+      <c r="K550" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L550" s="1" t="s">
@@ -24204,16 +24219,16 @@
       </c>
     </row>
     <row r="551" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A551" s="7" t="s">
+      <c r="A551" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B551" s="7" t="s">
+      <c r="B551" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="C551" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D551" s="7" t="s">
+      <c r="C551" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D551" s="6" t="s">
         <v>389</v>
       </c>
       <c r="E551" s="1" t="s">
@@ -24228,13 +24243,13 @@
       <c r="H551" s="1">
         <v>2268</v>
       </c>
-      <c r="I551" s="7">
+      <c r="I551" s="6">
         <v>1</v>
       </c>
-      <c r="J551" s="12" t="s">
+      <c r="J551" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K551" s="13" t="s">
+      <c r="K551" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L551" s="1" t="s">
@@ -24242,16 +24257,16 @@
       </c>
     </row>
     <row r="552" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A552" s="7" t="s">
+      <c r="A552" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B552" s="7" t="s">
+      <c r="B552" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="C552" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D552" s="7" t="s">
+      <c r="C552" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D552" s="6" t="s">
         <v>393</v>
       </c>
       <c r="E552" s="1" t="s">
@@ -24266,13 +24281,13 @@
       <c r="H552" s="1">
         <v>685</v>
       </c>
-      <c r="I552" s="7">
+      <c r="I552" s="6">
         <v>2</v>
       </c>
-      <c r="J552" s="12" t="s">
+      <c r="J552" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K552" s="13" t="s">
+      <c r="K552" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L552" s="1" t="s">
@@ -24280,16 +24295,16 @@
       </c>
     </row>
     <row r="553" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A553" s="7" t="s">
+      <c r="A553" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B553" s="7" t="s">
+      <c r="B553" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="C553" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D553" s="7" t="s">
+      <c r="C553" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D553" s="6" t="s">
         <v>394</v>
       </c>
       <c r="E553" s="1" t="s">
@@ -24304,13 +24319,13 @@
       <c r="H553" s="1">
         <v>1562</v>
       </c>
-      <c r="I553" s="7">
+      <c r="I553" s="6">
         <v>2</v>
       </c>
-      <c r="J553" s="12" t="s">
+      <c r="J553" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K553" s="13" t="s">
+      <c r="K553" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L553" s="1" t="s">
@@ -24318,16 +24333,16 @@
       </c>
     </row>
     <row r="554" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A554" s="7" t="s">
+      <c r="A554" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B554" s="7" t="s">
+      <c r="B554" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="C554" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D554" s="7" t="s">
+      <c r="C554" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D554" s="6" t="s">
         <v>395</v>
       </c>
       <c r="E554" s="1" t="s">
@@ -24342,13 +24357,13 @@
       <c r="H554" s="1">
         <v>1109</v>
       </c>
-      <c r="I554" s="7">
+      <c r="I554" s="6">
         <v>2</v>
       </c>
-      <c r="J554" s="12" t="s">
+      <c r="J554" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K554" s="13" t="s">
+      <c r="K554" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L554" s="1" t="s">
@@ -24356,16 +24371,16 @@
       </c>
     </row>
     <row r="555" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A555" s="7" t="s">
+      <c r="A555" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B555" s="7" t="s">
+      <c r="B555" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="C555" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D555" s="7" t="s">
+      <c r="C555" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D555" s="6" t="s">
         <v>396</v>
       </c>
       <c r="E555" s="1" t="s">
@@ -24380,13 +24395,13 @@
       <c r="H555" s="1">
         <v>1070</v>
       </c>
-      <c r="I555" s="7">
+      <c r="I555" s="6">
         <v>1</v>
       </c>
-      <c r="J555" s="12" t="s">
+      <c r="J555" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K555" s="13" t="s">
+      <c r="K555" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L555" s="1" t="s">
@@ -24394,16 +24409,16 @@
       </c>
     </row>
     <row r="556" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A556" s="7" t="s">
+      <c r="A556" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B556" s="7" t="s">
+      <c r="B556" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="C556" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D556" s="7" t="s">
+      <c r="C556" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D556" s="6" t="s">
         <v>397</v>
       </c>
       <c r="E556" s="1" t="s">
@@ -24418,13 +24433,13 @@
       <c r="H556" s="1">
         <v>1760</v>
       </c>
-      <c r="I556" s="7">
+      <c r="I556" s="6">
         <v>2</v>
       </c>
-      <c r="J556" s="12" t="s">
+      <c r="J556" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K556" s="13" t="s">
+      <c r="K556" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L556" s="1" t="s">
@@ -24432,16 +24447,16 @@
       </c>
     </row>
     <row r="557" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A557" s="7" t="s">
+      <c r="A557" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B557" s="7" t="s">
+      <c r="B557" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="C557" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D557" s="7" t="s">
+      <c r="C557" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D557" s="6" t="s">
         <v>413</v>
       </c>
       <c r="E557" s="1" t="s">
@@ -24456,13 +24471,13 @@
       <c r="H557" s="1">
         <v>441</v>
       </c>
-      <c r="I557" s="7">
+      <c r="I557" s="6">
         <v>2</v>
       </c>
-      <c r="J557" s="12" t="s">
+      <c r="J557" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K557" s="13" t="s">
+      <c r="K557" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L557" s="1" t="s">
@@ -24470,16 +24485,16 @@
       </c>
     </row>
     <row r="558" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A558" s="7" t="s">
+      <c r="A558" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B558" s="7" t="s">
+      <c r="B558" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C558" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D558" s="7" t="s">
+      <c r="C558" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D558" s="6" t="s">
         <v>414</v>
       </c>
       <c r="E558" s="1" t="s">
@@ -24494,13 +24509,13 @@
       <c r="H558" s="1">
         <v>567</v>
       </c>
-      <c r="I558" s="7">
+      <c r="I558" s="6">
         <v>2</v>
       </c>
-      <c r="J558" s="12" t="s">
+      <c r="J558" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K558" s="13" t="s">
+      <c r="K558" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L558" s="1" t="s">
@@ -24508,16 +24523,16 @@
       </c>
     </row>
     <row r="559" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A559" s="7" t="s">
+      <c r="A559" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B559" s="7" t="s">
+      <c r="B559" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C559" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D559" s="7" t="s">
+      <c r="C559" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D559" s="6" t="s">
         <v>415</v>
       </c>
       <c r="E559" s="1" t="s">
@@ -24532,13 +24547,13 @@
       <c r="H559" s="1">
         <v>1008</v>
       </c>
-      <c r="I559" s="7">
+      <c r="I559" s="6">
         <v>1</v>
       </c>
-      <c r="J559" s="12" t="s">
+      <c r="J559" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K559" s="13" t="s">
+      <c r="K559" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L559" s="1" t="s">
@@ -24546,16 +24561,16 @@
       </c>
     </row>
     <row r="560" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A560" s="7" t="s">
+      <c r="A560" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B560" s="7" t="s">
+      <c r="B560" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="C560" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D560" s="7" t="s">
+      <c r="C560" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D560" s="6" t="s">
         <v>416</v>
       </c>
       <c r="E560" s="1" t="s">
@@ -24570,13 +24585,13 @@
       <c r="H560" s="1">
         <v>1008</v>
       </c>
-      <c r="I560" s="7">
+      <c r="I560" s="6">
         <v>1</v>
       </c>
-      <c r="J560" s="12" t="s">
+      <c r="J560" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="K560" s="13" t="s">
+      <c r="K560" s="12" t="s">
         <v>617</v>
       </c>
       <c r="L560" s="1" t="s">
@@ -26077,52 +26092,52 @@
     <cfRule type="duplicateValues" dxfId="60" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A553">
-    <cfRule type="duplicateValues" dxfId="59" priority="1603"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="1602"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="1602"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="1603"/>
     <cfRule type="duplicateValues" dxfId="57" priority="1604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A554:A560">
-    <cfRule type="duplicateValues" dxfId="56" priority="1606"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="1605"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1605"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1606"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="54" priority="1597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D355">
-    <cfRule type="duplicateValues" dxfId="53" priority="255" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="256" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="254" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="254" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="255" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="256" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D364">
-    <cfRule type="duplicateValues" dxfId="48" priority="260" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="257"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="259" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="259" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="260" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="44" priority="261" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D365:D395 D356:D363 D341:D354">
-    <cfRule type="duplicateValues" dxfId="43" priority="274" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="274" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D365:D395">
-    <cfRule type="duplicateValues" dxfId="41" priority="276" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="276" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D371:D390">
     <cfRule type="duplicateValues" dxfId="39" priority="272" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D440">
-    <cfRule type="duplicateValues" dxfId="38" priority="246" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="244" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="245" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="244" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="245" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="246" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D442 D423:D439 D396:D398">
-    <cfRule type="duplicateValues" dxfId="33" priority="308" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="308" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D442">
     <cfRule type="duplicateValues" dxfId="31" priority="309"/>
@@ -26130,8 +26145,8 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="D445:D454">
     <cfRule type="duplicateValues" dxfId="29" priority="1668"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="1670"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="1669"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1669"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1670"/>
     <cfRule type="duplicateValues" dxfId="26" priority="1671"/>
     <cfRule type="duplicateValues" dxfId="25" priority="1672"/>
     <cfRule type="duplicateValues" dxfId="24" priority="1673"/>
@@ -26139,32 +26154,32 @@
     <cfRule type="duplicateValues" dxfId="22" priority="1675" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D456:D463 D465:D466">
-    <cfRule type="duplicateValues" dxfId="21" priority="1447"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="1443"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="1444"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="1445"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1449" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="1446"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="1448"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1443"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1444"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1445"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1446"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1447"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1448"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1449" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="14" priority="1450" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D475:D479">
-    <cfRule type="duplicateValues" dxfId="13" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="127" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="126" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="126" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="127" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
     <cfRule type="duplicateValues" dxfId="5" priority="1595"/>
     <cfRule type="duplicateValues" dxfId="4" priority="1596" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="3" priority="1226" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1225"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1225"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1226" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
     <cfRule type="duplicateValues" dxfId="1" priority="1223"/>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810A5F8E-1495-465D-B307-29E1894A8818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B2CB57-4BDE-46D9-BBA3-8CCEDEC0A69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -2433,6 +2433,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -2497,6 +2517,18 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2519,38 +2551,6 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3363,6 +3363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L617"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3419,7 +3420,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -3457,7 +3458,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -3495,7 +3496,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -3533,7 +3534,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -3571,7 +3572,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -3609,7 +3610,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -3647,7 +3648,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -3685,7 +3686,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -3723,7 +3724,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -3761,7 +3762,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -3799,7 +3800,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3837,7 +3838,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -3875,7 +3876,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -3913,7 +3914,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -3951,7 +3952,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -3989,7 +3990,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -4027,7 +4028,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -4065,7 +4066,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -4103,7 +4104,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -4141,7 +4142,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -4179,7 +4180,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -4217,7 +4218,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -4255,7 +4256,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -4293,7 +4294,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -4331,7 +4332,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -4369,7 +4370,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -4407,7 +4408,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -4445,7 +4446,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -4483,7 +4484,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -4521,7 +4522,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>41</v>
       </c>
@@ -4559,7 +4560,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>42</v>
       </c>
@@ -4597,7 +4598,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>43</v>
       </c>
@@ -4635,7 +4636,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>44</v>
       </c>
@@ -4673,7 +4674,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>45</v>
       </c>
@@ -4711,7 +4712,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>46</v>
       </c>
@@ -4749,7 +4750,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>47</v>
       </c>
@@ -4787,7 +4788,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>48</v>
       </c>
@@ -4825,7 +4826,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>49</v>
       </c>
@@ -4863,7 +4864,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -4901,7 +4902,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -4939,7 +4940,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>52</v>
       </c>
@@ -4977,7 +4978,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>53</v>
       </c>
@@ -5015,7 +5016,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>54</v>
       </c>
@@ -5053,7 +5054,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>55</v>
       </c>
@@ -5091,7 +5092,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>56</v>
       </c>
@@ -5129,7 +5130,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>57</v>
       </c>
@@ -5167,7 +5168,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>58</v>
       </c>
@@ -5243,7 +5244,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>60</v>
       </c>
@@ -5281,7 +5282,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -5319,7 +5320,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>62</v>
       </c>
@@ -5357,7 +5358,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>63</v>
       </c>
@@ -5395,7 +5396,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>64</v>
       </c>
@@ -5433,7 +5434,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>65</v>
       </c>
@@ -5471,7 +5472,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>66</v>
       </c>
@@ -5509,7 +5510,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>67</v>
       </c>
@@ -5547,7 +5548,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>68</v>
       </c>
@@ -5585,7 +5586,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -5623,7 +5624,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>70</v>
       </c>
@@ -5661,7 +5662,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>71</v>
       </c>
@@ -5699,7 +5700,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>72</v>
       </c>
@@ -5737,7 +5738,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>73</v>
       </c>
@@ -5775,7 +5776,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>74</v>
       </c>
@@ -5813,7 +5814,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -5851,7 +5852,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>76</v>
       </c>
@@ -5889,7 +5890,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>77</v>
       </c>
@@ -5927,7 +5928,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>78</v>
       </c>
@@ -5965,7 +5966,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>79</v>
       </c>
@@ -6003,7 +6004,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>80</v>
       </c>
@@ -6041,7 +6042,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -6079,7 +6080,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>82</v>
       </c>
@@ -6117,7 +6118,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -6155,7 +6156,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>84</v>
       </c>
@@ -6193,7 +6194,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>85</v>
       </c>
@@ -6231,7 +6232,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>86</v>
       </c>
@@ -6269,7 +6270,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>87</v>
       </c>
@@ -6307,7 +6308,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>88</v>
       </c>
@@ -6345,7 +6346,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>89</v>
       </c>
@@ -6383,7 +6384,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>90</v>
       </c>
@@ -6421,7 +6422,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -6459,7 +6460,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -6497,7 +6498,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>93</v>
       </c>
@@ -6535,7 +6536,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>94</v>
       </c>
@@ -6573,7 +6574,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>95</v>
       </c>
@@ -6611,7 +6612,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>96</v>
       </c>
@@ -6649,7 +6650,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>97</v>
       </c>
@@ -6687,7 +6688,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>98</v>
       </c>
@@ -6725,7 +6726,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>99</v>
       </c>
@@ -6763,7 +6764,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>100</v>
       </c>
@@ -6801,7 +6802,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>101</v>
       </c>
@@ -6839,7 +6840,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>102</v>
       </c>
@@ -6877,7 +6878,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>103</v>
       </c>
@@ -6915,7 +6916,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>104</v>
       </c>
@@ -6953,7 +6954,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>105</v>
       </c>
@@ -6991,7 +6992,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>106</v>
       </c>
@@ -7029,7 +7030,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>107</v>
       </c>
@@ -7067,7 +7068,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>108</v>
       </c>
@@ -7105,7 +7106,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>109</v>
       </c>
@@ -7143,7 +7144,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>110</v>
       </c>
@@ -7181,7 +7182,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>111</v>
       </c>
@@ -7219,7 +7220,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>112</v>
       </c>
@@ -7257,7 +7258,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>113</v>
       </c>
@@ -7295,7 +7296,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>114</v>
       </c>
@@ -7333,7 +7334,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>115</v>
       </c>
@@ -7371,7 +7372,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>116</v>
       </c>
@@ -7409,7 +7410,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>117</v>
       </c>
@@ -7447,7 +7448,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>118</v>
       </c>
@@ -7485,7 +7486,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>119</v>
       </c>
@@ -7523,7 +7524,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>120</v>
       </c>
@@ -7561,7 +7562,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>121</v>
       </c>
@@ -7599,7 +7600,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>122</v>
       </c>
@@ -7637,7 +7638,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>123</v>
       </c>
@@ -7675,7 +7676,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>124</v>
       </c>
@@ -7713,7 +7714,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>125</v>
       </c>
@@ -7751,7 +7752,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>126</v>
       </c>
@@ -7789,7 +7790,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>127</v>
       </c>
@@ -7827,7 +7828,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>128</v>
       </c>
@@ -7865,7 +7866,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>129</v>
       </c>
@@ -7903,7 +7904,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>130</v>
       </c>
@@ -7941,7 +7942,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>131</v>
       </c>
@@ -7979,7 +7980,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>132</v>
       </c>
@@ -8017,7 +8018,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>133</v>
       </c>
@@ -8055,7 +8056,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>134</v>
       </c>
@@ -8093,7 +8094,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>135</v>
       </c>
@@ -8131,7 +8132,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>136</v>
       </c>
@@ -8169,7 +8170,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>137</v>
       </c>
@@ -8207,7 +8208,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>138</v>
       </c>
@@ -8245,7 +8246,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -8283,7 +8284,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>140</v>
       </c>
@@ -8321,7 +8322,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>141</v>
       </c>
@@ -8359,7 +8360,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>142</v>
       </c>
@@ -8397,7 +8398,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>143</v>
       </c>
@@ -8435,7 +8436,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>144</v>
       </c>
@@ -8473,7 +8474,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>145</v>
       </c>
@@ -8511,7 +8512,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>146</v>
       </c>
@@ -8549,7 +8550,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>147</v>
       </c>
@@ -8587,7 +8588,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>148</v>
       </c>
@@ -8625,7 +8626,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>149</v>
       </c>
@@ -8663,7 +8664,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>127</v>
       </c>
@@ -8701,7 +8702,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>128</v>
       </c>
@@ -8739,7 +8740,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>40</v>
       </c>
@@ -8777,7 +8778,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>150</v>
       </c>
@@ -8853,7 +8854,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>152</v>
       </c>
@@ -8891,7 +8892,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>40</v>
       </c>
@@ -8929,7 +8930,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>66</v>
       </c>
@@ -8967,7 +8968,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -9005,7 +9006,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>21</v>
       </c>
@@ -9043,7 +9044,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>22</v>
       </c>
@@ -9081,7 +9082,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>40</v>
       </c>
@@ -9119,7 +9120,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>54</v>
       </c>
@@ -9157,7 +9158,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>58</v>
       </c>
@@ -9195,7 +9196,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>60</v>
       </c>
@@ -9233,7 +9234,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>66</v>
       </c>
@@ -9271,7 +9272,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>69</v>
       </c>
@@ -9309,7 +9310,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>72</v>
       </c>
@@ -9347,7 +9348,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>12</v>
       </c>
@@ -9385,7 +9386,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>14</v>
       </c>
@@ -9423,7 +9424,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>16</v>
       </c>
@@ -9461,7 +9462,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>17</v>
       </c>
@@ -9499,7 +9500,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -9537,7 +9538,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>21</v>
       </c>
@@ -9575,7 +9576,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>22</v>
       </c>
@@ -9613,7 +9614,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>27</v>
       </c>
@@ -9651,7 +9652,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>30</v>
       </c>
@@ -9689,7 +9690,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>31</v>
       </c>
@@ -9727,7 +9728,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>34</v>
       </c>
@@ -9765,7 +9766,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>36</v>
       </c>
@@ -9803,7 +9804,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>38</v>
       </c>
@@ -9841,7 +9842,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>40</v>
       </c>
@@ -9879,7 +9880,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>41</v>
       </c>
@@ -9917,7 +9918,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>153</v>
       </c>
@@ -9955,7 +9956,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>44</v>
       </c>
@@ -9993,7 +9994,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>45</v>
       </c>
@@ -10031,7 +10032,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>46</v>
       </c>
@@ -10069,7 +10070,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>47</v>
       </c>
@@ -10107,7 +10108,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>52</v>
       </c>
@@ -10145,7 +10146,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>54</v>
       </c>
@@ -10183,7 +10184,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>55</v>
       </c>
@@ -10221,7 +10222,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>56</v>
       </c>
@@ -10259,7 +10260,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>58</v>
       </c>
@@ -10297,7 +10298,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>60</v>
       </c>
@@ -10335,7 +10336,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>61</v>
       </c>
@@ -10373,7 +10374,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>64</v>
       </c>
@@ -10411,7 +10412,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>65</v>
       </c>
@@ -10449,7 +10450,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>66</v>
       </c>
@@ -10487,7 +10488,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>67</v>
       </c>
@@ -10525,7 +10526,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>68</v>
       </c>
@@ -10563,7 +10564,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>69</v>
       </c>
@@ -10601,7 +10602,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>70</v>
       </c>
@@ -10639,7 +10640,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>72</v>
       </c>
@@ -10677,7 +10678,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>73</v>
       </c>
@@ -10715,7 +10716,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>74</v>
       </c>
@@ -10753,7 +10754,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>75</v>
       </c>
@@ -10791,7 +10792,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>76</v>
       </c>
@@ -10829,7 +10830,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>77</v>
       </c>
@@ -10867,7 +10868,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>78</v>
       </c>
@@ -10905,7 +10906,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>79</v>
       </c>
@@ -10943,7 +10944,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>80</v>
       </c>
@@ -10981,7 +10982,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>81</v>
       </c>
@@ -11019,7 +11020,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>87</v>
       </c>
@@ -11057,7 +11058,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>89</v>
       </c>
@@ -11095,7 +11096,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>92</v>
       </c>
@@ -11133,7 +11134,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>93</v>
       </c>
@@ -11171,7 +11172,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>94</v>
       </c>
@@ -11209,7 +11210,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>40</v>
       </c>
@@ -11247,7 +11248,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>83</v>
       </c>
@@ -11285,7 +11286,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>119</v>
       </c>
@@ -11323,7 +11324,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>12</v>
       </c>
@@ -11361,7 +11362,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>77</v>
       </c>
@@ -11399,7 +11400,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>112</v>
       </c>
@@ -11437,7 +11438,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>16</v>
       </c>
@@ -11475,7 +11476,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>87</v>
       </c>
@@ -11513,7 +11514,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>113</v>
       </c>
@@ -11551,7 +11552,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -11589,7 +11590,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>75</v>
       </c>
@@ -11627,7 +11628,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>17</v>
       </c>
@@ -11665,7 +11666,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>80</v>
       </c>
@@ -11703,7 +11704,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>42</v>
       </c>
@@ -11741,7 +11742,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>49</v>
       </c>
@@ -11779,7 +11780,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>117</v>
       </c>
@@ -11817,7 +11818,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>28</v>
       </c>
@@ -11855,7 +11856,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>81</v>
       </c>
@@ -11893,7 +11894,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>58</v>
       </c>
@@ -11931,7 +11932,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>23</v>
       </c>
@@ -11969,7 +11970,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>73</v>
       </c>
@@ -12007,7 +12008,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>78</v>
       </c>
@@ -12045,7 +12046,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>79</v>
       </c>
@@ -12121,7 +12122,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>19</v>
       </c>
@@ -12159,7 +12160,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>38</v>
       </c>
@@ -12197,7 +12198,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>25</v>
       </c>
@@ -12235,7 +12236,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>93</v>
       </c>
@@ -12273,7 +12274,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>74</v>
       </c>
@@ -12311,7 +12312,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>30</v>
       </c>
@@ -12349,7 +12350,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>84</v>
       </c>
@@ -12387,7 +12388,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>120</v>
       </c>
@@ -12425,7 +12426,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>455</v>
       </c>
@@ -12463,7 +12464,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>62</v>
       </c>
@@ -12501,7 +12502,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>94</v>
       </c>
@@ -12539,7 +12540,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>116</v>
       </c>
@@ -12577,7 +12578,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>135</v>
       </c>
@@ -12615,7 +12616,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>57</v>
       </c>
@@ -12653,7 +12654,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>88</v>
       </c>
@@ -12691,7 +12692,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>142</v>
       </c>
@@ -12729,7 +12730,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>86</v>
       </c>
@@ -12767,7 +12768,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>153</v>
       </c>
@@ -12805,7 +12806,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>61</v>
       </c>
@@ -12843,7 +12844,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>122</v>
       </c>
@@ -12881,7 +12882,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>143</v>
       </c>
@@ -12919,7 +12920,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>100</v>
       </c>
@@ -12957,7 +12958,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>27</v>
       </c>
@@ -12995,7 +12996,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>98</v>
       </c>
@@ -13033,7 +13034,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>21</v>
       </c>
@@ -13071,7 +13072,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>138</v>
       </c>
@@ -13109,7 +13110,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>149</v>
       </c>
@@ -13147,7 +13148,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>76</v>
       </c>
@@ -13185,7 +13186,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>68</v>
       </c>
@@ -13223,7 +13224,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="260" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>82</v>
       </c>
@@ -13261,7 +13262,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="261" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>56</v>
       </c>
@@ -13299,7 +13300,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>69</v>
       </c>
@@ -13337,7 +13338,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>14</v>
       </c>
@@ -13375,7 +13376,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>13</v>
       </c>
@@ -13413,7 +13414,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>141</v>
       </c>
@@ -13451,7 +13452,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>123</v>
       </c>
@@ -13489,7 +13490,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="267" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>108</v>
       </c>
@@ -13527,7 +13528,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>109</v>
       </c>
@@ -13565,7 +13566,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>145</v>
       </c>
@@ -13603,7 +13604,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>97</v>
       </c>
@@ -13641,7 +13642,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="271" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>20</v>
       </c>
@@ -13679,7 +13680,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="272" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>54</v>
       </c>
@@ -13717,7 +13718,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>35</v>
       </c>
@@ -13755,7 +13756,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="274" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>39</v>
       </c>
@@ -13793,7 +13794,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>26</v>
       </c>
@@ -13831,7 +13832,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="276" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>132</v>
       </c>
@@ -13869,7 +13870,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="277" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>456</v>
       </c>
@@ -13907,7 +13908,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="278" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>136</v>
       </c>
@@ -13945,7 +13946,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="279" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>51</v>
       </c>
@@ -13983,7 +13984,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>107</v>
       </c>
@@ -14021,7 +14022,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>105</v>
       </c>
@@ -14059,7 +14060,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="282" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>72</v>
       </c>
@@ -14097,7 +14098,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>36</v>
       </c>
@@ -14135,7 +14136,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="284" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>55</v>
       </c>
@@ -14173,7 +14174,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>137</v>
       </c>
@@ -14211,7 +14212,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>133</v>
       </c>
@@ -14249,7 +14250,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="287" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>60</v>
       </c>
@@ -14287,7 +14288,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>99</v>
       </c>
@@ -14325,7 +14326,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>53</v>
       </c>
@@ -14363,7 +14364,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>67</v>
       </c>
@@ -14401,7 +14402,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="291" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>91</v>
       </c>
@@ -14439,7 +14440,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="292" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>106</v>
       </c>
@@ -14477,7 +14478,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="293" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>150</v>
       </c>
@@ -14515,7 +14516,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="294" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>115</v>
       </c>
@@ -14553,7 +14554,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="295" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>128</v>
       </c>
@@ -14591,7 +14592,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="296" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>121</v>
       </c>
@@ -14629,7 +14630,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>103</v>
       </c>
@@ -14667,7 +14668,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>31</v>
       </c>
@@ -14705,7 +14706,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>102</v>
       </c>
@@ -14743,7 +14744,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="300" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>85</v>
       </c>
@@ -14781,7 +14782,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="301" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>22</v>
       </c>
@@ -14819,7 +14820,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="302" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>96</v>
       </c>
@@ -14857,7 +14858,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="303" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>50</v>
       </c>
@@ -14895,7 +14896,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="304" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>111</v>
       </c>
@@ -14933,7 +14934,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="305" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>71</v>
       </c>
@@ -14971,7 +14972,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="306" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>457</v>
       </c>
@@ -15009,7 +15010,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="307" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>130</v>
       </c>
@@ -15047,7 +15048,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="308" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>125</v>
       </c>
@@ -15085,7 +15086,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="309" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>89</v>
       </c>
@@ -15161,7 +15162,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="311" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>134</v>
       </c>
@@ -15199,7 +15200,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="312" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>32</v>
       </c>
@@ -15237,7 +15238,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>52</v>
       </c>
@@ -15275,7 +15276,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>92</v>
       </c>
@@ -15313,7 +15314,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="315" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>131</v>
       </c>
@@ -15351,7 +15352,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="316" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>66</v>
       </c>
@@ -15389,7 +15390,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="317" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>129</v>
       </c>
@@ -15427,7 +15428,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="318" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>43</v>
       </c>
@@ -15465,7 +15466,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="319" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>15</v>
       </c>
@@ -15503,7 +15504,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="320" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>127</v>
       </c>
@@ -15541,7 +15542,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>48</v>
       </c>
@@ -15579,7 +15580,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="322" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>101</v>
       </c>
@@ -15617,7 +15618,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="323" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>29</v>
       </c>
@@ -15655,7 +15656,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="324" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>34</v>
       </c>
@@ -15693,7 +15694,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="325" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>90</v>
       </c>
@@ -15731,7 +15732,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="326" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>70</v>
       </c>
@@ -15769,7 +15770,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="327" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>110</v>
       </c>
@@ -15807,7 +15808,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="328" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>45</v>
       </c>
@@ -15845,7 +15846,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="329" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>104</v>
       </c>
@@ -15883,7 +15884,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="330" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>64</v>
       </c>
@@ -15921,7 +15922,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="331" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>114</v>
       </c>
@@ -15959,7 +15960,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="332" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>95</v>
       </c>
@@ -15997,7 +15998,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>65</v>
       </c>
@@ -16035,7 +16036,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>140</v>
       </c>
@@ -16073,7 +16074,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>126</v>
       </c>
@@ -16111,7 +16112,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
         <v>30</v>
       </c>
@@ -16149,7 +16150,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="337" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
         <v>61</v>
       </c>
@@ -16187,7 +16188,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="338" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
         <v>75</v>
       </c>
@@ -16225,7 +16226,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="339" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
         <v>12</v>
       </c>
@@ -16263,7 +16264,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="340" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
         <v>21</v>
       </c>
@@ -16301,7 +16302,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="341" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
         <v>78</v>
       </c>
@@ -16339,7 +16340,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="342" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="3" t="s">
         <v>77</v>
       </c>
@@ -16377,7 +16378,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="343" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
         <v>69</v>
       </c>
@@ -16415,7 +16416,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="344" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="3" t="s">
         <v>81</v>
       </c>
@@ -16453,7 +16454,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="345" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
         <v>68</v>
       </c>
@@ -16491,7 +16492,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="346" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3" t="s">
         <v>79</v>
       </c>
@@ -16529,7 +16530,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="347" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
         <v>64</v>
       </c>
@@ -16567,7 +16568,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="348" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
         <v>40</v>
       </c>
@@ -16605,7 +16606,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="349" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
         <v>31</v>
       </c>
@@ -16643,7 +16644,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="350" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3" t="s">
         <v>14</v>
       </c>
@@ -16681,7 +16682,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="351" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
         <v>17</v>
       </c>
@@ -16719,7 +16720,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="352" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="3" t="s">
         <v>80</v>
       </c>
@@ -16757,7 +16758,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="353" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
         <v>22</v>
       </c>
@@ -16795,7 +16796,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="354" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
         <v>58</v>
       </c>
@@ -16833,7 +16834,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="355" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
         <v>83</v>
       </c>
@@ -16871,7 +16872,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="356" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
         <v>42</v>
       </c>
@@ -16900,7 +16901,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="357" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
         <v>50</v>
       </c>
@@ -16938,7 +16939,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="358" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="3" t="s">
         <v>54</v>
       </c>
@@ -16976,7 +16977,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="359" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
         <v>76</v>
       </c>
@@ -17014,7 +17015,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="360" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="3" t="s">
         <v>27</v>
       </c>
@@ -17052,7 +17053,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="361" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
         <v>15</v>
       </c>
@@ -17090,7 +17091,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="362" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
         <v>20</v>
       </c>
@@ -17128,7 +17129,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="363" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
         <v>67</v>
       </c>
@@ -17166,7 +17167,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="364" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
         <v>49</v>
       </c>
@@ -17204,7 +17205,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="365" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
         <v>60</v>
       </c>
@@ -17242,7 +17243,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="366" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
         <v>46</v>
       </c>
@@ -17280,7 +17281,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="367" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
         <v>57</v>
       </c>
@@ -17318,7 +17319,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="368" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
         <v>25</v>
       </c>
@@ -17356,7 +17357,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="369" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
         <v>55</v>
       </c>
@@ -17394,7 +17395,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="370" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="3" t="s">
         <v>62</v>
       </c>
@@ -17432,7 +17433,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="371" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
         <v>65</v>
       </c>
@@ -17470,7 +17471,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="372" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="3" t="s">
         <v>74</v>
       </c>
@@ -17508,7 +17509,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="373" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
         <v>29</v>
       </c>
@@ -17546,7 +17547,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="374" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
         <v>56</v>
       </c>
@@ -17584,7 +17585,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="375" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
         <v>34</v>
       </c>
@@ -17622,7 +17623,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="376" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
         <v>23</v>
       </c>
@@ -17660,7 +17661,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="377" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
         <v>89</v>
       </c>
@@ -17698,7 +17699,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="3" t="s">
         <v>32</v>
       </c>
@@ -17736,7 +17737,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="379" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
         <v>36</v>
       </c>
@@ -17774,7 +17775,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="380" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="3" t="s">
         <v>19</v>
       </c>
@@ -17812,7 +17813,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="381" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
         <v>47</v>
       </c>
@@ -17850,7 +17851,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="382" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
         <v>53</v>
       </c>
@@ -17888,7 +17889,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="383" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
         <v>13</v>
       </c>
@@ -17926,7 +17927,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="384" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="3" t="s">
         <v>51</v>
       </c>
@@ -17964,7 +17965,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="385" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
         <v>66</v>
       </c>
@@ -18002,7 +18003,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="386" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="3" t="s">
         <v>37</v>
       </c>
@@ -18040,7 +18041,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="387" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
         <v>26</v>
       </c>
@@ -18078,7 +18079,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="388" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
         <v>18</v>
       </c>
@@ -18116,7 +18117,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="389" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
         <v>70</v>
       </c>
@@ -18154,7 +18155,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="390" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="3" t="s">
         <v>72</v>
       </c>
@@ -18192,7 +18193,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="391" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
         <v>24</v>
       </c>
@@ -18230,7 +18231,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="392" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="3" t="s">
         <v>43</v>
       </c>
@@ -18268,7 +18269,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="393" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
         <v>153</v>
       </c>
@@ -18306,7 +18307,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="394" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="3" t="s">
         <v>465</v>
       </c>
@@ -18344,7 +18345,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="395" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
         <v>35</v>
       </c>
@@ -18420,7 +18421,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="397" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
         <v>467</v>
       </c>
@@ -18458,7 +18459,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="398" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="3" t="s">
         <v>33</v>
       </c>
@@ -18496,7 +18497,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="399" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
         <v>28</v>
       </c>
@@ -18534,7 +18535,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="400" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
         <v>44</v>
       </c>
@@ -18572,7 +18573,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="401" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
         <v>38</v>
       </c>
@@ -18610,7 +18611,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="402" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="3" t="s">
         <v>41</v>
       </c>
@@ -18648,7 +18649,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="403" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
         <v>469</v>
       </c>
@@ -18686,7 +18687,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="404" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="3" t="s">
         <v>471</v>
       </c>
@@ -18724,7 +18725,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="405" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
         <v>45</v>
       </c>
@@ -18762,7 +18763,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="406" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
         <v>63</v>
       </c>
@@ -18800,7 +18801,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="407" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
         <v>457</v>
       </c>
@@ -18838,7 +18839,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="408" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="3" t="s">
         <v>473</v>
       </c>
@@ -18876,7 +18877,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="409" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
         <v>475</v>
       </c>
@@ -18914,7 +18915,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="410" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="3" t="s">
         <v>477</v>
       </c>
@@ -18952,7 +18953,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="411" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
         <v>479</v>
       </c>
@@ -18990,7 +18991,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="412" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="3" t="s">
         <v>481</v>
       </c>
@@ -19028,7 +19029,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="413" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
         <v>483</v>
       </c>
@@ -19066,7 +19067,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="414" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="3" t="s">
         <v>485</v>
       </c>
@@ -19104,7 +19105,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="415" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
         <v>487</v>
       </c>
@@ -19142,7 +19143,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="416" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="3" t="s">
         <v>489</v>
       </c>
@@ -19180,7 +19181,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="417" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
         <v>491</v>
       </c>
@@ -19218,7 +19219,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="418" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="3" t="s">
         <v>71</v>
       </c>
@@ -19256,7 +19257,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="419" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
         <v>493</v>
       </c>
@@ -19294,7 +19295,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="420" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="3" t="s">
         <v>495</v>
       </c>
@@ -19332,7 +19333,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="421" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
         <v>497</v>
       </c>
@@ -19370,7 +19371,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="422" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="3" t="s">
         <v>499</v>
       </c>
@@ -19408,7 +19409,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="423" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
         <v>501</v>
       </c>
@@ -19446,7 +19447,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="3" t="s">
         <v>503</v>
       </c>
@@ -19484,7 +19485,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="425" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
         <v>16</v>
       </c>
@@ -19522,7 +19523,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="426" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="3" t="s">
         <v>505</v>
       </c>
@@ -19560,7 +19561,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
         <v>507</v>
       </c>
@@ -19598,7 +19599,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="3" t="s">
         <v>509</v>
       </c>
@@ -19636,7 +19637,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="429" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
         <v>455</v>
       </c>
@@ -19674,7 +19675,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="430" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="3" t="s">
         <v>511</v>
       </c>
@@ -19712,7 +19713,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="431" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
         <v>513</v>
       </c>
@@ -19750,7 +19751,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="432" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="3" t="s">
         <v>515</v>
       </c>
@@ -19788,7 +19789,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="433" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
         <v>517</v>
       </c>
@@ -19826,7 +19827,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="434" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="3" t="s">
         <v>519</v>
       </c>
@@ -19864,7 +19865,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="435" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
         <v>39</v>
       </c>
@@ -19902,7 +19903,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="436" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="3" t="s">
         <v>521</v>
       </c>
@@ -19940,7 +19941,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="437" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
         <v>48</v>
       </c>
@@ -19978,7 +19979,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="438" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="3" t="s">
         <v>523</v>
       </c>
@@ -20016,7 +20017,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="439" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
         <v>525</v>
       </c>
@@ -20054,7 +20055,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="440" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="3" t="s">
         <v>527</v>
       </c>
@@ -20092,7 +20093,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="441" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
         <v>529</v>
       </c>
@@ -20121,7 +20122,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="442" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="3" t="s">
         <v>52</v>
       </c>
@@ -20159,7 +20160,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="443" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
         <v>73</v>
       </c>
@@ -20188,7 +20189,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="444" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="3" t="s">
         <v>87</v>
       </c>
@@ -20226,7 +20227,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="445" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
         <v>90</v>
       </c>
@@ -20264,7 +20265,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="446" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="3" t="s">
         <v>88</v>
       </c>
@@ -20302,7 +20303,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="447" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
         <v>94</v>
       </c>
@@ -20340,7 +20341,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="448" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3" t="s">
         <v>92</v>
       </c>
@@ -20378,7 +20379,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="449" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
         <v>93</v>
       </c>
@@ -20416,7 +20417,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3" t="s">
         <v>109</v>
       </c>
@@ -20454,7 +20455,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="451" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
         <v>110</v>
       </c>
@@ -20492,7 +20493,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="452" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3" t="s">
         <v>111</v>
       </c>
@@ -20530,7 +20531,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="453" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
         <v>112</v>
       </c>
@@ -20568,7 +20569,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="454" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
         <v>91</v>
       </c>
@@ -20606,7 +20607,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="455" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
         <v>113</v>
       </c>
@@ -20644,7 +20645,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="456" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
         <v>126</v>
       </c>
@@ -20682,7 +20683,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
         <v>129</v>
       </c>
@@ -20720,7 +20721,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="458" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
         <v>131</v>
       </c>
@@ -20758,7 +20759,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="459" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
         <v>132</v>
       </c>
@@ -20796,7 +20797,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="460" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
         <v>133</v>
       </c>
@@ -20834,7 +20835,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="461" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
         <v>134</v>
       </c>
@@ -20872,7 +20873,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="462" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
         <v>136</v>
       </c>
@@ -20910,7 +20911,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="463" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
         <v>138</v>
       </c>
@@ -20948,7 +20949,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="464" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
         <v>128</v>
       </c>
@@ -20977,7 +20978,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="465" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
         <v>127</v>
       </c>
@@ -21015,7 +21016,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="466" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
         <v>125</v>
       </c>
@@ -21053,7 +21054,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="467" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
         <v>85</v>
       </c>
@@ -21091,7 +21092,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="468" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
         <v>144</v>
       </c>
@@ -21129,7 +21130,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="469" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
         <v>124</v>
       </c>
@@ -21167,7 +21168,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="470" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
         <v>145</v>
       </c>
@@ -21205,7 +21206,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="471" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
         <v>140</v>
       </c>
@@ -21243,7 +21244,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="472" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
         <v>141</v>
       </c>
@@ -21281,7 +21282,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="473" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
         <v>142</v>
       </c>
@@ -21319,7 +21320,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="474" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
         <v>143</v>
       </c>
@@ -21357,7 +21358,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="475" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
         <v>146</v>
       </c>
@@ -21395,7 +21396,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="476" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
         <v>532</v>
       </c>
@@ -21433,7 +21434,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="477" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
         <v>147</v>
       </c>
@@ -21471,7 +21472,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="478" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
         <v>148</v>
       </c>
@@ -21509,7 +21510,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="479" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
         <v>117</v>
       </c>
@@ -21547,7 +21548,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="480" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="10" t="s">
         <v>14</v>
       </c>
@@ -21585,7 +21586,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="481" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="10" t="s">
         <v>88</v>
       </c>
@@ -21623,7 +21624,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="482" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="10" t="s">
         <v>83</v>
       </c>
@@ -21661,7 +21662,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="483" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="10" t="s">
         <v>16</v>
       </c>
@@ -21699,7 +21700,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="484" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="10" t="s">
         <v>91</v>
       </c>
@@ -21737,7 +21738,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="485" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="10" t="s">
         <v>75</v>
       </c>
@@ -21775,7 +21776,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="486" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="10" t="s">
         <v>93</v>
       </c>
@@ -21813,7 +21814,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="487" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="10" t="s">
         <v>56</v>
       </c>
@@ -21851,7 +21852,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="488" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="10" t="s">
         <v>74</v>
       </c>
@@ -21889,7 +21890,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="489" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="10" t="s">
         <v>70</v>
       </c>
@@ -21927,7 +21928,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="490" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="10" t="s">
         <v>12</v>
       </c>
@@ -21965,7 +21966,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="491" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="10" t="s">
         <v>68</v>
       </c>
@@ -22003,7 +22004,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="492" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="10" t="s">
         <v>90</v>
       </c>
@@ -22041,7 +22042,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="493" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="10" t="s">
         <v>78</v>
       </c>
@@ -22079,7 +22080,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="494" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="10" t="s">
         <v>22</v>
       </c>
@@ -22117,7 +22118,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="495" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="10" t="s">
         <v>30</v>
       </c>
@@ -22155,7 +22156,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="496" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="10" t="s">
         <v>112</v>
       </c>
@@ -22193,7 +22194,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="497" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="10" t="s">
         <v>128</v>
       </c>
@@ -22222,7 +22223,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="498" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="10" t="s">
         <v>131</v>
       </c>
@@ -22260,7 +22261,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="499" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="10" t="s">
         <v>71</v>
       </c>
@@ -22298,7 +22299,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="500" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="10" t="s">
         <v>138</v>
       </c>
@@ -22336,7 +22337,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="501" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="10" t="s">
         <v>145</v>
       </c>
@@ -22374,7 +22375,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="502" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="10" t="s">
         <v>531</v>
       </c>
@@ -22412,7 +22413,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="503" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="10" t="s">
         <v>575</v>
       </c>
@@ -22441,7 +22442,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="504" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="10" t="s">
         <v>144</v>
       </c>
@@ -22479,7 +22480,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="505" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="10" t="s">
         <v>124</v>
       </c>
@@ -22517,7 +22518,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="506" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="10" t="s">
         <v>134</v>
       </c>
@@ -22555,7 +22556,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="507" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="10" t="s">
         <v>133</v>
       </c>
@@ -22593,7 +22594,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="508" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
         <v>146</v>
       </c>
@@ -22631,7 +22632,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="509" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="s">
         <v>532</v>
       </c>
@@ -22669,7 +22670,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="510" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="4" t="s">
         <v>147</v>
       </c>
@@ -22707,7 +22708,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="511" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="4" t="s">
         <v>148</v>
       </c>
@@ -22745,7 +22746,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="512" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="4" t="s">
         <v>117</v>
       </c>
@@ -22783,7 +22784,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="513" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="6" t="s">
         <v>56</v>
       </c>
@@ -22821,7 +22822,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="514" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="6" t="s">
         <v>68</v>
       </c>
@@ -22859,7 +22860,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="515" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="6" t="s">
         <v>12</v>
       </c>
@@ -22897,7 +22898,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="516" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="6" t="s">
         <v>40</v>
       </c>
@@ -22926,7 +22927,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="517" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="6" t="s">
         <v>75</v>
       </c>
@@ -22964,7 +22965,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="518" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="6" t="s">
         <v>69</v>
       </c>
@@ -23002,7 +23003,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="519" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="6" t="s">
         <v>70</v>
       </c>
@@ -23040,7 +23041,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="520" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="6" t="s">
         <v>12</v>
       </c>
@@ -23078,7 +23079,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="521" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="6" t="s">
         <v>14</v>
       </c>
@@ -23116,7 +23117,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="522" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="6" t="s">
         <v>15</v>
       </c>
@@ -23154,7 +23155,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="523" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="6" t="s">
         <v>16</v>
       </c>
@@ -23192,7 +23193,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="524" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="6" t="s">
         <v>19</v>
       </c>
@@ -23230,7 +23231,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="525" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="6" t="s">
         <v>23</v>
       </c>
@@ -23268,7 +23269,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="526" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="6" t="s">
         <v>24</v>
       </c>
@@ -23306,7 +23307,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="527" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="6" t="s">
         <v>25</v>
       </c>
@@ -23344,7 +23345,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="528" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="6" t="s">
         <v>26</v>
       </c>
@@ -23382,7 +23383,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="529" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="6" t="s">
         <v>27</v>
       </c>
@@ -23420,7 +23421,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="530" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="6" t="s">
         <v>28</v>
       </c>
@@ -23458,7 +23459,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="531" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="6" t="s">
         <v>29</v>
       </c>
@@ -23496,7 +23497,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="532" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="6" t="s">
         <v>38</v>
       </c>
@@ -23534,7 +23535,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="533" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="6" t="s">
         <v>40</v>
       </c>
@@ -23572,7 +23573,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="534" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="6" t="s">
         <v>54</v>
       </c>
@@ -23610,7 +23611,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="535" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="6" t="s">
         <v>56</v>
       </c>
@@ -23648,7 +23649,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="536" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="6" t="s">
         <v>57</v>
       </c>
@@ -23686,7 +23687,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="537" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="6" t="s">
         <v>64</v>
       </c>
@@ -23724,7 +23725,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="538" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="6" t="s">
         <v>66</v>
       </c>
@@ -23762,7 +23763,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="539" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="6" t="s">
         <v>67</v>
       </c>
@@ -23800,7 +23801,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="540" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="6" t="s">
         <v>68</v>
       </c>
@@ -23838,7 +23839,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="541" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="6" t="s">
         <v>70</v>
       </c>
@@ -23876,7 +23877,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="542" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="6" t="s">
         <v>71</v>
       </c>
@@ -23914,7 +23915,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="543" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A543" s="6" t="s">
         <v>74</v>
       </c>
@@ -23952,7 +23953,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="544" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A544" s="6" t="s">
         <v>75</v>
       </c>
@@ -23990,7 +23991,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="545" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="6" t="s">
         <v>77</v>
       </c>
@@ -24028,7 +24029,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="546" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A546" s="6" t="s">
         <v>78</v>
       </c>
@@ -24066,7 +24067,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="547" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A547" s="6" t="s">
         <v>79</v>
       </c>
@@ -24104,7 +24105,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="548" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A548" s="6" t="s">
         <v>80</v>
       </c>
@@ -24142,7 +24143,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="549" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A549" s="6" t="s">
         <v>82</v>
       </c>
@@ -24180,7 +24181,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="550" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A550" s="6" t="s">
         <v>83</v>
       </c>
@@ -24218,7 +24219,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="551" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="6" t="s">
         <v>84</v>
       </c>
@@ -24256,7 +24257,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="552" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A552" s="6" t="s">
         <v>88</v>
       </c>
@@ -24294,7 +24295,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="553" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A553" s="6" t="s">
         <v>90</v>
       </c>
@@ -24332,7 +24333,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="554" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A554" s="6" t="s">
         <v>91</v>
       </c>
@@ -24370,7 +24371,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="555" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A555" s="6" t="s">
         <v>92</v>
       </c>
@@ -24408,7 +24409,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="556" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="6" t="s">
         <v>93</v>
       </c>
@@ -24446,7 +24447,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="557" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A557" s="6" t="s">
         <v>109</v>
       </c>
@@ -24484,7 +24485,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="558" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A558" s="6" t="s">
         <v>110</v>
       </c>
@@ -24522,7 +24523,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="559" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A559" s="6" t="s">
         <v>111</v>
       </c>
@@ -24560,7 +24561,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="560" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="6" t="s">
         <v>112</v>
       </c>
@@ -24598,7 +24599,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="561" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="s">
         <v>30</v>
       </c>
@@ -24624,7 +24625,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="562" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
         <v>65</v>
       </c>
@@ -24650,7 +24651,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="563" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A563" s="1" t="s">
         <v>109</v>
       </c>
@@ -24676,7 +24677,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="564" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
         <v>110</v>
       </c>
@@ -24702,7 +24703,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="565" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565" s="1" t="s">
         <v>129</v>
       </c>
@@ -24728,7 +24729,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="566" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>136</v>
       </c>
@@ -24754,7 +24755,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="567" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="s">
         <v>138</v>
       </c>
@@ -24780,7 +24781,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="568" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
         <v>580</v>
       </c>
@@ -24806,7 +24807,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="569" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="s">
         <v>581</v>
       </c>
@@ -24832,7 +24833,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="570" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
         <v>582</v>
       </c>
@@ -24858,7 +24859,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="571" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="1" t="s">
         <v>583</v>
       </c>
@@ -24884,7 +24885,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="572" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
         <v>584</v>
       </c>
@@ -24910,7 +24911,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="573" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>585</v>
       </c>
@@ -24936,7 +24937,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="574" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
         <v>586</v>
       </c>
@@ -24962,7 +24963,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="575" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="s">
         <v>587</v>
       </c>
@@ -24988,7 +24989,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="576" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
         <v>588</v>
       </c>
@@ -25014,7 +25015,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="577" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="s">
         <v>589</v>
       </c>
@@ -25040,7 +25041,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="578" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
         <v>590</v>
       </c>
@@ -25066,7 +25067,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="579" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="s">
         <v>591</v>
       </c>
@@ -25092,7 +25093,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="580" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
         <v>592</v>
       </c>
@@ -25118,7 +25119,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="581" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A581" s="1" t="s">
         <v>117</v>
       </c>
@@ -25144,7 +25145,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="582" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
         <v>593</v>
       </c>
@@ -25170,7 +25171,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="583" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A583" s="1" t="s">
         <v>594</v>
       </c>
@@ -25196,7 +25197,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="584" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
         <v>595</v>
       </c>
@@ -25222,7 +25223,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="585" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A585" s="1" t="s">
         <v>75</v>
       </c>
@@ -25248,7 +25249,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="586" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
         <v>12</v>
       </c>
@@ -25274,7 +25275,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="587" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="s">
         <v>77</v>
       </c>
@@ -25300,7 +25301,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="588" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
         <v>68</v>
       </c>
@@ -25326,7 +25327,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="589" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A589" s="1" t="s">
         <v>40</v>
       </c>
@@ -25352,7 +25353,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="590" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
         <v>83</v>
       </c>
@@ -25378,7 +25379,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="591" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="s">
         <v>42</v>
       </c>
@@ -25404,7 +25405,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="592" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
         <v>54</v>
       </c>
@@ -25430,7 +25431,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="593" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A593" s="1" t="s">
         <v>27</v>
       </c>
@@ -25456,7 +25457,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="594" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
         <v>60</v>
       </c>
@@ -25482,7 +25483,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="595" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A595" s="1" t="s">
         <v>55</v>
       </c>
@@ -25508,7 +25509,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="596" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
         <v>74</v>
       </c>
@@ -25534,7 +25535,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="597" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A597" s="1" t="s">
         <v>23</v>
       </c>
@@ -25560,7 +25561,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="598" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
         <v>13</v>
       </c>
@@ -25586,7 +25587,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="599" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A599" s="1" t="s">
         <v>66</v>
       </c>
@@ -25612,7 +25613,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="600" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
         <v>24</v>
       </c>
@@ -25638,7 +25639,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="601" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="s">
         <v>52</v>
       </c>
@@ -25664,7 +25665,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="602" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
         <v>87</v>
       </c>
@@ -25690,7 +25691,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="603" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A603" s="1" t="s">
         <v>109</v>
       </c>
@@ -25716,7 +25717,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="604" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
         <v>110</v>
       </c>
@@ -25742,7 +25743,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="605" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="s">
         <v>112</v>
       </c>
@@ -25768,7 +25769,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="606" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
         <v>129</v>
       </c>
@@ -25794,7 +25795,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="607" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A607" s="1" t="s">
         <v>130</v>
       </c>
@@ -25820,7 +25821,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="608" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
         <v>133</v>
       </c>
@@ -25846,7 +25847,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="609" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A609" s="1" t="s">
         <v>134</v>
       </c>
@@ -25872,7 +25873,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="610" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
         <v>136</v>
       </c>
@@ -25898,7 +25899,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="611" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A611" s="1" t="s">
         <v>138</v>
       </c>
@@ -25924,7 +25925,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="612" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
         <v>144</v>
       </c>
@@ -25950,7 +25951,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="613" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A613" s="1" t="s">
         <v>117</v>
       </c>
@@ -25976,7 +25977,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="614" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
         <v>593</v>
       </c>
@@ -26002,7 +26003,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="615" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A615" s="1" t="s">
         <v>594</v>
       </c>
@@ -26028,7 +26029,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="616" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A616" s="1" t="s">
         <v>720</v>
       </c>
@@ -26051,7 +26052,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="617" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:12" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A617" s="1" t="s">
         <v>721</v>
       </c>
@@ -26075,6 +26076,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L617" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="AM-C42"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A444">
     <cfRule type="duplicateValues" dxfId="64" priority="1676"/>
@@ -26092,52 +26100,52 @@
     <cfRule type="duplicateValues" dxfId="60" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A553">
-    <cfRule type="duplicateValues" dxfId="59" priority="1602"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="1603"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="1603"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="1602"/>
     <cfRule type="duplicateValues" dxfId="57" priority="1604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A554:A560">
-    <cfRule type="duplicateValues" dxfId="56" priority="1605"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="1606"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1606"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="54" priority="1597"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D355">
-    <cfRule type="duplicateValues" dxfId="53" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="254" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="255" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="256" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="255" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="256" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="254" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D364">
-    <cfRule type="duplicateValues" dxfId="48" priority="257"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="259" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="260" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="260" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="259" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="44" priority="261" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D365:D395 D356:D363 D341:D354">
-    <cfRule type="duplicateValues" dxfId="43" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="274" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="274" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D365:D395">
-    <cfRule type="duplicateValues" dxfId="41" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="276" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="276" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D371:D390">
     <cfRule type="duplicateValues" dxfId="39" priority="272" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D440">
-    <cfRule type="duplicateValues" dxfId="38" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="244" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="245" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="246" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="246" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="244" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="245" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D442 D423:D439 D396:D398">
-    <cfRule type="duplicateValues" dxfId="33" priority="307"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="308" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="308" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="307"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D442">
     <cfRule type="duplicateValues" dxfId="31" priority="309"/>
@@ -26145,8 +26153,8 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="D445:D454">
     <cfRule type="duplicateValues" dxfId="29" priority="1668"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="1669"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="1670"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1670"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1669"/>
     <cfRule type="duplicateValues" dxfId="26" priority="1671"/>
     <cfRule type="duplicateValues" dxfId="25" priority="1672"/>
     <cfRule type="duplicateValues" dxfId="24" priority="1673"/>
@@ -26154,32 +26162,32 @@
     <cfRule type="duplicateValues" dxfId="22" priority="1675" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D456:D463 D465:D466">
-    <cfRule type="duplicateValues" dxfId="21" priority="1443"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="1444"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="1445"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="1446"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1447"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="1448"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="1449" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1447"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1443"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1444"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1445"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1449" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1446"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1448"/>
     <cfRule type="duplicateValues" dxfId="14" priority="1450" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D475:D479">
-    <cfRule type="duplicateValues" dxfId="13" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="126" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="127" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="127" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="126" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
     <cfRule type="duplicateValues" dxfId="5" priority="1595"/>
     <cfRule type="duplicateValues" dxfId="4" priority="1596" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="3" priority="1225"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1226" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1226" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
     <cfRule type="duplicateValues" dxfId="1" priority="1223"/>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 19\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCDC3F0-0C80-4C14-B878-B82612875ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99278C91-4E63-4DD6-A212-1F60CF535CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$610</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$665</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2203,7 +2203,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2211,7 +2211,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2301,8 +2300,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2325,6 +2322,8 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -7213,7 +7212,7 @@
         <v>438</v>
       </c>
       <c r="I221">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="J221" s="1" t="s">
         <v>513</v>
@@ -7233,7 +7232,7 @@
         <v>444</v>
       </c>
       <c r="I222">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="J222" s="1" t="s">
         <v>513</v>
@@ -7252,8 +7251,8 @@
       <c r="D223" t="s">
         <v>359</v>
       </c>
-      <c r="I223" s="3">
-        <v>1401</v>
+      <c r="I223">
+        <v>1327</v>
       </c>
       <c r="J223" s="1" t="s">
         <v>513</v>
@@ -7273,7 +7272,7 @@
         <v>502</v>
       </c>
       <c r="I224">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J224" s="1" t="s">
         <v>513</v>
@@ -7293,7 +7292,7 @@
         <v>393</v>
       </c>
       <c r="I225">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="J225" s="1" t="s">
         <v>513</v>
@@ -7313,7 +7312,7 @@
         <v>443</v>
       </c>
       <c r="I226">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J226" s="1" t="s">
         <v>513</v>
@@ -7333,7 +7332,7 @@
         <v>439</v>
       </c>
       <c r="I227">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J227" s="1" t="s">
         <v>513</v>
@@ -7353,7 +7352,7 @@
         <v>377</v>
       </c>
       <c r="I228">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="J228" s="1" t="s">
         <v>513</v>
@@ -7373,7 +7372,7 @@
         <v>421</v>
       </c>
       <c r="I229">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>513</v>
@@ -7393,7 +7392,7 @@
         <v>358</v>
       </c>
       <c r="I230">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="J230" s="1" t="s">
         <v>513</v>
@@ -7413,7 +7412,7 @@
         <v>426</v>
       </c>
       <c r="I231">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J231" s="1" t="s">
         <v>513</v>
@@ -7433,7 +7432,7 @@
         <v>407</v>
       </c>
       <c r="I232">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J232" s="1" t="s">
         <v>513</v>
@@ -7453,7 +7452,7 @@
         <v>357</v>
       </c>
       <c r="I233">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="J233" s="1" t="s">
         <v>513</v>
@@ -7473,7 +7472,7 @@
         <v>505</v>
       </c>
       <c r="I234">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J234" s="1" t="s">
         <v>513</v>
@@ -7533,7 +7532,7 @@
         <v>448</v>
       </c>
       <c r="I237">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J237" s="1" t="s">
         <v>513</v>
@@ -7553,7 +7552,7 @@
         <v>434</v>
       </c>
       <c r="I238">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J238" s="1" t="s">
         <v>513</v>
@@ -7573,7 +7572,7 @@
         <v>402</v>
       </c>
       <c r="I239">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J239" s="1" t="s">
         <v>513</v>
@@ -7593,7 +7592,7 @@
         <v>408</v>
       </c>
       <c r="I240">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="J240" s="1" t="s">
         <v>513</v>
@@ -7613,7 +7612,7 @@
         <v>371</v>
       </c>
       <c r="I241">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="J241" s="1" t="s">
         <v>513</v>
@@ -7673,7 +7672,7 @@
         <v>445</v>
       </c>
       <c r="I244">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J244" s="1" t="s">
         <v>513</v>
@@ -7692,7 +7691,9 @@
       <c r="D245" t="s">
         <v>592</v>
       </c>
-      <c r="I245"/>
+      <c r="I245">
+        <v>0</v>
+      </c>
       <c r="J245" s="1" t="s">
         <v>513</v>
       </c>
@@ -7731,7 +7732,7 @@
         <v>507</v>
       </c>
       <c r="I247">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J247" s="1" t="s">
         <v>513</v>
@@ -7750,7 +7751,9 @@
       <c r="D248" t="s">
         <v>374</v>
       </c>
-      <c r="I248"/>
+      <c r="I248">
+        <v>0</v>
+      </c>
       <c r="J248" s="1" t="s">
         <v>513</v>
       </c>
@@ -7769,7 +7772,7 @@
         <v>364</v>
       </c>
       <c r="I249">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J249" s="1" t="s">
         <v>513</v>
@@ -7788,7 +7791,9 @@
       <c r="D250" t="s">
         <v>410</v>
       </c>
-      <c r="I250"/>
+      <c r="I250">
+        <v>0</v>
+      </c>
       <c r="J250" s="1" t="s">
         <v>513</v>
       </c>
@@ -7827,7 +7832,7 @@
         <v>422</v>
       </c>
       <c r="I252">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J252" s="1" t="s">
         <v>513</v>
@@ -7887,7 +7892,7 @@
         <v>499</v>
       </c>
       <c r="I255">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J255" s="1" t="s">
         <v>513</v>
@@ -7907,7 +7912,7 @@
         <v>433</v>
       </c>
       <c r="I256">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J256" s="1" t="s">
         <v>513</v>
@@ -7947,7 +7952,7 @@
         <v>432</v>
       </c>
       <c r="I258">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J258" s="1" t="s">
         <v>513</v>
@@ -7987,7 +7992,7 @@
         <v>450</v>
       </c>
       <c r="I260">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J260" s="1" t="s">
         <v>513</v>
@@ -8007,7 +8012,7 @@
         <v>376</v>
       </c>
       <c r="I261">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J261" s="1" t="s">
         <v>513</v>
@@ -8027,7 +8032,7 @@
         <v>360</v>
       </c>
       <c r="I262">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J262" s="1" t="s">
         <v>513</v>
@@ -8047,7 +8052,7 @@
         <v>457</v>
       </c>
       <c r="I263">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="J263" s="1" t="s">
         <v>513</v>
@@ -8086,7 +8091,9 @@
       <c r="D265" t="s">
         <v>378</v>
       </c>
-      <c r="I265"/>
+      <c r="I265">
+        <v>0</v>
+      </c>
       <c r="J265" s="1" t="s">
         <v>513</v>
       </c>
@@ -8125,7 +8132,7 @@
         <v>479</v>
       </c>
       <c r="I267">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J267" s="1" t="s">
         <v>513</v>
@@ -8185,7 +8192,7 @@
         <v>424</v>
       </c>
       <c r="I270">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="J270" s="1" t="s">
         <v>513</v>
@@ -8245,7 +8252,7 @@
         <v>506</v>
       </c>
       <c r="I273">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J273" s="1" t="s">
         <v>513</v>
@@ -8265,7 +8272,7 @@
         <v>380</v>
       </c>
       <c r="I274">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J274" s="1" t="s">
         <v>513</v>
@@ -8305,7 +8312,7 @@
         <v>494</v>
       </c>
       <c r="I276">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J276" s="1" t="s">
         <v>513</v>
@@ -8325,7 +8332,7 @@
         <v>367</v>
       </c>
       <c r="I277">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J277" s="1" t="s">
         <v>513</v>
@@ -8344,7 +8351,9 @@
       <c r="D278" t="s">
         <v>396</v>
       </c>
-      <c r="I278"/>
+      <c r="I278">
+        <v>0</v>
+      </c>
       <c r="J278" s="1" t="s">
         <v>513</v>
       </c>
@@ -8423,7 +8432,7 @@
         <v>399</v>
       </c>
       <c r="I282">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J282" s="1" t="s">
         <v>513</v>
@@ -8442,7 +8451,9 @@
       <c r="D283" t="s">
         <v>396</v>
       </c>
-      <c r="I283"/>
+      <c r="I283">
+        <v>0</v>
+      </c>
       <c r="J283" s="1" t="s">
         <v>513</v>
       </c>
@@ -8461,7 +8472,7 @@
         <v>369</v>
       </c>
       <c r="I284">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J284" s="1" t="s">
         <v>513</v>
@@ -8481,7 +8492,7 @@
         <v>452</v>
       </c>
       <c r="I285">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J285" s="1" t="s">
         <v>513</v>
@@ -8500,7 +8511,9 @@
       <c r="D286" t="s">
         <v>413</v>
       </c>
-      <c r="I286"/>
+      <c r="I286">
+        <v>0</v>
+      </c>
       <c r="J286" s="1" t="s">
         <v>513</v>
       </c>
@@ -8519,7 +8532,7 @@
         <v>413</v>
       </c>
       <c r="I287">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J287" s="1" t="s">
         <v>513</v>
@@ -8539,7 +8552,7 @@
         <v>375</v>
       </c>
       <c r="I288">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="J288" s="1" t="s">
         <v>513</v>
@@ -8579,7 +8592,7 @@
         <v>436</v>
       </c>
       <c r="I290">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J290" s="1" t="s">
         <v>513</v>
@@ -8679,7 +8692,7 @@
         <v>387</v>
       </c>
       <c r="I295">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J295" s="1" t="s">
         <v>513</v>
@@ -8699,7 +8712,7 @@
         <v>370</v>
       </c>
       <c r="I296">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J296" s="1" t="s">
         <v>513</v>
@@ -8739,7 +8752,7 @@
         <v>391</v>
       </c>
       <c r="I298">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J298" s="1" t="s">
         <v>513</v>
@@ -8759,7 +8772,7 @@
         <v>425</v>
       </c>
       <c r="I299">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="J299" s="1" t="s">
         <v>513</v>
@@ -8839,7 +8852,7 @@
         <v>373</v>
       </c>
       <c r="I303">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J303" s="1" t="s">
         <v>513</v>
@@ -8859,7 +8872,7 @@
         <v>379</v>
       </c>
       <c r="I304">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J304" s="1" t="s">
         <v>513</v>
@@ -8879,7 +8892,7 @@
         <v>430</v>
       </c>
       <c r="I305">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J305" s="1" t="s">
         <v>513</v>
@@ -8919,7 +8932,7 @@
         <v>392</v>
       </c>
       <c r="I307">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J307" s="1" t="s">
         <v>513</v>
@@ -8999,7 +9012,7 @@
         <v>427</v>
       </c>
       <c r="I311">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J311" s="1" t="s">
         <v>513</v>
@@ -9079,7 +9092,7 @@
         <v>389</v>
       </c>
       <c r="I315">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J315" s="1" t="s">
         <v>513</v>
@@ -9119,7 +9132,7 @@
         <v>435</v>
       </c>
       <c r="I317">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="J317" s="1" t="s">
         <v>513</v>
@@ -9139,7 +9152,7 @@
         <v>363</v>
       </c>
       <c r="I318">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J318" s="1" t="s">
         <v>513</v>
@@ -9179,7 +9192,7 @@
         <v>478</v>
       </c>
       <c r="I320">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="J320" s="1" t="s">
         <v>513</v>
@@ -9199,7 +9212,7 @@
         <v>372</v>
       </c>
       <c r="I321">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J321" s="1" t="s">
         <v>513</v>
@@ -9219,7 +9232,7 @@
         <v>403</v>
       </c>
       <c r="I322">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J322" s="1" t="s">
         <v>513</v>
@@ -9279,7 +9292,7 @@
         <v>442</v>
       </c>
       <c r="I325">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J325" s="1" t="s">
         <v>513</v>
@@ -9319,7 +9332,7 @@
         <v>417</v>
       </c>
       <c r="I327">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J327" s="1" t="s">
         <v>513</v>
@@ -9339,7 +9352,7 @@
         <v>378</v>
       </c>
       <c r="I328">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J328" s="1" t="s">
         <v>513</v>
@@ -9379,7 +9392,7 @@
         <v>404</v>
       </c>
       <c r="I330">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="J330" s="1" t="s">
         <v>513</v>
@@ -9398,7 +9411,9 @@
       <c r="D331" t="s">
         <v>429</v>
       </c>
-      <c r="I331"/>
+      <c r="I331">
+        <v>0</v>
+      </c>
       <c r="J331" s="1" t="s">
         <v>513</v>
       </c>
@@ -9477,7 +9492,7 @@
         <v>388</v>
       </c>
       <c r="I335">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J335" s="1" t="s">
         <v>513</v>
@@ -9517,7 +9532,7 @@
         <v>488</v>
       </c>
       <c r="I337">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J337" s="1" t="s">
         <v>513</v>
@@ -9597,7 +9612,7 @@
         <v>361</v>
       </c>
       <c r="I341">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J341" s="1" t="s">
         <v>513</v>
@@ -9657,7 +9672,7 @@
         <v>482</v>
       </c>
       <c r="I344">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J344" s="1" t="s">
         <v>513</v>
@@ -9716,27 +9731,27 @@
       <c r="D347" t="s">
         <v>368</v>
       </c>
-      <c r="I347" s="3">
-        <v>1016</v>
+      <c r="I347">
+        <v>981</v>
       </c>
       <c r="J347" s="1" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="348" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A348" s="4" t="s">
+      <c r="A348" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B348" s="4" t="s">
+      <c r="B348" s="3" t="s">
         <v>192</v>
       </c>
       <c r="C348" t="s">
         <v>477</v>
       </c>
-      <c r="D348" s="7" t="s">
+      <c r="D348" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="I348" s="5">
+      <c r="I348" s="4">
         <v>1989</v>
       </c>
       <c r="J348" s="1" t="s">
@@ -9744,19 +9759,19 @@
       </c>
     </row>
     <row r="349" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A349" s="4" t="s">
+      <c r="A349" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B349" s="4" t="s">
+      <c r="B349" s="3" t="s">
         <v>222</v>
       </c>
       <c r="C349" t="s">
         <v>477</v>
       </c>
-      <c r="D349" s="7" t="s">
+      <c r="D349" s="6" t="s">
         <v>585</v>
       </c>
-      <c r="I349" s="5">
+      <c r="I349" s="4">
         <v>502</v>
       </c>
       <c r="J349" s="1" t="s">
@@ -9764,19 +9779,19 @@
       </c>
     </row>
     <row r="350" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A350" s="4" t="s">
+      <c r="A350" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B350" s="4" t="s">
+      <c r="B350" s="3" t="s">
         <v>236</v>
       </c>
       <c r="C350" t="s">
         <v>477</v>
       </c>
-      <c r="D350" s="7" t="s">
+      <c r="D350" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="I350" s="5">
+      <c r="I350" s="4">
         <v>859</v>
       </c>
       <c r="J350" s="1" t="s">
@@ -9784,19 +9799,19 @@
       </c>
     </row>
     <row r="351" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A351" s="4" t="s">
+      <c r="A351" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B351" s="4" t="s">
+      <c r="B351" s="3" t="s">
         <v>174</v>
       </c>
       <c r="C351" t="s">
         <v>477</v>
       </c>
-      <c r="D351" s="7" t="s">
+      <c r="D351" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="I351" s="5">
+      <c r="I351" s="4">
         <v>1036</v>
       </c>
       <c r="J351" s="1" t="s">
@@ -9804,19 +9819,19 @@
       </c>
     </row>
     <row r="352" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A352" s="4" t="s">
+      <c r="A352" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B352" s="4" t="s">
+      <c r="B352" s="3" t="s">
         <v>183</v>
       </c>
       <c r="C352" t="s">
         <v>477</v>
       </c>
-      <c r="D352" s="7" t="s">
+      <c r="D352" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="I352" s="5">
+      <c r="I352" s="4">
         <v>339</v>
       </c>
       <c r="J352" s="1" t="s">
@@ -9824,19 +9839,19 @@
       </c>
     </row>
     <row r="353" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A353" s="4" t="s">
+      <c r="A353" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B353" s="4" t="s">
+      <c r="B353" s="3" t="s">
         <v>239</v>
       </c>
       <c r="C353" t="s">
         <v>477</v>
       </c>
-      <c r="D353" s="7" t="s">
+      <c r="D353" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="I353" s="5">
+      <c r="I353" s="4">
         <v>587</v>
       </c>
       <c r="J353" s="1" t="s">
@@ -9844,19 +9859,19 @@
       </c>
     </row>
     <row r="354" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A354" s="4" t="s">
+      <c r="A354" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B354" s="4" t="s">
+      <c r="B354" s="3" t="s">
         <v>238</v>
       </c>
       <c r="C354" t="s">
         <v>477</v>
       </c>
-      <c r="D354" s="7" t="s">
+      <c r="D354" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="I354" s="5">
+      <c r="I354" s="4">
         <v>325</v>
       </c>
       <c r="J354" s="1" t="s">
@@ -9864,19 +9879,19 @@
       </c>
     </row>
     <row r="355" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A355" s="4" t="s">
+      <c r="A355" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B355" s="4" t="s">
+      <c r="B355" s="3" t="s">
         <v>230</v>
       </c>
       <c r="C355" t="s">
         <v>477</v>
       </c>
-      <c r="D355" s="7" t="s">
+      <c r="D355" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="I355" s="5">
+      <c r="I355" s="4">
         <v>46</v>
       </c>
       <c r="J355" s="1" t="s">
@@ -9884,19 +9899,19 @@
       </c>
     </row>
     <row r="356" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A356" s="4" t="s">
+      <c r="A356" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B356" s="4" t="s">
+      <c r="B356" s="3" t="s">
         <v>242</v>
       </c>
       <c r="C356" t="s">
         <v>477</v>
       </c>
-      <c r="D356" s="7" t="s">
+      <c r="D356" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="I356" s="5">
+      <c r="I356" s="4">
         <v>63</v>
       </c>
       <c r="J356" s="1" t="s">
@@ -9904,19 +9919,19 @@
       </c>
     </row>
     <row r="357" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A357" s="4" t="s">
+      <c r="A357" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B357" s="4" t="s">
+      <c r="B357" s="3" t="s">
         <v>229</v>
       </c>
       <c r="C357" t="s">
         <v>477</v>
       </c>
-      <c r="D357" s="7" t="s">
+      <c r="D357" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="I357" s="5">
+      <c r="I357" s="4">
         <v>10</v>
       </c>
       <c r="J357" s="1" t="s">
@@ -9924,19 +9939,19 @@
       </c>
     </row>
     <row r="358" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A358" s="4" t="s">
+      <c r="A358" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B358" s="4" t="s">
+      <c r="B358" s="3" t="s">
         <v>240</v>
       </c>
       <c r="C358" t="s">
         <v>477</v>
       </c>
-      <c r="D358" s="7" t="s">
+      <c r="D358" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="I358" s="5">
+      <c r="I358" s="4">
         <v>192</v>
       </c>
       <c r="J358" s="1" t="s">
@@ -9944,19 +9959,19 @@
       </c>
     </row>
     <row r="359" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A359" s="4" t="s">
+      <c r="A359" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B359" s="4" t="s">
+      <c r="B359" s="3" t="s">
         <v>225</v>
       </c>
       <c r="C359" t="s">
         <v>477</v>
       </c>
-      <c r="D359" s="7" t="s">
+      <c r="D359" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="I359" s="5">
+      <c r="I359" s="4">
         <v>1353</v>
       </c>
       <c r="J359" s="1" t="s">
@@ -9964,19 +9979,19 @@
       </c>
     </row>
     <row r="360" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A360" s="4" t="s">
+      <c r="A360" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B360" s="4" t="s">
+      <c r="B360" s="3" t="s">
         <v>201</v>
       </c>
       <c r="C360" t="s">
         <v>477</v>
       </c>
-      <c r="D360" s="7" t="s">
+      <c r="D360" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I360" s="5">
+      <c r="I360" s="4">
         <v>740</v>
       </c>
       <c r="J360" s="1" t="s">
@@ -9984,19 +9999,19 @@
       </c>
     </row>
     <row r="361" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A361" s="4" t="s">
+      <c r="A361" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B361" s="4" t="s">
+      <c r="B361" s="3" t="s">
         <v>193</v>
       </c>
       <c r="C361" t="s">
         <v>477</v>
       </c>
-      <c r="D361" s="7" t="s">
+      <c r="D361" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="I361" s="5">
+      <c r="I361" s="4">
         <v>144</v>
       </c>
       <c r="J361" s="1" t="s">
@@ -10004,19 +10019,19 @@
       </c>
     </row>
     <row r="362" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A362" s="4" t="s">
+      <c r="A362" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B362" s="4" t="s">
+      <c r="B362" s="3" t="s">
         <v>176</v>
       </c>
       <c r="C362" t="s">
         <v>477</v>
       </c>
-      <c r="D362" s="7" t="s">
+      <c r="D362" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="I362" s="5">
+      <c r="I362" s="4">
         <v>149</v>
       </c>
       <c r="J362" s="1" t="s">
@@ -10024,19 +10039,19 @@
       </c>
     </row>
     <row r="363" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A363" s="4" t="s">
+      <c r="A363" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B363" s="4" t="s">
+      <c r="B363" s="3" t="s">
         <v>179</v>
       </c>
       <c r="C363" t="s">
         <v>477</v>
       </c>
-      <c r="D363" s="7" t="s">
+      <c r="D363" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="I363" s="5">
+      <c r="I363" s="4">
         <v>385</v>
       </c>
       <c r="J363" s="1" t="s">
@@ -10044,19 +10059,19 @@
       </c>
     </row>
     <row r="364" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A364" s="4" t="s">
+      <c r="A364" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B364" s="4" t="s">
+      <c r="B364" s="3" t="s">
         <v>241</v>
       </c>
       <c r="C364" t="s">
         <v>477</v>
       </c>
-      <c r="D364" s="7" t="s">
+      <c r="D364" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="I364" s="5">
+      <c r="I364" s="4">
         <v>286</v>
       </c>
       <c r="J364" s="1" t="s">
@@ -10064,19 +10079,19 @@
       </c>
     </row>
     <row r="365" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A365" s="4" t="s">
+      <c r="A365" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B365" s="4" t="s">
+      <c r="B365" s="3" t="s">
         <v>184</v>
       </c>
       <c r="C365" t="s">
         <v>477</v>
       </c>
-      <c r="D365" s="7" t="s">
+      <c r="D365" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="I365" s="5">
+      <c r="I365" s="4">
         <v>374</v>
       </c>
       <c r="J365" s="1" t="s">
@@ -10084,19 +10099,19 @@
       </c>
     </row>
     <row r="366" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A366" s="4" t="s">
+      <c r="A366" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B366" s="4" t="s">
+      <c r="B366" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C366" t="s">
         <v>477</v>
       </c>
-      <c r="D366" s="7" t="s">
+      <c r="D366" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="I366" s="5">
+      <c r="I366" s="4">
         <v>183</v>
       </c>
       <c r="J366" s="1" t="s">
@@ -10104,19 +10119,19 @@
       </c>
     </row>
     <row r="367" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A367" s="4" t="s">
+      <c r="A367" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B367" s="4" t="s">
+      <c r="B367" s="3" t="s">
         <v>244</v>
       </c>
       <c r="C367" t="s">
         <v>477</v>
       </c>
-      <c r="D367" s="7" t="s">
+      <c r="D367" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="I367" s="5">
+      <c r="I367" s="4">
         <v>215</v>
       </c>
       <c r="J367" s="1" t="s">
@@ -10124,19 +10139,19 @@
       </c>
     </row>
     <row r="368" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A368" s="4" t="s">
+      <c r="A368" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B368" s="4" t="s">
+      <c r="B368" s="3" t="s">
         <v>203</v>
       </c>
       <c r="C368" t="s">
         <v>477</v>
       </c>
-      <c r="D368" s="7" t="s">
+      <c r="D368" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="I368" s="5">
+      <c r="I368" s="4">
         <v>398</v>
       </c>
       <c r="J368" s="1" t="s">
@@ -10144,19 +10159,19 @@
       </c>
     </row>
     <row r="369" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A369" s="4" t="s">
+      <c r="A369" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B369" s="4" t="s">
+      <c r="B369" s="3" t="s">
         <v>211</v>
       </c>
       <c r="C369" t="s">
         <v>477</v>
       </c>
-      <c r="D369" s="7" t="s">
+      <c r="D369" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="I369" s="5">
+      <c r="I369" s="4">
         <v>422</v>
       </c>
       <c r="J369" s="1" t="s">
@@ -10164,19 +10179,19 @@
       </c>
     </row>
     <row r="370" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A370" s="4" t="s">
+      <c r="A370" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B370" s="4" t="s">
+      <c r="B370" s="3" t="s">
         <v>215</v>
       </c>
       <c r="C370" t="s">
         <v>477</v>
       </c>
-      <c r="D370" s="7" t="s">
+      <c r="D370" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="I370" s="5">
+      <c r="I370" s="4">
         <v>7</v>
       </c>
       <c r="J370" s="1" t="s">
@@ -10184,19 +10199,19 @@
       </c>
     </row>
     <row r="371" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A371" s="4" t="s">
+      <c r="A371" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B371" s="4" t="s">
+      <c r="B371" s="3" t="s">
         <v>237</v>
       </c>
       <c r="C371" t="s">
         <v>477</v>
       </c>
-      <c r="D371" s="7" t="s">
+      <c r="D371" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="I371" s="5">
+      <c r="I371" s="4">
         <v>172</v>
       </c>
       <c r="J371" s="1" t="s">
@@ -10204,19 +10219,19 @@
       </c>
     </row>
     <row r="372" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A372" s="4" t="s">
+      <c r="A372" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B372" s="4" t="s">
+      <c r="B372" s="3" t="s">
         <v>189</v>
       </c>
       <c r="C372" t="s">
         <v>477</v>
       </c>
-      <c r="D372" s="7" t="s">
+      <c r="D372" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="I372" s="5">
+      <c r="I372" s="4">
         <v>117</v>
       </c>
       <c r="J372" s="1" t="s">
@@ -10224,19 +10239,19 @@
       </c>
     </row>
     <row r="373" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A373" s="4" t="s">
+      <c r="A373" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B373" s="4" t="s">
+      <c r="B373" s="3" t="s">
         <v>177</v>
       </c>
       <c r="C373" t="s">
         <v>477</v>
       </c>
-      <c r="D373" s="7" t="s">
+      <c r="D373" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="I373" s="5">
+      <c r="I373" s="4">
         <v>37</v>
       </c>
       <c r="J373" s="1" t="s">
@@ -10244,19 +10259,19 @@
       </c>
     </row>
     <row r="374" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A374" s="4" t="s">
+      <c r="A374" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B374" s="4" t="s">
+      <c r="B374" s="3" t="s">
         <v>182</v>
       </c>
       <c r="C374" t="s">
         <v>477</v>
       </c>
-      <c r="D374" s="7" t="s">
+      <c r="D374" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="I374" s="5">
+      <c r="I374" s="4">
         <v>9</v>
       </c>
       <c r="J374" s="1" t="s">
@@ -10264,19 +10279,19 @@
       </c>
     </row>
     <row r="375" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A375" s="4" t="s">
+      <c r="A375" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B375" s="4" t="s">
+      <c r="B375" s="3" t="s">
         <v>228</v>
       </c>
       <c r="C375" t="s">
         <v>477</v>
       </c>
-      <c r="D375" s="7" t="s">
+      <c r="D375" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I375" s="5">
+      <c r="I375" s="4">
         <v>152</v>
       </c>
       <c r="J375" s="1" t="s">
@@ -10284,19 +10299,19 @@
       </c>
     </row>
     <row r="376" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A376" s="4" t="s">
+      <c r="A376" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B376" s="4" t="s">
+      <c r="B376" s="3" t="s">
         <v>210</v>
       </c>
       <c r="C376" t="s">
         <v>477</v>
       </c>
-      <c r="D376" s="7" t="s">
+      <c r="D376" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="I376" s="5">
+      <c r="I376" s="4">
         <v>101</v>
       </c>
       <c r="J376" s="1" t="s">
@@ -10304,19 +10319,19 @@
       </c>
     </row>
     <row r="377" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A377" s="4" t="s">
+      <c r="A377" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B377" s="4" t="s">
+      <c r="B377" s="3" t="s">
         <v>221</v>
       </c>
       <c r="C377" t="s">
         <v>477</v>
       </c>
-      <c r="D377" s="7" t="s">
+      <c r="D377" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="I377" s="5">
+      <c r="I377" s="4">
         <v>252</v>
       </c>
       <c r="J377" s="1" t="s">
@@ -10324,19 +10339,19 @@
       </c>
     </row>
     <row r="378" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A378" s="4" t="s">
+      <c r="A378" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B378" s="4" t="s">
+      <c r="B378" s="3" t="s">
         <v>207</v>
       </c>
       <c r="C378" t="s">
         <v>477</v>
       </c>
-      <c r="D378" s="7" t="s">
+      <c r="D378" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="I378" s="5">
+      <c r="I378" s="4">
         <v>66</v>
       </c>
       <c r="J378" s="1" t="s">
@@ -10344,19 +10359,19 @@
       </c>
     </row>
     <row r="379" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A379" s="4" t="s">
+      <c r="A379" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B379" s="4" t="s">
+      <c r="B379" s="3" t="s">
         <v>218</v>
       </c>
       <c r="C379" t="s">
         <v>477</v>
       </c>
-      <c r="D379" s="7" t="s">
+      <c r="D379" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="I379" s="5">
+      <c r="I379" s="4">
         <v>89</v>
       </c>
       <c r="J379" s="1" t="s">
@@ -10364,19 +10379,19 @@
       </c>
     </row>
     <row r="380" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="4" t="s">
+      <c r="A380" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B380" s="4" t="s">
+      <c r="B380" s="3" t="s">
         <v>187</v>
       </c>
       <c r="C380" t="s">
         <v>477</v>
       </c>
-      <c r="D380" s="7" t="s">
+      <c r="D380" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="I380" s="5">
+      <c r="I380" s="4">
         <v>498</v>
       </c>
       <c r="J380" s="1" t="s">
@@ -10384,19 +10399,19 @@
       </c>
     </row>
     <row r="381" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A381" s="4" t="s">
+      <c r="A381" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B381" s="4" t="s">
+      <c r="B381" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C381" t="s">
         <v>477</v>
       </c>
-      <c r="D381" s="7" t="s">
+      <c r="D381" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="I381" s="5">
+      <c r="I381" s="4">
         <v>212</v>
       </c>
       <c r="J381" s="1" t="s">
@@ -10404,19 +10419,19 @@
       </c>
     </row>
     <row r="382" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A382" s="4" t="s">
+      <c r="A382" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B382" s="4" t="s">
+      <c r="B382" s="3" t="s">
         <v>223</v>
       </c>
       <c r="C382" t="s">
         <v>477</v>
       </c>
-      <c r="D382" s="7" t="s">
+      <c r="D382" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="I382" s="5">
+      <c r="I382" s="4">
         <v>747</v>
       </c>
       <c r="J382" s="1" t="s">
@@ -10424,19 +10439,19 @@
       </c>
     </row>
     <row r="383" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A383" s="4" t="s">
+      <c r="A383" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B383" s="4" t="s">
+      <c r="B383" s="3" t="s">
         <v>226</v>
       </c>
       <c r="C383" t="s">
         <v>477</v>
       </c>
-      <c r="D383" s="7" t="s">
+      <c r="D383" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="I383" s="5">
+      <c r="I383" s="4">
         <v>1021</v>
       </c>
       <c r="J383" s="1" t="s">
@@ -10444,19 +10459,19 @@
       </c>
     </row>
     <row r="384" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A384" s="4" t="s">
+      <c r="A384" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B384" s="4" t="s">
+      <c r="B384" s="3" t="s">
         <v>235</v>
       </c>
       <c r="C384" t="s">
         <v>477</v>
       </c>
-      <c r="D384" s="7" t="s">
+      <c r="D384" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="I384" s="5">
+      <c r="I384" s="4">
         <v>230</v>
       </c>
       <c r="J384" s="1" t="s">
@@ -10464,19 +10479,19 @@
       </c>
     </row>
     <row r="385" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A385" s="4" t="s">
+      <c r="A385" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B385" s="4" t="s">
+      <c r="B385" s="3" t="s">
         <v>191</v>
       </c>
       <c r="C385" t="s">
         <v>477</v>
       </c>
-      <c r="D385" s="7" t="s">
+      <c r="D385" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="I385" s="5">
+      <c r="I385" s="4">
         <v>0</v>
       </c>
       <c r="J385" s="1" t="s">
@@ -10484,19 +10499,19 @@
       </c>
     </row>
     <row r="386" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A386" s="4" t="s">
+      <c r="A386" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B386" s="4" t="s">
+      <c r="B386" s="3" t="s">
         <v>217</v>
       </c>
       <c r="C386" t="s">
         <v>477</v>
       </c>
-      <c r="D386" s="7" t="s">
+      <c r="D386" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="I386" s="5">
+      <c r="I386" s="4">
         <v>197</v>
       </c>
       <c r="J386" s="1" t="s">
@@ -10504,19 +10519,19 @@
       </c>
     </row>
     <row r="387" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A387" s="4" t="s">
+      <c r="A387" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B387" s="4" t="s">
+      <c r="B387" s="3" t="s">
         <v>196</v>
       </c>
       <c r="C387" t="s">
         <v>477</v>
       </c>
-      <c r="D387" s="7" t="s">
+      <c r="D387" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="I387" s="5">
+      <c r="I387" s="4">
         <v>6</v>
       </c>
       <c r="J387" s="1" t="s">
@@ -10524,19 +10539,19 @@
       </c>
     </row>
     <row r="388" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A388" s="4" t="s">
+      <c r="A388" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B388" s="4" t="s">
+      <c r="B388" s="3" t="s">
         <v>185</v>
       </c>
       <c r="C388" t="s">
         <v>477</v>
       </c>
-      <c r="D388" s="7" t="s">
+      <c r="D388" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="I388" s="5">
+      <c r="I388" s="4">
         <v>9</v>
       </c>
       <c r="J388" s="1" t="s">
@@ -10544,19 +10559,19 @@
       </c>
     </row>
     <row r="389" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A389" s="4" t="s">
+      <c r="A389" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B389" s="4" t="s">
+      <c r="B389" s="3" t="s">
         <v>250</v>
       </c>
       <c r="C389" t="s">
         <v>477</v>
       </c>
-      <c r="D389" s="7" t="s">
+      <c r="D389" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="I389" s="5">
+      <c r="I389" s="4">
         <v>42</v>
       </c>
       <c r="J389" s="1" t="s">
@@ -10564,19 +10579,19 @@
       </c>
     </row>
     <row r="390" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A390" s="4" t="s">
+      <c r="A390" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B390" s="4" t="s">
+      <c r="B390" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C390" t="s">
         <v>477</v>
       </c>
-      <c r="D390" s="7" t="s">
+      <c r="D390" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="I390" s="5">
+      <c r="I390" s="4">
         <v>17</v>
       </c>
       <c r="J390" s="1" t="s">
@@ -10584,19 +10599,19 @@
       </c>
     </row>
     <row r="391" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A391" s="4" t="s">
+      <c r="A391" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B391" s="4" t="s">
+      <c r="B391" s="3" t="s">
         <v>197</v>
       </c>
       <c r="C391" t="s">
         <v>477</v>
       </c>
-      <c r="D391" s="7" t="s">
+      <c r="D391" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="I391" s="5">
+      <c r="I391" s="4">
         <v>12</v>
       </c>
       <c r="J391" s="1" t="s">
@@ -10604,19 +10619,19 @@
       </c>
     </row>
     <row r="392" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A392" s="4" t="s">
+      <c r="A392" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B392" s="4" t="s">
+      <c r="B392" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C392" t="s">
         <v>477</v>
       </c>
-      <c r="D392" s="7" t="s">
+      <c r="D392" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="I392" s="5">
+      <c r="I392" s="4">
         <v>12</v>
       </c>
       <c r="J392" s="1" t="s">
@@ -10624,19 +10639,19 @@
       </c>
     </row>
     <row r="393" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A393" s="4" t="s">
+      <c r="A393" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B393" s="4" t="s">
+      <c r="B393" s="3" t="s">
         <v>208</v>
       </c>
       <c r="C393" t="s">
         <v>477</v>
       </c>
-      <c r="D393" s="7" t="s">
+      <c r="D393" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="I393" s="5">
+      <c r="I393" s="4">
         <v>43</v>
       </c>
       <c r="J393" s="1" t="s">
@@ -10644,19 +10659,19 @@
       </c>
     </row>
     <row r="394" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A394" s="4" t="s">
+      <c r="A394" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B394" s="4" t="s">
+      <c r="B394" s="3" t="s">
         <v>214</v>
       </c>
       <c r="C394" t="s">
         <v>477</v>
       </c>
-      <c r="D394" s="7" t="s">
+      <c r="D394" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="I394" s="5">
+      <c r="I394" s="4">
         <v>407</v>
       </c>
       <c r="J394" s="1" t="s">
@@ -10664,19 +10679,19 @@
       </c>
     </row>
     <row r="395" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A395" s="4" t="s">
+      <c r="A395" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B395" s="4" t="s">
+      <c r="B395" s="3" t="s">
         <v>175</v>
       </c>
       <c r="C395" t="s">
         <v>477</v>
       </c>
-      <c r="D395" s="7" t="s">
+      <c r="D395" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="I395" s="5">
+      <c r="I395" s="4">
         <v>58</v>
       </c>
       <c r="J395" s="1" t="s">
@@ -10684,19 +10699,19 @@
       </c>
     </row>
     <row r="396" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A396" s="4" t="s">
+      <c r="A396" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B396" s="4" t="s">
+      <c r="B396" s="3" t="s">
         <v>212</v>
       </c>
       <c r="C396" t="s">
         <v>477</v>
       </c>
-      <c r="D396" s="7" t="s">
+      <c r="D396" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="I396" s="5">
+      <c r="I396" s="4">
         <v>0</v>
       </c>
       <c r="J396" s="1" t="s">
@@ -10704,19 +10719,19 @@
       </c>
     </row>
     <row r="397" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A397" s="4" t="s">
+      <c r="A397" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B397" s="4" t="s">
+      <c r="B397" s="3" t="s">
         <v>227</v>
       </c>
       <c r="C397" t="s">
         <v>477</v>
       </c>
-      <c r="D397" s="7" t="s">
+      <c r="D397" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="I397" s="5">
+      <c r="I397" s="4">
         <v>102</v>
       </c>
       <c r="J397" s="1" t="s">
@@ -10724,19 +10739,19 @@
       </c>
     </row>
     <row r="398" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A398" s="4" t="s">
+      <c r="A398" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B398" s="4" t="s">
+      <c r="B398" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C398" t="s">
         <v>477</v>
       </c>
-      <c r="D398" s="7" t="s">
+      <c r="D398" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="I398" s="5">
+      <c r="I398" s="4">
         <v>18</v>
       </c>
       <c r="J398" s="1" t="s">
@@ -10744,19 +10759,19 @@
       </c>
     </row>
     <row r="399" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A399" s="4" t="s">
+      <c r="A399" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B399" s="4" t="s">
+      <c r="B399" s="3" t="s">
         <v>188</v>
       </c>
       <c r="C399" t="s">
         <v>477</v>
       </c>
-      <c r="D399" s="7" t="s">
+      <c r="D399" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="I399" s="5">
+      <c r="I399" s="4">
         <v>297</v>
       </c>
       <c r="J399" s="1" t="s">
@@ -10764,19 +10779,19 @@
       </c>
     </row>
     <row r="400" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A400" s="4" t="s">
+      <c r="A400" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B400" s="4" t="s">
+      <c r="B400" s="3" t="s">
         <v>180</v>
       </c>
       <c r="C400" t="s">
         <v>477</v>
       </c>
-      <c r="D400" s="7" t="s">
+      <c r="D400" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="I400" s="5">
+      <c r="I400" s="4">
         <v>969</v>
       </c>
       <c r="J400" s="1" t="s">
@@ -10784,19 +10799,19 @@
       </c>
     </row>
     <row r="401" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A401" s="4" t="s">
+      <c r="A401" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B401" s="4" t="s">
+      <c r="B401" s="3" t="s">
         <v>231</v>
       </c>
       <c r="C401" t="s">
         <v>477</v>
       </c>
-      <c r="D401" s="7" t="s">
+      <c r="D401" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="I401" s="5">
+      <c r="I401" s="4">
         <v>1660</v>
       </c>
       <c r="J401" s="1" t="s">
@@ -10804,19 +10819,19 @@
       </c>
     </row>
     <row r="402" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A402" s="4" t="s">
+      <c r="A402" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B402" s="4" t="s">
+      <c r="B402" s="3" t="s">
         <v>233</v>
       </c>
       <c r="C402" t="s">
         <v>477</v>
       </c>
-      <c r="D402" s="7" t="s">
+      <c r="D402" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="I402" s="5">
+      <c r="I402" s="4">
         <v>97</v>
       </c>
       <c r="J402" s="1" t="s">
@@ -10824,19 +10839,19 @@
       </c>
     </row>
     <row r="403" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A403" s="4" t="s">
+      <c r="A403" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B403" s="4" t="s">
+      <c r="B403" s="3" t="s">
         <v>186</v>
       </c>
       <c r="C403" t="s">
         <v>477</v>
       </c>
-      <c r="D403" s="7" t="s">
+      <c r="D403" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="I403" s="5">
+      <c r="I403" s="4">
         <v>1</v>
       </c>
       <c r="J403" s="1" t="s">
@@ -10844,19 +10859,19 @@
       </c>
     </row>
     <row r="404" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A404" s="4" t="s">
+      <c r="A404" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B404" s="4" t="s">
+      <c r="B404" s="3" t="s">
         <v>204</v>
       </c>
       <c r="C404" t="s">
         <v>477</v>
       </c>
-      <c r="D404" s="7" t="s">
+      <c r="D404" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="I404" s="5">
+      <c r="I404" s="4">
         <v>19</v>
       </c>
       <c r="J404" s="1" t="s">
@@ -10864,19 +10879,19 @@
       </c>
     </row>
     <row r="405" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A405" s="4" t="s">
+      <c r="A405" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B405" s="4" t="s">
+      <c r="B405" s="3" t="s">
         <v>349</v>
       </c>
       <c r="C405" t="s">
         <v>477</v>
       </c>
-      <c r="D405" s="7" t="s">
+      <c r="D405" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="I405" s="5">
+      <c r="I405" s="4">
         <v>3</v>
       </c>
       <c r="J405" s="1" t="s">
@@ -10884,19 +10899,19 @@
       </c>
     </row>
     <row r="406" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A406" s="4" t="s">
+      <c r="A406" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="B406" s="4" t="s">
+      <c r="B406" s="3" t="s">
         <v>516</v>
       </c>
       <c r="C406" t="s">
         <v>477</v>
       </c>
-      <c r="D406" s="7" t="s">
+      <c r="D406" s="6" t="s">
         <v>586</v>
       </c>
-      <c r="I406" s="5">
+      <c r="I406" s="4">
         <v>7</v>
       </c>
       <c r="J406" s="1" t="s">
@@ -10904,19 +10919,19 @@
       </c>
     </row>
     <row r="407" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A407" s="4" t="s">
+      <c r="A407" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="B407" s="4" t="s">
+      <c r="B407" s="3" t="s">
         <v>518</v>
       </c>
       <c r="C407" t="s">
         <v>477</v>
       </c>
-      <c r="D407" s="7" t="s">
+      <c r="D407" s="6" t="s">
         <v>587</v>
       </c>
-      <c r="I407" s="5">
+      <c r="I407" s="4">
         <v>0</v>
       </c>
       <c r="J407" s="1" t="s">
@@ -10924,19 +10939,19 @@
       </c>
     </row>
     <row r="408" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="4" t="s">
+      <c r="A408" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B408" s="4" t="s">
+      <c r="B408" s="3" t="s">
         <v>220</v>
       </c>
       <c r="C408" t="s">
         <v>477</v>
       </c>
-      <c r="D408" s="7" t="s">
+      <c r="D408" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="I408" s="5">
+      <c r="I408" s="4">
         <v>100</v>
       </c>
       <c r="J408" s="1" t="s">
@@ -10944,19 +10959,19 @@
       </c>
     </row>
     <row r="409" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A409" s="4" t="s">
+      <c r="A409" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="B409" s="4" t="s">
+      <c r="B409" s="3" t="s">
         <v>520</v>
       </c>
       <c r="C409" t="s">
         <v>477</v>
       </c>
-      <c r="D409" s="7" t="s">
+      <c r="D409" s="6" t="s">
         <v>588</v>
       </c>
-      <c r="I409" s="5">
+      <c r="I409" s="4">
         <v>0</v>
       </c>
       <c r="J409" s="1" t="s">
@@ -10964,19 +10979,19 @@
       </c>
     </row>
     <row r="410" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A410" s="4" t="s">
+      <c r="A410" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B410" s="4" t="s">
+      <c r="B410" s="3" t="s">
         <v>195</v>
       </c>
       <c r="C410" t="s">
         <v>477</v>
       </c>
-      <c r="D410" s="7" t="s">
+      <c r="D410" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="I410" s="5">
+      <c r="I410" s="4">
         <v>0</v>
       </c>
       <c r="J410" s="1" t="s">
@@ -10984,19 +10999,19 @@
       </c>
     </row>
     <row r="411" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A411" s="4" t="s">
+      <c r="A411" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B411" s="4" t="s">
+      <c r="B411" s="3" t="s">
         <v>190</v>
       </c>
       <c r="C411" t="s">
         <v>477</v>
       </c>
-      <c r="D411" s="7" t="s">
+      <c r="D411" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="I411" s="5">
+      <c r="I411" s="4">
         <v>284</v>
       </c>
       <c r="J411" s="1" t="s">
@@ -11004,19 +11019,19 @@
       </c>
     </row>
     <row r="412" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A412" s="4" t="s">
+      <c r="A412" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B412" s="4" t="s">
+      <c r="B412" s="3" t="s">
         <v>205</v>
       </c>
       <c r="C412" t="s">
         <v>477</v>
       </c>
-      <c r="D412" s="7" t="s">
+      <c r="D412" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="I412" s="5">
+      <c r="I412" s="4">
         <v>6</v>
       </c>
       <c r="J412" s="1" t="s">
@@ -11024,19 +11039,19 @@
       </c>
     </row>
     <row r="413" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A413" s="4" t="s">
+      <c r="A413" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B413" s="4" t="s">
+      <c r="B413" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C413" t="s">
         <v>477</v>
       </c>
-      <c r="D413" s="7" t="s">
+      <c r="D413" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="I413" s="5">
+      <c r="I413" s="4">
         <v>551</v>
       </c>
       <c r="J413" s="1" t="s">
@@ -11044,19 +11059,19 @@
       </c>
     </row>
     <row r="414" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A414" s="4" t="s">
+      <c r="A414" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B414" s="4" t="s">
+      <c r="B414" s="3" t="s">
         <v>202</v>
       </c>
       <c r="C414" t="s">
         <v>477</v>
       </c>
-      <c r="D414" s="7" t="s">
+      <c r="D414" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="I414" s="5">
+      <c r="I414" s="4">
         <v>10</v>
       </c>
       <c r="J414" s="1" t="s">
@@ -11064,19 +11079,19 @@
       </c>
     </row>
     <row r="415" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A415" s="4" t="s">
+      <c r="A415" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="B415" s="4" t="s">
+      <c r="B415" s="3" t="s">
         <v>522</v>
       </c>
       <c r="C415" t="s">
         <v>477</v>
       </c>
-      <c r="D415" s="7" t="s">
+      <c r="D415" s="6" t="s">
         <v>589</v>
       </c>
-      <c r="I415" s="5">
+      <c r="I415" s="4">
         <v>8</v>
       </c>
       <c r="J415" s="1" t="s">
@@ -11084,19 +11099,19 @@
       </c>
     </row>
     <row r="416" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A416" s="4" t="s">
+      <c r="A416" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="B416" s="4" t="s">
+      <c r="B416" s="3" t="s">
         <v>524</v>
       </c>
       <c r="C416" t="s">
         <v>477</v>
       </c>
-      <c r="D416" s="7" t="s">
+      <c r="D416" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="I416" s="5">
+      <c r="I416" s="4">
         <v>3</v>
       </c>
       <c r="J416" s="1" t="s">
@@ -11104,19 +11119,19 @@
       </c>
     </row>
     <row r="417" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A417" s="4" t="s">
+      <c r="A417" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B417" s="4" t="s">
+      <c r="B417" s="3" t="s">
         <v>206</v>
       </c>
       <c r="C417" t="s">
         <v>477</v>
       </c>
-      <c r="D417" s="7" t="s">
+      <c r="D417" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="I417" s="5">
+      <c r="I417" s="4">
         <v>9</v>
       </c>
       <c r="J417" s="1" t="s">
@@ -11124,19 +11139,19 @@
       </c>
     </row>
     <row r="418" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A418" s="4" t="s">
+      <c r="A418" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B418" s="4" t="s">
+      <c r="B418" s="3" t="s">
         <v>224</v>
       </c>
       <c r="C418" t="s">
         <v>477</v>
       </c>
-      <c r="D418" s="7" t="s">
+      <c r="D418" s="6" t="s">
         <v>591</v>
       </c>
-      <c r="I418" s="5">
+      <c r="I418" s="4">
         <v>6</v>
       </c>
       <c r="J418" s="1" t="s">
@@ -11144,19 +11159,19 @@
       </c>
     </row>
     <row r="419" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A419" s="4" t="s">
+      <c r="A419" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="B419" s="4" t="s">
+      <c r="B419" s="3" t="s">
         <v>354</v>
       </c>
       <c r="C419" t="s">
         <v>477</v>
       </c>
-      <c r="D419" s="7" t="s">
+      <c r="D419" s="6" t="s">
         <v>592</v>
       </c>
-      <c r="I419" s="5">
+      <c r="I419" s="4">
         <v>3</v>
       </c>
       <c r="J419" s="1" t="s">
@@ -11164,19 +11179,19 @@
       </c>
     </row>
     <row r="420" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A420" s="4" t="s">
+      <c r="A420" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="B420" s="4" t="s">
+      <c r="B420" s="3" t="s">
         <v>527</v>
       </c>
       <c r="C420" t="s">
         <v>477</v>
       </c>
-      <c r="D420" s="7" t="s">
+      <c r="D420" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="I420" s="5">
+      <c r="I420" s="4">
         <v>6</v>
       </c>
       <c r="J420" s="1" t="s">
@@ -11184,19 +11199,19 @@
       </c>
     </row>
     <row r="421" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="4" t="s">
+      <c r="A421" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="B421" s="4" t="s">
+      <c r="B421" s="3" t="s">
         <v>529</v>
       </c>
       <c r="C421" t="s">
         <v>477</v>
       </c>
-      <c r="D421" s="7" t="s">
+      <c r="D421" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="I421" s="5">
+      <c r="I421" s="4">
         <v>5</v>
       </c>
       <c r="J421" s="1" t="s">
@@ -11204,19 +11219,19 @@
       </c>
     </row>
     <row r="422" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A422" s="4" t="s">
+      <c r="A422" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="B422" s="4" t="s">
+      <c r="B422" s="3" t="s">
         <v>531</v>
       </c>
       <c r="C422" t="s">
         <v>477</v>
       </c>
-      <c r="D422" s="7" t="s">
+      <c r="D422" s="6" t="s">
         <v>595</v>
       </c>
-      <c r="I422" s="5">
+      <c r="I422" s="4">
         <v>4</v>
       </c>
       <c r="J422" s="1" t="s">
@@ -11224,19 +11239,19 @@
       </c>
     </row>
     <row r="423" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="4" t="s">
+      <c r="A423" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="B423" s="4" t="s">
+      <c r="B423" s="3" t="s">
         <v>533</v>
       </c>
       <c r="C423" t="s">
         <v>477</v>
       </c>
-      <c r="D423" s="7" t="s">
+      <c r="D423" s="6" t="s">
         <v>596</v>
       </c>
-      <c r="I423" s="5">
+      <c r="I423" s="4">
         <v>3</v>
       </c>
       <c r="J423" s="1" t="s">
@@ -11244,19 +11259,19 @@
       </c>
     </row>
     <row r="424" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A424" s="4" t="s">
+      <c r="A424" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="B424" s="4" t="s">
+      <c r="B424" s="3" t="s">
         <v>535</v>
       </c>
       <c r="C424" t="s">
         <v>477</v>
       </c>
-      <c r="D424" s="7" t="s">
+      <c r="D424" s="6" t="s">
         <v>597</v>
       </c>
-      <c r="I424" s="5">
+      <c r="I424" s="4">
         <v>7</v>
       </c>
       <c r="J424" s="1" t="s">
@@ -11264,19 +11279,19 @@
       </c>
     </row>
     <row r="425" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A425" s="4" t="s">
+      <c r="A425" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="B425" s="4" t="s">
+      <c r="B425" s="3" t="s">
         <v>537</v>
       </c>
       <c r="C425" t="s">
         <v>477</v>
       </c>
-      <c r="D425" s="7" t="s">
+      <c r="D425" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="I425" s="5">
+      <c r="I425" s="4">
         <v>3</v>
       </c>
       <c r="J425" s="1" t="s">
@@ -11284,19 +11299,19 @@
       </c>
     </row>
     <row r="426" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A426" s="4" t="s">
+      <c r="A426" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="B426" s="4" t="s">
+      <c r="B426" s="3" t="s">
         <v>539</v>
       </c>
       <c r="C426" t="s">
         <v>477</v>
       </c>
-      <c r="D426" s="7" t="s">
+      <c r="D426" s="6" t="s">
         <v>599</v>
       </c>
-      <c r="I426" s="5">
+      <c r="I426" s="4">
         <v>0</v>
       </c>
       <c r="J426" s="1" t="s">
@@ -11304,19 +11319,19 @@
       </c>
     </row>
     <row r="427" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A427" s="4" t="s">
+      <c r="A427" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="B427" s="4" t="s">
+      <c r="B427" s="3" t="s">
         <v>541</v>
       </c>
       <c r="C427" t="s">
         <v>477</v>
       </c>
-      <c r="D427" s="7" t="s">
+      <c r="D427" s="6" t="s">
         <v>600</v>
       </c>
-      <c r="I427" s="5">
+      <c r="I427" s="4">
         <v>1</v>
       </c>
       <c r="J427" s="1" t="s">
@@ -11324,19 +11339,19 @@
       </c>
     </row>
     <row r="428" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A428" s="4" t="s">
+      <c r="A428" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="B428" s="4" t="s">
+      <c r="B428" s="3" t="s">
         <v>543</v>
       </c>
       <c r="C428" t="s">
         <v>477</v>
       </c>
-      <c r="D428" s="7" t="s">
+      <c r="D428" s="6" t="s">
         <v>601</v>
       </c>
-      <c r="I428" s="5">
+      <c r="I428" s="4">
         <v>0</v>
       </c>
       <c r="J428" s="1" t="s">
@@ -11344,19 +11359,19 @@
       </c>
     </row>
     <row r="429" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A429" s="4" t="s">
+      <c r="A429" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="B429" s="4" t="s">
+      <c r="B429" s="3" t="s">
         <v>545</v>
       </c>
       <c r="C429" t="s">
         <v>477</v>
       </c>
-      <c r="D429" s="7" t="s">
+      <c r="D429" s="6" t="s">
         <v>602</v>
       </c>
-      <c r="I429" s="5">
+      <c r="I429" s="4">
         <v>3</v>
       </c>
       <c r="J429" s="1" t="s">
@@ -11364,19 +11379,19 @@
       </c>
     </row>
     <row r="430" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A430" s="4" t="s">
+      <c r="A430" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B430" s="4" t="s">
+      <c r="B430" s="3" t="s">
         <v>232</v>
       </c>
       <c r="C430" t="s">
         <v>477</v>
       </c>
-      <c r="D430" s="7" t="s">
+      <c r="D430" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="I430" s="5">
+      <c r="I430" s="4">
         <v>19</v>
       </c>
       <c r="J430" s="1" t="s">
@@ -11384,19 +11399,19 @@
       </c>
     </row>
     <row r="431" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A431" s="4" t="s">
+      <c r="A431" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="B431" s="4" t="s">
+      <c r="B431" s="3" t="s">
         <v>547</v>
       </c>
       <c r="C431" t="s">
         <v>477</v>
       </c>
-      <c r="D431" s="7" t="s">
+      <c r="D431" s="6" t="s">
         <v>603</v>
       </c>
-      <c r="I431" s="5">
+      <c r="I431" s="4">
         <v>0</v>
       </c>
       <c r="J431" s="1" t="s">
@@ -11404,19 +11419,19 @@
       </c>
     </row>
     <row r="432" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A432" s="4" t="s">
+      <c r="A432" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="B432" s="4" t="s">
+      <c r="B432" s="3" t="s">
         <v>549</v>
       </c>
       <c r="C432" t="s">
         <v>477</v>
       </c>
-      <c r="D432" s="7" t="s">
+      <c r="D432" s="6" t="s">
         <v>604</v>
       </c>
-      <c r="I432" s="5">
+      <c r="I432" s="4">
         <v>3</v>
       </c>
       <c r="J432" s="1" t="s">
@@ -11424,19 +11439,19 @@
       </c>
     </row>
     <row r="433" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A433" s="4" t="s">
+      <c r="A433" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="B433" s="4" t="s">
+      <c r="B433" s="3" t="s">
         <v>551</v>
       </c>
       <c r="C433" t="s">
         <v>477</v>
       </c>
-      <c r="D433" s="7" t="s">
+      <c r="D433" s="6" t="s">
         <v>605</v>
       </c>
-      <c r="I433" s="5">
+      <c r="I433" s="4">
         <v>0</v>
       </c>
       <c r="J433" s="1" t="s">
@@ -11444,19 +11459,19 @@
       </c>
     </row>
     <row r="434" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A434" s="4" t="s">
+      <c r="A434" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="B434" s="4" t="s">
+      <c r="B434" s="3" t="s">
         <v>553</v>
       </c>
       <c r="C434" t="s">
         <v>477</v>
       </c>
-      <c r="D434" s="7" t="s">
+      <c r="D434" s="6" t="s">
         <v>606</v>
       </c>
-      <c r="I434" s="5">
+      <c r="I434" s="4">
         <v>1</v>
       </c>
       <c r="J434" s="1" t="s">
@@ -11464,19 +11479,19 @@
       </c>
     </row>
     <row r="435" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A435" s="4" t="s">
+      <c r="A435" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="B435" s="4" t="s">
+      <c r="B435" s="3" t="s">
         <v>555</v>
       </c>
       <c r="C435" t="s">
         <v>477</v>
       </c>
-      <c r="D435" s="7" t="s">
+      <c r="D435" s="6" t="s">
         <v>607</v>
       </c>
-      <c r="I435" s="5">
+      <c r="I435" s="4">
         <v>2</v>
       </c>
       <c r="J435" s="1" t="s">
@@ -11484,19 +11499,19 @@
       </c>
     </row>
     <row r="436" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A436" s="4" t="s">
+      <c r="A436" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="B436" s="4" t="s">
+      <c r="B436" s="3" t="s">
         <v>557</v>
       </c>
       <c r="C436" t="s">
         <v>477</v>
       </c>
-      <c r="D436" s="7" t="s">
+      <c r="D436" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="I436" s="5">
+      <c r="I436" s="4">
         <v>1</v>
       </c>
       <c r="J436" s="1" t="s">
@@ -11504,19 +11519,19 @@
       </c>
     </row>
     <row r="437" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A437" s="4" t="s">
+      <c r="A437" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B437" s="4" t="s">
+      <c r="B437" s="3" t="s">
         <v>178</v>
       </c>
       <c r="C437" t="s">
         <v>477</v>
       </c>
-      <c r="D437" s="7" t="s">
+      <c r="D437" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="I437" s="5">
+      <c r="I437" s="4">
         <v>1786</v>
       </c>
       <c r="J437" s="1" t="s">
@@ -11524,19 +11539,19 @@
       </c>
     </row>
     <row r="438" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A438" s="4" t="s">
+      <c r="A438" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="B438" s="4" t="s">
+      <c r="B438" s="3" t="s">
         <v>559</v>
       </c>
       <c r="C438" t="s">
         <v>477</v>
       </c>
-      <c r="D438" s="7" t="s">
+      <c r="D438" s="6" t="s">
         <v>609</v>
       </c>
-      <c r="I438" s="5">
+      <c r="I438" s="4">
         <v>0</v>
       </c>
       <c r="J438" s="1" t="s">
@@ -11544,19 +11559,19 @@
       </c>
     </row>
     <row r="439" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A439" s="4" t="s">
+      <c r="A439" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="B439" s="4" t="s">
+      <c r="B439" s="3" t="s">
         <v>561</v>
       </c>
       <c r="C439" t="s">
         <v>477</v>
       </c>
-      <c r="D439" s="7" t="s">
+      <c r="D439" s="6" t="s">
         <v>610</v>
       </c>
-      <c r="I439" s="5">
+      <c r="I439" s="4">
         <v>0</v>
       </c>
       <c r="J439" s="1" t="s">
@@ -11564,19 +11579,19 @@
       </c>
     </row>
     <row r="440" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A440" s="4" t="s">
+      <c r="A440" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="B440" s="4" t="s">
+      <c r="B440" s="3" t="s">
         <v>563</v>
       </c>
       <c r="C440" t="s">
         <v>477</v>
       </c>
-      <c r="D440" s="7" t="s">
+      <c r="D440" s="6" t="s">
         <v>611</v>
       </c>
-      <c r="I440" s="5">
+      <c r="I440" s="4">
         <v>0</v>
       </c>
       <c r="J440" s="1" t="s">
@@ -11584,19 +11599,19 @@
       </c>
     </row>
     <row r="441" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A441" s="4" t="s">
+      <c r="A441" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="B441" s="4" t="s">
+      <c r="B441" s="3" t="s">
         <v>352</v>
       </c>
       <c r="C441" t="s">
         <v>477</v>
       </c>
-      <c r="D441" s="7" t="s">
+      <c r="D441" s="6" t="s">
         <v>612</v>
       </c>
-      <c r="I441" s="5">
+      <c r="I441" s="4">
         <v>3</v>
       </c>
       <c r="J441" s="1" t="s">
@@ -11604,19 +11619,19 @@
       </c>
     </row>
     <row r="442" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A442" s="4" t="s">
+      <c r="A442" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="B442" s="4" t="s">
+      <c r="B442" s="3" t="s">
         <v>566</v>
       </c>
       <c r="C442" t="s">
         <v>477</v>
       </c>
-      <c r="D442" s="7" t="s">
+      <c r="D442" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="I442" s="5">
+      <c r="I442" s="4">
         <v>1</v>
       </c>
       <c r="J442" s="1" t="s">
@@ -11624,19 +11639,19 @@
       </c>
     </row>
     <row r="443" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A443" s="4" t="s">
+      <c r="A443" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B443" s="4" t="s">
+      <c r="B443" s="3" t="s">
         <v>568</v>
       </c>
       <c r="C443" t="s">
         <v>477</v>
       </c>
-      <c r="D443" s="7" t="s">
+      <c r="D443" s="6" t="s">
         <v>614</v>
       </c>
-      <c r="I443" s="5">
+      <c r="I443" s="4">
         <v>1</v>
       </c>
       <c r="J443" s="1" t="s">
@@ -11644,19 +11659,19 @@
       </c>
     </row>
     <row r="444" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A444" s="4" t="s">
+      <c r="A444" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="B444" s="4" t="s">
+      <c r="B444" s="3" t="s">
         <v>570</v>
       </c>
       <c r="C444" t="s">
         <v>477</v>
       </c>
-      <c r="D444" s="7" t="s">
+      <c r="D444" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="I444" s="5">
+      <c r="I444" s="4">
         <v>3</v>
       </c>
       <c r="J444" s="1" t="s">
@@ -11664,19 +11679,19 @@
       </c>
     </row>
     <row r="445" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A445" s="4" t="s">
+      <c r="A445" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="B445" s="4" t="s">
+      <c r="B445" s="3" t="s">
         <v>572</v>
       </c>
       <c r="C445" t="s">
         <v>477</v>
       </c>
-      <c r="D445" s="7" t="s">
+      <c r="D445" s="6" t="s">
         <v>616</v>
       </c>
-      <c r="I445" s="5">
+      <c r="I445" s="4">
         <v>0</v>
       </c>
       <c r="J445" s="1" t="s">
@@ -11684,19 +11699,19 @@
       </c>
     </row>
     <row r="446" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A446" s="4" t="s">
+      <c r="A446" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="B446" s="4" t="s">
+      <c r="B446" s="3" t="s">
         <v>574</v>
       </c>
       <c r="C446" t="s">
         <v>477</v>
       </c>
-      <c r="D446" s="7" t="s">
+      <c r="D446" s="6" t="s">
         <v>617</v>
       </c>
-      <c r="I446" s="5">
+      <c r="I446" s="4">
         <v>1</v>
       </c>
       <c r="J446" s="1" t="s">
@@ -11704,19 +11719,19 @@
       </c>
     </row>
     <row r="447" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A447" s="4" t="s">
+      <c r="A447" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B447" s="4" t="s">
+      <c r="B447" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C447" t="s">
         <v>477</v>
       </c>
-      <c r="D447" s="7" t="s">
+      <c r="D447" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="I447" s="5">
+      <c r="I447" s="4">
         <v>221</v>
       </c>
       <c r="J447" s="1" t="s">
@@ -11724,19 +11739,19 @@
       </c>
     </row>
     <row r="448" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A448" s="4" t="s">
+      <c r="A448" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="B448" s="4" t="s">
+      <c r="B448" s="3" t="s">
         <v>576</v>
       </c>
       <c r="C448" t="s">
         <v>477</v>
       </c>
-      <c r="D448" s="7" t="s">
+      <c r="D448" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="I448" s="5">
+      <c r="I448" s="4">
         <v>0</v>
       </c>
       <c r="J448" s="1" t="s">
@@ -11744,19 +11759,19 @@
       </c>
     </row>
     <row r="449" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A449" s="4" t="s">
+      <c r="A449" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B449" s="4" t="s">
+      <c r="B449" s="3" t="s">
         <v>209</v>
       </c>
       <c r="C449" t="s">
         <v>477</v>
       </c>
-      <c r="D449" s="7" t="s">
+      <c r="D449" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="I449" s="5">
+      <c r="I449" s="4">
         <v>7</v>
       </c>
       <c r="J449" s="1" t="s">
@@ -11764,19 +11779,19 @@
       </c>
     </row>
     <row r="450" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A450" s="4" t="s">
+      <c r="A450" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="B450" s="4" t="s">
+      <c r="B450" s="3" t="s">
         <v>578</v>
       </c>
       <c r="C450" t="s">
         <v>477</v>
       </c>
-      <c r="D450" s="7" t="s">
+      <c r="D450" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="I450" s="5">
+      <c r="I450" s="4">
         <v>4</v>
       </c>
       <c r="J450" s="1" t="s">
@@ -11784,19 +11799,19 @@
       </c>
     </row>
     <row r="451" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A451" s="4" t="s">
+      <c r="A451" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="B451" s="4" t="s">
+      <c r="B451" s="3" t="s">
         <v>580</v>
       </c>
       <c r="C451" t="s">
         <v>477</v>
       </c>
-      <c r="D451" s="7" t="s">
+      <c r="D451" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="I451" s="5">
+      <c r="I451" s="4">
         <v>3</v>
       </c>
       <c r="J451" s="1" t="s">
@@ -11804,19 +11819,19 @@
       </c>
     </row>
     <row r="452" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A452" s="4" t="s">
+      <c r="A452" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="B452" s="4" t="s">
+      <c r="B452" s="3" t="s">
         <v>582</v>
       </c>
       <c r="C452" t="s">
         <v>477</v>
       </c>
-      <c r="D452" s="7" t="s">
+      <c r="D452" s="6" t="s">
         <v>621</v>
       </c>
-      <c r="I452" s="5">
+      <c r="I452" s="4">
         <v>0</v>
       </c>
       <c r="J452" s="1" t="s">
@@ -11824,19 +11839,19 @@
       </c>
     </row>
     <row r="453" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A453" s="4" t="s">
+      <c r="A453" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="B453" s="4" t="s">
+      <c r="B453" s="3" t="s">
         <v>584</v>
       </c>
       <c r="C453" t="s">
         <v>477</v>
       </c>
-      <c r="D453" s="7" t="s">
+      <c r="D453" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="I453" s="5">
+      <c r="I453" s="4">
         <v>1</v>
       </c>
       <c r="J453" s="1" t="s">
@@ -11844,19 +11859,19 @@
       </c>
     </row>
     <row r="454" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A454" s="4" t="s">
+      <c r="A454" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B454" s="4" t="s">
+      <c r="B454" s="3" t="s">
         <v>213</v>
       </c>
       <c r="C454" t="s">
         <v>477</v>
       </c>
-      <c r="D454" s="7" t="s">
+      <c r="D454" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="I454" s="5">
+      <c r="I454" s="4">
         <v>98</v>
       </c>
       <c r="J454" s="1" t="s">
@@ -11864,19 +11879,19 @@
       </c>
     </row>
     <row r="455" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A455" s="4" t="s">
+      <c r="A455" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B455" s="4" t="s">
+      <c r="B455" s="3" t="s">
         <v>234</v>
       </c>
       <c r="C455" t="s">
         <v>477</v>
       </c>
-      <c r="D455" s="12" t="s">
+      <c r="D455" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="I455" s="5">
+      <c r="I455" s="4">
         <v>200</v>
       </c>
       <c r="J455" s="1" t="s">
@@ -11884,19 +11899,19 @@
       </c>
     </row>
     <row r="456" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A456" s="4" t="s">
+      <c r="A456" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B456" s="4" t="s">
+      <c r="B456" s="3" t="s">
         <v>248</v>
       </c>
       <c r="C456" t="s">
         <v>477</v>
       </c>
-      <c r="D456" s="7" t="s">
+      <c r="D456" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="I456" s="5">
+      <c r="I456" s="4">
         <v>212</v>
       </c>
       <c r="J456" s="1" t="s">
@@ -11904,19 +11919,19 @@
       </c>
     </row>
     <row r="457" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A457" s="4" t="s">
+      <c r="A457" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B457" s="4" t="s">
+      <c r="B457" s="3" t="s">
         <v>251</v>
       </c>
       <c r="C457" t="s">
         <v>477</v>
       </c>
-      <c r="D457" s="7" t="s">
+      <c r="D457" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="I457" s="5">
+      <c r="I457" s="4">
         <v>574</v>
       </c>
       <c r="J457" s="1" t="s">
@@ -11924,19 +11939,19 @@
       </c>
     </row>
     <row r="458" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A458" s="4" t="s">
+      <c r="A458" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B458" s="4" t="s">
+      <c r="B458" s="3" t="s">
         <v>249</v>
       </c>
       <c r="C458" t="s">
         <v>477</v>
       </c>
-      <c r="D458" s="7" t="s">
+      <c r="D458" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="I458" s="5">
+      <c r="I458" s="4">
         <v>2236</v>
       </c>
       <c r="J458" s="1" t="s">
@@ -11944,19 +11959,19 @@
       </c>
     </row>
     <row r="459" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A459" s="4" t="s">
+      <c r="A459" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B459" s="4" t="s">
+      <c r="B459" s="3" t="s">
         <v>255</v>
       </c>
       <c r="C459" t="s">
         <v>477</v>
       </c>
-      <c r="D459" s="7" t="s">
+      <c r="D459" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="I459" s="5">
+      <c r="I459" s="4">
         <v>727</v>
       </c>
       <c r="J459" s="1" t="s">
@@ -11964,19 +11979,19 @@
       </c>
     </row>
     <row r="460" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A460" s="4" t="s">
+      <c r="A460" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B460" s="4" t="s">
+      <c r="B460" s="3" t="s">
         <v>253</v>
       </c>
       <c r="C460" t="s">
         <v>477</v>
       </c>
-      <c r="D460" s="7" t="s">
+      <c r="D460" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="I460" s="5">
+      <c r="I460" s="4">
         <v>374</v>
       </c>
       <c r="J460" s="1" t="s">
@@ -11984,19 +11999,19 @@
       </c>
     </row>
     <row r="461" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A461" s="4" t="s">
+      <c r="A461" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B461" s="4" t="s">
+      <c r="B461" s="3" t="s">
         <v>254</v>
       </c>
       <c r="C461" t="s">
         <v>477</v>
       </c>
-      <c r="D461" s="7" t="s">
+      <c r="D461" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="I461" s="5">
+      <c r="I461" s="4">
         <v>931</v>
       </c>
       <c r="J461" s="1" t="s">
@@ -12004,19 +12019,19 @@
       </c>
     </row>
     <row r="462" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A462" s="4" t="s">
+      <c r="A462" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B462" s="4" t="s">
+      <c r="B462" s="3" t="s">
         <v>270</v>
       </c>
       <c r="C462" t="s">
         <v>477</v>
       </c>
-      <c r="D462" s="7" t="s">
+      <c r="D462" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="I462" s="5">
+      <c r="I462" s="4">
         <v>0</v>
       </c>
       <c r="J462" s="1" t="s">
@@ -12024,19 +12039,19 @@
       </c>
     </row>
     <row r="463" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A463" s="4" t="s">
+      <c r="A463" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B463" s="4" t="s">
+      <c r="B463" s="3" t="s">
         <v>271</v>
       </c>
       <c r="C463" t="s">
         <v>477</v>
       </c>
-      <c r="D463" s="7" t="s">
+      <c r="D463" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="I463" s="5">
+      <c r="I463" s="4">
         <v>300</v>
       </c>
       <c r="J463" s="1" t="s">
@@ -12044,19 +12059,19 @@
       </c>
     </row>
     <row r="464" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A464" s="4" t="s">
+      <c r="A464" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B464" s="4" t="s">
+      <c r="B464" s="3" t="s">
         <v>272</v>
       </c>
       <c r="C464" t="s">
         <v>477</v>
       </c>
-      <c r="D464" s="7" t="s">
+      <c r="D464" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="I464" s="5">
+      <c r="I464" s="4">
         <v>492</v>
       </c>
       <c r="J464" s="1" t="s">
@@ -12064,19 +12079,19 @@
       </c>
     </row>
     <row r="465" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A465" s="4" t="s">
+      <c r="A465" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B465" s="4" t="s">
+      <c r="B465" s="3" t="s">
         <v>273</v>
       </c>
       <c r="C465" t="s">
         <v>477</v>
       </c>
-      <c r="D465" s="7" t="s">
+      <c r="D465" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="I465" s="5">
+      <c r="I465" s="4">
         <v>159</v>
       </c>
       <c r="J465" s="1" t="s">
@@ -12084,19 +12099,19 @@
       </c>
     </row>
     <row r="466" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A466" s="4" t="s">
+      <c r="A466" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B466" s="4" t="s">
+      <c r="B466" s="3" t="s">
         <v>252</v>
       </c>
       <c r="C466" t="s">
         <v>477</v>
       </c>
-      <c r="D466" s="7" t="s">
+      <c r="D466" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="I466" s="5">
+      <c r="I466" s="4">
         <v>2019</v>
       </c>
       <c r="J466" s="1" t="s">
@@ -12104,19 +12119,19 @@
       </c>
     </row>
     <row r="467" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A467" s="4" t="s">
+      <c r="A467" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B467" s="4" t="s">
+      <c r="B467" s="3" t="s">
         <v>274</v>
       </c>
       <c r="C467" t="s">
         <v>477</v>
       </c>
-      <c r="D467" s="7" t="s">
+      <c r="D467" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="I467" s="5">
+      <c r="I467" s="4">
         <v>310</v>
       </c>
       <c r="J467" s="1" t="s">
@@ -12124,19 +12139,19 @@
       </c>
     </row>
     <row r="468" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A468" s="4" t="s">
+      <c r="A468" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B468" s="5" t="s">
+      <c r="B468" s="4" t="s">
         <v>287</v>
       </c>
       <c r="C468" t="s">
         <v>477</v>
       </c>
-      <c r="D468" s="7" t="s">
+      <c r="D468" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="I468" s="5">
+      <c r="I468" s="4">
         <v>271</v>
       </c>
       <c r="J468" s="1" t="s">
@@ -12144,19 +12159,19 @@
       </c>
     </row>
     <row r="469" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A469" s="4" t="s">
+      <c r="A469" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B469" s="5" t="s">
+      <c r="B469" s="4" t="s">
         <v>290</v>
       </c>
       <c r="C469" t="s">
         <v>477</v>
       </c>
-      <c r="D469" s="7" t="s">
+      <c r="D469" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="I469" s="5">
+      <c r="I469" s="4">
         <v>320</v>
       </c>
       <c r="J469" s="1" t="s">
@@ -12164,19 +12179,19 @@
       </c>
     </row>
     <row r="470" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A470" s="4" t="s">
+      <c r="A470" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B470" s="5" t="s">
+      <c r="B470" s="4" t="s">
         <v>292</v>
       </c>
       <c r="C470" t="s">
         <v>477</v>
       </c>
-      <c r="D470" s="7" t="s">
+      <c r="D470" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="I470" s="5">
+      <c r="I470" s="4">
         <v>0</v>
       </c>
       <c r="J470" s="1" t="s">
@@ -12184,19 +12199,19 @@
       </c>
     </row>
     <row r="471" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A471" s="4" t="s">
+      <c r="A471" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B471" s="5" t="s">
+      <c r="B471" s="4" t="s">
         <v>293</v>
       </c>
       <c r="C471" t="s">
         <v>477</v>
       </c>
-      <c r="D471" s="7" t="s">
+      <c r="D471" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="I471" s="5">
+      <c r="I471" s="4">
         <v>3</v>
       </c>
       <c r="J471" s="1" t="s">
@@ -12204,19 +12219,19 @@
       </c>
     </row>
     <row r="472" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A472" s="4" t="s">
+      <c r="A472" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B472" s="5" t="s">
+      <c r="B472" s="4" t="s">
         <v>294</v>
       </c>
       <c r="C472" t="s">
         <v>477</v>
       </c>
-      <c r="D472" s="7" t="s">
+      <c r="D472" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="I472" s="5">
+      <c r="I472" s="4">
         <v>2</v>
       </c>
       <c r="J472" s="1" t="s">
@@ -12224,19 +12239,19 @@
       </c>
     </row>
     <row r="473" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A473" s="4" t="s">
+      <c r="A473" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B473" s="5" t="s">
+      <c r="B473" s="4" t="s">
         <v>295</v>
       </c>
       <c r="C473" t="s">
         <v>477</v>
       </c>
-      <c r="D473" s="7" t="s">
+      <c r="D473" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="I473" s="5">
+      <c r="I473" s="4">
         <v>1</v>
       </c>
       <c r="J473" s="1" t="s">
@@ -12244,19 +12259,19 @@
       </c>
     </row>
     <row r="474" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A474" s="4" t="s">
+      <c r="A474" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B474" s="5" t="s">
+      <c r="B474" s="4" t="s">
         <v>297</v>
       </c>
       <c r="C474" t="s">
         <v>477</v>
       </c>
-      <c r="D474" s="7" t="s">
+      <c r="D474" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="I474" s="5">
+      <c r="I474" s="4">
         <v>132</v>
       </c>
       <c r="J474" s="1" t="s">
@@ -12264,19 +12279,19 @@
       </c>
     </row>
     <row r="475" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A475" s="4" t="s">
+      <c r="A475" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B475" s="5" t="s">
+      <c r="B475" s="4" t="s">
         <v>299</v>
       </c>
       <c r="C475" t="s">
         <v>477</v>
       </c>
-      <c r="D475" s="7" t="s">
+      <c r="D475" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="I475" s="5">
+      <c r="I475" s="4">
         <v>14</v>
       </c>
       <c r="J475" s="1" t="s">
@@ -12284,19 +12299,19 @@
       </c>
     </row>
     <row r="476" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A476" s="4" t="s">
+      <c r="A476" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B476" s="5" t="s">
+      <c r="B476" s="4" t="s">
         <v>289</v>
       </c>
       <c r="C476" t="s">
         <v>477</v>
       </c>
-      <c r="D476" s="12" t="s">
+      <c r="D476" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="I476" s="5">
+      <c r="I476" s="4">
         <v>347</v>
       </c>
       <c r="J476" s="1" t="s">
@@ -12304,19 +12319,19 @@
       </c>
     </row>
     <row r="477" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A477" s="4" t="s">
+      <c r="A477" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B477" s="5" t="s">
+      <c r="B477" s="4" t="s">
         <v>288</v>
       </c>
       <c r="C477" t="s">
         <v>477</v>
       </c>
-      <c r="D477" s="7" t="s">
+      <c r="D477" s="6" t="s">
         <v>622</v>
       </c>
-      <c r="I477" s="5">
+      <c r="I477" s="4">
         <v>648</v>
       </c>
       <c r="J477" s="1" t="s">
@@ -12324,19 +12339,19 @@
       </c>
     </row>
     <row r="478" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A478" s="4" t="s">
+      <c r="A478" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B478" s="5" t="s">
+      <c r="B478" s="4" t="s">
         <v>286</v>
       </c>
       <c r="C478" t="s">
         <v>477</v>
       </c>
-      <c r="D478" s="7" t="s">
+      <c r="D478" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="I478" s="5">
+      <c r="I478" s="4">
         <v>289</v>
       </c>
       <c r="J478" s="1" t="s">
@@ -12344,19 +12359,19 @@
       </c>
     </row>
     <row r="479" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A479" s="4" t="s">
+      <c r="A479" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B479" s="5" t="s">
+      <c r="B479" s="4" t="s">
         <v>246</v>
       </c>
       <c r="C479" t="s">
         <v>477</v>
       </c>
-      <c r="D479" s="7" t="s">
+      <c r="D479" s="6" t="s">
         <v>623</v>
       </c>
-      <c r="I479" s="5">
+      <c r="I479" s="4">
         <v>657</v>
       </c>
       <c r="J479" s="1" t="s">
@@ -12364,19 +12379,19 @@
       </c>
     </row>
     <row r="480" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A480" s="4" t="s">
+      <c r="A480" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B480" s="5" t="s">
+      <c r="B480" s="4" t="s">
         <v>308</v>
       </c>
       <c r="C480" t="s">
         <v>477</v>
       </c>
-      <c r="D480" s="7" t="s">
+      <c r="D480" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="I480" s="5">
+      <c r="I480" s="4">
         <v>0</v>
       </c>
       <c r="J480" s="1" t="s">
@@ -12384,19 +12399,19 @@
       </c>
     </row>
     <row r="481" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A481" s="4" t="s">
+      <c r="A481" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B481" s="5" t="s">
+      <c r="B481" s="4" t="s">
         <v>285</v>
       </c>
       <c r="C481" t="s">
         <v>477</v>
       </c>
-      <c r="D481" s="7" t="s">
+      <c r="D481" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="I481" s="5">
+      <c r="I481" s="4">
         <v>800</v>
       </c>
       <c r="J481" s="1" t="s">
@@ -12404,19 +12419,19 @@
       </c>
     </row>
     <row r="482" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A482" s="4" t="s">
+      <c r="A482" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B482" s="5" t="s">
+      <c r="B482" s="4" t="s">
         <v>320</v>
       </c>
       <c r="C482" t="s">
         <v>477</v>
       </c>
-      <c r="D482" s="7" t="s">
+      <c r="D482" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="I482" s="5">
+      <c r="I482" s="4">
         <v>3</v>
       </c>
       <c r="J482" s="1" t="s">
@@ -12424,19 +12439,19 @@
       </c>
     </row>
     <row r="483" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A483" s="4" t="s">
+      <c r="A483" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B483" s="5" t="s">
+      <c r="B483" s="4" t="s">
         <v>304</v>
       </c>
       <c r="C483" t="s">
         <v>477</v>
       </c>
-      <c r="D483" s="7" t="s">
+      <c r="D483" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="I483" s="5">
+      <c r="I483" s="4">
         <v>256</v>
       </c>
       <c r="J483" s="1" t="s">
@@ -12444,19 +12459,19 @@
       </c>
     </row>
     <row r="484" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A484" s="4" t="s">
+      <c r="A484" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B484" s="5" t="s">
+      <c r="B484" s="4" t="s">
         <v>305</v>
       </c>
       <c r="C484" t="s">
         <v>477</v>
       </c>
-      <c r="D484" s="7" t="s">
+      <c r="D484" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="I484" s="5">
+      <c r="I484" s="4">
         <v>59</v>
       </c>
       <c r="J484" s="1" t="s">
@@ -12464,19 +12479,19 @@
       </c>
     </row>
     <row r="485" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A485" s="4" t="s">
+      <c r="A485" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B485" s="5" t="s">
+      <c r="B485" s="4" t="s">
         <v>306</v>
       </c>
       <c r="C485" t="s">
         <v>477</v>
       </c>
-      <c r="D485" s="7" t="s">
+      <c r="D485" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="I485" s="5">
+      <c r="I485" s="4">
         <v>20</v>
       </c>
       <c r="J485" s="1" t="s">
@@ -12484,19 +12499,19 @@
       </c>
     </row>
     <row r="486" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A486" s="4" t="s">
+      <c r="A486" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B486" s="5" t="s">
+      <c r="B486" s="4" t="s">
         <v>307</v>
       </c>
       <c r="C486" t="s">
         <v>477</v>
       </c>
-      <c r="D486" s="7" t="s">
+      <c r="D486" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="I486" s="5">
+      <c r="I486" s="4">
         <v>0</v>
       </c>
       <c r="J486" s="1" t="s">
@@ -12504,19 +12519,19 @@
       </c>
     </row>
     <row r="487" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A487" s="4" t="s">
+      <c r="A487" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B487" s="5" t="s">
+      <c r="B487" s="4" t="s">
         <v>323</v>
       </c>
       <c r="C487" t="s">
         <v>477</v>
       </c>
-      <c r="D487" s="7" t="s">
+      <c r="D487" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="I487" s="5">
+      <c r="I487" s="4">
         <v>3</v>
       </c>
       <c r="J487" s="1" t="s">
@@ -12524,19 +12539,19 @@
       </c>
     </row>
     <row r="488" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A488" s="4" t="s">
+      <c r="A488" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="B488" s="5" t="s">
+      <c r="B488" s="4" t="s">
         <v>356</v>
       </c>
       <c r="C488" t="s">
         <v>477</v>
       </c>
-      <c r="D488" s="7" t="s">
+      <c r="D488" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="I488" s="5">
+      <c r="I488" s="4">
         <v>3</v>
       </c>
       <c r="J488" s="1" t="s">
@@ -12544,19 +12559,19 @@
       </c>
     </row>
     <row r="489" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A489" s="4" t="s">
+      <c r="A489" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B489" s="5" t="s">
+      <c r="B489" s="4" t="s">
         <v>324</v>
       </c>
       <c r="C489" t="s">
         <v>477</v>
       </c>
-      <c r="D489" s="7" t="s">
+      <c r="D489" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="I489" s="5">
+      <c r="I489" s="4">
         <v>2</v>
       </c>
       <c r="J489" s="1" t="s">
@@ -12564,19 +12579,19 @@
       </c>
     </row>
     <row r="490" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A490" s="4" t="s">
+      <c r="A490" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B490" s="5" t="s">
+      <c r="B490" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C490" t="s">
         <v>477</v>
       </c>
-      <c r="D490" s="7" t="s">
+      <c r="D490" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="I490" s="5">
+      <c r="I490" s="4">
         <v>3</v>
       </c>
       <c r="J490" s="1" t="s">
@@ -12584,19 +12599,19 @@
       </c>
     </row>
     <row r="491" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A491" s="4" t="s">
+      <c r="A491" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B491" s="5" t="s">
+      <c r="B491" s="4" t="s">
         <v>278</v>
       </c>
       <c r="C491" t="s">
         <v>477</v>
       </c>
-      <c r="D491" s="7" t="s">
+      <c r="D491" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="I491" s="5">
+      <c r="I491" s="4">
         <v>765</v>
       </c>
       <c r="J491" s="1" t="s">
@@ -12604,19 +12619,19 @@
       </c>
     </row>
     <row r="492" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A492" s="4" t="s">
+      <c r="A492" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B492" s="5" t="s">
+      <c r="B492" s="4" t="s">
         <v>319</v>
       </c>
       <c r="C492" t="s">
         <v>477</v>
       </c>
-      <c r="D492" s="7" t="s">
+      <c r="D492" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="I492" s="5">
+      <c r="I492" s="4">
         <v>36</v>
       </c>
       <c r="J492" s="1" t="s">
@@ -12624,19 +12639,19 @@
       </c>
     </row>
     <row r="493" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A493" s="4" t="s">
+      <c r="A493" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B493" s="5" t="s">
+      <c r="B493" s="4" t="s">
         <v>301</v>
       </c>
       <c r="C493" t="s">
         <v>477</v>
       </c>
-      <c r="D493" s="7" t="s">
+      <c r="D493" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="I493" s="5">
+      <c r="I493" s="4">
         <v>16</v>
       </c>
       <c r="J493" s="1" t="s">
@@ -12644,19 +12659,19 @@
       </c>
     </row>
     <row r="494" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A494" s="4" t="s">
+      <c r="A494" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B494" s="5" t="s">
+      <c r="B494" s="4" t="s">
         <v>310</v>
       </c>
       <c r="C494" t="s">
         <v>477</v>
       </c>
-      <c r="D494" s="7" t="s">
+      <c r="D494" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="I494" s="5">
+      <c r="I494" s="4">
         <v>468</v>
       </c>
       <c r="J494" s="1" t="s">
@@ -12664,19 +12679,19 @@
       </c>
     </row>
     <row r="495" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A495" s="4" t="s">
+      <c r="A495" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B495" s="5" t="s">
+      <c r="B495" s="4" t="s">
         <v>309</v>
       </c>
       <c r="C495" t="s">
         <v>477</v>
       </c>
-      <c r="D495" s="7" t="s">
+      <c r="D495" s="6" t="s">
         <v>625</v>
       </c>
-      <c r="I495" s="5">
+      <c r="I495" s="4">
         <v>468</v>
       </c>
       <c r="J495" s="1" t="s">
@@ -12684,19 +12699,19 @@
       </c>
     </row>
     <row r="496" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A496" s="4" t="s">
+      <c r="A496" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B496" s="5" t="s">
+      <c r="B496" s="4" t="s">
         <v>321</v>
       </c>
       <c r="C496" t="s">
         <v>477</v>
       </c>
-      <c r="D496" s="7" t="s">
+      <c r="D496" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="I496" s="5">
+      <c r="I496" s="4">
         <v>233</v>
       </c>
       <c r="J496" s="1" t="s">
@@ -12704,19 +12719,19 @@
       </c>
     </row>
     <row r="497" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A497" s="4" t="s">
+      <c r="A497" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B497" s="5" t="s">
+      <c r="B497" s="4" t="s">
         <v>322</v>
       </c>
       <c r="C497" t="s">
         <v>477</v>
       </c>
-      <c r="D497" s="7" t="s">
+      <c r="D497" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="I497" s="5">
+      <c r="I497" s="4">
         <v>233</v>
       </c>
       <c r="J497" s="1" t="s">
@@ -12724,19 +12739,19 @@
       </c>
     </row>
     <row r="498" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A498" s="4" t="s">
+      <c r="A498" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B498" s="5" t="s">
+      <c r="B498" s="4" t="s">
         <v>311</v>
       </c>
       <c r="C498" t="s">
         <v>477</v>
       </c>
-      <c r="D498" s="7" t="s">
+      <c r="D498" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="I498" s="5">
+      <c r="I498" s="4">
         <v>17</v>
       </c>
       <c r="J498" s="1" t="s">
@@ -12744,19 +12759,19 @@
       </c>
     </row>
     <row r="499" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A499" s="4" t="s">
+      <c r="A499" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B499" s="5" t="s">
+      <c r="B499" s="4" t="s">
         <v>312</v>
       </c>
       <c r="C499" t="s">
         <v>477</v>
       </c>
-      <c r="D499" s="7" t="s">
+      <c r="D499" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="I499" s="5">
+      <c r="I499" s="4">
         <v>17</v>
       </c>
       <c r="J499" s="1" t="s">
@@ -12764,19 +12779,19 @@
       </c>
     </row>
     <row r="500" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A500" s="4" t="s">
+      <c r="A500" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B500" s="5" t="s">
+      <c r="B500" s="4" t="s">
         <v>313</v>
       </c>
       <c r="C500" t="s">
         <v>477</v>
       </c>
-      <c r="D500" s="7" t="s">
+      <c r="D500" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="I500" s="5">
+      <c r="I500" s="4">
         <v>36</v>
       </c>
       <c r="J500" s="1" t="s">
@@ -12784,19 +12799,19 @@
       </c>
     </row>
     <row r="501" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A501" s="4" t="s">
+      <c r="A501" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B501" s="5" t="s">
+      <c r="B501" s="4" t="s">
         <v>314</v>
       </c>
       <c r="C501" t="s">
         <v>477</v>
       </c>
-      <c r="D501" s="7" t="s">
+      <c r="D501" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="I501" s="5">
+      <c r="I501" s="4">
         <v>17</v>
       </c>
       <c r="J501" s="1" t="s">
@@ -12804,19 +12819,19 @@
       </c>
     </row>
     <row r="502" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A502" s="4" t="s">
+      <c r="A502" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B502" s="5" t="s">
+      <c r="B502" s="4" t="s">
         <v>315</v>
       </c>
       <c r="C502" t="s">
         <v>477</v>
       </c>
-      <c r="D502" s="7" t="s">
+      <c r="D502" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="I502" s="5">
+      <c r="I502" s="4">
         <v>17</v>
       </c>
       <c r="J502" s="1" t="s">
@@ -12824,19 +12839,19 @@
       </c>
     </row>
     <row r="503" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A503" s="4" t="s">
+      <c r="A503" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B503" s="5" t="s">
+      <c r="B503" s="4" t="s">
         <v>327</v>
       </c>
       <c r="C503" t="s">
         <v>477</v>
       </c>
-      <c r="D503" s="7" t="s">
+      <c r="D503" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="I503" s="5">
+      <c r="I503" s="4">
         <v>182</v>
       </c>
       <c r="J503" s="1" t="s">
@@ -12844,19 +12859,19 @@
       </c>
     </row>
     <row r="504" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A504" s="4" t="s">
+      <c r="A504" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B504" s="5" t="s">
+      <c r="B504" s="4" t="s">
         <v>328</v>
       </c>
       <c r="C504" t="s">
         <v>477</v>
       </c>
-      <c r="D504" s="7" t="s">
+      <c r="D504" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="I504" s="5">
+      <c r="I504" s="4">
         <v>82</v>
       </c>
       <c r="J504" s="1" t="s">
@@ -12864,19 +12879,19 @@
       </c>
     </row>
     <row r="505" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A505" s="4" t="s">
+      <c r="A505" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B505" s="5" t="s">
+      <c r="B505" s="4" t="s">
         <v>316</v>
       </c>
       <c r="C505" t="s">
         <v>477</v>
       </c>
-      <c r="D505" s="7" t="s">
+      <c r="D505" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="I505" s="5">
+      <c r="I505" s="4">
         <v>194</v>
       </c>
       <c r="J505" s="1" t="s">
@@ -12884,19 +12899,19 @@
       </c>
     </row>
     <row r="506" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A506" s="4" t="s">
+      <c r="A506" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B506" s="5" t="s">
+      <c r="B506" s="4" t="s">
         <v>317</v>
       </c>
       <c r="C506" t="s">
         <v>477</v>
       </c>
-      <c r="D506" s="7" t="s">
+      <c r="D506" s="6" t="s">
         <v>627</v>
       </c>
-      <c r="I506" s="5">
+      <c r="I506" s="4">
         <v>94</v>
       </c>
       <c r="J506" s="1" t="s">
@@ -12904,19 +12919,19 @@
       </c>
     </row>
     <row r="507" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A507" s="4" t="s">
+      <c r="A507" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B507" s="5" t="s">
+      <c r="B507" s="4" t="s">
         <v>318</v>
       </c>
       <c r="C507" t="s">
         <v>477</v>
       </c>
-      <c r="D507" s="7" t="s">
+      <c r="D507" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="I507" s="5">
+      <c r="I507" s="4">
         <v>94</v>
       </c>
       <c r="J507" s="1" t="s">
@@ -12924,19 +12939,19 @@
       </c>
     </row>
     <row r="508" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A508" s="8" t="s">
+      <c r="A508" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B508" s="5" t="s">
+      <c r="B508" s="4" t="s">
         <v>181</v>
       </c>
       <c r="C508" t="s">
         <v>477</v>
       </c>
-      <c r="D508" s="5" t="s">
+      <c r="D508" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="I508" s="8">
+      <c r="I508" s="7">
         <v>6</v>
       </c>
       <c r="J508" s="1" t="s">
@@ -12944,19 +12959,19 @@
       </c>
     </row>
     <row r="509" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A509" s="8" t="s">
+      <c r="A509" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B509" s="5" t="s">
+      <c r="B509" s="4" t="s">
         <v>177</v>
       </c>
       <c r="C509" t="s">
         <v>477</v>
       </c>
-      <c r="D509" s="5" t="s">
+      <c r="D509" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="I509" s="8">
+      <c r="I509" s="7">
         <v>6</v>
       </c>
       <c r="J509" s="1" t="s">
@@ -12964,19 +12979,19 @@
       </c>
     </row>
     <row r="510" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A510" s="8" t="s">
+      <c r="A510" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B510" s="5" t="s">
+      <c r="B510" s="4" t="s">
         <v>189</v>
       </c>
       <c r="C510" t="s">
         <v>477</v>
       </c>
-      <c r="D510" s="5" t="s">
+      <c r="D510" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="I510" s="8">
+      <c r="I510" s="7">
         <v>2</v>
       </c>
       <c r="J510" s="1" t="s">
@@ -12984,19 +12999,19 @@
       </c>
     </row>
     <row r="511" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A511" s="8" t="s">
+      <c r="A511" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B511" s="5" t="s">
+      <c r="B511" s="4" t="s">
         <v>176</v>
       </c>
       <c r="C511" t="s">
         <v>477</v>
       </c>
-      <c r="D511" s="5" t="s">
+      <c r="D511" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="I511" s="8">
+      <c r="I511" s="7">
         <v>38</v>
       </c>
       <c r="J511" s="1" t="s">
@@ -13004,19 +13019,19 @@
       </c>
     </row>
     <row r="512" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A512" s="8" t="s">
+      <c r="A512" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B512" s="5" t="s">
+      <c r="B512" s="4" t="s">
         <v>241</v>
       </c>
       <c r="C512" t="s">
         <v>477</v>
       </c>
-      <c r="D512" s="5" t="s">
+      <c r="D512" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="I512" s="8">
+      <c r="I512" s="7">
         <v>5</v>
       </c>
       <c r="J512" s="1" t="s">
@@ -13024,19 +13039,19 @@
       </c>
     </row>
     <row r="513" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A513" s="8" t="s">
+      <c r="A513" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B513" s="5" t="s">
+      <c r="B513" s="4" t="s">
         <v>238</v>
       </c>
       <c r="C513" t="s">
         <v>477</v>
       </c>
-      <c r="D513" s="5" t="s">
+      <c r="D513" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="I513" s="8">
+      <c r="I513" s="7">
         <v>8</v>
       </c>
       <c r="J513" s="1" t="s">
@@ -13044,19 +13059,19 @@
       </c>
     </row>
     <row r="514" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A514" s="8" t="s">
+      <c r="A514" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B514" s="5" t="s">
+      <c r="B514" s="4" t="s">
         <v>188</v>
       </c>
       <c r="C514" t="s">
         <v>477</v>
       </c>
-      <c r="D514" s="5" t="s">
+      <c r="D514" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="I514" s="8">
+      <c r="I514" s="7">
         <v>3</v>
       </c>
       <c r="J514" s="1" t="s">
@@ -13064,19 +13079,19 @@
       </c>
     </row>
     <row r="515" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A515" s="8" t="s">
+      <c r="A515" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B515" s="5" t="s">
+      <c r="B515" s="4" t="s">
         <v>225</v>
       </c>
       <c r="C515" t="s">
         <v>477</v>
       </c>
-      <c r="D515" s="5" t="s">
+      <c r="D515" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="I515" s="8">
+      <c r="I515" s="7">
         <v>4</v>
       </c>
       <c r="J515" s="1" t="s">
@@ -13084,19 +13099,19 @@
       </c>
     </row>
     <row r="516" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A516" s="8" t="s">
+      <c r="A516" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B516" s="5" t="s">
+      <c r="B516" s="4" t="s">
         <v>187</v>
       </c>
       <c r="C516" t="s">
         <v>477</v>
       </c>
-      <c r="D516" s="5" t="s">
+      <c r="D516" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="I516" s="8">
+      <c r="I516" s="7">
         <v>4</v>
       </c>
       <c r="J516" s="1" t="s">
@@ -13104,19 +13119,19 @@
       </c>
     </row>
     <row r="517" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A517" s="8" t="s">
+      <c r="A517" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B517" s="5" t="s">
+      <c r="B517" s="4" t="s">
         <v>199</v>
       </c>
       <c r="C517" t="s">
         <v>477</v>
       </c>
-      <c r="D517" s="5" t="s">
+      <c r="D517" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="I517" s="8">
+      <c r="I517" s="7">
         <v>5</v>
       </c>
       <c r="J517" s="1" t="s">
@@ -13124,19 +13139,19 @@
       </c>
     </row>
     <row r="518" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A518" s="8" t="s">
+      <c r="A518" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B518" s="5" t="s">
+      <c r="B518" s="4" t="s">
         <v>249</v>
       </c>
       <c r="C518" t="s">
         <v>477</v>
       </c>
-      <c r="D518" s="5" t="s">
+      <c r="D518" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="I518" s="8">
+      <c r="I518" s="7">
         <v>102</v>
       </c>
       <c r="J518" s="1" t="s">
@@ -13144,19 +13159,19 @@
       </c>
     </row>
     <row r="519" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A519" s="8" t="s">
+      <c r="A519" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B519" s="5" t="s">
+      <c r="B519" s="4" t="s">
         <v>218</v>
       </c>
       <c r="C519" t="s">
         <v>477</v>
       </c>
-      <c r="D519" s="5" t="s">
+      <c r="D519" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="I519" s="8">
+      <c r="I519" s="7">
         <v>3</v>
       </c>
       <c r="J519" s="1" t="s">
@@ -13164,19 +13179,19 @@
       </c>
     </row>
     <row r="520" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A520" s="8" t="s">
+      <c r="A520" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B520" s="5" t="s">
+      <c r="B520" s="4" t="s">
         <v>228</v>
       </c>
       <c r="C520" t="s">
         <v>477</v>
       </c>
-      <c r="D520" s="5" t="s">
+      <c r="D520" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="I520" s="8">
+      <c r="I520" s="7">
         <v>3</v>
       </c>
       <c r="J520" s="1" t="s">
@@ -13184,19 +13199,19 @@
       </c>
     </row>
     <row r="521" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A521" s="8" t="s">
+      <c r="A521" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B521" s="5" t="s">
+      <c r="B521" s="4" t="s">
         <v>201</v>
       </c>
       <c r="C521" t="s">
         <v>477</v>
       </c>
-      <c r="D521" s="12" t="s">
+      <c r="D521" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="I521" s="8">
+      <c r="I521" s="7">
         <v>4</v>
       </c>
       <c r="J521" s="1" t="s">
@@ -13204,19 +13219,19 @@
       </c>
     </row>
     <row r="522" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A522" s="8" t="s">
+      <c r="A522" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B522" s="5" t="s">
+      <c r="B522" s="4" t="s">
         <v>244</v>
       </c>
       <c r="C522" t="s">
         <v>477</v>
       </c>
-      <c r="D522" s="5" t="s">
+      <c r="D522" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="I522" s="8">
+      <c r="I522" s="7">
         <v>50</v>
       </c>
       <c r="J522" s="1" t="s">
@@ -13224,19 +13239,19 @@
       </c>
     </row>
     <row r="523" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A523" s="8" t="s">
+      <c r="A523" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B523" s="5" t="s">
+      <c r="B523" s="4" t="s">
         <v>178</v>
       </c>
       <c r="C523" t="s">
         <v>477</v>
       </c>
-      <c r="D523" s="5" t="s">
+      <c r="D523" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="I523" s="8">
+      <c r="I523" s="7">
         <v>64</v>
       </c>
       <c r="J523" s="1" t="s">
@@ -13244,19 +13259,19 @@
       </c>
     </row>
     <row r="524" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A524" s="8" t="s">
+      <c r="A524" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B524" s="5" t="s">
+      <c r="B524" s="4" t="s">
         <v>252</v>
       </c>
       <c r="C524" t="s">
         <v>477</v>
       </c>
-      <c r="D524" s="5" t="s">
+      <c r="D524" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="I524" s="8">
+      <c r="I524" s="7">
         <v>116</v>
       </c>
       <c r="J524" s="1" t="s">
@@ -13264,19 +13279,19 @@
       </c>
     </row>
     <row r="525" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A525" s="8" t="s">
+      <c r="A525" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B525" s="5" t="s">
+      <c r="B525" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C525" t="s">
         <v>477</v>
       </c>
-      <c r="D525" s="5" t="s">
+      <c r="D525" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="I525" s="8">
+      <c r="I525" s="7">
         <v>28</v>
       </c>
       <c r="J525" s="1" t="s">
@@ -13284,19 +13299,19 @@
       </c>
     </row>
     <row r="526" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A526" s="8" t="s">
+      <c r="A526" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B526" s="5" t="s">
+      <c r="B526" s="4" t="s">
         <v>254</v>
       </c>
       <c r="C526" t="s">
         <v>477</v>
       </c>
-      <c r="D526" s="5" t="s">
+      <c r="D526" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="I526" s="8">
+      <c r="I526" s="7">
         <v>36</v>
       </c>
       <c r="J526" s="1" t="s">
@@ -13304,19 +13319,19 @@
       </c>
     </row>
     <row r="527" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A527" s="8" t="s">
+      <c r="A527" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B527" s="5" t="s">
+      <c r="B527" s="4" t="s">
         <v>217</v>
       </c>
       <c r="C527" t="s">
         <v>477</v>
       </c>
-      <c r="D527" s="5" t="s">
+      <c r="D527" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="I527" s="8">
+      <c r="I527" s="7">
         <v>42</v>
       </c>
       <c r="J527" s="1" t="s">
@@ -13324,19 +13339,19 @@
       </c>
     </row>
     <row r="528" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A528" s="8" t="s">
+      <c r="A528" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B528" s="5" t="s">
+      <c r="B528" s="4" t="s">
         <v>235</v>
       </c>
       <c r="C528" t="s">
         <v>477</v>
       </c>
-      <c r="D528" s="5" t="s">
+      <c r="D528" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="I528" s="8">
+      <c r="I528" s="7">
         <v>47</v>
       </c>
       <c r="J528" s="1" t="s">
@@ -13344,19 +13359,19 @@
       </c>
     </row>
     <row r="529" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A529" s="8" t="s">
+      <c r="A529" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B529" s="5" t="s">
+      <c r="B529" s="4" t="s">
         <v>231</v>
       </c>
       <c r="C529" t="s">
         <v>477</v>
       </c>
-      <c r="D529" s="5" t="s">
+      <c r="D529" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="I529" s="8">
+      <c r="I529" s="7">
         <v>86</v>
       </c>
       <c r="J529" s="1" t="s">
@@ -13364,19 +13379,19 @@
       </c>
     </row>
     <row r="530" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A530" s="8" t="s">
+      <c r="A530" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B530" s="5" t="s">
+      <c r="B530" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C530" t="s">
         <v>477</v>
       </c>
-      <c r="D530" s="5" t="s">
+      <c r="D530" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="I530" s="8">
+      <c r="I530" s="7">
         <v>132</v>
       </c>
       <c r="J530" s="1" t="s">
@@ -13384,19 +13399,19 @@
       </c>
     </row>
     <row r="531" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A531" s="8" t="s">
+      <c r="A531" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B531" s="5" t="s">
+      <c r="B531" s="4" t="s">
         <v>229</v>
       </c>
       <c r="C531" t="s">
         <v>477</v>
       </c>
-      <c r="D531" s="5" t="s">
+      <c r="D531" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="I531" s="8">
+      <c r="I531" s="7">
         <v>26</v>
       </c>
       <c r="J531" s="1" t="s">
@@ -13404,19 +13419,19 @@
       </c>
     </row>
     <row r="532" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A532" s="8" t="s">
+      <c r="A532" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B532" s="5" t="s">
+      <c r="B532" s="4" t="s">
         <v>251</v>
       </c>
       <c r="C532" t="s">
         <v>477</v>
       </c>
-      <c r="D532" s="5" t="s">
+      <c r="D532" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="I532" s="8">
+      <c r="I532" s="7">
         <v>65</v>
       </c>
       <c r="J532" s="1" t="s">
@@ -13424,19 +13439,19 @@
       </c>
     </row>
     <row r="533" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A533" s="8" t="s">
+      <c r="A533" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B533" s="5" t="s">
+      <c r="B533" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C533" t="s">
         <v>477</v>
       </c>
-      <c r="D533" s="5" t="s">
+      <c r="D533" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="I533" s="8">
+      <c r="I533" s="7">
         <v>5</v>
       </c>
       <c r="J533" s="1" t="s">
@@ -13444,19 +13459,19 @@
       </c>
     </row>
     <row r="534" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A534" s="8" t="s">
+      <c r="A534" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B534" s="5" t="s">
+      <c r="B534" s="4" t="s">
         <v>191</v>
       </c>
       <c r="C534" t="s">
         <v>477</v>
       </c>
-      <c r="D534" s="5" t="s">
+      <c r="D534" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="I534" s="8">
+      <c r="I534" s="7">
         <v>3</v>
       </c>
       <c r="J534" s="1" t="s">
@@ -13464,19 +13479,19 @@
       </c>
     </row>
     <row r="535" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A535" s="8" t="s">
+      <c r="A535" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B535" s="5" t="s">
+      <c r="B535" s="4" t="s">
         <v>227</v>
       </c>
       <c r="C535" t="s">
         <v>477</v>
       </c>
-      <c r="D535" s="5" t="s">
+      <c r="D535" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="I535" s="8">
+      <c r="I535" s="7">
         <v>6</v>
       </c>
       <c r="J535" s="1" t="s">
@@ -13484,19 +13499,19 @@
       </c>
     </row>
     <row r="536" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A536" s="8" t="s">
+      <c r="A536" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B536" s="5" t="s">
+      <c r="B536" s="4" t="s">
         <v>239</v>
       </c>
       <c r="C536" t="s">
         <v>477</v>
       </c>
-      <c r="D536" s="5" t="s">
+      <c r="D536" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="I536" s="8">
+      <c r="I536" s="7">
         <v>108</v>
       </c>
       <c r="J536" s="1" t="s">
@@ -13504,19 +13519,19 @@
       </c>
     </row>
     <row r="537" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A537" s="8" t="s">
+      <c r="A537" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B537" s="5" t="s">
+      <c r="B537" s="4" t="s">
         <v>271</v>
       </c>
       <c r="C537" t="s">
         <v>477</v>
       </c>
-      <c r="D537" s="5" t="s">
+      <c r="D537" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="I537" s="8">
+      <c r="I537" s="7">
         <v>3</v>
       </c>
       <c r="J537" s="1" t="s">
@@ -13524,19 +13539,19 @@
       </c>
     </row>
     <row r="538" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A538" s="8" t="s">
+      <c r="A538" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B538" s="5" t="s">
+      <c r="B538" s="4" t="s">
         <v>184</v>
       </c>
       <c r="C538" t="s">
         <v>477</v>
       </c>
-      <c r="D538" s="5" t="s">
+      <c r="D538" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="I538" s="8">
+      <c r="I538" s="7">
         <v>20</v>
       </c>
       <c r="J538" s="1" t="s">
@@ -13544,19 +13559,19 @@
       </c>
     </row>
     <row r="539" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A539" s="8" t="s">
+      <c r="A539" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B539" s="5" t="s">
+      <c r="B539" s="4" t="s">
         <v>192</v>
       </c>
       <c r="C539" t="s">
         <v>477</v>
       </c>
-      <c r="D539" s="5" t="s">
+      <c r="D539" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="I539" s="8">
+      <c r="I539" s="7">
         <v>46</v>
       </c>
       <c r="J539" s="1" t="s">
@@ -13564,19 +13579,19 @@
       </c>
     </row>
     <row r="540" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A540" s="8" t="s">
+      <c r="A540" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B540" s="5" t="s">
+      <c r="B540" s="4" t="s">
         <v>273</v>
       </c>
       <c r="C540" t="s">
         <v>477</v>
       </c>
-      <c r="D540" s="5" t="s">
+      <c r="D540" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="I540" s="8">
+      <c r="I540" s="7">
         <v>39</v>
       </c>
       <c r="J540" s="1" t="s">
@@ -13584,19 +13599,19 @@
       </c>
     </row>
     <row r="541" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A541" s="8" t="s">
+      <c r="A541" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B541" s="5" t="s">
+      <c r="B541" s="4" t="s">
         <v>240</v>
       </c>
       <c r="C541" t="s">
         <v>477</v>
       </c>
-      <c r="D541" s="5" t="s">
+      <c r="D541" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="I541" s="8">
+      <c r="I541" s="7">
         <v>5</v>
       </c>
       <c r="J541" s="1" t="s">
@@ -13604,19 +13619,19 @@
       </c>
     </row>
     <row r="542" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A542" s="8" t="s">
+      <c r="A542" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B542" s="5" t="s">
+      <c r="B542" s="4" t="s">
         <v>289</v>
       </c>
       <c r="C542" t="s">
         <v>477</v>
       </c>
-      <c r="D542" s="5" t="s">
+      <c r="D542" s="4" t="s">
         <v>633</v>
       </c>
-      <c r="I542" s="8">
+      <c r="I542" s="7">
         <v>1</v>
       </c>
       <c r="J542" s="1" t="s">
@@ -13624,19 +13639,19 @@
       </c>
     </row>
     <row r="543" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A543" s="8" t="s">
+      <c r="A543" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B543" s="5" t="s">
+      <c r="B543" s="4" t="s">
         <v>292</v>
       </c>
       <c r="C543" t="s">
         <v>477</v>
       </c>
-      <c r="D543" s="5" t="s">
+      <c r="D543" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="I543" s="8">
+      <c r="I543" s="7">
         <v>2</v>
       </c>
       <c r="J543" s="1" t="s">
@@ -13644,19 +13659,19 @@
       </c>
     </row>
     <row r="544" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A544" s="8" t="s">
+      <c r="A544" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B544" s="5" t="s">
+      <c r="B544" s="4" t="s">
         <v>232</v>
       </c>
       <c r="C544" t="s">
         <v>477</v>
       </c>
-      <c r="D544" s="5" t="s">
+      <c r="D544" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="I544" s="8">
+      <c r="I544" s="7">
         <v>9</v>
       </c>
       <c r="J544" s="1" t="s">
@@ -13664,19 +13679,19 @@
       </c>
     </row>
     <row r="545" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A545" s="8" t="s">
+      <c r="A545" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B545" s="5" t="s">
+      <c r="B545" s="4" t="s">
         <v>270</v>
       </c>
       <c r="C545" t="s">
         <v>477</v>
       </c>
-      <c r="D545" s="5" t="s">
+      <c r="D545" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="I545" s="8">
+      <c r="I545" s="7">
         <v>16</v>
       </c>
       <c r="J545" s="1" t="s">
@@ -13684,19 +13699,19 @@
       </c>
     </row>
     <row r="546" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A546" s="8" t="s">
+      <c r="A546" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B546" s="5" t="s">
+      <c r="B546" s="4" t="s">
         <v>299</v>
       </c>
       <c r="C546" t="s">
         <v>477</v>
       </c>
-      <c r="D546" s="5" t="s">
+      <c r="D546" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="I546" s="8">
+      <c r="I546" s="7">
         <v>9</v>
       </c>
       <c r="J546" s="1" t="s">
@@ -13704,19 +13719,19 @@
       </c>
     </row>
     <row r="547" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A547" s="8" t="s">
+      <c r="A547" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="B547" s="5" t="s">
+      <c r="B547" s="4" t="s">
         <v>320</v>
       </c>
       <c r="C547" t="s">
         <v>477</v>
       </c>
-      <c r="D547" s="5" t="s">
+      <c r="D547" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="I547" s="8">
+      <c r="I547" s="7">
         <v>19</v>
       </c>
       <c r="J547" s="1" t="s">
@@ -13724,19 +13739,19 @@
       </c>
     </row>
     <row r="548" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A548" s="8" t="s">
+      <c r="A548" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B548" s="5" t="s">
+      <c r="B548" s="4" t="s">
         <v>302</v>
       </c>
       <c r="C548" t="s">
         <v>477</v>
       </c>
-      <c r="D548" s="5" t="s">
+      <c r="D548" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="I548" s="8">
+      <c r="I548" s="7">
         <v>1</v>
       </c>
       <c r="J548" s="1" t="s">
@@ -13744,19 +13759,19 @@
       </c>
     </row>
     <row r="549" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A549" s="8" t="s">
+      <c r="A549" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B549" s="5" t="s">
+      <c r="B549" s="4" t="s">
         <v>308</v>
       </c>
       <c r="C549" t="s">
         <v>477</v>
       </c>
-      <c r="D549" s="5" t="s">
+      <c r="D549" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="I549" s="8">
+      <c r="I549" s="7">
         <v>30</v>
       </c>
       <c r="J549" s="1" t="s">
@@ -13764,19 +13779,19 @@
       </c>
     </row>
     <row r="550" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A550" s="8" t="s">
+      <c r="A550" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B550" s="5" t="s">
+      <c r="B550" s="4" t="s">
         <v>285</v>
       </c>
       <c r="C550" t="s">
         <v>477</v>
       </c>
-      <c r="D550" s="5" t="s">
+      <c r="D550" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="I550" s="8">
+      <c r="I550" s="7">
         <v>50</v>
       </c>
       <c r="J550" s="1" t="s">
@@ -13784,19 +13799,19 @@
       </c>
     </row>
     <row r="551" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A551" s="8" t="s">
+      <c r="A551" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B551" s="5" t="s">
+      <c r="B551" s="4" t="s">
         <v>215</v>
       </c>
       <c r="C551" t="s">
         <v>477</v>
       </c>
-      <c r="D551" s="5" t="s">
+      <c r="D551" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="I551" s="8">
+      <c r="I551" s="7">
         <v>2</v>
       </c>
       <c r="J551" s="1" t="s">
@@ -13804,19 +13819,19 @@
       </c>
     </row>
     <row r="552" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A552" s="8" t="s">
+      <c r="A552" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B552" s="5" t="s">
+      <c r="B552" s="4" t="s">
         <v>295</v>
       </c>
       <c r="C552" t="s">
         <v>477</v>
       </c>
-      <c r="D552" s="5" t="s">
+      <c r="D552" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="I552" s="8">
+      <c r="I552" s="7">
         <v>5</v>
       </c>
       <c r="J552" s="1" t="s">
@@ -13824,19 +13839,19 @@
       </c>
     </row>
     <row r="553" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A553" s="8" t="s">
+      <c r="A553" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B553" s="5" t="s">
+      <c r="B553" s="4" t="s">
         <v>294</v>
       </c>
       <c r="C553" t="s">
         <v>477</v>
       </c>
-      <c r="D553" s="5" t="s">
+      <c r="D553" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="I553" s="8">
+      <c r="I553" s="7">
         <v>15</v>
       </c>
       <c r="J553" s="1" t="s">
@@ -13844,19 +13859,19 @@
       </c>
     </row>
     <row r="554" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A554" s="8" t="s">
+      <c r="A554" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B554" s="5" t="s">
+      <c r="B554" s="4" t="s">
         <v>272</v>
       </c>
       <c r="C554" t="s">
         <v>477</v>
       </c>
-      <c r="D554" s="5" t="s">
+      <c r="D554" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="I554" s="8">
+      <c r="I554" s="7">
         <v>10</v>
       </c>
       <c r="J554" s="1" t="s">
@@ -13864,19 +13879,19 @@
       </c>
     </row>
     <row r="555" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A555" s="6" t="s">
+      <c r="A555" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B555" s="5" t="s">
+      <c r="B555" s="4" t="s">
         <v>323</v>
       </c>
       <c r="C555" t="s">
         <v>477</v>
       </c>
-      <c r="D555" s="5" t="s">
+      <c r="D555" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="I555" s="8">
+      <c r="I555" s="7">
         <v>5</v>
       </c>
       <c r="J555" s="1" t="s">
@@ -13884,19 +13899,19 @@
       </c>
     </row>
     <row r="556" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A556" s="6" t="s">
+      <c r="A556" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="B556" s="5" t="s">
+      <c r="B556" s="4" t="s">
         <v>356</v>
       </c>
       <c r="C556" t="s">
         <v>477</v>
       </c>
-      <c r="D556" s="5" t="s">
+      <c r="D556" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="I556" s="8">
+      <c r="I556" s="7">
         <v>5</v>
       </c>
       <c r="J556" s="1" t="s">
@@ -13904,19 +13919,19 @@
       </c>
     </row>
     <row r="557" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A557" s="6" t="s">
+      <c r="A557" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B557" s="5" t="s">
+      <c r="B557" s="4" t="s">
         <v>356</v>
       </c>
       <c r="C557" t="s">
         <v>477</v>
       </c>
-      <c r="D557" s="5" t="s">
+      <c r="D557" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="I557" s="8">
+      <c r="I557" s="7">
         <v>5</v>
       </c>
       <c r="J557" s="1" t="s">
@@ -13924,19 +13939,19 @@
       </c>
     </row>
     <row r="558" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A558" s="6" t="s">
+      <c r="A558" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B558" s="5" t="s">
+      <c r="B558" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C558" t="s">
         <v>477</v>
       </c>
-      <c r="D558" s="5" t="s">
+      <c r="D558" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="I558" s="8">
+      <c r="I558" s="7">
         <v>5</v>
       </c>
       <c r="J558" s="1" t="s">
@@ -13944,19 +13959,19 @@
       </c>
     </row>
     <row r="559" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A559" s="6" t="s">
+      <c r="A559" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B559" s="5" t="s">
+      <c r="B559" s="4" t="s">
         <v>278</v>
       </c>
       <c r="C559" t="s">
         <v>477</v>
       </c>
-      <c r="D559" s="5" t="s">
+      <c r="D559" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="I559" s="8">
+      <c r="I559" s="7">
         <v>49</v>
       </c>
       <c r="J559" s="1" t="s">
@@ -13964,19 +13979,19 @@
       </c>
     </row>
     <row r="560" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A560" s="8" t="s">
+      <c r="A560" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B560" s="5" t="s">
+      <c r="B560" s="4" t="s">
         <v>185</v>
       </c>
       <c r="C560" t="s">
         <v>477</v>
       </c>
-      <c r="D560" s="5" t="s">
+      <c r="D560" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="I560" s="8">
+      <c r="I560" s="7">
         <v>3</v>
       </c>
       <c r="J560" s="1" t="s">
@@ -13984,19 +13999,19 @@
       </c>
     </row>
     <row r="561" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A561" s="8" t="s">
+      <c r="A561" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B561" s="5" t="s">
+      <c r="B561" s="4" t="s">
         <v>186</v>
       </c>
       <c r="C561" t="s">
         <v>477</v>
       </c>
-      <c r="D561" s="5" t="s">
+      <c r="D561" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="I561" s="8">
+      <c r="I561" s="7">
         <v>3</v>
       </c>
       <c r="J561" s="1" t="s">
@@ -14004,1045 +14019,1045 @@
       </c>
     </row>
     <row r="562" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A562" s="5" t="s">
+      <c r="A562" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B562" s="5" t="s">
+      <c r="B562" s="4" t="s">
         <v>217</v>
       </c>
       <c r="C562" t="s">
         <v>477</v>
       </c>
-      <c r="D562" s="5" t="s">
+      <c r="D562" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="I562" s="5">
+      <c r="I562" s="4">
         <v>78</v>
       </c>
-      <c r="J562" s="9" t="s">
+      <c r="J562" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="K562" s="10"/>
+      <c r="K562" s="9"/>
     </row>
     <row r="563" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A563" s="5" t="s">
+      <c r="A563" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B563" s="5" t="s">
+      <c r="B563" s="4" t="s">
         <v>229</v>
       </c>
       <c r="C563" t="s">
         <v>477</v>
       </c>
-      <c r="D563" s="5" t="s">
+      <c r="D563" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="I563" s="5">
+      <c r="I563" s="4">
         <v>137</v>
       </c>
-      <c r="J563" s="9" t="s">
+      <c r="J563" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="K563" s="10"/>
+      <c r="K563" s="9"/>
     </row>
     <row r="564" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A564" s="5" t="s">
+      <c r="A564" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B564" s="5" t="s">
+      <c r="B564" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C564" t="s">
         <v>477</v>
       </c>
-      <c r="D564" s="5" t="s">
+      <c r="D564" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="I564" s="5">
+      <c r="I564" s="4">
         <v>22</v>
       </c>
-      <c r="J564" s="9" t="s">
+      <c r="J564" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="K564" s="10"/>
+      <c r="K564" s="9"/>
     </row>
     <row r="565" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A565" s="5" t="s">
+      <c r="A565" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B565" s="5" t="s">
+      <c r="B565" s="4" t="s">
         <v>201</v>
       </c>
       <c r="C565" t="s">
         <v>477</v>
       </c>
-      <c r="D565" s="5" t="s">
+      <c r="D565" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="I565" s="5">
+      <c r="I565" s="4">
         <v>58</v>
       </c>
-      <c r="J565" s="9" t="s">
+      <c r="J565" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="K565" s="10"/>
+      <c r="K565" s="9"/>
     </row>
     <row r="566" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A566" s="5" t="s">
+      <c r="A566" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B566" s="5" t="s">
+      <c r="B566" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C566" t="s">
         <v>477</v>
       </c>
-      <c r="D566" s="5" t="s">
+      <c r="D566" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="I566" s="5">
+      <c r="I566" s="4">
         <v>42</v>
       </c>
-      <c r="J566" s="9" t="s">
+      <c r="J566" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="K566" s="10"/>
+      <c r="K566" s="9"/>
     </row>
     <row r="567" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A567" s="5" t="s">
+      <c r="A567" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B567" s="5" t="s">
+      <c r="B567" s="4" t="s">
         <v>230</v>
       </c>
       <c r="C567" t="s">
         <v>477</v>
       </c>
-      <c r="D567" s="5" t="s">
+      <c r="D567" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="I567" s="5">
+      <c r="I567" s="4">
         <v>61</v>
       </c>
-      <c r="J567" s="9" t="s">
+      <c r="J567" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="K567" s="10"/>
+      <c r="K567" s="9"/>
     </row>
     <row r="568" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A568" s="5" t="s">
+      <c r="A568" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B568" s="5" t="s">
+      <c r="B568" s="4" t="s">
         <v>231</v>
       </c>
       <c r="C568" t="s">
         <v>477</v>
       </c>
-      <c r="D568" s="5" t="s">
+      <c r="D568" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="I568" s="5">
+      <c r="I568" s="4">
         <v>4</v>
       </c>
-      <c r="J568" s="9" t="s">
+      <c r="J568" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="K568" s="10"/>
+      <c r="K568" s="9"/>
     </row>
     <row r="569" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A569" s="5" t="s">
+      <c r="A569" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B569" s="5" t="s">
+      <c r="B569" s="4" t="s">
         <v>249</v>
       </c>
       <c r="C569" t="s">
         <v>477</v>
       </c>
-      <c r="D569" s="5" t="s">
+      <c r="D569" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="I569" s="5">
+      <c r="I569" s="4">
         <v>28</v>
       </c>
-      <c r="J569" s="9" t="s">
+      <c r="J569" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="K569" s="10"/>
+      <c r="K569" s="9"/>
     </row>
     <row r="570" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A570" s="11" t="s">
+      <c r="A570" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B570" s="11" t="s">
+      <c r="B570" s="10" t="s">
         <v>336</v>
       </c>
       <c r="C570" t="s">
         <v>477</v>
       </c>
-      <c r="D570" s="11" t="s">
+      <c r="D570" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="I570" s="11">
+      <c r="I570" s="10">
         <v>2</v>
       </c>
-      <c r="J570" s="9" t="s">
+      <c r="J570" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K570" s="10"/>
+      <c r="K570" s="9"/>
     </row>
     <row r="571" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A571" s="11" t="s">
+      <c r="A571" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B571" s="11" t="s">
+      <c r="B571" s="10" t="s">
         <v>337</v>
       </c>
       <c r="C571" t="s">
         <v>477</v>
       </c>
-      <c r="D571" s="11" t="s">
+      <c r="D571" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="I571" s="11">
+      <c r="I571" s="10">
         <v>1</v>
       </c>
-      <c r="J571" s="9" t="s">
+      <c r="J571" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K571" s="10"/>
+      <c r="K571" s="9"/>
     </row>
     <row r="572" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A572" s="11" t="s">
+      <c r="A572" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B572" s="11" t="s">
+      <c r="B572" s="10" t="s">
         <v>332</v>
       </c>
       <c r="C572" t="s">
         <v>477</v>
       </c>
-      <c r="D572" s="11" t="s">
+      <c r="D572" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="I572" s="11">
+      <c r="I572" s="10">
         <v>1</v>
       </c>
-      <c r="J572" s="9" t="s">
+      <c r="J572" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K572" s="10"/>
+      <c r="K572" s="9"/>
     </row>
     <row r="573" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A573" s="11" t="s">
+      <c r="A573" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B573" s="11" t="s">
+      <c r="B573" s="10" t="s">
         <v>333</v>
       </c>
       <c r="C573" t="s">
         <v>477</v>
       </c>
-      <c r="D573" s="11" t="s">
+      <c r="D573" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="I573" s="11">
+      <c r="I573" s="10">
         <v>2</v>
       </c>
-      <c r="J573" s="9" t="s">
+      <c r="J573" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K573" s="10"/>
+      <c r="K573" s="9"/>
     </row>
     <row r="574" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A574" s="11" t="s">
+      <c r="A574" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B574" s="11" t="s">
+      <c r="B574" s="10" t="s">
         <v>338</v>
       </c>
       <c r="C574" t="s">
         <v>477</v>
       </c>
-      <c r="D574" s="11" t="s">
+      <c r="D574" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="I574" s="11">
+      <c r="I574" s="10">
         <v>1</v>
       </c>
-      <c r="J574" s="9" t="s">
+      <c r="J574" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K574" s="10"/>
+      <c r="K574" s="9"/>
     </row>
     <row r="575" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A575" s="11" t="s">
+      <c r="A575" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B575" s="11" t="s">
+      <c r="B575" s="10" t="s">
         <v>339</v>
       </c>
       <c r="C575" t="s">
         <v>477</v>
       </c>
-      <c r="D575" s="11" t="s">
+      <c r="D575" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="I575" s="11">
+      <c r="I575" s="10">
         <v>1</v>
       </c>
-      <c r="J575" s="9" t="s">
+      <c r="J575" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K575" s="10"/>
+      <c r="K575" s="9"/>
     </row>
     <row r="576" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A576" s="11" t="s">
+      <c r="A576" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B576" s="11" t="s">
+      <c r="B576" s="10" t="s">
         <v>186</v>
       </c>
       <c r="C576" t="s">
         <v>477</v>
       </c>
-      <c r="D576" s="11" t="s">
+      <c r="D576" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="I576" s="11">
+      <c r="I576" s="10">
         <v>1</v>
       </c>
-      <c r="J576" s="9" t="s">
+      <c r="J576" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K576" s="10"/>
+      <c r="K576" s="9"/>
     </row>
     <row r="577" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A577" s="11" t="s">
+      <c r="A577" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B577" s="11" t="s">
+      <c r="B577" s="10" t="s">
         <v>340</v>
       </c>
       <c r="C577" t="s">
         <v>477</v>
       </c>
-      <c r="D577" s="11" t="s">
+      <c r="D577" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="I577" s="11">
+      <c r="I577" s="10">
         <v>1</v>
       </c>
-      <c r="J577" s="9" t="s">
+      <c r="J577" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K577" s="10"/>
+      <c r="K577" s="9"/>
     </row>
     <row r="578" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A578" s="11" t="s">
+      <c r="A578" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B578" s="11" t="s">
+      <c r="B578" s="10" t="s">
         <v>341</v>
       </c>
       <c r="C578" t="s">
         <v>477</v>
       </c>
-      <c r="D578" s="11" t="s">
+      <c r="D578" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="I578" s="11">
+      <c r="I578" s="10">
         <v>1</v>
       </c>
-      <c r="J578" s="9" t="s">
+      <c r="J578" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K578" s="10"/>
+      <c r="K578" s="9"/>
     </row>
     <row r="579" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A579" s="11" t="s">
+      <c r="A579" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B579" s="11" t="s">
+      <c r="B579" s="10" t="s">
         <v>342</v>
       </c>
       <c r="C579" t="s">
         <v>477</v>
       </c>
-      <c r="D579" s="11" t="s">
+      <c r="D579" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="I579" s="11">
+      <c r="I579" s="10">
         <v>2</v>
       </c>
-      <c r="J579" s="9" t="s">
+      <c r="J579" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K579" s="10"/>
+      <c r="K579" s="9"/>
     </row>
     <row r="580" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A580" s="11" t="s">
+      <c r="A580" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B580" s="11" t="s">
+      <c r="B580" s="10" t="s">
         <v>343</v>
       </c>
       <c r="C580" t="s">
         <v>477</v>
       </c>
-      <c r="D580" s="11" t="s">
+      <c r="D580" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="I580" s="11">
+      <c r="I580" s="10">
         <v>1</v>
       </c>
-      <c r="J580" s="9" t="s">
+      <c r="J580" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K580" s="10"/>
+      <c r="K580" s="9"/>
     </row>
     <row r="581" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A581" s="11" t="s">
+      <c r="A581" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B581" s="11" t="s">
+      <c r="B581" s="10" t="s">
         <v>344</v>
       </c>
       <c r="C581" t="s">
         <v>477</v>
       </c>
-      <c r="D581" s="11" t="s">
+      <c r="D581" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="I581" s="11">
+      <c r="I581" s="10">
         <v>1</v>
       </c>
-      <c r="J581" s="9" t="s">
+      <c r="J581" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K581" s="10"/>
+      <c r="K581" s="9"/>
     </row>
     <row r="582" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A582" s="11" t="s">
+      <c r="A582" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B582" s="11" t="s">
+      <c r="B582" s="10" t="s">
         <v>345</v>
       </c>
       <c r="C582" t="s">
         <v>477</v>
       </c>
-      <c r="D582" s="11" t="s">
+      <c r="D582" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="I582" s="11">
+      <c r="I582" s="10">
         <v>1</v>
       </c>
-      <c r="J582" s="9" t="s">
+      <c r="J582" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K582" s="10"/>
+      <c r="K582" s="9"/>
     </row>
     <row r="583" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A583" s="11" t="s">
+      <c r="A583" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B583" s="11" t="s">
+      <c r="B583" s="10" t="s">
         <v>346</v>
       </c>
       <c r="C583" t="s">
         <v>477</v>
       </c>
-      <c r="D583" s="11" t="s">
+      <c r="D583" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="I583" s="11">
+      <c r="I583" s="10">
         <v>2</v>
       </c>
-      <c r="J583" s="9" t="s">
+      <c r="J583" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K583" s="10"/>
+      <c r="K583" s="9"/>
     </row>
     <row r="584" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A584" s="11" t="s">
+      <c r="A584" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B584" s="11" t="s">
+      <c r="B584" s="10" t="s">
         <v>347</v>
       </c>
       <c r="C584" t="s">
         <v>477</v>
       </c>
-      <c r="D584" s="11" t="s">
+      <c r="D584" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="I584" s="11">
+      <c r="I584" s="10">
         <v>1</v>
       </c>
-      <c r="J584" s="9" t="s">
+      <c r="J584" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K584" s="10"/>
+      <c r="K584" s="9"/>
     </row>
     <row r="585" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A585" s="11" t="s">
+      <c r="A585" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B585" s="11" t="s">
+      <c r="B585" s="10" t="s">
         <v>217</v>
       </c>
       <c r="C585" t="s">
         <v>477</v>
       </c>
-      <c r="D585" s="11" t="s">
+      <c r="D585" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="I585" s="11">
+      <c r="I585" s="10">
         <v>2</v>
       </c>
-      <c r="J585" s="9" t="s">
+      <c r="J585" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K585" s="10"/>
+      <c r="K585" s="9"/>
     </row>
     <row r="586" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A586" s="11" t="s">
+      <c r="A586" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B586" s="11" t="s">
+      <c r="B586" s="10" t="s">
         <v>218</v>
       </c>
       <c r="C586" t="s">
         <v>477</v>
       </c>
-      <c r="D586" s="11" t="s">
+      <c r="D586" s="10" t="s">
         <v>386</v>
       </c>
-      <c r="I586" s="11">
+      <c r="I586" s="10">
         <v>1</v>
       </c>
-      <c r="J586" s="9" t="s">
+      <c r="J586" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K586" s="10"/>
+      <c r="K586" s="9"/>
     </row>
     <row r="587" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A587" s="11" t="s">
+      <c r="A587" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B587" s="11" t="s">
+      <c r="B587" s="10" t="s">
         <v>225</v>
       </c>
       <c r="C587" t="s">
         <v>477</v>
       </c>
-      <c r="D587" s="11" t="s">
+      <c r="D587" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="I587" s="11">
+      <c r="I587" s="10">
         <v>1</v>
       </c>
-      <c r="J587" s="9" t="s">
+      <c r="J587" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K587" s="10"/>
+      <c r="K587" s="9"/>
     </row>
     <row r="588" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A588" s="11" t="s">
+      <c r="A588" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B588" s="11" t="s">
+      <c r="B588" s="10" t="s">
         <v>227</v>
       </c>
       <c r="C588" t="s">
         <v>477</v>
       </c>
-      <c r="D588" s="11" t="s">
+      <c r="D588" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="I588" s="11">
+      <c r="I588" s="10">
         <v>1</v>
       </c>
-      <c r="J588" s="9" t="s">
+      <c r="J588" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K588" s="10"/>
+      <c r="K588" s="9"/>
     </row>
     <row r="589" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A589" s="11" t="s">
+      <c r="A589" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B589" s="11" t="s">
+      <c r="B589" s="10" t="s">
         <v>350</v>
       </c>
       <c r="C589" t="s">
         <v>477</v>
       </c>
-      <c r="D589" s="11" t="s">
+      <c r="D589" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="I589" s="11">
+      <c r="I589" s="10">
         <v>2</v>
       </c>
-      <c r="J589" s="9" t="s">
+      <c r="J589" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K589" s="10"/>
+      <c r="K589" s="9"/>
     </row>
     <row r="590" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A590" s="11" t="s">
+      <c r="A590" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B590" s="11" t="s">
+      <c r="B590" s="10" t="s">
         <v>334</v>
       </c>
       <c r="C590" t="s">
         <v>477</v>
       </c>
-      <c r="D590" s="11" t="s">
+      <c r="D590" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="I590" s="11">
+      <c r="I590" s="10">
         <v>1</v>
       </c>
-      <c r="J590" s="9" t="s">
+      <c r="J590" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K590" s="10"/>
+      <c r="K590" s="9"/>
     </row>
     <row r="591" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A591" s="11" t="s">
+      <c r="A591" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B591" s="11" t="s">
+      <c r="B591" s="10" t="s">
         <v>335</v>
       </c>
       <c r="C591" t="s">
         <v>477</v>
       </c>
-      <c r="D591" s="11" t="s">
+      <c r="D591" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="I591" s="11">
+      <c r="I591" s="10">
         <v>2</v>
       </c>
-      <c r="J591" s="9" t="s">
+      <c r="J591" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K591" s="10"/>
+      <c r="K591" s="9"/>
     </row>
     <row r="592" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A592" s="11" t="s">
+      <c r="A592" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B592" s="11" t="s">
+      <c r="B592" s="10" t="s">
         <v>348</v>
       </c>
       <c r="C592" t="s">
         <v>477</v>
       </c>
-      <c r="D592" s="11" t="s">
+      <c r="D592" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="I592" s="11">
+      <c r="I592" s="10">
         <v>1</v>
       </c>
-      <c r="J592" s="9" t="s">
+      <c r="J592" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K592" s="10"/>
+      <c r="K592" s="9"/>
     </row>
     <row r="593" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A593" s="11" t="s">
+      <c r="A593" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B593" s="11" t="s">
+      <c r="B593" s="10" t="s">
         <v>235</v>
       </c>
       <c r="C593" t="s">
         <v>477</v>
       </c>
-      <c r="D593" s="11" t="s">
+      <c r="D593" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="I593" s="11">
+      <c r="I593" s="10">
         <v>1</v>
       </c>
-      <c r="J593" s="9" t="s">
+      <c r="J593" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K593" s="10"/>
+      <c r="K593" s="9"/>
     </row>
     <row r="594" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A594" s="11" t="s">
+      <c r="A594" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B594" s="11" t="s">
+      <c r="B594" s="10" t="s">
         <v>236</v>
       </c>
       <c r="C594" t="s">
         <v>477</v>
       </c>
-      <c r="D594" s="11" t="s">
+      <c r="D594" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="I594" s="11">
+      <c r="I594" s="10">
         <v>1</v>
       </c>
-      <c r="J594" s="9" t="s">
+      <c r="J594" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K594" s="10"/>
+      <c r="K594" s="9"/>
     </row>
     <row r="595" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A595" s="11" t="s">
+      <c r="A595" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B595" s="11" t="s">
+      <c r="B595" s="10" t="s">
         <v>238</v>
       </c>
       <c r="C595" t="s">
         <v>477</v>
       </c>
-      <c r="D595" s="11" t="s">
+      <c r="D595" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="I595" s="11">
+      <c r="I595" s="10">
         <v>1</v>
       </c>
-      <c r="J595" s="9" t="s">
+      <c r="J595" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K595" s="10"/>
+      <c r="K595" s="9"/>
     </row>
     <row r="596" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A596" s="11" t="s">
+      <c r="A596" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B596" s="11" t="s">
+      <c r="B596" s="10" t="s">
         <v>239</v>
       </c>
       <c r="C596" t="s">
         <v>477</v>
       </c>
-      <c r="D596" s="11" t="s">
+      <c r="D596" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="I596" s="11">
+      <c r="I596" s="10">
         <v>1</v>
       </c>
-      <c r="J596" s="9" t="s">
+      <c r="J596" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K596" s="10"/>
+      <c r="K596" s="9"/>
     </row>
     <row r="597" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A597" s="11" t="s">
+      <c r="A597" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B597" s="11" t="s">
+      <c r="B597" s="10" t="s">
         <v>240</v>
       </c>
       <c r="C597" t="s">
         <v>477</v>
       </c>
-      <c r="D597" s="11" t="s">
+      <c r="D597" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="I597" s="11">
+      <c r="I597" s="10">
         <v>1</v>
       </c>
-      <c r="J597" s="9" t="s">
+      <c r="J597" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K597" s="10"/>
+      <c r="K597" s="9"/>
     </row>
     <row r="598" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A598" s="11" t="s">
+      <c r="A598" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B598" s="11" t="s">
+      <c r="B598" s="10" t="s">
         <v>241</v>
       </c>
       <c r="C598" t="s">
         <v>477</v>
       </c>
-      <c r="D598" s="11" t="s">
+      <c r="D598" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="I598" s="11">
+      <c r="I598" s="10">
         <v>1</v>
       </c>
-      <c r="J598" s="9" t="s">
+      <c r="J598" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K598" s="10"/>
+      <c r="K598" s="9"/>
     </row>
     <row r="599" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A599" s="11" t="s">
+      <c r="A599" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B599" s="11" t="s">
+      <c r="B599" s="10" t="s">
         <v>243</v>
       </c>
       <c r="C599" t="s">
         <v>477</v>
       </c>
-      <c r="D599" s="11" t="s">
+      <c r="D599" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="I599" s="11">
+      <c r="I599" s="10">
         <v>1</v>
       </c>
-      <c r="J599" s="9" t="s">
+      <c r="J599" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K599" s="10"/>
+      <c r="K599" s="9"/>
     </row>
     <row r="600" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A600" s="11" t="s">
+      <c r="A600" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B600" s="11" t="s">
+      <c r="B600" s="10" t="s">
         <v>244</v>
       </c>
       <c r="C600" t="s">
         <v>477</v>
       </c>
-      <c r="D600" s="11" t="s">
+      <c r="D600" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="I600" s="11">
+      <c r="I600" s="10">
         <v>2</v>
       </c>
-      <c r="J600" s="9" t="s">
+      <c r="J600" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K600" s="10"/>
+      <c r="K600" s="9"/>
     </row>
     <row r="601" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A601" s="11" t="s">
+      <c r="A601" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B601" s="11" t="s">
+      <c r="B601" s="10" t="s">
         <v>245</v>
       </c>
       <c r="C601" t="s">
         <v>477</v>
       </c>
-      <c r="D601" s="11" t="s">
+      <c r="D601" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="I601" s="11">
+      <c r="I601" s="10">
         <v>1</v>
       </c>
-      <c r="J601" s="9" t="s">
+      <c r="J601" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K601" s="10"/>
+      <c r="K601" s="9"/>
     </row>
     <row r="602" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A602" s="11" t="s">
+      <c r="A602" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B602" s="11" t="s">
+      <c r="B602" s="10" t="s">
         <v>249</v>
       </c>
       <c r="C602" t="s">
         <v>477</v>
       </c>
-      <c r="D602" s="11" t="s">
+      <c r="D602" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="I602" s="11">
+      <c r="I602" s="10">
         <v>2</v>
       </c>
-      <c r="J602" s="9" t="s">
+      <c r="J602" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K602" s="10"/>
+      <c r="K602" s="9"/>
     </row>
     <row r="603" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A603" s="11" t="s">
+      <c r="A603" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B603" s="11" t="s">
+      <c r="B603" s="10" t="s">
         <v>251</v>
       </c>
       <c r="C603" t="s">
         <v>477</v>
       </c>
-      <c r="D603" s="11" t="s">
+      <c r="D603" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="I603" s="11">
+      <c r="I603" s="10">
         <v>2</v>
       </c>
-      <c r="J603" s="9" t="s">
+      <c r="J603" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K603" s="10"/>
+      <c r="K603" s="9"/>
     </row>
     <row r="604" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A604" s="11" t="s">
+      <c r="A604" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B604" s="11" t="s">
+      <c r="B604" s="10" t="s">
         <v>252</v>
       </c>
       <c r="C604" t="s">
         <v>477</v>
       </c>
-      <c r="D604" s="11" t="s">
+      <c r="D604" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="I604" s="11">
+      <c r="I604" s="10">
         <v>2</v>
       </c>
-      <c r="J604" s="9" t="s">
+      <c r="J604" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K604" s="10"/>
+      <c r="K604" s="9"/>
     </row>
     <row r="605" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A605" s="11" t="s">
+      <c r="A605" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B605" s="11" t="s">
+      <c r="B605" s="10" t="s">
         <v>253</v>
       </c>
       <c r="C605" t="s">
         <v>477</v>
       </c>
-      <c r="D605" s="11" t="s">
+      <c r="D605" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="I605" s="11">
+      <c r="I605" s="10">
         <v>1</v>
       </c>
-      <c r="J605" s="9" t="s">
+      <c r="J605" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K605" s="10"/>
+      <c r="K605" s="9"/>
     </row>
     <row r="606" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A606" s="11" t="s">
+      <c r="A606" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B606" s="11" t="s">
+      <c r="B606" s="10" t="s">
         <v>254</v>
       </c>
       <c r="C606" t="s">
         <v>477</v>
       </c>
-      <c r="D606" s="11" t="s">
+      <c r="D606" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="I606" s="11">
+      <c r="I606" s="10">
         <v>2</v>
       </c>
-      <c r="J606" s="9" t="s">
+      <c r="J606" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K606" s="10"/>
+      <c r="K606" s="9"/>
     </row>
     <row r="607" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A607" s="11" t="s">
+      <c r="A607" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B607" s="11" t="s">
+      <c r="B607" s="10" t="s">
         <v>270</v>
       </c>
       <c r="C607" t="s">
         <v>477</v>
       </c>
-      <c r="D607" s="11" t="s">
+      <c r="D607" s="10" t="s">
         <v>431</v>
       </c>
-      <c r="I607" s="11">
+      <c r="I607" s="10">
         <v>2</v>
       </c>
-      <c r="J607" s="9" t="s">
+      <c r="J607" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K607" s="10"/>
+      <c r="K607" s="9"/>
     </row>
     <row r="608" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A608" s="11" t="s">
+      <c r="A608" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B608" s="11" t="s">
+      <c r="B608" s="10" t="s">
         <v>271</v>
       </c>
       <c r="C608" t="s">
         <v>477</v>
       </c>
-      <c r="D608" s="11" t="s">
+      <c r="D608" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="I608" s="11">
+      <c r="I608" s="10">
         <v>2</v>
       </c>
-      <c r="J608" s="9" t="s">
+      <c r="J608" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K608" s="10"/>
+      <c r="K608" s="9"/>
     </row>
     <row r="609" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A609" s="11" t="s">
+      <c r="A609" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B609" s="11" t="s">
+      <c r="B609" s="10" t="s">
         <v>272</v>
       </c>
       <c r="C609" t="s">
         <v>477</v>
       </c>
-      <c r="D609" s="11" t="s">
+      <c r="D609" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="I609" s="11">
+      <c r="I609" s="10">
         <v>1</v>
       </c>
-      <c r="J609" s="9" t="s">
+      <c r="J609" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K609" s="10"/>
+      <c r="K609" s="9"/>
     </row>
     <row r="610" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A610" s="11" t="s">
+      <c r="A610" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B610" s="11" t="s">
+      <c r="B610" s="10" t="s">
         <v>273</v>
       </c>
       <c r="C610" t="s">
         <v>477</v>
       </c>
-      <c r="D610" s="11" t="s">
+      <c r="D610" s="10" t="s">
         <v>434</v>
       </c>
-      <c r="I610" s="11">
+      <c r="I610" s="10">
         <v>1</v>
       </c>
-      <c r="J610" s="9" t="s">
+      <c r="J610" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K610" s="10"/>
+      <c r="K610" s="9"/>
     </row>
     <row r="611" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A611" s="4" t="s">
+      <c r="A611" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B611" s="4" t="s">
+      <c r="B611" s="3" t="s">
         <v>270</v>
       </c>
       <c r="C611" t="s">
         <v>477</v>
       </c>
-      <c r="D611" s="13" t="s">
+      <c r="D611" s="12" t="s">
         <v>431</v>
       </c>
       <c r="I611" s="1">
@@ -15053,16 +15068,16 @@
       </c>
     </row>
     <row r="612" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A612" s="4" t="s">
+      <c r="A612" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B612" s="4" t="s">
+      <c r="B612" s="3" t="s">
         <v>271</v>
       </c>
       <c r="C612" t="s">
         <v>477</v>
       </c>
-      <c r="D612" s="13" t="s">
+      <c r="D612" s="12" t="s">
         <v>432</v>
       </c>
       <c r="I612" s="1">
@@ -16073,7 +16088,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L610" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A348:A507">
     <cfRule type="duplicateValues" dxfId="17" priority="1602"/>
@@ -16081,33 +16095,33 @@
   <conditionalFormatting sqref="A456">
     <cfRule type="duplicateValues" dxfId="16" priority="1600"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A611:A612">
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="15" priority="1362"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1362"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D611:D612">
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="14" priority="1573"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="1574" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1573"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1574" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="12" priority="1360"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="1361" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1360"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1361" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="10" priority="1358"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1359" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A611:A612">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D611:D612">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1358"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1359" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 20\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62A32D2-15CD-4151-9CDB-F2AC24DA0A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -2210,6 +2210,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -2222,8 +2252,88 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2458,96 +2568,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -2562,26 +2582,6 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -18306,100 +18306,100 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A345:A503">
+    <cfRule type="duplicateValues" dxfId="58" priority="1977"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A452">
+    <cfRule type="duplicateValues" dxfId="57" priority="1935"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A542:A548">
+    <cfRule type="duplicateValues" dxfId="56" priority="1807"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A553:A568">
+    <cfRule type="duplicateValues" dxfId="55" priority="1798"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A568">
-    <cfRule type="duplicateValues" dxfId="58" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="57" priority="1477"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="1477"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D542">
-    <cfRule type="duplicateValues" dxfId="56" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="108" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="109" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="52" priority="110" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="109" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="108" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D543:D544">
-    <cfRule type="duplicateValues" dxfId="51" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="103" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="105" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="105" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="103" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D545">
-    <cfRule type="duplicateValues" dxfId="47" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="99" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="101" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="99" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="101" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D546:D548">
-    <cfRule type="duplicateValues" dxfId="43" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="83" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="84" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="84" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="83" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D549:D552">
+    <cfRule type="duplicateValues" dxfId="31" priority="1802"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1806" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="1805" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1804"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1803"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1801"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1800"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1799"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D558">
-    <cfRule type="duplicateValues" dxfId="35" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="60" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="61" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="62" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="60" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="61" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="62" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D560:D567 D555:D557">
-    <cfRule type="duplicateValues" dxfId="30" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="64" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="66" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="64" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="66" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D562:D566">
-    <cfRule type="duplicateValues" dxfId="26" priority="57" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="57" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D574:D582 D569:D572 D584">
-    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="17" priority="1688"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="1689" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1688"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1689" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="15" priority="1475"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1476" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1475"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1476" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="13" priority="1473"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="1474" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A553:A568">
-    <cfRule type="duplicateValues" dxfId="11" priority="1798"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D549:D552">
-    <cfRule type="duplicateValues" dxfId="10" priority="1799"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1800"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="1801"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1802"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1803"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1804"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1805" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1806" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A542:A548">
-    <cfRule type="duplicateValues" dxfId="2" priority="1807"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A452">
-    <cfRule type="duplicateValues" dxfId="1" priority="1935"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A345:A503">
-    <cfRule type="duplicateValues" dxfId="0" priority="1977"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1473"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1474" stopIfTrue="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="D164" r:id="rId1" display="AM-S@" xr:uid="{37AA604F-FE54-4C74-9AF1-3DD921AFCBB5}"/>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 24\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD16BB63-0941-444D-8C2C-20365E523D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6406275B-F8F7-4F5B-9F7C-A8ACE2670D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$426</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$373</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="463">
   <si>
     <t>SKU</t>
   </si>
@@ -1260,9 +1260,6 @@
     <t>Pipeline</t>
   </si>
   <si>
-    <t>In-Transit Inventory</t>
-  </si>
-  <si>
     <t>FBA80119</t>
   </si>
   <si>
@@ -1306,17 +1303,136 @@
   </si>
   <si>
     <t>Dispatch Partner</t>
+  </si>
+  <si>
+    <t>AM-C46</t>
+  </si>
+  <si>
+    <t>AM-C1</t>
+  </si>
+  <si>
+    <t>AI-04 Red</t>
+  </si>
+  <si>
+    <t>AM-S1</t>
+  </si>
+  <si>
+    <t>AC-6XL</t>
+  </si>
+  <si>
+    <t>AM-C10</t>
+  </si>
+  <si>
+    <t>AM-C43</t>
+  </si>
+  <si>
+    <t>AM-C45</t>
+  </si>
+  <si>
+    <t>AM-W45</t>
+  </si>
+  <si>
+    <t>AM-C2</t>
+  </si>
+  <si>
+    <t>AI-12</t>
+  </si>
+  <si>
+    <t>AM-C5</t>
+  </si>
+  <si>
+    <t>AA-19</t>
+  </si>
+  <si>
+    <t>AA-26</t>
+  </si>
+  <si>
+    <t>AI-13</t>
+  </si>
+  <si>
+    <t>BE-4T</t>
+  </si>
+  <si>
+    <t>AM-Mix6</t>
+  </si>
+  <si>
+    <t>AM-Mix10</t>
+  </si>
+  <si>
+    <t>AI-14</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t>AM-C5 White</t>
+  </si>
+  <si>
+    <t>AM-W32</t>
+  </si>
+  <si>
+    <t>AM-W17</t>
+  </si>
+  <si>
+    <t>AM-W10</t>
+  </si>
+  <si>
+    <t>AM-W11</t>
+  </si>
+  <si>
+    <t>AM-S6</t>
+  </si>
+  <si>
+    <t>AM-S2</t>
+  </si>
+  <si>
+    <t>BE-4</t>
+  </si>
+  <si>
+    <t>AM-C53</t>
+  </si>
+  <si>
+    <t>AM-C54</t>
+  </si>
+  <si>
+    <t>AM-C55</t>
+  </si>
+  <si>
+    <t>AM-C56</t>
+  </si>
+  <si>
+    <t>AM-W25</t>
+  </si>
+  <si>
+    <t>AA-26 Pro</t>
+  </si>
+  <si>
+    <t>AA-27</t>
+  </si>
+  <si>
+    <t>AA-28</t>
+  </si>
+  <si>
+    <t>AH-53</t>
+  </si>
+  <si>
+    <t>AH-50-DH</t>
+  </si>
+  <si>
+    <t>AH-40 Pro</t>
+  </si>
+  <si>
+    <t>AH-53 Pro</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1375,19 +1491,13 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1403,12 +1513,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1437,13 +1541,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1472,25 +1575,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Comma" xfId="3" builtinId="3"/>
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
@@ -2006,7 +2098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L426"/>
+  <dimension ref="A1:L419"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -10251,1614 +10343,1294 @@
       </c>
     </row>
     <row r="358" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A358" s="4" t="s">
+      <c r="A358" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B358" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I358" s="10">
+        <v>6</v>
+      </c>
+      <c r="J358" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K358" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L358" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="359" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A359" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B359" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I359" s="10">
+        <v>25</v>
+      </c>
+      <c r="J359" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K359" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L359" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="360" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A360" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B358" s="4" t="s">
+      <c r="B360" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="C358" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I358" s="11">
+      <c r="C360" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I360" s="10">
+        <v>4</v>
+      </c>
+      <c r="J360" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K360" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L360" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="361" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A361" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B361" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I361" s="10">
+        <v>10</v>
+      </c>
+      <c r="J361" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K361" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L361" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="362" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A362" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B362" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I362" s="10">
+        <v>5</v>
+      </c>
+      <c r="J362" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K362" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L362" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="363" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A363" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B363" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I363" s="10">
+        <v>5</v>
+      </c>
+      <c r="J363" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K363" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L363" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="364" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A364" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B364" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I364" s="10">
+        <v>5</v>
+      </c>
+      <c r="J364" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K364" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L364" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A365" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B365" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I365" s="10">
+        <v>9</v>
+      </c>
+      <c r="J365" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K365" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L365" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="366" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A366" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B366" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I366" s="10">
+        <v>10</v>
+      </c>
+      <c r="J366" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K366" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L366" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="367" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A367" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B367" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I367" s="10">
+        <v>4</v>
+      </c>
+      <c r="J367" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K367" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L367" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="368" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A368" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B368" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I368" s="10">
+        <v>30</v>
+      </c>
+      <c r="J368" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K368" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L368" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="369" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A369" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B369" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I369" s="10">
+        <v>3</v>
+      </c>
+      <c r="J369" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K369" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L369" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="370" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A370" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B370" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I370" s="10">
+        <v>3</v>
+      </c>
+      <c r="J370" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K370" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L370" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="371" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A371" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B371" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I371" s="10">
+        <v>5</v>
+      </c>
+      <c r="J371" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K371" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L371" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="372" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A372" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B372" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I372" s="10">
+        <v>25</v>
+      </c>
+      <c r="J372" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K372" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L372" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="373" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A373" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B373" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I373" s="10">
+        <v>5</v>
+      </c>
+      <c r="J373" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="K373" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="L373" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="374" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A374" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="I374" s="1">
         <v>1008</v>
       </c>
-      <c r="J358" s="8" t="s">
+      <c r="J374" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="K358" s="10" t="s">
+    </row>
+    <row r="375" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A375" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="I375" s="1">
+        <v>3000</v>
+      </c>
+      <c r="J375" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="376" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A376" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="I376" s="1">
+        <v>3000</v>
+      </c>
+      <c r="J376" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A377" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="I377" s="1">
+        <v>1496</v>
+      </c>
+      <c r="J377" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="378" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A378" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="I378" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J378" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="379" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A379" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B379" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D379" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="I379" s="1">
+        <v>504</v>
+      </c>
+      <c r="J379" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="380" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A380" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B380" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="I380" s="1">
+        <v>504</v>
+      </c>
+      <c r="J380" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="381" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A381" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B381" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C381" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="I381" s="1">
+        <v>512</v>
+      </c>
+      <c r="J381" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="382" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A382" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D382" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="I382" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J382" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="383" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A383" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B383" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D383" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="I383" s="1">
+        <v>504</v>
+      </c>
+      <c r="J383" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A384" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D384" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="I384" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J384" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A385" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="I385" s="1">
+        <v>300</v>
+      </c>
+      <c r="J385" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A386" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B386" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="I386" s="1">
+        <v>504</v>
+      </c>
+      <c r="J386" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A387" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D387" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I387" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J387" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A388" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C388" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D388" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="I388" s="1">
+        <v>1300</v>
+      </c>
+      <c r="J388" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A389" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D389" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="I389" s="1">
+        <v>200</v>
+      </c>
+      <c r="J389" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A390" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B390" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C390" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D390" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="I390" s="1">
+        <v>40</v>
+      </c>
+      <c r="J390" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A391" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B391" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C391" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D391" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="I391" s="1">
+        <v>50</v>
+      </c>
+      <c r="J391" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A392" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B392" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C392" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D392" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="I392" s="1">
+        <v>300</v>
+      </c>
+      <c r="J392" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A393" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B393" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="I393" s="1">
+        <v>200</v>
+      </c>
+      <c r="J393" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A394" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B394" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="I394" s="1">
+        <v>300</v>
+      </c>
+      <c r="J394" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="395" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A395" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="I395" s="1">
+        <v>358</v>
+      </c>
+      <c r="J395" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="396" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A396" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="I396" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J396" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A397" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B397" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D397" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="I397" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J397" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A398" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="I398" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J398" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A399" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="I399" s="1">
+        <v>480</v>
+      </c>
+      <c r="J399" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="400" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A400" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B400" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D400" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="I400" s="1">
+        <v>500</v>
+      </c>
+      <c r="J400" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A401" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B401" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D401" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="I401" s="1">
+        <v>400</v>
+      </c>
+      <c r="J401" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="402" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A402" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D402" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="I402" s="1">
+        <v>100</v>
+      </c>
+      <c r="J402" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A403" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="I403" s="1">
+        <v>100</v>
+      </c>
+      <c r="J403" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A404" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="I404" s="1">
+        <v>100</v>
+      </c>
+      <c r="J404" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A405" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B405" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D405" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="I405" s="1">
+        <v>50</v>
+      </c>
+      <c r="J405" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A406" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D406" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="I406" s="1">
+        <v>1004</v>
+      </c>
+      <c r="J406" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A407" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D407" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="I407" s="1">
+        <v>400</v>
+      </c>
+      <c r="J407" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A408" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="L358" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="359" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A359" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B359" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C359" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I359" s="11">
-        <v>3000</v>
-      </c>
-      <c r="J359" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K359" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L359" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="360" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A360" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B360" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C360" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I360" s="11">
-        <v>3000</v>
-      </c>
-      <c r="J360" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K360" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L360" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="361" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A361" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B361" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="C361" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I361" s="11">
-        <v>1496</v>
-      </c>
-      <c r="J361" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K361" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L361" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="362" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A362" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B362" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C362" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I362" s="11">
-        <v>2000</v>
-      </c>
-      <c r="J362" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K362" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L362" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="363" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A363" s="4" t="s">
+      <c r="C408" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D408" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="I408" s="1">
+        <v>510</v>
+      </c>
+      <c r="J408" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="409" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A409" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D409" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="I409" s="1">
+        <v>510</v>
+      </c>
+      <c r="J409" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="410" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A410" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C410" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D410" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="I410" s="1">
+        <v>500</v>
+      </c>
+      <c r="J410" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A411" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C411" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D411" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="I411" s="1">
+        <v>504</v>
+      </c>
+      <c r="J411" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A412" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D412" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="I412" s="1">
+        <v>60</v>
+      </c>
+      <c r="J412" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="413" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A413" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C413" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D413" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="I413" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J413" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A414" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C414" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D414" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="I414" s="1">
+        <v>100</v>
+      </c>
+      <c r="J414" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A415" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D415" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="I415" s="1">
+        <v>100</v>
+      </c>
+      <c r="J415" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A416" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D416" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="I416" s="1">
+        <v>100</v>
+      </c>
+      <c r="J416" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A417" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C417" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D417" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="I417" s="1">
+        <v>100</v>
+      </c>
+      <c r="J417" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="418" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A418" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C418" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="I418" s="1">
+        <v>100</v>
+      </c>
+      <c r="J418" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A419" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D419" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="I419" s="1">
         <v>50</v>
       </c>
-      <c r="B363" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C363" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I363" s="11">
-        <v>501</v>
-      </c>
-      <c r="J363" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K363" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L363" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="364" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A364" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B364" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C364" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I364" s="11">
-        <v>504</v>
-      </c>
-      <c r="J364" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K364" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L364" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="365" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A365" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B365" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C365" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I365" s="11">
-        <v>504</v>
-      </c>
-      <c r="J365" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K365" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L365" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="366" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A366" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B366" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C366" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I366" s="11">
-        <v>201</v>
-      </c>
-      <c r="J366" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K366" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L366" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="367" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A367" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B367" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C367" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I367" s="11">
-        <v>512</v>
-      </c>
-      <c r="J367" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K367" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L367" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="368" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A368" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B368" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C368" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I368" s="11">
-        <v>1000</v>
-      </c>
-      <c r="J368" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K368" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L368" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="369" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A369" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B369" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C369" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I369" s="11">
-        <v>504</v>
-      </c>
-      <c r="J369" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K369" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L369" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="370" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A370" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B370" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C370" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I370" s="11">
-        <v>1000</v>
-      </c>
-      <c r="J370" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K370" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L370" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="371" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A371" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B371" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C371" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I371" s="11">
-        <v>300</v>
-      </c>
-      <c r="J371" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K371" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L371" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="372" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A372" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B372" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C372" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I372" s="11">
-        <v>504</v>
-      </c>
-      <c r="J372" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K372" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L372" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="373" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A373" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B373" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="C373" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I373" s="11">
-        <v>2000</v>
-      </c>
-      <c r="J373" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K373" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L373" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="374" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A374" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B374" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C374" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I374" s="11">
-        <v>990</v>
-      </c>
-      <c r="J374" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K374" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L374" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="375" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A375" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B375" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="C375" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I375" s="11">
-        <v>744</v>
-      </c>
-      <c r="J375" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K375" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L375" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="376" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A376" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B376" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C376" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I376" s="11">
-        <v>500</v>
-      </c>
-      <c r="J376" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K376" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L376" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="377" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A377" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B377" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C377" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I377" s="11">
-        <v>1300</v>
-      </c>
-      <c r="J377" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K377" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L377" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="378" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A378" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B378" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C378" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I378" s="11">
-        <v>200</v>
-      </c>
-      <c r="J378" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K378" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L378" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="379" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A379" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B379" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C379" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I379" s="11">
-        <v>40</v>
-      </c>
-      <c r="J379" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K379" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L379" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="380" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B380" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C380" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I380" s="11">
-        <v>50</v>
-      </c>
-      <c r="J380" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K380" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L380" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="381" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A381" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B381" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C381" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I381" s="11">
-        <v>300</v>
-      </c>
-      <c r="J381" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K381" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L381" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="382" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A382" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B382" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C382" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I382" s="11">
-        <v>200</v>
-      </c>
-      <c r="J382" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K382" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L382" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="383" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A383" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B383" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C383" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I383" s="11">
-        <v>300</v>
-      </c>
-      <c r="J383" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K383" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L383" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="384" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A384" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="B384" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="C384" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I384" s="11">
-        <v>20</v>
-      </c>
-      <c r="J384" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K384" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L384" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="385" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A385" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="B385" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="C385" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I385" s="11">
-        <v>20</v>
-      </c>
-      <c r="J385" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K385" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L385" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="386" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A386" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="B386" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="C386" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I386" s="11">
-        <v>358</v>
-      </c>
-      <c r="J386" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="K386" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L386" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="387" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A387" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B387" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="C387" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I387" s="11">
-        <v>1000</v>
-      </c>
-      <c r="J387" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K387" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L387" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="388" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A388" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B388" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C388" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I388" s="11">
-        <v>1000</v>
-      </c>
-      <c r="J388" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K388" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L388" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="389" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A389" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B389" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C389" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I389" s="11">
-        <v>1000</v>
-      </c>
-      <c r="J389" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K389" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L389" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="390" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A390" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B390" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C390" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I390" s="11">
-        <v>480</v>
-      </c>
-      <c r="J390" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K390" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L390" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="391" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A391" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B391" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C391" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I391" s="11">
-        <v>500</v>
-      </c>
-      <c r="J391" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K391" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L391" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="392" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A392" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B392" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C392" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I392" s="11">
-        <v>400</v>
-      </c>
-      <c r="J392" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K392" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L392" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="393" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A393" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B393" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C393" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I393" s="11">
-        <v>100</v>
-      </c>
-      <c r="J393" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K393" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L393" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="394" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A394" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B394" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C394" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I394" s="11">
-        <v>100</v>
-      </c>
-      <c r="J394" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K394" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L394" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="395" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A395" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B395" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C395" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I395" s="11">
-        <v>100</v>
-      </c>
-      <c r="J395" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K395" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L395" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="396" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A396" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="B396" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="C396" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I396" s="11">
-        <v>50</v>
-      </c>
-      <c r="J396" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K396" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L396" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="397" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A397" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B397" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C397" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I397" s="11">
-        <v>1004</v>
-      </c>
-      <c r="J397" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K397" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L397" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="398" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A398" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="B398" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C398" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I398" s="11">
-        <v>400</v>
-      </c>
-      <c r="J398" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K398" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L398" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="399" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A399" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="B399" s="3"/>
-      <c r="C399" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I399" s="11">
-        <v>510</v>
-      </c>
-      <c r="J399" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K399" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L399" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="400" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A400" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="B400" s="3"/>
-      <c r="C400" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I400" s="11">
-        <v>510</v>
-      </c>
-      <c r="J400" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K400" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L400" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="401" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A401" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="B401" s="3"/>
-      <c r="C401" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I401" s="11">
-        <v>500</v>
-      </c>
-      <c r="J401" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K401" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L401" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="402" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A402" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="B402" s="3"/>
-      <c r="C402" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I402" s="11">
-        <v>504</v>
-      </c>
-      <c r="J402" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K402" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L402" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="403" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A403" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="B403" s="3"/>
-      <c r="C403" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I403" s="11">
-        <v>60</v>
-      </c>
-      <c r="J403" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K403" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L403" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="404" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A404" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="B404" s="3"/>
-      <c r="C404" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I404" s="11">
-        <v>1000</v>
-      </c>
-      <c r="J404" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K404" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L404" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="405" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A405" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="B405" s="3"/>
-      <c r="C405" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I405" s="11">
-        <v>100</v>
-      </c>
-      <c r="J405" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K405" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L405" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="406" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A406" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="B406" s="3"/>
-      <c r="C406" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I406" s="11">
-        <v>100</v>
-      </c>
-      <c r="J406" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K406" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L406" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="407" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A407" s="13" t="s">
-        <v>416</v>
-      </c>
-      <c r="B407" s="3"/>
-      <c r="C407" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I407" s="11">
-        <v>100</v>
-      </c>
-      <c r="J407" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K407" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L407" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="408" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="13" t="s">
-        <v>417</v>
-      </c>
-      <c r="B408" s="3"/>
-      <c r="C408" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I408" s="11">
-        <v>100</v>
-      </c>
-      <c r="J408" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K408" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L408" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="409" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A409" s="13" t="s">
-        <v>418</v>
-      </c>
-      <c r="B409" s="3"/>
-      <c r="C409" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I409" s="11">
-        <v>100</v>
-      </c>
-      <c r="J409" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K409" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L409" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="410" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A410" s="13" t="s">
+      <c r="J419" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B410" s="3"/>
-      <c r="C410" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I410" s="11">
-        <v>50</v>
-      </c>
-      <c r="J410" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="K410" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="L410" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="411" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A411" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B411" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="C411" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I411" s="14">
-        <v>6</v>
-      </c>
-      <c r="J411" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K411" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L411" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="412" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A412" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="B412" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="C412" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I412" s="14">
-        <v>25</v>
-      </c>
-      <c r="J412" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K412" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L412" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="413" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A413" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B413" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="C413" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I413" s="14">
-        <v>4</v>
-      </c>
-      <c r="J413" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K413" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L413" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="414" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A414" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B414" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="C414" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I414" s="14">
-        <v>10</v>
-      </c>
-      <c r="J414" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K414" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L414" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="415" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A415" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B415" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="C415" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I415" s="14">
-        <v>5</v>
-      </c>
-      <c r="J415" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K415" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L415" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="416" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A416" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B416" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="C416" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I416" s="14">
-        <v>5</v>
-      </c>
-      <c r="J416" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K416" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L416" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="417" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A417" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B417" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="C417" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I417" s="14">
-        <v>5</v>
-      </c>
-      <c r="J417" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K417" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L417" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="418" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A418" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B418" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="C418" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I418" s="14">
-        <v>9</v>
-      </c>
-      <c r="J418" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K418" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L418" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="419" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A419" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="B419" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="C419" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I419" s="14">
-        <v>10</v>
-      </c>
-      <c r="J419" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K419" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L419" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="420" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A420" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B420" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="C420" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I420" s="14">
-        <v>4</v>
-      </c>
-      <c r="J420" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K420" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L420" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="421" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="B421" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="C421" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I421" s="14">
-        <v>30</v>
-      </c>
-      <c r="J421" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K421" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L421" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="422" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A422" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B422" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="C422" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I422" s="14">
-        <v>3</v>
-      </c>
-      <c r="J422" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K422" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L422" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="423" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B423" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="C423" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I423" s="14">
-        <v>3</v>
-      </c>
-      <c r="J423" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K423" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L423" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="424" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A424" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="B424" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="C424" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I424" s="14">
-        <v>5</v>
-      </c>
-      <c r="J424" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K424" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L424" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="425" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A425" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="B425" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="C425" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I425" s="14">
-        <v>25</v>
-      </c>
-      <c r="J425" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K425" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L425" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="426" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A426" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B426" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="C426" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I426" s="14">
-        <v>5</v>
-      </c>
-      <c r="J426" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="K426" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="L426" s="1" t="s">
-        <v>345</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L426" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
+  <autoFilter ref="A1:L373" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A170:A297">
+    <cfRule type="duplicateValues" dxfId="17" priority="2193"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A259">
+    <cfRule type="duplicateValues" dxfId="16" priority="2191"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A298:A299">
+    <cfRule type="duplicateValues" dxfId="15" priority="2184"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A358:A365">
+    <cfRule type="duplicateValues" dxfId="11" priority="2180"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A358:A371">
+    <cfRule type="duplicateValues" dxfId="10" priority="2181"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A373">
-    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A426">
-    <cfRule type="duplicateValues" dxfId="16" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="13" priority="1894"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="12" priority="2105"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="2106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2105"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2106" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="10" priority="1892"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1893" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1892"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1893" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="8" priority="1890"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1891" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A411:A418">
-    <cfRule type="duplicateValues" dxfId="6" priority="2180"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A411:A424">
-    <cfRule type="duplicateValues" dxfId="5" priority="2181"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A387:A391">
-    <cfRule type="duplicateValues" dxfId="4" priority="2182"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A358:A376">
-    <cfRule type="duplicateValues" dxfId="3" priority="2183"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A298:A299">
-    <cfRule type="duplicateValues" dxfId="2" priority="2184"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A259">
-    <cfRule type="duplicateValues" dxfId="1" priority="2191"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A170:A297">
-    <cfRule type="duplicateValues" dxfId="0" priority="2193"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1890"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1891" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 29\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 30\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091F4279-9FD9-45CD-9AB7-BA588E9220BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09035412-E2C3-47E4-8AAA-D10C42D07395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$242</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="472">
   <si>
     <t>SKU</t>
   </si>
@@ -387,9 +387,6 @@
     <t>FBA80005</t>
   </si>
   <si>
-    <t>FBA80007</t>
-  </si>
-  <si>
     <t>FBA80009</t>
   </si>
   <si>
@@ -720,9 +717,6 @@
     <t>B0GW96CQMG</t>
   </si>
   <si>
-    <t>B0GN2LHJY4</t>
-  </si>
-  <si>
     <t>B0GW8R2RYM</t>
   </si>
   <si>
@@ -1332,9 +1326,6 @@
     <t>A3-XLR</t>
   </si>
   <si>
-    <t>MT-12</t>
-  </si>
-  <si>
     <t>JT-01, BM 320 Pro</t>
   </si>
   <si>
@@ -1459,6 +1450,9 @@
   </si>
   <si>
     <t>AI-04 Pro</t>
+  </si>
+  <si>
+    <t>AM-W47 WIRLESS</t>
   </si>
 </sst>
 </file>
@@ -1683,7 +1677,7 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="53">
+  <dxfs count="57">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2012,6 +2006,46 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2560,7 +2594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L238"/>
+  <dimension ref="A1:L242"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -2621,19 +2655,19 @@
         <v>29</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I2" s="3">
         <v>1161</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2641,19 +2675,19 @@
         <v>55</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I3" s="3">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2661,19 +2695,19 @@
         <v>68</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I4" s="3">
-        <v>1716</v>
+        <v>1720</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2681,19 +2715,19 @@
         <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I5" s="3">
-        <v>1441</v>
+        <v>1404</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2701,19 +2735,19 @@
         <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I6" s="3">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2721,19 +2755,19 @@
         <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I7" s="3">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2741,19 +2775,19 @@
         <v>70</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I8" s="3">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2761,19 +2795,19 @@
         <v>62</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I9" s="3">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2781,19 +2815,19 @@
         <v>74</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I10" s="3">
         <v>31</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2801,19 +2835,19 @@
         <v>61</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I11" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2821,19 +2855,19 @@
         <v>72</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I12" s="3">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2841,19 +2875,19 @@
         <v>57</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I13" s="3">
-        <v>1173</v>
+        <v>1197</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2861,19 +2895,19 @@
         <v>36</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I14" s="3">
-        <v>2394</v>
+        <v>1933</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2881,19 +2915,19 @@
         <v>30</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="I15" s="3">
         <v>2</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2901,19 +2935,19 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I16" s="3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2921,19 +2955,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I17" s="3">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2941,19 +2975,19 @@
         <v>73</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="I18" s="3">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2961,19 +2995,19 @@
         <v>21</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I19" s="3">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2981,19 +3015,19 @@
         <v>52</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="I20" s="3">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3001,19 +3035,19 @@
         <v>75</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="I21" s="3">
-        <v>1379</v>
+        <v>1131</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3021,19 +3055,19 @@
         <v>38</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I22" s="3">
-        <v>1987</v>
+        <v>1784</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3041,19 +3075,19 @@
         <v>45</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="I23" s="3">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3061,19 +3095,19 @@
         <v>48</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="I24" s="3">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3081,19 +3115,19 @@
         <v>69</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="I25" s="3">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3101,19 +3135,19 @@
         <v>26</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I26" s="3">
-        <v>541</v>
+        <v>492</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3121,19 +3155,19 @@
         <v>15</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I27" s="3">
         <v>27</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3141,19 +3175,19 @@
         <v>19</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I28" s="3">
         <v>22</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3161,19 +3195,19 @@
         <v>60</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I29" s="3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3181,19 +3215,19 @@
         <v>44</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I30" s="3">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3201,19 +3235,19 @@
         <v>54</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I31" s="3">
-        <v>456</v>
+        <v>402</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3221,19 +3255,19 @@
         <v>42</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I32" s="3">
         <v>67</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3241,19 +3275,19 @@
         <v>51</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I33" s="3">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3261,19 +3295,19 @@
         <v>24</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I34" s="3">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3281,19 +3315,19 @@
         <v>49</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I35" s="3">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3301,19 +3335,19 @@
         <v>56</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I36" s="3">
-        <v>637</v>
+        <v>593</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3321,19 +3355,19 @@
         <v>58</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I37" s="3">
-        <v>762</v>
+        <v>618</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3341,4086 +3375,4172 @@
         <v>67</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="I38" s="3">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I39" s="3">
-        <v>353</v>
+        <v>1</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="I40" s="3">
-        <v>4</v>
+        <v>306</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>191</v>
+        <v>133</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="I41" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I42" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I43" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I44" s="3">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="I45" s="3">
-        <v>381</v>
+        <v>43</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I46" s="3">
-        <v>221</v>
+        <v>371</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I47" s="3">
-        <v>915</v>
+        <v>182</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="I48" s="3">
-        <v>11</v>
+        <v>874</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I49" s="3">
-        <v>247</v>
+        <v>11</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I50" s="3">
-        <v>733</v>
+        <v>267</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="I51" s="3">
-        <v>1497</v>
+        <v>772</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I52" s="3">
-        <v>57</v>
+        <v>1462</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="I53" s="3">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>267</v>
+        <v>39</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>268</v>
+        <v>150</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="I54" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>53</v>
+        <v>265</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>165</v>
+        <v>266</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="I55" s="3">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I56" s="3">
-        <v>233</v>
+        <v>51</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I57" s="3">
-        <v>4</v>
+        <v>195</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="I58" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>245</v>
+        <v>148</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I59" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="I60" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>41</v>
+        <v>267</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>153</v>
+        <v>268</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I61" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>271</v>
+        <v>41</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>272</v>
+        <v>152</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I62" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I63" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I64" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>275</v>
+        <v>244</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>276</v>
+        <v>245</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="I65" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I66" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I67" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I68" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>281</v>
+        <v>246</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>282</v>
+        <v>247</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="I69" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="I70" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I71" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>64</v>
+        <v>283</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="I72" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>287</v>
+        <v>64</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>288</v>
+        <v>175</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I73" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="I74" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I75" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I76" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>16</v>
+        <v>291</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>128</v>
+        <v>292</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="I77" s="3">
-        <v>1767</v>
+        <v>1</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>295</v>
+        <v>16</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>296</v>
+        <v>127</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I78" s="3">
-        <v>1</v>
+        <v>1762</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="I79" s="3">
         <v>1</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="I80" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I81" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>35</v>
+        <v>299</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>147</v>
+        <v>300</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="I82" s="3">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>303</v>
+        <v>35</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>304</v>
+        <v>146</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="I83" s="3">
-        <v>2</v>
+        <v>148</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="I84" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="I85" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="I86" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>46</v>
+        <v>307</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>158</v>
+        <v>308</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="I87" s="3">
-        <v>298</v>
+        <v>1</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="I88" s="3">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="I89" s="3">
-        <v>1444</v>
+        <v>176</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I90" s="3">
-        <v>490</v>
+        <v>1259</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I91" s="3">
-        <v>1766</v>
+        <v>496</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="I92" s="3">
-        <v>731</v>
+        <v>1591</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="I93" s="3">
-        <v>181</v>
+        <v>727</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="I94" s="3">
-        <v>915</v>
+        <v>210</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="I95" s="3">
-        <v>1514</v>
+        <v>899</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I96" s="3">
-        <v>1238</v>
+        <v>1394</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I97" s="3">
-        <v>415</v>
+        <v>958</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="I98" s="3">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="I99" s="3">
-        <v>988</v>
+        <v>401</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="I100" s="3">
-        <v>213</v>
+        <v>632</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>205</v>
+        <v>89</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="I101" s="3">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I102" s="3">
-        <v>779</v>
+        <v>231</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>240</v>
+        <v>96</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I103" s="3">
-        <v>165</v>
+        <v>427</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>97</v>
+        <v>238</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I104" s="3">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="I105" s="3">
-        <v>211</v>
+        <v>47</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="I106" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="I107" s="3">
-        <v>227</v>
+        <v>129</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="I108" s="3">
-        <v>289</v>
+        <v>2</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="I109" s="3">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="I110" s="3">
-        <v>583</v>
+        <v>129</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>203</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="I111" s="3">
-        <v>799</v>
+        <v>237</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="I112" s="3">
-        <v>218</v>
+        <v>569</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="I113" s="3">
-        <v>53</v>
+        <v>799</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="I114" s="3">
-        <v>1</v>
+        <v>208</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="I115" s="3">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="I116" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="I117" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>235</v>
+        <v>229</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="I118" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>235</v>
+        <v>230</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="I119" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>235</v>
+        <v>201</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="I120" s="3">
-        <v>371</v>
+        <v>10</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="I121" s="3">
-        <v>403</v>
+        <v>11</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="I122" s="3">
-        <v>182</v>
+        <v>2</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="I123" s="3">
-        <v>177</v>
+        <v>371</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="I124" s="3">
-        <v>1</v>
+        <v>382</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="I125" s="3">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="I126" s="3">
-        <v>13</v>
+        <v>161</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="I127" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="I128" s="3">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="I129" s="3">
-        <v>187</v>
+        <v>13</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="I130" s="3">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="I131" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="I132" s="3">
-        <v>60</v>
+        <v>198</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
-        <v>236</v>
+        <v>112</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>455</v>
+        <v>233</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>449</v>
       </c>
       <c r="I133" s="3">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
-        <v>237</v>
+        <v>113</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>456</v>
+        <v>233</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>450</v>
       </c>
       <c r="I134" s="3">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
-        <v>242</v>
+        <v>114</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="C135" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="I135" s="3">
+        <v>59</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="I136" s="3">
+        <v>7</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="D135" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="I135" s="3">
+      <c r="B137" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="I137" s="3">
+        <v>8</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="I138" s="3">
         <v>286</v>
       </c>
-      <c r="J135" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C136" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="D136" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="I136" s="13">
-        <v>6</v>
-      </c>
-      <c r="J136" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="B137" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="C137" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="D137" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="I137" s="13">
-        <v>1</v>
-      </c>
-      <c r="J137" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B138" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C138" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="D138" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="I138" s="13">
-        <v>33</v>
-      </c>
       <c r="J138" s="1" t="s">
-        <v>312</v>
+        <v>264</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="18" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="B139" s="14" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D139" s="14" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="I139" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="18" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="B140" s="14" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D140" s="14" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="I140" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="18" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B141" s="14" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D141" s="14" t="s">
-        <v>364</v>
+        <v>328</v>
       </c>
       <c r="I141" s="13">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="18" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B142" s="14" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D142" s="14" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I142" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="143" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="18" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="B143" s="14" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D143" s="14" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="I143" s="13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="18" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B144" s="14" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D144" s="14" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="I144" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="18" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B145" s="14" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D145" s="14" t="s">
-        <v>408</v>
+        <v>325</v>
       </c>
       <c r="I145" s="13">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="18" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="B146" s="14" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D146" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I146" s="13">
         <v>3</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="18" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="B147" s="14" t="s">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D147" s="14" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="I147" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="18" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="B148" s="14" t="s">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D148" s="14" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="I148" s="13">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="18" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="B149" s="14" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D149" s="14" t="s">
-        <v>416</v>
+        <v>345</v>
       </c>
       <c r="I149" s="13">
-        <v>108</v>
+        <v>3</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="18" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B150" s="14" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D150" s="14" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="I150" s="13">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="18" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="B151" s="14" t="s">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D151" s="14" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="I151" s="13">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="18" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="B152" s="14" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D152" s="14" t="s">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="I152" s="13">
-        <v>8</v>
+        <v>108</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B153" s="14" t="s">
         <v>179</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D153" s="14" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="I153" s="13">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="18" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="B154" s="14" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D154" s="14" t="s">
-        <v>366</v>
+        <v>409</v>
       </c>
       <c r="I154" s="13">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="18" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B155" s="14" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D155" s="14" t="s">
-        <v>319</v>
+        <v>352</v>
       </c>
       <c r="I155" s="13">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="18" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B156" s="14" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D156" s="14" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="I156" s="13">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="18" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B157" s="14" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D157" s="14" t="s">
-        <v>407</v>
+        <v>364</v>
       </c>
       <c r="I157" s="13">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="18" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B158" s="14" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D158" s="14" t="s">
-        <v>372</v>
+        <v>317</v>
       </c>
       <c r="I158" s="13">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="18" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B159" s="14" t="s">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D159" s="14" t="s">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="I159" s="13">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="18" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="B160" s="14" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D160" s="14" t="s">
-        <v>362</v>
+        <v>405</v>
       </c>
       <c r="I160" s="13">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="18" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="B161" s="14" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D161" s="14" t="s">
-        <v>321</v>
+        <v>370</v>
       </c>
       <c r="I161" s="13">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="18" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="B162" s="14" t="s">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D162" s="14" t="s">
-        <v>413</v>
+        <v>351</v>
       </c>
       <c r="I162" s="13">
         <v>2</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="18" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="B163" s="14" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="C163" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D163" s="14" t="s">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="I163" s="13">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="18" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="B164" s="14" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D164" s="14" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I164" s="13">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B165" s="14" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C165" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D165" s="14" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="I165" s="13">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="18" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="B166" s="14" t="s">
-        <v>184</v>
+        <v>132</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D166" s="14" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="I166" s="13">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="18" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="B167" s="14" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="C167" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D167" s="14" t="s">
-        <v>389</v>
+        <v>314</v>
       </c>
       <c r="I167" s="13">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="18" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D168" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I168" s="13">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="18" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="B169" s="14" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="C169" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D169" s="14" t="s">
-        <v>431</v>
+        <v>324</v>
       </c>
       <c r="I169" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="18" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="B170" s="14" t="s">
-        <v>311</v>
+        <v>175</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D170" s="14" t="s">
-        <v>432</v>
+        <v>387</v>
       </c>
       <c r="I170" s="13">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="18" t="s">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="B171" s="14" t="s">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="I171" s="13">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="18" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B172" s="14" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D172" s="14" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I172" s="13">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="18" t="s">
-        <v>48</v>
+        <v>248</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>160</v>
+        <v>249</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>338</v>
+        <v>427</v>
       </c>
       <c r="I173" s="13">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="18" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D174" s="14" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="I174" s="13">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B175" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C175" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="D175" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="I175" s="13">
+        <v>2</v>
+      </c>
+      <c r="J175" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B176" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="C176" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="D176" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="I176" s="13">
+        <v>2</v>
+      </c>
+      <c r="J176" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B175" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="C175" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="D175" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="I175" s="13">
+      <c r="B177" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="C177" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="D177" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="I177" s="13">
         <v>9</v>
       </c>
-      <c r="J175" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C176" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="D176" s="14" t="s">
-        <v>437</v>
-      </c>
-      <c r="I176" s="13">
-        <v>3</v>
-      </c>
-      <c r="J176" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C177" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="D177" s="14" t="s">
-        <v>438</v>
-      </c>
-      <c r="I177" s="13">
-        <v>5</v>
-      </c>
       <c r="J177" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="178" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C178" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="D178" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="I178" s="13">
+        <v>3</v>
+      </c>
+      <c r="J178" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C179" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="D179" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="I179" s="13">
+        <v>5</v>
+      </c>
+      <c r="J179" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B178" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C178" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="D178" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="I178" s="13">
+      <c r="B180" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C180" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="D180" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="I180" s="13">
         <v>22</v>
       </c>
-      <c r="J178" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="18" t="s">
+      <c r="J180" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B179" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="C179" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="D179" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="I179" s="13">
+      <c r="B181" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C181" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="D181" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="I181" s="13">
         <v>3</v>
       </c>
-      <c r="J179" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C180" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D180" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="I180" s="3">
-        <v>60</v>
-      </c>
-      <c r="J180" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C181" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="I181" s="3">
-        <v>160</v>
-      </c>
       <c r="J181" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="182" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>319</v>
+        <v>352</v>
       </c>
       <c r="I182" s="3">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="183" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>458</v>
+        <v>323</v>
       </c>
       <c r="I183" s="3">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="184" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>180</v>
+        <v>123</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I184" s="3">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="185" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>323</v>
+        <v>455</v>
       </c>
       <c r="I185" s="3">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="186" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="I186" s="3">
+        <v>35</v>
+      </c>
+      <c r="J186" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="I187" s="3">
+        <v>17</v>
+      </c>
+      <c r="J187" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B186" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C186" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="I186" s="3">
-        <v>6</v>
-      </c>
-      <c r="J186" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C187" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="I187" s="14">
-        <v>30</v>
-      </c>
-      <c r="J187" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="19" t="s">
-        <v>81</v>
-      </c>
       <c r="B188" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D188" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="I188" s="14">
-        <v>25</v>
+      <c r="I188" s="3">
+        <v>6</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="189" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="14" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>366</v>
+        <v>410</v>
       </c>
       <c r="I189" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="190" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="14" t="s">
-        <v>60</v>
+      <c r="A190" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>343</v>
+        <v>414</v>
       </c>
       <c r="I190" s="14">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="14" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>413</v>
+        <v>364</v>
       </c>
       <c r="I191" s="14">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="192" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="14" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="I192" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="193" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="14" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>340</v>
+        <v>411</v>
       </c>
       <c r="I193" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="194" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="14" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="I194" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="195" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="14" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>407</v>
+        <v>338</v>
       </c>
       <c r="I195" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="14" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>408</v>
+        <v>316</v>
       </c>
       <c r="I196" s="14">
         <v>4</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="197" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="I197" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="14" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="I198" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="199" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="14" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="I199" s="14">
         <v>3</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="B200" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D200" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="I200" s="11">
-        <v>400</v>
-      </c>
-      <c r="J200" s="7" t="s">
-        <v>252</v>
+      <c r="A200" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="I200" s="14">
+        <v>3</v>
+      </c>
+      <c r="J200" s="1" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B201" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D201" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="I201" s="11">
-        <v>100</v>
-      </c>
-      <c r="J201" s="7" t="s">
-        <v>252</v>
+      <c r="A201" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I201" s="14">
+        <v>3</v>
+      </c>
+      <c r="J201" s="1" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
-        <v>98</v>
+        <v>238</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D202" s="6" t="s">
-        <v>422</v>
+        <v>233</v>
+      </c>
+      <c r="D202" s="9" t="s">
+        <v>456</v>
       </c>
       <c r="I202" s="11">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="J202" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D203" s="9" t="s">
-        <v>423</v>
+        <v>233</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>419</v>
       </c>
       <c r="I203" s="11">
         <v>100</v>
       </c>
       <c r="J203" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="204" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B204" s="3" t="s">
-        <v>202</v>
+        <v>98</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>209</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="I204" s="8">
-        <v>888</v>
+        <v>420</v>
+      </c>
+      <c r="I204" s="11">
+        <v>100</v>
       </c>
       <c r="J204" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="B205" s="10" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D205" s="6" t="s">
-        <v>450</v>
+        <v>233</v>
+      </c>
+      <c r="D205" s="9" t="s">
+        <v>421</v>
       </c>
       <c r="I205" s="11">
+        <v>100</v>
+      </c>
+      <c r="J205" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="I206" s="8">
+        <v>888</v>
+      </c>
+      <c r="J206" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="I207" s="11">
         <v>400</v>
       </c>
-      <c r="J205" s="7" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="B206" s="3"/>
-      <c r="C206" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D206" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="I206" s="8">
-        <v>100</v>
-      </c>
-      <c r="J206" s="7" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="207" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="B207" s="3"/>
-      <c r="C207" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D207" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="I207" s="8">
-        <v>100</v>
-      </c>
       <c r="J207" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="208" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B208" s="3"/>
       <c r="C208" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="I208" s="8">
         <v>100</v>
       </c>
       <c r="J208" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="209" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="9" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B209" s="3"/>
       <c r="C209" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="I209" s="8">
+        <v>100</v>
+      </c>
+      <c r="J209" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B210" s="3"/>
+      <c r="C210" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D210" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="I210" s="8">
+        <v>100</v>
+      </c>
+      <c r="J210" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B211" s="3"/>
+      <c r="C211" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D211" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="I211" s="8">
         <v>50</v>
       </c>
-      <c r="J209" s="7" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B210" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C210" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D210" s="15" t="s">
-        <v>319</v>
-      </c>
-      <c r="I210" s="8">
-        <v>5004</v>
-      </c>
-      <c r="J210" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B211" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C211" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D211" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="I211" s="8">
-        <v>500</v>
-      </c>
       <c r="J211" s="7" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="212" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D212" s="15" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I212" s="8">
-        <v>1000</v>
+        <v>5004</v>
       </c>
       <c r="J212" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D213" s="15" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="I213" s="8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J213" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="214" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D214" s="15" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="I214" s="8">
-        <v>2010</v>
+        <v>1000</v>
       </c>
       <c r="J214" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="I215" s="8">
-        <v>504</v>
+        <v>1000</v>
       </c>
       <c r="J215" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="216" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D216" s="15" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="I216" s="8">
-        <v>501</v>
+        <v>2010</v>
       </c>
       <c r="J216" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="217" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D217" s="15" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="I217" s="8">
         <v>504</v>
       </c>
       <c r="J217" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="218" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="I218" s="8">
-        <v>1000</v>
+        <v>501</v>
       </c>
       <c r="J218" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D219" s="15" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="I219" s="8">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="J219" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="220" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D220" s="15" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="I220" s="8">
-        <v>504</v>
+        <v>1000</v>
       </c>
       <c r="J220" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="221" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D221" s="15" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="I221" s="8">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="J221" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="222" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D222" s="15" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="I222" s="8">
-        <v>2040</v>
+        <v>504</v>
       </c>
       <c r="J222" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="223" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D223" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="I223" s="8">
+        <v>500</v>
+      </c>
+      <c r="J223" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D224" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="I224" s="8">
+        <v>2040</v>
+      </c>
+      <c r="J224" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D225" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="I225" s="8">
+        <v>504</v>
+      </c>
+      <c r="J225" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B223" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D223" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="I223" s="8">
+      <c r="B226" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D226" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="I226" s="8">
         <v>3000</v>
       </c>
-      <c r="J223" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="224" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D224" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="I224" s="8">
-        <v>1500</v>
-      </c>
-      <c r="J224" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B225" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D225" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="I225" s="8">
-        <v>500</v>
-      </c>
-      <c r="J225" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C226" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D226" s="16" t="s">
-        <v>424</v>
-      </c>
-      <c r="I226" s="17">
-        <v>200</v>
-      </c>
       <c r="J226" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="227" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D227" s="6" t="s">
-        <v>426</v>
+        <v>233</v>
+      </c>
+      <c r="D227" s="9" t="s">
+        <v>417</v>
       </c>
       <c r="I227" s="8">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="J227" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="228" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>251</v>
+        <v>99</v>
+      </c>
+      <c r="B228" s="10" t="s">
+        <v>210</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D228" s="6" t="s">
-        <v>460</v>
+        <v>233</v>
+      </c>
+      <c r="D228" s="9" t="s">
+        <v>421</v>
       </c>
       <c r="I228" s="8">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="J228" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="229" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D229" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="I229" s="8">
-        <v>2108</v>
+        <v>233</v>
+      </c>
+      <c r="D229" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="I229" s="17">
+        <v>200</v>
       </c>
       <c r="J229" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="230" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B230" s="3"/>
+        <v>95</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C230" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="I230" s="8">
-        <v>510</v>
+        <v>1500</v>
       </c>
       <c r="J230" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="B231" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="C231" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>462</v>
+        <v>424</v>
       </c>
       <c r="I231" s="8">
-        <v>510</v>
+        <v>2000</v>
       </c>
       <c r="J231" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="232" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B232" s="3"/>
+        <v>248</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>249</v>
+      </c>
       <c r="C232" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="I232" s="8">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="J232" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="233" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="B233" s="3"/>
+        <v>90</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="C233" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>464</v>
+        <v>436</v>
       </c>
       <c r="I233" s="8">
-        <v>504</v>
+        <v>2108</v>
       </c>
       <c r="J233" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="234" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B234" s="3"/>
       <c r="C234" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="I234" s="8">
-        <v>60</v>
+        <v>510</v>
       </c>
       <c r="J234" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="235" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B235" s="3"/>
       <c r="C235" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="I235" s="8">
-        <v>1000</v>
+        <v>510</v>
       </c>
       <c r="J235" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="236" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B236" s="3"/>
       <c r="C236" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="I236" s="8">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="J236" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="237" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B237" s="3"/>
       <c r="C237" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="I237" s="8">
-        <v>100</v>
+        <v>504</v>
       </c>
       <c r="J237" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="238" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="9" t="s">
-        <v>315</v>
+      <c r="A238" s="6" t="s">
+        <v>255</v>
       </c>
       <c r="B238" s="3"/>
       <c r="C238" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D238" s="9" t="s">
-        <v>473</v>
+        <v>233</v>
+      </c>
+      <c r="D238" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="I238" s="8">
+        <v>60</v>
+      </c>
+      <c r="J238" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B239" s="3"/>
+      <c r="C239" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D239" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="I239" s="8">
         <v>1000</v>
       </c>
-      <c r="J238" s="7" t="s">
-        <v>265</v>
+      <c r="J239" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B240" s="3"/>
+      <c r="C240" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D240" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="I240" s="8">
+        <v>100</v>
+      </c>
+      <c r="J240" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B241" s="3"/>
+      <c r="C241" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D241" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="I241" s="8">
+        <v>100</v>
+      </c>
+      <c r="J241" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="B242" s="3"/>
+      <c r="C242" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D242" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="I242" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J242" s="7" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L238" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
+  <autoFilter ref="A1:L242" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A135">
-    <cfRule type="duplicateValues" dxfId="52" priority="93"/>
+  <conditionalFormatting sqref="A138">
+    <cfRule type="duplicateValues" dxfId="56" priority="110"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A176">
-    <cfRule type="duplicateValues" dxfId="51" priority="84"/>
+  <conditionalFormatting sqref="A178">
+    <cfRule type="duplicateValues" dxfId="55" priority="101"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A177:A178">
-    <cfRule type="duplicateValues" dxfId="50" priority="83"/>
+  <conditionalFormatting sqref="A179:A180">
+    <cfRule type="duplicateValues" dxfId="54" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="49" priority="2241"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="2365"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D212:D221">
-    <cfRule type="duplicateValues" dxfId="48" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="42" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="44" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D214:D223">
+    <cfRule type="duplicateValues" dxfId="52" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="46" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="48" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D218:D220">
-    <cfRule type="duplicateValues" dxfId="44" priority="40" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D220:D222">
+    <cfRule type="duplicateValues" dxfId="48" priority="44" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D225">
+    <cfRule type="duplicateValues" dxfId="47" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="41" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="43" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="43" priority="2452"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="2453" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="2576"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="2577" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="41" priority="2239"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="2240" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="2363"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="2364" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="39" priority="2237"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="2238" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="2361"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="2362" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D225:D238">
-    <cfRule type="duplicateValues" dxfId="37" priority="2535"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="2536"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="2537"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="2538"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="2539"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="2540"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="2541" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="2542" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D228:D242">
+    <cfRule type="duplicateValues" dxfId="37" priority="2654"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="2655"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="2656"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2657"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="2658"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="2659"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="2660" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="2661" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A210:A223">
-    <cfRule type="duplicateValues" dxfId="29" priority="2543"/>
+  <conditionalFormatting sqref="A212:A226">
+    <cfRule type="duplicateValues" dxfId="29" priority="2662"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D223">
-    <cfRule type="duplicateValues" dxfId="28" priority="2545"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="2546"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="2547"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="2548"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="2549"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="2550"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="2551" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="2552" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D226">
+    <cfRule type="duplicateValues" dxfId="28" priority="2664"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="2665"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="2666"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="2667"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2668"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2669"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2670" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2671" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D200:D209">
-    <cfRule type="duplicateValues" dxfId="20" priority="2553"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="2554"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="2555"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="2556"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="2557"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="2558"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="2559" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="2560" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D202:D211">
+    <cfRule type="duplicateValues" dxfId="20" priority="2672"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2673"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="2674"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2675"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2676"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2677"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2678" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2679" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A187:A199">
-    <cfRule type="duplicateValues" dxfId="12" priority="2573"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="2574"/>
+  <conditionalFormatting sqref="A189:A201">
+    <cfRule type="duplicateValues" dxfId="12" priority="2692"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2693"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A133:A134">
-    <cfRule type="duplicateValues" dxfId="10" priority="2575"/>
+  <conditionalFormatting sqref="A136:A137">
+    <cfRule type="duplicateValues" dxfId="10" priority="2694"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D133:D135">
-    <cfRule type="duplicateValues" dxfId="9" priority="2576"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="2577"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2578"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2579"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="2580"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2581"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2582" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2583" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D136:D138">
+    <cfRule type="duplicateValues" dxfId="9" priority="2695"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2696"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2697"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2698"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2699"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2700"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2701" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2702" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A89">
-    <cfRule type="duplicateValues" dxfId="1" priority="2590"/>
+  <conditionalFormatting sqref="A90">
+    <cfRule type="duplicateValues" dxfId="1" priority="2709"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A132">
-    <cfRule type="duplicateValues" dxfId="0" priority="2592"/>
+  <conditionalFormatting sqref="A2:A135">
+    <cfRule type="duplicateValues" dxfId="0" priority="2711"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L267"/>
+  <dimension ref="A1:L262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,7 +504,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>1834</v>
+        <v>1717</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>1057</v>
+        <v>942</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>1687</v>
+        <v>1590</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>324</v>
+        <v>250</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>484</v>
+        <v>454</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>119</v>
+        <v>34</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>427</v>
+        <v>363</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>597</v>
+        <v>371</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1813,12 +1813,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1836,7 +1836,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1849,12 +1849,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA79722</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0F2HYY7JF</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1872,7 +1872,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1885,12 +1885,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBA79722</t>
+          <t>FBA76716</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B0F2HYY7JF</t>
+          <t>B0BLK8DNPD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-C13</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1908,7 +1908,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -1921,12 +1921,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBA76716</t>
+          <t>FBA76730</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B0BLK8DNPD</t>
+          <t>B0BLKB6FRR</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AM-C13</t>
+          <t>AM-C27</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1944,7 +1944,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -1957,12 +1957,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA76730</t>
+          <t>FBA78423</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B0BLKB6FRR</t>
+          <t>B0C598Q6PT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AM-C27</t>
+          <t>AM-C36</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1980,7 +1980,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -1993,12 +1993,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FBA78423</t>
+          <t>FBA78974</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B0C598Q6PT</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AM-C36</t>
+          <t>AA-20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2016,7 +2016,7 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>43</v>
+        <v>363</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2029,12 +2029,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FBA78974</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AA-20</t>
+          <t>AM-C2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2052,7 +2052,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>363</v>
+        <v>144</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2065,12 +2065,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AM-C2</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2088,7 +2088,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>159</v>
+        <v>591</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2101,12 +2101,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA76742</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0BLKBJ5HN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-K1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2124,7 +2124,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>647</v>
+        <v>11</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2137,12 +2137,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FBA76742</t>
+          <t>FBA75689</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B0BLKBJ5HN</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AM-K1</t>
+          <t>AM-W13</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2160,7 +2160,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>11</v>
+        <v>227</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2173,12 +2173,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FBA75689</t>
+          <t>FBA75679</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AM-W13</t>
+          <t>AA-02</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>264</v>
+        <v>771</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2209,12 +2209,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FBA75679</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AA-02</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2232,7 +2232,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>772</v>
+        <v>1463</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2245,12 +2245,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA79355</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2268,7 +2268,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>1463</v>
+        <v>33</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2281,12 +2281,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FBA79355</t>
+          <t>FBA78203</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>AM-C30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2317,12 +2317,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FBA78203</t>
+          <t>FBA79010</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AM-C30</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FBA79010</t>
+          <t>FBA75691</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AM-W14</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2376,7 +2376,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2389,12 +2389,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FBA75691</t>
+          <t>FBA78205</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0C539RBGL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AM-W14</t>
+          <t>AM-C32</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2412,7 +2412,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>185</v>
+        <v>4</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2425,12 +2425,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FBA78205</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B0C539RBGL</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AM-C32</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2448,7 +2448,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2461,12 +2461,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA77011</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0BPMN89NG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-C29</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2497,12 +2497,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FBA77011</t>
+          <t>FBA78425</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B0BPMN89NG</t>
+          <t>B0C55QXL83</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AM-C29</t>
+          <t>AM-C38</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2520,7 +2520,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2533,12 +2533,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FBA78425</t>
+          <t>FBA76715</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B0C55QXL83</t>
+          <t>B0BLK31PYH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AM-C38</t>
+          <t>AM-C12</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2569,12 +2569,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FBA76715</t>
+          <t>FBA78206</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B0BLK31PYH</t>
+          <t>B0C4YSV3XL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AM-C12</t>
+          <t>AM-W15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2605,12 +2605,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FBA78206</t>
+          <t>FBA79070</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B0C4YSV3XL</t>
+          <t>B0CLH7G5WH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AM-W15</t>
+          <t>AI-02</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2641,12 +2641,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBA79070</t>
+          <t>FBA76721</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B0CLH7G5WH</t>
+          <t>B0BLKB55BM</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AI-02</t>
+          <t>AM-C18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA76721</t>
+          <t>FBA76726</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B0BLKB55BM</t>
+          <t>B0BLKD4815</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AM-C18</t>
+          <t>AM-C23</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2700,7 +2700,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2713,12 +2713,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FBA76726</t>
+          <t>FBA78422</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B0BLKD4815</t>
+          <t>B0C598MNMC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AM-C23</t>
+          <t>AM-C35</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2736,7 +2736,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2749,12 +2749,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FBA78422</t>
+          <t>FBA76718</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B0C598MNMC</t>
+          <t>B0BLKD8FVG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AM-C35</t>
+          <t>AM-C15</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2785,12 +2785,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FBA76718</t>
+          <t>FBA76734</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B0BLKD8FVG</t>
+          <t>B0BLKHVCDX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AM-C15</t>
+          <t>AA-07</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2808,7 +2808,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2821,12 +2821,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FBA76734</t>
+          <t>FBA76739</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B0BLKHVCDX</t>
+          <t>B0BLRK37TB</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AA-07</t>
+          <t>AA-12</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2857,12 +2857,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FBA76739</t>
+          <t>FBA76725</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B0BLRK37TB</t>
+          <t>B0BLKCSJ7Z</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AA-12</t>
+          <t>AM-C22</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -2893,12 +2893,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBA76725</t>
+          <t>FBA75682</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B0BLKCSJ7Z</t>
+          <t>B0B4FVV78V</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AM-C22</t>
+          <t>AM-C8</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2916,7 +2916,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -2929,12 +2929,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FBA75682</t>
+          <t>FBA79014</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B0B4FVV78V</t>
+          <t>B0CH4WFQF6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AM-C8</t>
+          <t>AI-09</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2952,7 +2952,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -2965,12 +2965,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FBA79014</t>
+          <t>FBA79230</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B0CH4WFQF6</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AI-09</t>
+          <t>AM-W46</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3001,12 +3001,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FBA79230</t>
+          <t>FBA76743</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0BLK8PXNY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AM-W46</t>
+          <t>AM-K2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3037,12 +3037,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBA76743</t>
+          <t>FBA79013</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B0BLK8PXNY</t>
+          <t>B0CH4TDGPG</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AM-K2</t>
+          <t>AI-08</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3060,7 +3060,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3073,12 +3073,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FBA79013</t>
+          <t>FBA78421</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B0CH4TDGPG</t>
+          <t>B0C594FZLM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>AI-08</t>
+          <t>AM-C34</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3096,7 +3096,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3109,12 +3109,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FBA78421</t>
+          <t>FBA75685</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B0C594FZLM</t>
+          <t>B0B4FXDHXW</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AM-C34</t>
+          <t>AM-C9</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBA75685</t>
+          <t>FBA75677</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B0B4FXDHXW</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AM-C9</t>
+          <t>AM-C5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3168,7 +3168,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>1687</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3181,12 +3181,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FBA75677</t>
+          <t>FBA76729</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0BLNDQ757</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AM-C5</t>
+          <t>AM-C26</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
-        <v>1712</v>
+        <v>1</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3217,12 +3217,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FBA76729</t>
+          <t>FBA76735</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B0BLNDQ757</t>
+          <t>B0BLKGPL4X</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AM-C26</t>
+          <t>AA-08</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3253,12 +3253,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FBA76735</t>
+          <t>FBA76736</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B0BLKGPL4X</t>
+          <t>B0BLS63XCL</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AA-08</t>
+          <t>AA-09</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3289,12 +3289,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBA76736</t>
+          <t>FBA76741</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B0BLS63XCL</t>
+          <t>B0BLS2HJ68</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AA-09</t>
+          <t>AA-14</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3312,7 +3312,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3325,12 +3325,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBA76741</t>
+          <t>FBA76863</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B0BLS2HJ68</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AA-14</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3348,7 +3348,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>149</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3361,12 +3361,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FBA76863</t>
+          <t>FBA78424</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AM-C37</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>148</v>
+        <v>2</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3397,12 +3397,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FBA78424</t>
+          <t>FBA78419</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0C55M2GBN</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AM-C37</t>
+          <t>AM-A1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3420,7 +3420,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3433,12 +3433,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FBA78419</t>
+          <t>FBA76737</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B0C55M2GBN</t>
+          <t>B0C59G1C4N</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AM-A1</t>
+          <t>AA-10</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3456,7 +3456,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3469,12 +3469,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FBA76737</t>
+          <t>FBA76732</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B0C59G1C4N</t>
+          <t>B0BLKCB2JY</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AA-10</t>
+          <t>AS-01</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3492,7 +3492,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FBA76732</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B0BLKCB2JY</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AS-01</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3541,12 +3541,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA79356</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AA-19 WL</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3577,12 +3577,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FBA79356</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AA-19 WL</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3600,7 +3600,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
-        <v>172</v>
+        <v>977</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3613,12 +3613,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3636,7 +3636,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
-        <v>1083</v>
+        <v>350</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -3649,12 +3649,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3672,7 +3672,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>380</v>
+        <v>1577</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3685,12 +3685,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA79820</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AC-3XL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3708,7 +3708,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>1584</v>
+        <v>724</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3721,12 +3721,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBA79820</t>
+          <t>FBA79815</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AC-3XL</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3744,7 +3744,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
-        <v>727</v>
+        <v>209</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -3757,12 +3757,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA79815</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
-        <v>208</v>
+        <v>868</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -3793,12 +3793,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>881</v>
+        <v>1336</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -3829,12 +3829,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3852,7 +3852,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
-        <v>1336</v>
+        <v>867</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -3865,12 +3865,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AH-60 RD</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3888,7 +3888,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>904</v>
+        <v>437</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -3901,12 +3901,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA79841</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AH-60 RD</t>
+          <t>AH-60 BL</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>441</v>
+        <v>346</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -3937,12 +3937,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AH-60 BL</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3960,7 +3960,7 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>373</v>
+        <v>522</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -3973,12 +3973,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>545</v>
+        <v>203</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4009,12 +4009,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA79958</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4045,12 +4045,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA79961</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -4068,7 +4068,7 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
-        <v>221</v>
+        <v>368</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4081,12 +4081,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA79962</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AM-Mix4</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -4104,7 +4104,7 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="n">
-        <v>380</v>
+        <v>95</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4117,12 +4117,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FBA79962</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AM-Mix4</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -4140,7 +4140,7 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4153,12 +4153,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -4176,7 +4176,7 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4189,12 +4189,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA79968</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -4212,7 +4212,7 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4225,12 +4225,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA79972</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -4248,7 +4248,7 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4261,12 +4261,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-W47 WIRELESS</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -4284,7 +4284,7 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="n">
-        <v>206</v>
+        <v>151</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="n">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -5341,12 +5341,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA79904</t>
+          <t>FBA79654</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+          <t>AM-C11 Pro - AM-C11 &amp; AA-05</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -5364,7 +5364,7 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="n">
-        <v>10</v>
+        <v>566</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -5377,12 +5377,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA79654</t>
+          <t>FBA79826</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AM-C11 Pro - AM-C11 &amp; AA-05</t>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -5400,7 +5400,7 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="n">
-        <v>566</v>
+        <v>2</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -5413,12 +5413,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA79655</t>
+          <t>FBA79846</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AM-C44 Pro - AM-C44 &amp; AA-05</t>
+          <t>AM-C11X Pro - AM-C11x &amp; AA-05</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -5436,7 +5436,7 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -5449,12 +5449,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA79826</t>
+          <t>FBA79822</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+          <t>KB-01 (AM-W32 + AI-12)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -5472,7 +5472,7 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -5485,12 +5485,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA79846</t>
+          <t>FBA79825</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>AM-C11X Pro - AM-C11x &amp; AA-05</t>
+          <t>GB-02 (AM-C43 + AI-11)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -5508,7 +5508,7 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -5521,12 +5521,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FBA79844</t>
+          <t>FBA79833</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>PB-08 (AM-C1 + AI-04)</t>
+          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -5557,12 +5557,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FBA79822</t>
+          <t>FBA79845</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>KB-01 (AM-W32 + AI-12)</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -5580,7 +5580,7 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -5593,12 +5593,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FBA79825</t>
+          <t>FBA79824</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>GB-02 (AM-C43 + AI-11)</t>
+          <t>GB-01 (AM-C43 +AI-10)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -5616,7 +5616,7 @@
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -5629,12 +5629,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FBA79830</t>
+          <t>FBA79653</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
+          <t>AM-C45 Pro - AM-C45 &amp; AA-05</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -5652,7 +5652,7 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -5665,12 +5665,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FBA79833</t>
+          <t>FBA79832</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
+          <t>GB-05 (AM-C43 + AI-06)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -5688,7 +5688,7 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -5701,12 +5701,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FBA79845</t>
+          <t>FBA79906</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>UB-02 (AM-S1 + AA-21)</t>
+          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -5724,7 +5724,7 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -5737,12 +5737,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FBA79824</t>
+          <t>FBA79847</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>GB-01 (AM-C43 +AI-10)</t>
+          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -5760,7 +5760,7 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -5773,12 +5773,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FBA79653</t>
+          <t>FBA79831</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>AM-C45 Pro - AM-C45 &amp; AA-05</t>
+          <t>GB-04 (AM-C45 + AI-06)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -5796,7 +5796,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FBA79832</t>
+          <t>FBA79905</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>GB-05 (AM-C43 + AI-06)</t>
+          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -5832,7 +5832,7 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -5845,12 +5845,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FBA79906</t>
+          <t>FBA79835</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -5868,7 +5868,7 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FBA79834</t>
+          <t>FBA79836</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>B0FJ8T4WXM</t>
+          <t>B0FJ8Z1W81</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
+          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -5904,7 +5904,7 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -5917,12 +5917,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FBA79847</t>
+          <t>FBA79908</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
+          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -5940,7 +5940,7 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -5953,12 +5953,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FBA79831</t>
+          <t>FBA80074</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>B0FJ8W5Y9Q</t>
+          <t>B0GY827J9C</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>GB-04 (AM-C45 + AI-06)</t>
+          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -5976,7 +5976,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -5989,12 +5989,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FBA79905</t>
+          <t>FBA80076</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0GY857139</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+          <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -6012,7 +6012,7 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -6025,12 +6025,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FBA79835</t>
+          <t>FBA80105</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>B0FJ8TWCQZ</t>
+          <t>B0H2FNV2RC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
+          <t>UB-05 (AM-S2+AA-21)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -6048,7 +6048,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -6061,12 +6061,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FBA79836</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>B0FJ8Z1W81</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -6084,11 +6084,11 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -6097,12 +6097,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FBA79908</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6120,11 +6120,11 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -6133,12 +6133,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FBA80074</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>B0GY827J9C</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -6156,11 +6156,11 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -6169,12 +6169,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FBA80076</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>B0GY857139</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -6192,11 +6192,11 @@
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -6205,12 +6205,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FBA80105</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>B0H2FNV2RC</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>UB-05 (AM-S2+AA-21)</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -6228,11 +6228,11 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -6241,12 +6241,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FBA75676</t>
+          <t>FBA79482</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>AM-C4</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -6264,11 +6264,11 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -6300,11 +6300,11 @@
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -6313,12 +6313,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FBA75675</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>AM-C3</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -6336,11 +6336,11 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -6349,12 +6349,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FBA79448</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -6372,11 +6372,11 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -6385,12 +6385,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -6408,11 +6408,11 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -6421,12 +6421,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FBA75689</t>
+          <t>FBA79815</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>AM-W13</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -6444,11 +6444,11 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -6457,12 +6457,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FBA79103</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>AI-10</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -6493,12 +6493,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FBA75688</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>AM-W12</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -6529,12 +6529,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA75676</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-C4</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -6552,11 +6552,11 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -6565,12 +6565,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA75690</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-C10</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -6588,11 +6588,11 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -6601,12 +6601,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FBA79008</t>
+          <t>FBA75675</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>AI-06</t>
+          <t>AM-C3</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -6624,11 +6624,11 @@
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -6637,12 +6637,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FBA79482</t>
+          <t>FBA79448</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>AM-W35</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -6660,11 +6660,11 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -6673,12 +6673,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>FBA75677</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>AM-C5</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -6696,11 +6696,11 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -6709,12 +6709,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA75689</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AM-W13</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -6732,11 +6732,11 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -6745,12 +6745,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA79103</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AI-10</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -6768,11 +6768,11 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -6781,12 +6781,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA75688</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AM-W12</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -6804,11 +6804,11 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -6817,12 +6817,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -6840,11 +6840,11 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -6853,12 +6853,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FBA79379</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>AM-C45</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -6876,11 +6876,11 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -6889,12 +6889,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA79008</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -6912,11 +6912,11 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -6925,12 +6925,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA79482</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -6948,11 +6948,11 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -6961,12 +6961,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA75677</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AM-C5</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -6984,11 +6984,11 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -6997,12 +6997,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -7020,11 +7020,11 @@
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -7033,12 +7033,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>FBA75691</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>AM-W14</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -7056,11 +7056,11 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -7069,12 +7069,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FBA75692</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>AM-C11</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -7092,11 +7092,11 @@
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -7105,12 +7105,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -7128,11 +7128,11 @@
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -7141,12 +7141,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FBA79446</t>
+          <t>FBA79379</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>AM-W33</t>
+          <t>AM-C45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -7164,11 +7164,11 @@
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -7177,12 +7177,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -7200,11 +7200,11 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -7213,12 +7213,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FBA75684</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>AA-04</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -7236,11 +7236,11 @@
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -7249,12 +7249,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FBA76414</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>AA-05</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -7272,11 +7272,11 @@
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -7285,12 +7285,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>AH-60 BL</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -7308,11 +7308,11 @@
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -7321,12 +7321,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FBA79447</t>
+          <t>FBA75691</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>AM-W34</t>
+          <t>AM-W14</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -7344,11 +7344,11 @@
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -7357,12 +7357,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FBA79230</t>
+          <t>FBA75692</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>AM-W46</t>
+          <t>AM-C11</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -7380,11 +7380,11 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -7393,12 +7393,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -7416,11 +7416,11 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -7429,12 +7429,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FBA79976</t>
+          <t>FBA79446</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>JT-01, BM 320 Pro</t>
+          <t>AM-W33</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -7452,11 +7452,11 @@
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -7465,12 +7465,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FBA79983</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>B0GN321RXQ</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>AM-W48</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -7488,11 +7488,11 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -7501,12 +7501,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FBA79956</t>
+          <t>FBA75684</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>B0GMPGNXX3</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>A3-XLR</t>
+          <t>AA-04</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -7524,11 +7524,11 @@
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -7537,12 +7537,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA76414</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AA-05</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -7560,11 +7560,11 @@
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -7573,12 +7573,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79841</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AH-60 BL</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -7596,11 +7596,11 @@
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -7609,12 +7609,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA79447</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>AH-60 RD</t>
+          <t>AM-W34</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -7632,11 +7632,11 @@
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -7645,12 +7645,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FBA80013</t>
+          <t>FBA79230</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>B0GTZLGPFR</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>XM-16</t>
+          <t>AM-W46</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -7668,11 +7668,11 @@
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -7681,12 +7681,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FBA80014</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>B0GTZ9X8Q2</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>XM-24</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -7704,11 +7704,11 @@
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -7717,12 +7717,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79976</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>JT-01, BM 320 Pro</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -7740,11 +7740,11 @@
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -7753,12 +7753,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA79983</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0GN321RXQ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>AM-W48</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -7776,11 +7776,11 @@
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -7789,12 +7789,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79956</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0GMPGNXX3</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>A3-XLR</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -7812,11 +7812,11 @@
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -7825,12 +7825,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -7848,11 +7848,11 @@
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -7861,12 +7861,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -7884,11 +7884,11 @@
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -7897,12 +7897,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AH-60 RD</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -7920,11 +7920,11 @@
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -7933,12 +7933,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA80013</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0GTZLGPFR</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>XM-16</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -7956,11 +7956,11 @@
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -7969,12 +7969,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>FBA79482</t>
+          <t>FBA80014</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0GTZ9X8Q2</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>XM-24</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -7992,11 +7992,11 @@
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -8005,12 +8005,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>FBA75690</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>AM-C10</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -8028,11 +8028,11 @@
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -8041,12 +8041,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -8064,11 +8064,11 @@
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -8077,12 +8077,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -8100,11 +8100,11 @@
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -8113,12 +8113,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -8136,11 +8136,11 @@
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -8149,12 +8149,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FBA79815</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -8172,11 +8172,11 @@
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -8185,12 +8185,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AI-04</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -8208,11 +8208,11 @@
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -8221,12 +8221,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -8244,11 +8244,11 @@
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -8257,12 +8257,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA79108</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AM-W16</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -8280,7 +8280,7 @@
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -8293,12 +8293,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -8316,7 +8316,7 @@
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="n">
-        <v>160</v>
+        <v>33</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -8329,12 +8329,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA79958</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -8352,7 +8352,7 @@
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -8365,12 +8365,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA80124</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0HBWDYW2G</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>AI-04</t>
+          <t>AA-26 Pro</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -8388,11 +8388,11 @@
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="n">
-        <v>73</v>
+        <v>1000</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -8401,12 +8401,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA80116</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0HBW4XTRH</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AH-40 Pro</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -8424,11 +8424,11 @@
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -8437,12 +8437,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FBA79108</t>
+          <t>FBA80117</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0HBW4T618</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>AM-W16</t>
+          <t>AH-53 Pro</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -8460,11 +8460,11 @@
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -8473,12 +8473,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -8496,11 +8496,11 @@
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
-        <v>34</v>
+        <v>504</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -8509,12 +8509,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -8532,11 +8532,11 @@
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
-        <v>11</v>
+        <v>501</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -8545,12 +8545,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FBA80124</t>
+          <t>FBA75687</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>B0HBWDYW2G</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>AA-26 Pro</t>
+          <t>AM-W11</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -8568,11 +8568,11 @@
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -8581,12 +8581,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FBA80116</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>B0HBW4XTRH</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>AH-40 Pro</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -8604,11 +8604,11 @@
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
-        <v>100</v>
+        <v>2040</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -8617,12 +8617,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>FBA80117</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>B0HBW4T618</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>AH-53 Pro</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -8640,11 +8640,11 @@
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
-        <v>50</v>
+        <v>480</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -8653,12 +8653,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -8676,7 +8676,7 @@
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
-        <v>504</v>
+        <v>1008</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -8689,12 +8689,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AM-C2</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -8712,11 +8712,11 @@
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -8725,12 +8725,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FBA75687</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>AM-W11</t>
+          <t>AM-W47 WIRED</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -8748,7 +8748,7 @@
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -8761,12 +8761,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-W47 WIRLESS</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -8784,11 +8784,11 @@
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
-        <v>2040</v>
+        <v>160</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -8797,12 +8797,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>AM-W47 WIRLESS</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -8820,7 +8820,7 @@
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
-        <v>480</v>
+        <v>1340</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -8833,12 +8833,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -8856,7 +8856,7 @@
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -8869,12 +8869,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA76597</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>AM-C2</t>
+          <t>AA-06</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -8905,12 +8905,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA75683</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>AM-W47 WIRED</t>
+          <t>AA-03</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -8928,7 +8928,7 @@
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -8941,12 +8941,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79962</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>AM-W47 WIRLESS</t>
+          <t>BE-4T</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -8964,7 +8964,7 @@
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -8977,12 +8977,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA80114</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0HBVYQLS4</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>AM-W47 WIRLESS</t>
+          <t>AH-53</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -9000,11 +9000,11 @@
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
-        <v>1340</v>
+        <v>100</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -9013,12 +9013,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA80115</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0HBWD8WWW</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AH-50-DH</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9036,11 +9036,11 @@
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -9049,12 +9049,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>FBA76597</t>
+          <t>FBA80121</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0HBWHNKDS</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>AA-06</t>
+          <t>AM-C55</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -9072,11 +9072,11 @@
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="n">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -9085,12 +9085,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FBA75683</t>
+          <t>FBA80123</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0HBWM83FL</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>AA-03</t>
+          <t>AM-W25</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -9108,11 +9108,11 @@
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -9121,12 +9121,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FBA79962</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>BE-4T</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -9144,11 +9144,11 @@
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -9157,12 +9157,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>FBA80114</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>B0HBVYQLS4</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>AH-53</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -9180,7 +9180,7 @@
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -9193,12 +9193,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>FBA80115</t>
+          <t>FBA79961</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>B0HBWD8WWW</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>AH-50-DH</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -9216,7 +9216,7 @@
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -9229,12 +9229,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>FBA80121</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>B0HBWHNKDS</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>AM-C55</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -9252,7 +9252,7 @@
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>FBA80123</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>B0HBWM83FL</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>AM-W25</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -9288,7 +9288,7 @@
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -9301,14 +9301,10 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FBA79445</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>B0DFMLS8JG</t>
-        </is>
-      </c>
+          <t>FBA80181</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9316,7 +9312,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AI-04 Pro</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -9337,12 +9333,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9352,7 +9348,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -9360,11 +9356,11 @@
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -9373,12 +9369,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9388,7 +9384,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -9396,11 +9392,11 @@
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
-        <v>1500</v>
+        <v>5004</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -9409,12 +9405,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9424,7 +9420,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -9432,11 +9428,11 @@
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
-        <v>100</v>
+        <v>2010</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -9445,12 +9441,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9460,7 +9456,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -9468,7 +9464,7 @@
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -9481,10 +9477,14 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>FBA80181</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr"/>
+          <t>FBA79972</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>B0GCP1J2HC</t>
+        </is>
+      </c>
       <c r="C252" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9492,7 +9492,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>AI-04 Pro</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -9500,11 +9500,11 @@
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -9513,12 +9513,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA79983</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0GN321RXQ</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AM-S6</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -9536,7 +9536,7 @@
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -9549,12 +9549,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -9572,11 +9572,11 @@
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
-        <v>5004</v>
+        <v>888</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -9585,12 +9585,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -9608,7 +9608,7 @@
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
-        <v>2010</v>
+        <v>2092</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -9621,12 +9621,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA79968</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -9644,7 +9644,7 @@
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -9657,12 +9657,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA80109</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0H2ZCQFTZ</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -9680,11 +9680,11 @@
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -9693,12 +9693,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>FBA79983</t>
+          <t>FBA80125</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>B0GN321RXQ</t>
+          <t>B0H15CTPGS</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>AM-S6</t>
+          <t>AA-27</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -9729,12 +9729,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA80126</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0HBWQP96C</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AA-28</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -9752,7 +9752,7 @@
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="n">
-        <v>888</v>
+        <v>60</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -9765,12 +9765,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA80119</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0HBWNJSSQ</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-C53</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -9788,11 +9788,11 @@
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="n">
-        <v>2092</v>
+        <v>510</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -9801,12 +9801,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA80120</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0HBWNWZVC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>AM-C54</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -9824,7 +9824,7 @@
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="n">
-        <v>600</v>
+        <v>510</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -9837,12 +9837,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>FBA80109</t>
+          <t>FBA80122</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>B0H2ZCQFTZ</t>
+          <t>B0HBWGNK1T</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>AM-C56</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -9860,7 +9860,7 @@
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="n">
-        <v>50</v>
+        <v>504</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -9869,186 +9869,6 @@
       </c>
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>FBA80125</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>B0H15CTPGS</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>AA-27</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="n">
-        <v>50</v>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>FBA80126</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>B0HBWQP96C</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>AA-28</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="n">
-        <v>60</v>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>FBA80119</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>B0HBWNJSSQ</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>AM-C53</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
-      <c r="I265" t="n">
-        <v>510</v>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>FBA80120</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>B0HBWNWZVC</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>AM-C54</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="n">
-        <v>510</v>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>FBA80122</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>B0HBWGNK1T</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>AM-C56</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr"/>
-      <c r="I267" t="n">
-        <v>504</v>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L262"/>
+  <dimension ref="A1:L281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,7 +504,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>1156</v>
+        <v>1115</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>1708</v>
+        <v>1703</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>876</v>
+        <v>772</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>1173</v>
+        <v>1127</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>1717</v>
+        <v>1210</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>1590</v>
+        <v>1516</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1237,12 +1237,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA79444</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1273,12 +1273,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBA79444</t>
+          <t>FBA75690</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AM-C10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>109</v>
+        <v>445</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1309,12 +1309,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA75690</t>
+          <t>FBA75676</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AM-C10</t>
+          <t>AM-C4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>454</v>
+        <v>21</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1345,12 +1345,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBA75676</t>
+          <t>FBA75681</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0B4FZS38V</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AM-C4</t>
+          <t>AM-C7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1368,7 +1368,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1381,12 +1381,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA75681</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B0B4FZS38V</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AM-C7</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1404,7 +1404,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1417,12 +1417,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA78925</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AM-C11X</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1440,7 +1440,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1453,12 +1453,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA78925</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AM-C11X</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1489,12 +1489,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA78420</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0C5957W3P</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AM-C33</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1525,12 +1525,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FBA78420</t>
+          <t>FBA79008</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B0C5957W3P</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AM-C33</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1561,12 +1561,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FBA79008</t>
+          <t>FBA75688</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AI-06</t>
+          <t>AM-W12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1584,7 +1584,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>78</v>
+        <v>359</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1597,12 +1597,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FBA75688</t>
+          <t>FBA78976</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AM-W12</t>
+          <t>AA-22</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1620,7 +1620,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>363</v>
+        <v>276</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1633,12 +1633,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FBA78976</t>
+          <t>FBA79064</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AA-22</t>
+          <t>AA-25</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1656,7 +1656,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>284</v>
+        <v>515</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1669,12 +1669,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FBA79064</t>
+          <t>FBA79104</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AA-25</t>
+          <t>AI-11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>568</v>
+        <v>366</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1705,12 +1705,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FBA79104</t>
+          <t>FBA79379</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AI-11</t>
+          <t>AM-C45</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>371</v>
+        <v>671</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1741,12 +1741,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FBA79379</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AM-C45</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1764,7 +1764,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>672</v>
+        <v>4</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FBA75692</t>
+          <t>FBA79722</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0F2HYY7JF</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AM-C11</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1800,7 +1800,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1813,12 +1813,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA76716</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0BLK8DNPD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>AM-C13</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1836,7 +1836,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1849,12 +1849,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBA79722</t>
+          <t>FBA76730</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B0F2HYY7JF</t>
+          <t>B0BLKB6FRR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-C27</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1872,7 +1872,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1885,12 +1885,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBA76716</t>
+          <t>FBA78423</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B0BLK8DNPD</t>
+          <t>B0C598Q6PT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AM-C13</t>
+          <t>AM-C36</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1908,7 +1908,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -1921,12 +1921,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBA76730</t>
+          <t>FBA78974</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B0BLKB6FRR</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AM-C27</t>
+          <t>AA-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1944,7 +1944,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>358</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -1957,12 +1957,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA78423</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B0C598Q6PT</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AM-C36</t>
+          <t>AM-C2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1980,7 +1980,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -1993,12 +1993,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FBA78974</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AA-20</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2016,7 +2016,7 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>363</v>
+        <v>518</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2029,12 +2029,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA76742</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0BLKBJ5HN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AM-C2</t>
+          <t>AM-K1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2052,7 +2052,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2065,12 +2065,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA75689</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-W13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2088,7 +2088,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>591</v>
+        <v>212</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2101,12 +2101,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FBA76742</t>
+          <t>FBA75679</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B0BLKBJ5HN</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AM-K1</t>
+          <t>AA-02</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2124,7 +2124,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>11</v>
+        <v>771</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2137,12 +2137,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FBA75689</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AM-W13</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2160,7 +2160,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>227</v>
+        <v>1433</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2173,12 +2173,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FBA75679</t>
+          <t>FBA79355</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AA-02</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>771</v>
+        <v>33</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2209,12 +2209,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA78203</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AM-C30</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2232,7 +2232,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>1463</v>
+        <v>7</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2245,12 +2245,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FBA79355</t>
+          <t>FBA79010</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2268,7 +2268,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2281,12 +2281,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FBA78203</t>
+          <t>FBA75691</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AM-C30</t>
+          <t>AM-W14</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>7</v>
+        <v>166</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2317,12 +2317,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FBA79010</t>
+          <t>FBA78205</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0C539RBGL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AM-C32</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FBA75691</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>AM-W14</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2376,7 +2376,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2389,12 +2389,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FBA78205</t>
+          <t>FBA77011</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B0C539RBGL</t>
+          <t>B0BPMN89NG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AM-C32</t>
+          <t>AM-C29</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2412,7 +2412,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2425,12 +2425,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA78425</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0C55QXL83</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-C38</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2448,7 +2448,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2461,12 +2461,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FBA77011</t>
+          <t>FBA76715</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B0BPMN89NG</t>
+          <t>B0BLK31PYH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>AM-C29</t>
+          <t>AM-C12</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2497,12 +2497,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FBA78425</t>
+          <t>FBA78206</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B0C55QXL83</t>
+          <t>B0C4YSV3XL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AM-C38</t>
+          <t>AM-W15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2520,7 +2520,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2533,12 +2533,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FBA76715</t>
+          <t>FBA79070</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B0BLK31PYH</t>
+          <t>B0CLH7G5WH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AM-C12</t>
+          <t>AI-02</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2569,12 +2569,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FBA78206</t>
+          <t>FBA76721</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B0C4YSV3XL</t>
+          <t>B0BLKB55BM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AM-W15</t>
+          <t>AM-C18</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2605,12 +2605,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FBA79070</t>
+          <t>FBA76726</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B0CLH7G5WH</t>
+          <t>B0BLKD4815</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AI-02</t>
+          <t>AM-C23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2628,7 +2628,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2641,12 +2641,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBA76721</t>
+          <t>FBA78422</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B0BLKB55BM</t>
+          <t>B0C598MNMC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AM-C18</t>
+          <t>AM-C35</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA76726</t>
+          <t>FBA76718</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B0BLKD4815</t>
+          <t>B0BLKD8FVG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AM-C23</t>
+          <t>AM-C15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2700,7 +2700,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2713,12 +2713,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FBA78422</t>
+          <t>FBA76734</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B0C598MNMC</t>
+          <t>B0BLKHVCDX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AM-C35</t>
+          <t>AA-07</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2736,7 +2736,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2749,12 +2749,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FBA76718</t>
+          <t>FBA76739</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B0BLKD8FVG</t>
+          <t>B0BLRK37TB</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AM-C15</t>
+          <t>AA-12</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2785,12 +2785,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FBA76734</t>
+          <t>FBA76725</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B0BLKHVCDX</t>
+          <t>B0BLKCSJ7Z</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AA-07</t>
+          <t>AM-C22</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2821,12 +2821,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FBA76739</t>
+          <t>FBA75682</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B0BLRK37TB</t>
+          <t>B0B4FVV78V</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AA-12</t>
+          <t>AM-C8</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2857,12 +2857,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FBA76725</t>
+          <t>FBA79014</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B0BLKCSJ7Z</t>
+          <t>B0CH4WFQF6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AM-C22</t>
+          <t>AI-09</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -2893,12 +2893,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBA75682</t>
+          <t>FBA79230</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B0B4FVV78V</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AM-C8</t>
+          <t>AM-W46</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2916,7 +2916,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -2929,12 +2929,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FBA79014</t>
+          <t>FBA76743</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B0CH4WFQF6</t>
+          <t>B0BLK8PXNY</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AI-09</t>
+          <t>AM-K2</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2952,7 +2952,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -2965,12 +2965,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FBA79230</t>
+          <t>FBA79013</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0CH4TDGPG</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AM-W46</t>
+          <t>AI-08</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3001,12 +3001,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FBA76743</t>
+          <t>FBA78421</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B0BLK8PXNY</t>
+          <t>B0C594FZLM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AM-K2</t>
+          <t>AM-C34</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3037,12 +3037,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBA79013</t>
+          <t>FBA75685</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B0CH4TDGPG</t>
+          <t>B0B4FXDHXW</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AI-08</t>
+          <t>AM-C9</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3073,12 +3073,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FBA78421</t>
+          <t>FBA75677</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B0C594FZLM</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>AM-C34</t>
+          <t>AM-C5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3096,7 +3096,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>1684</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3109,12 +3109,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FBA75685</t>
+          <t>FBA76729</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B0B4FXDHXW</t>
+          <t>B0BLNDQ757</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AM-C9</t>
+          <t>AM-C26</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3145,12 +3145,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBA75677</t>
+          <t>FBA76735</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0BLKGPL4X</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AM-C5</t>
+          <t>AA-08</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3168,7 +3168,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
-        <v>1687</v>
+        <v>1</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3181,12 +3181,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FBA76729</t>
+          <t>FBA76736</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B0BLNDQ757</t>
+          <t>B0BLS63XCL</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AM-C26</t>
+          <t>AA-09</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3217,12 +3217,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FBA76735</t>
+          <t>FBA76741</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B0BLKGPL4X</t>
+          <t>B0BLS2HJ68</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AA-08</t>
+          <t>AA-14</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3253,12 +3253,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FBA76736</t>
+          <t>FBA76863</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B0BLS63XCL</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AA-09</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>139</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3289,12 +3289,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBA76741</t>
+          <t>FBA78424</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B0BLS2HJ68</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AA-14</t>
+          <t>AM-C37</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3312,7 +3312,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3325,12 +3325,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBA76863</t>
+          <t>FBA78419</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0C55M2GBN</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AM-A1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3348,7 +3348,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3361,12 +3361,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FBA78424</t>
+          <t>FBA76737</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0C59G1C4N</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AM-C37</t>
+          <t>AA-10</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3397,12 +3397,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FBA78419</t>
+          <t>FBA76732</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B0C55M2GBN</t>
+          <t>B0BLKCB2JY</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AM-A1</t>
+          <t>AS-01</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3420,7 +3420,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3433,12 +3433,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FBA76737</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B0C59G1C4N</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AA-10</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3456,7 +3456,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3469,12 +3469,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FBA76732</t>
+          <t>FBA79356</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B0BLKCB2JY</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AS-01</t>
+          <t>AA-19 WL</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3492,7 +3492,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
-        <v>60</v>
+        <v>871</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3541,12 +3541,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FBA79356</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AA-19 WL</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>172</v>
+        <v>346</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3577,12 +3577,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3600,7 +3600,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
-        <v>977</v>
+        <v>1573</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3613,12 +3613,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA79820</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AC-3XL</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3636,7 +3636,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
-        <v>350</v>
+        <v>703</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -3649,12 +3649,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA79815</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3672,7 +3672,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>1577</v>
+        <v>209</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3685,12 +3685,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBA79820</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AC-3XL</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3708,7 +3708,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>724</v>
+        <v>845</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3721,12 +3721,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBA79815</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3744,7 +3744,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
-        <v>209</v>
+        <v>1302</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -3757,12 +3757,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
-        <v>868</v>
+        <v>625</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -3793,12 +3793,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AH-60 RD</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>1336</v>
+        <v>428</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -3829,12 +3829,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA79841</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AH-60 BL</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3852,7 +3852,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
-        <v>867</v>
+        <v>333</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -3865,12 +3865,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AH-60 RD</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3888,7 +3888,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>437</v>
+        <v>203</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -3901,12 +3901,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA79958</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AH-60 BL</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>346</v>
+        <v>180</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -3937,12 +3937,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA79961</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3960,7 +3960,7 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>522</v>
+        <v>82</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -3973,12 +3973,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA79962</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AM-Mix4</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>203</v>
+        <v>88</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4009,12 +4009,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
-        <v>222</v>
+        <v>45</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4045,12 +4045,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -4068,7 +4068,7 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
-        <v>368</v>
+        <v>7</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4081,12 +4081,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FBA79962</t>
+          <t>FBA79968</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AM-Mix4</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -4104,7 +4104,7 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4117,12 +4117,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79972</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -4140,7 +4140,7 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4153,12 +4153,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AM-W47 WIRELESS</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -4176,7 +4176,7 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4189,12 +4189,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>AM-W47 WIRED</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -4212,7 +4212,7 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4225,12 +4225,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79957</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-W23</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -4248,7 +4248,7 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>228</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4261,12 +4261,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79654</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>AM-W47 WIRELESS</t>
+          <t>AM-C11 PRO</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -4284,7 +4284,7 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="n">
-        <v>36</v>
+        <v>564</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -4297,12 +4297,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA79956</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0GMPGNXX3</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>AM-W47 WIRED</t>
+          <t>A3-XLR</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -4320,7 +4320,7 @@
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="n">
-        <v>151</v>
+        <v>769</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -4333,12 +4333,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FBA79957</t>
+          <t>FBA80007</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>AM-W23</t>
+          <t>MT-12</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
-        <v>238</v>
+        <v>1</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4369,12 +4369,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FBA79654</t>
+          <t>FBA79979</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>AM-C11 PRO</t>
+          <t>AK-37-B</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>564</v>
+        <v>206</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4405,12 +4405,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FBA79956</t>
+          <t>FBA79980</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B0GMPGNXX3</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>A3-XLR</t>
+          <t>AK-37-W</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -4428,7 +4428,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="n">
-        <v>799</v>
+        <v>21</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -4441,12 +4441,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FBA80007</t>
+          <t>FBA80011</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0GTZND3ZN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>MT-12</t>
+          <t>AM-Pro16</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -4464,7 +4464,7 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -4477,12 +4477,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBA79979</t>
+          <t>FBA80013</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0GTZLGPFR</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>AK-37-B</t>
+          <t>XM-16</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -4500,7 +4500,7 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
-        <v>206</v>
+        <v>2</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBA79980</t>
+          <t>FBA80014</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0GTZ9X8Q2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>AK-37-W</t>
+          <t>XM-24</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -4536,7 +4536,7 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -4549,12 +4549,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FBA80011</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B0GTZND3ZN</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>AM-Pro16</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -4572,7 +4572,7 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -4585,12 +4585,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FBA80013</t>
+          <t>FBA80005</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B0GTZLGPFR</t>
+          <t>B0GW96CQMG</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>XM-16</t>
+          <t>T-835</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -4608,7 +4608,7 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -4621,12 +4621,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FBA80014</t>
+          <t>FBA79975</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B0GTZ9X8Q2</t>
+          <t>B0GXP7LJ75</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>XM-24</t>
+          <t>AE831</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -4644,7 +4644,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79996</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-C49</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -4680,7 +4680,7 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>10</v>
+        <v>362</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -4693,12 +4693,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FBA80005</t>
+          <t>FBA79995</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B0GW96CQMG</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>T-835</t>
+          <t>AM-C50</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -4716,7 +4716,7 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>11</v>
+        <v>382</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -4729,12 +4729,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FBA79975</t>
+          <t>FBA80009</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B0GXP7LJ75</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>AE831</t>
+          <t>AM-C51</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -4752,7 +4752,7 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>167</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -4765,12 +4765,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FBA79996</t>
+          <t>FBA80010</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>AM-C49</t>
+          <t>AM-C52</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -4788,7 +4788,7 @@
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>364</v>
+        <v>161</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -4801,12 +4801,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBA79995</t>
+          <t>FBA79998</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0GW8YC59C</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>AM-C50</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -4824,7 +4824,7 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
-        <v>382</v>
+        <v>1</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -4837,12 +4837,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA80009</t>
+          <t>FBA79999</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0GW92TVVC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>AM-C51</t>
+          <t>JTG800</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -4860,7 +4860,7 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -4873,12 +4873,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA80010</t>
+          <t>FBA80000</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0GW8XGPB2</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>AM-C52</t>
+          <t>DP-718H</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -4896,7 +4896,7 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="n">
-        <v>161</v>
+        <v>13</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -4909,12 +4909,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBA79998</t>
+          <t>FBA80001</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0GW8YC59C</t>
+          <t>B0GW92TQGV</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>USB718</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -4932,7 +4932,7 @@
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -4945,12 +4945,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBA79999</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0GW92TVVC</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>JTG800</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -4968,7 +4968,7 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -4981,12 +4981,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBA80000</t>
+          <t>FBA80085</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0GW8XGPB2</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>DP-718H</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -5004,7 +5004,7 @@
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="n">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -5017,12 +5017,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBA80001</t>
+          <t>FBA80002</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0GW92TQGV</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>USB718</t>
+          <t>AM-W33 pro</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -5040,7 +5040,7 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="n">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -5053,12 +5053,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA80003</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AM-W32 pro</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -5076,7 +5076,7 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -5089,12 +5089,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBA80085</t>
+          <t>FBA80004</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>AM-W36 PRO</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -5112,7 +5112,7 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="n">
-        <v>154</v>
+        <v>30</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -5125,12 +5125,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBA80002</t>
+          <t>FBA80109</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0H2ZCQFTZ</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>AM-W33 pro</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -5148,7 +5148,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="n">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -5161,12 +5161,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBA80003</t>
+          <t>FBA80110</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0GW92TTMS</t>
+          <t>B0H2Z6R6V8</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>AM-W32 pro</t>
+          <t>X5</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -5184,7 +5184,7 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -5197,12 +5197,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA80004</t>
+          <t>FBA80142</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0H3LHF2WW</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>AM-W36 PRO</t>
+          <t>AM-C5 White</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -5220,7 +5220,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
-        <v>49</v>
+        <v>251</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -5233,12 +5233,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FBA80109</t>
+          <t>FBA79904</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0H2ZCQFTZ</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -5269,12 +5269,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FBA80110</t>
+          <t>FBA79654</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0H2Z6R6V8</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>X5</t>
+          <t>AM-C11 Pro - AM-C11 &amp; AA-05</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -5292,7 +5292,7 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="n">
-        <v>8</v>
+        <v>564</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -5305,12 +5305,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA80142</t>
+          <t>FBA79655</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0H3LHF2WW</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>AM-C5 White</t>
+          <t>AM-C44 Pro - AM-C44 &amp; AA-05</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -5328,7 +5328,7 @@
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="n">
-        <v>251</v>
+        <v>4</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -5341,12 +5341,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA79654</t>
+          <t>FBA79826</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AM-C11 Pro - AM-C11 &amp; AA-05</t>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -5364,7 +5364,7 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="n">
-        <v>566</v>
+        <v>2</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -5377,12 +5377,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA79826</t>
+          <t>FBA79846</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+          <t>AM-C11X Pro - AM-C11x &amp; AA-05</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -5400,7 +5400,7 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -5413,12 +5413,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA79846</t>
+          <t>FBA79822</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AM-C11X Pro - AM-C11x &amp; AA-05</t>
+          <t>KB-01 (AM-W32 + AI-12)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -5436,7 +5436,7 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -5449,12 +5449,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA79822</t>
+          <t>FBA79825</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>KB-01 (AM-W32 + AI-12)</t>
+          <t>GB-02 (AM-C43 + AI-11)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -5472,7 +5472,7 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -5485,12 +5485,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA79825</t>
+          <t>FBA79830</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>GB-02 (AM-C43 + AI-11)</t>
+          <t>GB-03 (AI-12 + AM-C43)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -5508,7 +5508,7 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -8077,12 +8077,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA80124</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0HBWDYW2G</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AA-26 Pro</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -8100,11 +8100,11 @@
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="n">
-        <v>54</v>
+        <v>1000</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -8113,12 +8113,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA80116</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0HBW4XTRH</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AH-40 Pro</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -8136,11 +8136,11 @@
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -8149,12 +8149,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA80116</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0HBW4XTRH</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AH-40 Pro</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -8172,11 +8172,11 @@
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -8185,12 +8185,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA80117</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0HBW4T618</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>AI-04</t>
+          <t>AH-53 Pro</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -8208,11 +8208,11 @@
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -8221,12 +8221,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA80117</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0HBW4T618</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AH-53 Pro</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -8244,11 +8244,11 @@
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -8257,12 +8257,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FBA79108</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>AM-W16</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -8280,11 +8280,11 @@
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="n">
-        <v>28</v>
+        <v>504</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -8293,12 +8293,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -8316,11 +8316,11 @@
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="n">
-        <v>33</v>
+        <v>501</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -8329,12 +8329,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA75687</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>AM-W11</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -8352,11 +8352,11 @@
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Blinkit</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -8365,12 +8365,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>FBA80124</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>B0HBWDYW2G</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>AA-26 Pro</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -8388,7 +8388,7 @@
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -8401,12 +8401,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>FBA80116</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>B0HBW4XTRH</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>AH-40 Pro</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -8424,11 +8424,11 @@
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -8437,12 +8437,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FBA80117</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>B0HBW4T618</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>AH-53 Pro</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -8460,11 +8460,11 @@
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="n">
-        <v>50</v>
+        <v>480</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -8473,12 +8473,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA80085</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -8496,7 +8496,7 @@
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -8509,12 +8509,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -8532,7 +8532,7 @@
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -8545,12 +8545,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FBA75687</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>AM-W11</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -8568,7 +8568,7 @@
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -8581,12 +8581,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -8604,7 +8604,7 @@
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
-        <v>2040</v>
+        <v>504</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -8617,12 +8617,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>AM-C2</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -8640,11 +8640,11 @@
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -8653,12 +8653,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -8676,7 +8676,7 @@
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -8689,12 +8689,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>AM-C2</t>
+          <t>AM-W47 WIRLESS</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -8712,11 +8712,11 @@
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
-        <v>504</v>
+        <v>1840</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -8725,12 +8725,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>AM-W47 WIRED</t>
+          <t>AM-W47 WIRLESS</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -8761,12 +8761,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>AM-W47 WIRLESS</t>
+          <t>AM-W47 WIRED</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -8784,7 +8784,7 @@
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
-        <v>160</v>
+        <v>2000</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -8797,12 +8797,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>AM-W47 WIRLESS</t>
+          <t>AM-W47 WIRED</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -8820,7 +8820,7 @@
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
-        <v>1340</v>
+        <v>2000</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -8905,12 +8905,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FBA75683</t>
+          <t>FBA76597</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>AA-03</t>
+          <t>AA-06</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -8928,7 +8928,7 @@
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -8941,12 +8941,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>FBA79962</t>
+          <t>FBA75683</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>BE-4T</t>
+          <t>AA-03</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -8964,7 +8964,7 @@
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -8977,12 +8977,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>FBA80114</t>
+          <t>FBA79962</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>B0HBVYQLS4</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>AH-53</t>
+          <t>BE-4T</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -9000,7 +9000,7 @@
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -9013,12 +9013,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FBA80115</t>
+          <t>FBA79963</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>B0HBWD8WWW</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>AH-50-DH</t>
+          <t>AM-Pro8</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9036,11 +9036,11 @@
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -9049,12 +9049,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>FBA80121</t>
+          <t>FBA80114</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>B0HBWHNKDS</t>
+          <t>B0HBVYQLS4</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>AM-C55</t>
+          <t>AH-53</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -9072,7 +9072,7 @@
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -9085,12 +9085,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FBA80123</t>
+          <t>FBA80114</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>B0HBWM83FL</t>
+          <t>B0HBVYQLS4</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>AM-W25</t>
+          <t>AH-53</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -9108,11 +9108,11 @@
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -9121,12 +9121,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA80115</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0HBWD8WWW</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AH-50-DH</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -9144,11 +9144,11 @@
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -9157,12 +9157,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA80115</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0HBWD8WWW</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AH-50-DH</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -9180,11 +9180,11 @@
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -9193,12 +9193,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA80121</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0HBWHNKDS</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AM-C55</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -9216,7 +9216,7 @@
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -9229,12 +9229,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA80123</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0HBWM83FL</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AM-W25</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -9252,7 +9252,7 @@
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -9288,11 +9288,11 @@
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -9301,10 +9301,14 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FBA80181</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr"/>
+          <t>FBA80141</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>B0FJS57732</t>
+        </is>
+      </c>
       <c r="C247" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9312,7 +9316,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>AI-04 Pro</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -9333,12 +9337,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9348,7 +9352,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -9356,11 +9360,11 @@
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -9369,12 +9373,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9384,7 +9388,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -9392,7 +9396,7 @@
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
-        <v>5004</v>
+        <v>500</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -9405,12 +9409,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79964</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9420,7 +9424,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-Pro12</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -9428,7 +9432,7 @@
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
-        <v>2010</v>
+        <v>50</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -9441,12 +9445,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA79961</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9456,7 +9460,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -9464,7 +9468,7 @@
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -9477,12 +9481,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9492,7 +9496,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -9500,7 +9504,7 @@
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -9513,12 +9517,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FBA79983</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>B0GN321RXQ</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9528,7 +9532,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>AM-S6</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -9536,7 +9540,7 @@
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -9549,12 +9553,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9564,7 +9568,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -9572,7 +9576,7 @@
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
-        <v>888</v>
+        <v>100</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -9585,14 +9589,10 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>FBA79848</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
+          <t>FBA80299</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9600,7 +9600,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>M8 Speaker</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -9608,7 +9608,7 @@
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
-        <v>2092</v>
+        <v>20</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -9621,14 +9621,10 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>FBA79968</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>B0G53M9258</t>
-        </is>
-      </c>
+          <t>FBA80181</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9636,7 +9632,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>AI-04 Pro</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -9644,11 +9640,11 @@
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -9657,12 +9653,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>FBA80109</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>B0H2ZCQFTZ</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9672,7 +9668,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -9680,11 +9676,11 @@
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -9693,12 +9689,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>FBA80125</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>B0H15CTPGS</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9708,7 +9704,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>AA-27</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -9716,11 +9712,11 @@
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -9729,12 +9725,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>FBA80126</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>B0HBWQP96C</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9744,7 +9740,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>AA-28</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -9752,7 +9748,7 @@
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="n">
-        <v>60</v>
+        <v>2508</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -9765,12 +9761,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>FBA80119</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>B0HBWNJSSQ</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9780,7 +9776,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>AM-C53</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -9788,11 +9784,11 @@
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="n">
-        <v>510</v>
+        <v>2496</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -9801,12 +9797,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>FBA80120</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>B0HBWNWZVC</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9816,7 +9812,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>AM-C54</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -9824,11 +9820,11 @@
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="n">
-        <v>510</v>
+        <v>2010</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -9837,12 +9833,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>FBA80122</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>B0HBWGNK1T</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9852,7 +9848,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>AM-C56</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -9860,15 +9856,699 @@
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="n">
-        <v>504</v>
+        <v>3000</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>FBA79972</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>B0GCP1J2HC</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="n">
+        <v>200</v>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>FBA79972</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>B0GCP1J2HC</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="n">
+        <v>500</v>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>FBA79838</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>B0FQBX8J17</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>AH-40 SL</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>FBA79839</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>B0FQBXS6Y2</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>AH-45 BK</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="n">
+        <v>1512</v>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>FBA79983</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>B0GN321RXQ</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>AM-S6</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="n">
+        <v>49</v>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>FBA79848</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="n">
+        <v>976</v>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>FBA79848</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>FBA79848</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="n">
+        <v>888</v>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>FBA79848</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>FBA79848</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="n">
+        <v>92</v>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>FBA79830</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>B0FJ8TSQK1</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>GB-03 (AI-12 + AM-C43)</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>FBA79968</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>B0G53M9258</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>AI-14</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="n">
+        <v>500</v>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>FBA79968</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>B0G53M9258</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>AI-14</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="n">
+        <v>100</v>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>FBA80109</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>B0H2ZCQFTZ</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="n">
+        <v>50</v>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>FBA80125</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>B0H15CTPGS</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>AA-27</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="n">
+        <v>50</v>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>FBA80126</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>B0HBWQP96C</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>AA-28</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="n">
+        <v>60</v>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>FBA80119</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>B0HBWNJSSQ</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>AM-C53</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="n">
+        <v>510</v>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>FBA80120</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>B0HBWNWZVC</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>AM-C54</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="n">
+        <v>510</v>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>FBA80122</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>B0HBWGNK1T</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>AM-C56</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="n">
+        <v>504</v>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L281"/>
+  <dimension ref="A1:L270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8077,12 +8077,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FBA80124</t>
+          <t>FBA80116</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>B0HBWDYW2G</t>
+          <t>B0HBW4XTRH</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>AA-26 Pro</t>
+          <t>AH-40 Pro</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -8100,7 +8100,7 @@
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -8149,12 +8149,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FBA80116</t>
+          <t>FBA80117</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>B0HBW4XTRH</t>
+          <t>B0HBW4T618</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>AH-40 Pro</t>
+          <t>AH-53 Pro</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -8172,11 +8172,11 @@
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -8221,12 +8221,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FBA80117</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>B0HBW4T618</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>AH-53 Pro</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -8244,11 +8244,11 @@
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="n">
-        <v>50</v>
+        <v>504</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -8257,12 +8257,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -8280,7 +8280,7 @@
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="n">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -8293,12 +8293,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA75687</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AM-W11</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -8316,11 +8316,11 @@
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -8329,12 +8329,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FBA75687</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>AM-W11</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -8352,11 +8352,11 @@
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -8365,12 +8365,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -8401,12 +8401,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -8424,7 +8424,7 @@
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
-        <v>2000</v>
+        <v>480</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -8437,12 +8437,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA80085</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -8460,7 +8460,7 @@
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -8473,12 +8473,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FBA80085</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -8496,11 +8496,11 @@
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -8545,12 +8545,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -8581,12 +8581,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AM-C2</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -8617,12 +8617,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>AM-C2</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -8640,11 +8640,11 @@
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
-        <v>504</v>
+        <v>1000</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -8653,12 +8653,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-W47 WIRLESS</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -8676,11 +8676,11 @@
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
-        <v>1000</v>
+        <v>1840</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -8712,11 +8712,11 @@
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
-        <v>1840</v>
+        <v>2000</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -8725,12 +8725,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>AM-W47 WIRLESS</t>
+          <t>AM-W47 WIRED</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -8797,12 +8797,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>AM-W47 WIRED</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -8820,7 +8820,7 @@
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -8833,12 +8833,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA76597</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AA-06</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -8856,11 +8856,11 @@
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
-        <v>1000</v>
+        <v>504</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -8905,12 +8905,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FBA76597</t>
+          <t>FBA75683</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>AA-06</t>
+          <t>AA-03</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -8928,11 +8928,11 @@
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -8941,12 +8941,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>FBA75683</t>
+          <t>FBA79962</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>AA-03</t>
+          <t>BE-4T</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -8964,7 +8964,7 @@
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -8977,12 +8977,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>FBA79962</t>
+          <t>FBA79963</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>BE-4T</t>
+          <t>AM-Pro8</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -9000,11 +9000,11 @@
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -9013,12 +9013,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FBA79963</t>
+          <t>FBA80114</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0HBVYQLS4</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>AM-Pro8</t>
+          <t>AH-53</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9036,11 +9036,11 @@
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -9085,12 +9085,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FBA80114</t>
+          <t>FBA80115</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>B0HBVYQLS4</t>
+          <t>B0HBWD8WWW</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>AH-53</t>
+          <t>AH-50-DH</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -9148,7 +9148,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -9157,12 +9157,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>FBA80115</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>B0HBWD8WWW</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>AH-50-DH</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -9180,7 +9180,7 @@
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -9193,12 +9193,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>FBA80121</t>
+          <t>FBA80141</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>B0HBWHNKDS</t>
+          <t>B0FJS57732</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>AM-C55</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -9216,11 +9216,11 @@
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
-        <v>500</v>
+        <v>1008</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -9229,12 +9229,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>FBA80123</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>B0HBWM83FL</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>AM-W25</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -9252,7 +9252,7 @@
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -9288,7 +9288,7 @@
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -9301,12 +9301,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FBA80141</t>
+          <t>FBA79964</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>B0FJS57732</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-Pro12</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -9324,7 +9324,7 @@
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -9337,12 +9337,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -9360,7 +9360,7 @@
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -9396,7 +9396,7 @@
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -9409,12 +9409,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>FBA79964</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>AM-Pro12</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -9432,11 +9432,11 @@
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -9445,14 +9445,10 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FBA79961</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>B0G53H49BS</t>
-        </is>
-      </c>
+          <t>FBA80299</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9460,7 +9456,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>M8 Speaker</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -9468,11 +9464,11 @@
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
-        <v>1500</v>
+        <v>20</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -9481,14 +9477,10 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>FBA79966</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>B0G53KWRVW</t>
-        </is>
-      </c>
+          <t>FBA80181</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9496,7 +9488,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AI-04 Pro</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -9504,11 +9496,11 @@
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -9517,12 +9509,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9532,7 +9524,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -9540,11 +9532,11 @@
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -9553,12 +9545,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9568,7 +9560,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -9576,11 +9568,11 @@
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -9589,10 +9581,14 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>FBA80299</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr"/>
+          <t>FBA75673</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>B0B4DPX2J2</t>
+        </is>
+      </c>
       <c r="C255" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9600,7 +9596,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>M8 Speaker</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -9608,11 +9604,11 @@
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
-        <v>20</v>
+        <v>2508</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -9621,10 +9617,14 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>FBA80181</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr"/>
+          <t>FBA75673</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>B0B4DPX2J2</t>
+        </is>
+      </c>
       <c r="C256" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9632,7 +9632,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>AI-04 Pro</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -9640,7 +9640,7 @@
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
-        <v>1000</v>
+        <v>2496</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -9653,12 +9653,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -9676,11 +9676,11 @@
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="n">
-        <v>1000</v>
+        <v>2010</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -9689,12 +9689,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA79972</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -9712,7 +9712,7 @@
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -9725,12 +9725,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -9748,11 +9748,11 @@
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="n">
-        <v>2508</v>
+        <v>2025</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -9761,12 +9761,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -9784,7 +9784,7 @@
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="n">
-        <v>2496</v>
+        <v>1512</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -9797,12 +9797,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79983</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0GN321RXQ</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-S6</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -9820,11 +9820,11 @@
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="n">
-        <v>2010</v>
+        <v>49</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -9833,12 +9833,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -9856,7 +9856,7 @@
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="n">
-        <v>3000</v>
+        <v>976</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -9869,12 +9869,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -9892,11 +9892,11 @@
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="n">
-        <v>200</v>
+        <v>1024</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -9905,12 +9905,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -9928,11 +9928,11 @@
       <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="n">
-        <v>500</v>
+        <v>888</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -9941,12 +9941,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -9964,7 +9964,7 @@
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="n">
-        <v>2025</v>
+        <v>2000</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -9977,12 +9977,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -10000,11 +10000,11 @@
       <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="n">
-        <v>1512</v>
+        <v>92</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -10013,12 +10013,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>FBA79983</t>
+          <t>FBA79830</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>B0GN321RXQ</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>AM-S6</t>
+          <t>GB-03 (AI-12 + AM-C43)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -10036,11 +10036,11 @@
       <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="n">
-        <v>49</v>
+        <v>1000</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -10049,12 +10049,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79968</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -10072,7 +10072,7 @@
       <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="n">
-        <v>976</v>
+        <v>100</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -10085,12 +10085,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA80109</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0H2ZCQFTZ</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -10108,7 +10108,7 @@
       <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="n">
-        <v>1024</v>
+        <v>50</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -10121,12 +10121,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA80122</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0HBWGNK1T</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-C56</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -10144,411 +10144,15 @@
       <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="n">
-        <v>888</v>
+        <v>504</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>FBA79848</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>AM-S2</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>FBA79848</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>AM-S2</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="n">
-        <v>92</v>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>FBA79830</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>B0FJ8TSQK1</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
-      <c r="I273" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>FBA79968</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>B0G53M9258</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>AI-14</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr"/>
-      <c r="I274" t="n">
-        <v>500</v>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>FBA79968</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>B0G53M9258</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>AI-14</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
-      <c r="I275" t="n">
-        <v>100</v>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>FBA80109</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>B0H2ZCQFTZ</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr"/>
-      <c r="I276" t="n">
-        <v>50</v>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>FBA80125</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>B0H15CTPGS</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>AA-27</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="n">
-        <v>50</v>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>FBA80126</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>B0HBWQP96C</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>AA-28</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
-      <c r="I278" t="n">
-        <v>60</v>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>FBA80119</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>B0HBWNJSSQ</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>AM-C53</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
-      <c r="H279" t="inlineStr"/>
-      <c r="I279" t="n">
-        <v>510</v>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>FBA80120</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>B0HBWNWZVC</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>AM-C54</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr"/>
-      <c r="I280" t="n">
-        <v>510</v>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>FBA80122</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>B0HBWGNK1T</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>AM-C56</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr"/>
-      <c r="H281" t="inlineStr"/>
-      <c r="I281" t="n">
-        <v>504</v>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L270"/>
+  <dimension ref="A1:L279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,7 +504,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>1115</v>
+        <v>966</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>1703</v>
+        <v>1662</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>772</v>
+        <v>704</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -769,12 +769,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBA79449</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AM-W36</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -792,7 +792,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -805,12 +805,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA79447</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AM-W34</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -828,7 +828,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -841,12 +841,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FBA79447</t>
+          <t>FBA79103</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AM-W34</t>
+          <t>AI-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -864,7 +864,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>130</v>
+        <v>1110</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -877,12 +877,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FBA79103</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AI-10</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -900,7 +900,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>1127</v>
+        <v>938</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -913,12 +913,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA75678</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AA-01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -936,7 +936,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>1210</v>
+        <v>329</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBA75675</t>
+          <t>FBA79448</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AM-C3</t>
+          <t>AM-W35</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -972,7 +972,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>268</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -985,12 +985,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBA75678</t>
+          <t>FBA75684</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AA-01</t>
+          <t>AA-04</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>334</v>
+        <v>163</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1021,12 +1021,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FBA79448</t>
+          <t>FBA79009</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>269</v>
+        <v>92</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1057,12 +1057,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBA75684</t>
+          <t>FBA79482</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AA-04</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>173</v>
+        <v>674</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1093,12 +1093,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FBA79009</t>
+          <t>FBA77171</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t xml:space="preserve">AC-6XL	</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>97</v>
+        <v>1283</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1129,12 +1129,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FBA79482</t>
+          <t>FBA78960</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>AM-C39</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1152,7 +1152,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>935</v>
+        <v>65</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1165,12 +1165,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FBA77171</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">AC-6XL	</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1188,7 +1188,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>1516</v>
+        <v>313</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBA78960</t>
+          <t>FBA79444</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AM-C39</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>251</v>
+        <v>100</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1237,12 +1237,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA79444</t>
+          <t>FBA75690</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AM-C10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>100</v>
+        <v>427</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1273,12 +1273,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBA75690</t>
+          <t>FBA75676</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AM-C10</t>
+          <t>AM-C4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>445</v>
+        <v>13</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1309,12 +1309,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA75676</t>
+          <t>FBA75681</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0B4FZS38V</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AM-C4</t>
+          <t>AM-C7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1345,12 +1345,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBA75681</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B0B4FZS38V</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AM-C7</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1368,7 +1368,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1381,12 +1381,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA78925</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AM-C11X</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1404,7 +1404,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1417,12 +1417,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA78925</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AM-C11X</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1440,7 +1440,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1453,12 +1453,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA78420</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0C5957W3P</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AM-C33</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1489,12 +1489,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FBA78420</t>
+          <t>FBA79008</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B0C5957W3P</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AM-C33</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1525,12 +1525,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FBA79008</t>
+          <t>FBA75688</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AI-06</t>
+          <t>AM-W12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>75</v>
+        <v>296</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1561,12 +1561,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FBA75688</t>
+          <t>FBA78976</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AM-W12</t>
+          <t>AA-22</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1584,7 +1584,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>359</v>
+        <v>260</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1597,12 +1597,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FBA78976</t>
+          <t>FBA79064</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AA-22</t>
+          <t>AA-25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1620,7 +1620,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>276</v>
+        <v>485</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1633,12 +1633,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FBA79064</t>
+          <t>FBA79104</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AA-25</t>
+          <t>AI-11</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1656,7 +1656,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>515</v>
+        <v>121</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1669,12 +1669,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FBA79104</t>
+          <t>FBA79379</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI-11</t>
+          <t>AM-C45</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>366</v>
+        <v>668</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1705,12 +1705,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FBA79379</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AM-C45</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>671</v>
+        <v>4</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1741,12 +1741,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA79722</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0F2HYY7JF</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1764,7 +1764,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FBA79722</t>
+          <t>FBA76716</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B0F2HYY7JF</t>
+          <t>B0BLK8DNPD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-C13</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1800,7 +1800,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1813,12 +1813,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA76716</t>
+          <t>FBA76730</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B0BLK8DNPD</t>
+          <t>B0BLKB6FRR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AM-C13</t>
+          <t>AM-C27</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1836,7 +1836,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1849,12 +1849,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBA76730</t>
+          <t>FBA78423</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B0BLKB6FRR</t>
+          <t>B0C598Q6PT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AM-C27</t>
+          <t>AM-C36</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1872,7 +1872,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1885,12 +1885,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBA78423</t>
+          <t>FBA78974</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B0C598Q6PT</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AM-C36</t>
+          <t>AA-20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1908,7 +1908,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>43</v>
+        <v>352</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -1921,12 +1921,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBA78974</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AA-20</t>
+          <t>AM-C2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1944,7 +1944,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>358</v>
+        <v>91</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -1957,12 +1957,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AM-C2</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1980,7 +1980,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>121</v>
+        <v>286</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -1993,12 +1993,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA76742</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0BLKBJ5HN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-K1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2016,7 +2016,7 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>518</v>
+        <v>8</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2029,12 +2029,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FBA76742</t>
+          <t>FBA75689</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B0BLKBJ5HN</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AM-K1</t>
+          <t>AM-W13</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2052,7 +2052,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>11</v>
+        <v>124</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2065,12 +2065,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FBA75689</t>
+          <t>FBA75679</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AM-W13</t>
+          <t>AA-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2088,7 +2088,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>212</v>
+        <v>771</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2101,12 +2101,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FBA75679</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AA-02</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2124,7 +2124,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>771</v>
+        <v>1433</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2137,12 +2137,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA79355</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2160,7 +2160,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>1433</v>
+        <v>33</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2173,12 +2173,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FBA79355</t>
+          <t>FBA78203</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>AM-C30</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2209,12 +2209,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FBA78203</t>
+          <t>FBA79010</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AM-C30</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2232,7 +2232,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2245,12 +2245,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FBA79010</t>
+          <t>FBA75691</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AM-W14</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2268,7 +2268,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2281,12 +2281,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FBA75691</t>
+          <t>FBA78205</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0C539RBGL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AM-W14</t>
+          <t>AM-C32</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>166</v>
+        <v>4</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2317,12 +2317,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FBA78205</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B0C539RBGL</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AM-C32</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA77011</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0BPMN89NG</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-C29</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2376,7 +2376,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2389,12 +2389,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FBA77011</t>
+          <t>FBA78425</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B0BPMN89NG</t>
+          <t>B0C55QXL83</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AM-C29</t>
+          <t>AM-C38</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2412,7 +2412,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2425,12 +2425,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FBA78425</t>
+          <t>FBA76715</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B0C55QXL83</t>
+          <t>B0BLK31PYH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AM-C38</t>
+          <t>AM-C12</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2448,7 +2448,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2461,12 +2461,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FBA76715</t>
+          <t>FBA78206</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B0BLK31PYH</t>
+          <t>B0C4YSV3XL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>AM-C12</t>
+          <t>AM-W15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2497,12 +2497,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FBA78206</t>
+          <t>FBA79070</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B0C4YSV3XL</t>
+          <t>B0CLH7G5WH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AM-W15</t>
+          <t>AI-02</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2533,12 +2533,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FBA79070</t>
+          <t>FBA76721</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B0CLH7G5WH</t>
+          <t>B0BLKB55BM</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AI-02</t>
+          <t>AM-C18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2569,12 +2569,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FBA76721</t>
+          <t>FBA76726</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B0BLKB55BM</t>
+          <t>B0BLKD4815</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AM-C18</t>
+          <t>AM-C23</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2605,12 +2605,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FBA76726</t>
+          <t>FBA78422</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B0BLKD4815</t>
+          <t>B0C598MNMC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AM-C23</t>
+          <t>AM-C35</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2628,7 +2628,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2641,12 +2641,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBA78422</t>
+          <t>FBA76718</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B0C598MNMC</t>
+          <t>B0BLKD8FVG</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AM-C35</t>
+          <t>AM-C15</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA76718</t>
+          <t>FBA76734</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B0BLKD8FVG</t>
+          <t>B0BLKHVCDX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AM-C15</t>
+          <t>AA-07</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2700,7 +2700,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2713,12 +2713,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FBA76734</t>
+          <t>FBA76739</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B0BLKHVCDX</t>
+          <t>B0BLRK37TB</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AA-07</t>
+          <t>AA-12</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2736,7 +2736,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2749,12 +2749,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FBA76739</t>
+          <t>FBA76725</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B0BLRK37TB</t>
+          <t>B0BLKCSJ7Z</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AA-12</t>
+          <t>AM-C22</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2785,12 +2785,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FBA76725</t>
+          <t>FBA75682</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B0BLKCSJ7Z</t>
+          <t>B0B4FVV78V</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AM-C22</t>
+          <t>AM-C8</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2808,7 +2808,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2821,12 +2821,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FBA75682</t>
+          <t>FBA79014</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B0B4FVV78V</t>
+          <t>B0CH4WFQF6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AM-C8</t>
+          <t>AI-09</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2857,12 +2857,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FBA79014</t>
+          <t>FBA79230</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B0CH4WFQF6</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AI-09</t>
+          <t>AM-W46</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -2893,12 +2893,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBA79230</t>
+          <t>FBA76743</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0BLK8PXNY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AM-W46</t>
+          <t>AM-K2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2916,7 +2916,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -2929,12 +2929,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FBA76743</t>
+          <t>FBA79013</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B0BLK8PXNY</t>
+          <t>B0CH4TDGPG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AM-K2</t>
+          <t>AI-08</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2952,7 +2952,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -2965,12 +2965,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FBA79013</t>
+          <t>FBA78421</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B0CH4TDGPG</t>
+          <t>B0C594FZLM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AI-08</t>
+          <t>AM-C34</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3001,12 +3001,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FBA78421</t>
+          <t>FBA75685</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B0C594FZLM</t>
+          <t>B0B4FXDHXW</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AM-C34</t>
+          <t>AM-C9</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3037,12 +3037,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBA75685</t>
+          <t>FBA75677</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B0B4FXDHXW</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AM-C9</t>
+          <t>AM-C5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3060,7 +3060,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>1657</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3073,12 +3073,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FBA75677</t>
+          <t>FBA76729</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0BLNDQ757</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>AM-C5</t>
+          <t>AM-C26</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3096,7 +3096,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>1684</v>
+        <v>1</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3109,12 +3109,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FBA76729</t>
+          <t>FBA76735</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B0BLNDQ757</t>
+          <t>B0BLKGPL4X</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AM-C26</t>
+          <t>AA-08</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3145,12 +3145,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBA76735</t>
+          <t>FBA76736</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B0BLKGPL4X</t>
+          <t>B0BLS63XCL</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AA-08</t>
+          <t>AA-09</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3168,7 +3168,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3181,12 +3181,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FBA76736</t>
+          <t>FBA76741</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B0BLS63XCL</t>
+          <t>B0BLS2HJ68</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AA-09</t>
+          <t>AA-14</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3217,12 +3217,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FBA76741</t>
+          <t>FBA76863</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B0BLS2HJ68</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AA-14</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3253,12 +3253,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FBA76863</t>
+          <t>FBA78424</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AM-C37</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
-        <v>139</v>
+        <v>2</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3289,12 +3289,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBA78424</t>
+          <t>FBA78419</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0C55M2GBN</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AM-C37</t>
+          <t>AM-A1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3312,7 +3312,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3325,12 +3325,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBA78419</t>
+          <t>FBA76737</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B0C55M2GBN</t>
+          <t>B0C59G1C4N</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AM-A1</t>
+          <t>AA-10</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3348,7 +3348,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3361,12 +3361,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FBA76737</t>
+          <t>FBA76732</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B0C59G1C4N</t>
+          <t>B0BLKCB2JY</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AA-10</t>
+          <t>AS-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3397,12 +3397,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FBA76732</t>
+          <t>FBA79356</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B0BLKCB2JY</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AS-01</t>
+          <t>AA-19 WL</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3420,7 +3420,7 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>168</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3433,12 +3433,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3456,7 +3456,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
-        <v>60</v>
+        <v>774</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3469,12 +3469,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FBA79356</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AA-19 WL</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3492,7 +3492,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
-        <v>871</v>
+        <v>1568</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3541,12 +3541,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA79820</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AC-3XL</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>346</v>
+        <v>671</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3577,12 +3577,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA79815</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3600,7 +3600,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
-        <v>1573</v>
+        <v>209</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3613,12 +3613,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FBA79820</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AC-3XL</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3636,7 +3636,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
-        <v>703</v>
+        <v>841</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -3649,12 +3649,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBA79815</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3672,7 +3672,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>209</v>
+        <v>1251</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3685,12 +3685,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3708,7 +3708,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>845</v>
+        <v>351</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3721,12 +3721,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AH-60 RD</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3744,7 +3744,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
-        <v>1302</v>
+        <v>402</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -3757,12 +3757,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA79841</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AH-60 BL</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
-        <v>625</v>
+        <v>286</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -3793,12 +3793,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AH-60 RD</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>428</v>
+        <v>2996</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -3829,12 +3829,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AH-60 BL</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3852,7 +3852,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
-        <v>333</v>
+        <v>203</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -3865,12 +3865,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA79958</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3888,7 +3888,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>203</v>
+        <v>157</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -3901,12 +3901,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA79961</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>180</v>
+        <v>1435</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -3937,12 +3937,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA79962</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AM-Mix4 OTG(BE-4T)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3960,7 +3960,7 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -3973,12 +3973,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBA79962</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AM-Mix4</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4009,12 +4009,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4045,12 +4045,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA79968</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -4068,7 +4068,7 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
-        <v>7</v>
+        <v>598</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4081,12 +4081,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA79972</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -4104,7 +4104,7 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4117,12 +4117,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79957</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-W23</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -4140,7 +4140,7 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>228</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4153,12 +4153,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79654</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>AM-W47 WIRELESS</t>
+          <t>AM-C11 PRO</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -4176,7 +4176,7 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>30</v>
+        <v>559</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4189,12 +4189,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA79956</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0GMPGNXX3</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>AM-W47 WIRED</t>
+          <t>A3-XLR</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -4212,7 +4212,7 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
-        <v>23</v>
+        <v>769</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4225,12 +4225,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FBA79957</t>
+          <t>FBA80007</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>AM-W23</t>
+          <t>MT-12</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -4248,7 +4248,7 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
-        <v>228</v>
+        <v>1</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4261,12 +4261,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FBA79654</t>
+          <t>FBA79979</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>AM-C11 PRO</t>
+          <t>AK-37-B</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -4284,7 +4284,7 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="n">
-        <v>564</v>
+        <v>164</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -4297,12 +4297,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FBA79956</t>
+          <t>FBA79980</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B0GMPGNXX3</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>A3-XLR</t>
+          <t>AK-37-W</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -4320,7 +4320,7 @@
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="n">
-        <v>769</v>
+        <v>4</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -4333,12 +4333,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FBA80007</t>
+          <t>FBA80011</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0GTZND3ZN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>MT-12</t>
+          <t>AM-Pro16</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4369,12 +4369,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FBA79979</t>
+          <t>FBA80013</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0GTZLGPFR</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>AK-37-B</t>
+          <t>XM-16</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>206</v>
+        <v>2</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4405,12 +4405,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FBA79980</t>
+          <t>FBA80014</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0GTZ9X8Q2</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>AK-37-W</t>
+          <t>XM-24</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -4428,7 +4428,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -4441,12 +4441,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FBA80011</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>B0GTZND3ZN</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>AM-Pro16</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -4464,7 +4464,7 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>192</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -4477,12 +4477,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBA80013</t>
+          <t>FBA80005</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B0GTZLGPFR</t>
+          <t>B0GW96CQMG</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>XM-16</t>
+          <t>T-835</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -4500,7 +4500,7 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBA80014</t>
+          <t>FBA79975</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>B0GTZ9X8Q2</t>
+          <t>B0GXP7LJ75</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>XM-24</t>
+          <t>AE831</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -4536,7 +4536,7 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -4549,12 +4549,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79996</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-C49</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -4572,7 +4572,7 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
-        <v>7</v>
+        <v>326</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -4585,12 +4585,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FBA80005</t>
+          <t>FBA79995</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B0GW96CQMG</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>T-835</t>
+          <t>AM-C50</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -4608,7 +4608,7 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>11</v>
+        <v>382</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -4621,12 +4621,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FBA79975</t>
+          <t>FBA80009</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B0GXP7LJ75</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>AE831</t>
+          <t>AM-C51</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -4644,7 +4644,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>167</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FBA79996</t>
+          <t>FBA80010</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AM-C49</t>
+          <t>AM-C52</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -4680,7 +4680,7 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>362</v>
+        <v>161</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -4693,12 +4693,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FBA79995</t>
+          <t>FBA79998</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0GW8YC59C</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>AM-C50</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -4716,7 +4716,7 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>382</v>
+        <v>1</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -4729,12 +4729,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FBA80009</t>
+          <t>FBA79999</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0GW92TVVC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>AM-C51</t>
+          <t>JTG800</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -4752,7 +4752,7 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>167</v>
+        <v>16</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -4765,12 +4765,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FBA80010</t>
+          <t>FBA80000</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0GW8XGPB2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>AM-C52</t>
+          <t>DP-718H</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -4788,7 +4788,7 @@
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>161</v>
+        <v>13</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -4801,12 +4801,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBA79998</t>
+          <t>FBA80001</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B0GW8YC59C</t>
+          <t>B0GW92TQGV</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>USB718</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -4824,7 +4824,7 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -4837,12 +4837,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA79999</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0GW92TVVC</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>JTG800</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -4860,7 +4860,7 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -4873,12 +4873,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA80000</t>
+          <t>FBA80085</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0GW8XGPB2</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>DP-718H</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -4896,7 +4896,7 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="n">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -4909,12 +4909,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBA80001</t>
+          <t>FBA80002</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0GW92TQGV</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>USB718</t>
+          <t>AM-W33 pro</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -4932,7 +4932,7 @@
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="n">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -4945,12 +4945,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA80003</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AM-W32 pro</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -4968,7 +4968,7 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -4981,12 +4981,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBA80085</t>
+          <t>FBA80004</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>AM-W36 PRO</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -5004,7 +5004,7 @@
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="n">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -5017,12 +5017,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBA80002</t>
+          <t>FBA80109</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0H2ZCQFTZ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>AM-W33 pro</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -5040,7 +5040,7 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="n">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -5053,12 +5053,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBA80003</t>
+          <t>FBA80110</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0GW92TTMS</t>
+          <t>B0H2Z6R6V8</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>AM-W32 pro</t>
+          <t>X5</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -5076,7 +5076,7 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -5089,12 +5089,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBA80004</t>
+          <t>FBA80142</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0H3LHF2WW</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>AM-W36 PRO</t>
+          <t>AM-C5 White</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -5112,7 +5112,7 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="n">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -5125,12 +5125,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBA80109</t>
+          <t>FBA79654</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0H2ZCQFTZ</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>AM-C11 Pro - AM-C11 &amp; AA-05</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -5148,7 +5148,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="n">
-        <v>7</v>
+        <v>559</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -5161,12 +5161,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBA80110</t>
+          <t>FBA79655</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0H2Z6R6V8</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>X5</t>
+          <t>AM-C44 Pro - AM-C44 &amp; AA-05</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -5184,7 +5184,7 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -5197,12 +5197,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA80142</t>
+          <t>FBA79826</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0H3LHF2WW</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>AM-C5 White</t>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -5220,7 +5220,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
-        <v>251</v>
+        <v>2</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -5233,12 +5233,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FBA79904</t>
+          <t>FBA79846</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+          <t>AM-C11X Pro - AM-C11x &amp; AA-05</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -5269,12 +5269,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FBA79654</t>
+          <t>FBA79822</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>AM-C11 Pro - AM-C11 &amp; AA-05</t>
+          <t>KB-01 (AM-W32 + AI-12)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -5292,7 +5292,7 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="n">
-        <v>564</v>
+        <v>4</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -5305,12 +5305,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA79655</t>
+          <t>FBA79833</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>AM-C44 Pro - AM-C44 &amp; AA-05</t>
+          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -5328,7 +5328,7 @@
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -5341,12 +5341,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA79826</t>
+          <t>FBA79845</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -5364,7 +5364,7 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -5377,12 +5377,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA79846</t>
+          <t>FBA79824</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AM-C11X Pro - AM-C11x &amp; AA-05</t>
+          <t>GB-01 (AM-C43 +AI-10)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -5400,7 +5400,7 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -5413,12 +5413,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA79822</t>
+          <t>FBA79653</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>KB-01 (AM-W32 + AI-12)</t>
+          <t>AM-C45 Pro - AM-C45 &amp; AA-05</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -5436,7 +5436,7 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -5449,12 +5449,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA79825</t>
+          <t>FBA79832</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>GB-02 (AM-C43 + AI-11)</t>
+          <t>GB-05 (AM-C43 + AI-06)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -5472,7 +5472,7 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -5485,12 +5485,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA79830</t>
+          <t>FBA79847</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
+          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -5508,7 +5508,7 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -5521,12 +5521,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FBA79833</t>
+          <t>FBA79831</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
+          <t>GB-04 (AM-C45 + AI-06)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -5557,12 +5557,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FBA79845</t>
+          <t>FBA79905</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>UB-02 (AM-S1 + AA-21)</t>
+          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -5580,7 +5580,7 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -5593,12 +5593,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FBA79824</t>
+          <t>FBA79835</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>GB-01 (AM-C43 +AI-10)</t>
+          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -5616,7 +5616,7 @@
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -5629,12 +5629,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FBA79653</t>
+          <t>FBA79836</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0FJ8Z1W81</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>AM-C45 Pro - AM-C45 &amp; AA-05</t>
+          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -5652,7 +5652,7 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -5665,12 +5665,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FBA79832</t>
+          <t>FBA79908</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>GB-05 (AM-C43 + AI-06)</t>
+          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -5688,7 +5688,7 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -5701,12 +5701,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FBA79906</t>
+          <t>FBA80074</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0GY827J9C</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -5724,7 +5724,7 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -5737,12 +5737,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FBA79847</t>
+          <t>FBA80105</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0H2FNV2RC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
+          <t>UB-05 (AM-S2+AA-21)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -5760,7 +5760,7 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -5773,12 +5773,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FBA79831</t>
+          <t>FBA80119</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>B0FJ8W5Y9Q</t>
+          <t>B0HBWNJSSQ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>GB-04 (AM-C45 + AI-06)</t>
+          <t>AM-C53</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -5796,7 +5796,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
-        <v>12</v>
+        <v>460</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FBA79905</t>
+          <t>FBA80120</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0HBWNWZVC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+          <t>AM-C54</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -5832,7 +5832,7 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>460</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -5845,12 +5845,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FBA79835</t>
+          <t>FBA80121</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>B0FJ8TWCQZ</t>
+          <t>B0HBWHNKDS</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
+          <t>AM-C55</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -5868,7 +5868,7 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
-        <v>3</v>
+        <v>450</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FBA79836</t>
+          <t>FBA80123</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>B0FJ8Z1W81</t>
+          <t>B0HBWM83FL</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
+          <t>AM-W25</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -5904,7 +5904,7 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -5917,12 +5917,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FBA79908</t>
+          <t>FBA80124</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0HBWDYW2G</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+          <t>AA-26 Pro</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -5940,7 +5940,7 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
-        <v>10</v>
+        <v>918</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -5953,12 +5953,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FBA80074</t>
+          <t>FBA80125</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>B0GY827J9C</t>
+          <t>B0H15CTPGS</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
+          <t>AA-27</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -5976,7 +5976,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -5989,12 +5989,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FBA80076</t>
+          <t>FBA80126</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>B0GY857139</t>
+          <t>B0HBWQP96C</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
+          <t>AA-28</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -6012,7 +6012,7 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -6025,12 +6025,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FBA80105</t>
+          <t>FBA80115</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>B0H2FNV2RC</t>
+          <t>B0HBWD8WWW</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>UB-05 (AM-S2+AA-21)</t>
+          <t>AH-50-DH</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -6048,7 +6048,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -6061,12 +6061,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA80117</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0HBW4T618</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AH-53 PRO</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -6084,11 +6084,11 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -6097,12 +6097,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA80114</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0HBVYQLS4</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AH-53</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6120,11 +6120,11 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -6133,12 +6133,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA80116</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0HBW4XTRH</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AH-40 PRO</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -6156,11 +6156,11 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>AMPM</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -6169,12 +6169,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA75676</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AM-C4</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -6192,11 +6192,11 @@
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -6205,12 +6205,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA75690</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AM-C10</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -6228,11 +6228,11 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -6241,12 +6241,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FBA79482</t>
+          <t>FBA75675</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>AM-C3</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -6264,11 +6264,11 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -6277,12 +6277,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FBA75690</t>
+          <t>FBA79448</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>AM-C10</t>
+          <t>AM-W35</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -6313,12 +6313,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -6336,11 +6336,11 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -6349,12 +6349,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA75689</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-W13</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -6372,11 +6372,11 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -6385,12 +6385,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA79103</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AI-10</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -6408,11 +6408,11 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -6421,12 +6421,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FBA79815</t>
+          <t>FBA75688</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AM-W12</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -6457,12 +6457,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -6480,11 +6480,11 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -6493,12 +6493,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -6516,11 +6516,11 @@
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>YNT</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -6529,12 +6529,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FBA75676</t>
+          <t>FBA79008</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>AM-C4</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -6552,7 +6552,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -6565,12 +6565,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FBA75690</t>
+          <t>FBA79482</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>AM-C10</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -6601,12 +6601,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FBA75675</t>
+          <t>FBA75677</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>AM-C3</t>
+          <t>AM-C5</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -6624,7 +6624,7 @@
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -6637,12 +6637,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FBA79448</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -6660,7 +6660,7 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -6673,12 +6673,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -6696,7 +6696,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -6709,12 +6709,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FBA75689</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>AM-W13</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -6732,7 +6732,7 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -6745,12 +6745,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>FBA79103</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>AI-10</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -6768,7 +6768,7 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -6781,12 +6781,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>FBA75688</t>
+          <t>FBA79379</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>AM-W12</t>
+          <t>AM-C45</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -6804,7 +6804,7 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -6817,12 +6817,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -6840,7 +6840,7 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -6853,12 +6853,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -6876,7 +6876,7 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -6889,12 +6889,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>FBA79008</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>AI-06</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -6912,7 +6912,7 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -6925,12 +6925,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FBA79482</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -6948,7 +6948,7 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FBA75677</t>
+          <t>FBA75691</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>AM-C5</t>
+          <t>AM-W14</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -6984,7 +6984,7 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -6997,12 +6997,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA75692</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AM-C11</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -7020,7 +7020,7 @@
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -7033,12 +7033,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -7056,7 +7056,7 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79446</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AM-W33</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -7092,7 +7092,7 @@
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -7105,12 +7105,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -7128,7 +7128,7 @@
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -7141,12 +7141,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FBA79379</t>
+          <t>FBA75684</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>AM-C45</t>
+          <t>AA-04</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -7164,7 +7164,7 @@
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -7177,12 +7177,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA76414</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AA-05</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -7200,7 +7200,7 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -7213,12 +7213,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA79841</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AH-60 BL</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -7236,7 +7236,7 @@
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -7249,12 +7249,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA79447</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AM-W34</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -7272,7 +7272,7 @@
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -7285,12 +7285,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA79230</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-W46</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -7308,7 +7308,7 @@
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -7321,12 +7321,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FBA75691</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>AM-W14</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -7344,7 +7344,7 @@
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -7357,12 +7357,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FBA75692</t>
+          <t>FBA79976</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>AM-C11</t>
+          <t>JT-01, BM 320 Pro</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -7380,7 +7380,7 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -7393,12 +7393,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA79983</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0GN321RXQ</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-W48</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -7416,7 +7416,7 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -7429,12 +7429,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FBA79446</t>
+          <t>FBA79956</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0GMPGNXX3</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>AM-W33</t>
+          <t>A3-XLR</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -7452,7 +7452,7 @@
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -7465,12 +7465,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -7501,12 +7501,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FBA75684</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>AA-04</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -7524,7 +7524,7 @@
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -7537,12 +7537,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FBA76414</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>AA-05</t>
+          <t>AH-60 RD</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -7560,7 +7560,7 @@
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -7573,12 +7573,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA80013</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0GTZLGPFR</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>AH-60 BL</t>
+          <t>XM-16</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -7596,7 +7596,7 @@
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -7609,12 +7609,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FBA79447</t>
+          <t>FBA80014</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0GTZ9X8Q2</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>AM-W34</t>
+          <t>XM-24</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -7645,12 +7645,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FBA79230</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>AM-W46</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -7668,7 +7668,7 @@
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -7681,12 +7681,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -7704,7 +7704,7 @@
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -7717,12 +7717,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>FBA79976</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>JT-01, BM 320 Pro</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -7740,11 +7740,11 @@
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -7753,12 +7753,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>FBA79983</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>B0GN321RXQ</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>AM-W48</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -7789,12 +7789,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>FBA79956</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>B0GMPGNXX3</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>A3-XLR</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -7812,11 +7812,11 @@
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -7825,12 +7825,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -7848,11 +7848,11 @@
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -7861,12 +7861,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -7884,11 +7884,11 @@
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -7897,12 +7897,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA79482</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>AH-60 RD</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -7933,12 +7933,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>FBA80013</t>
+          <t>FBA75690</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>B0GTZLGPFR</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>XM-16</t>
+          <t>AM-C10</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -7956,11 +7956,11 @@
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -7969,12 +7969,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>FBA80014</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>B0GTZ9X8Q2</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>XM-24</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -7992,11 +7992,11 @@
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -8005,12 +8005,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -8028,11 +8028,11 @@
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -8041,12 +8041,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -8064,11 +8064,11 @@
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -8077,12 +8077,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FBA80116</t>
+          <t>FBA79815</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>B0HBW4XTRH</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>AH-40 Pro</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -8100,11 +8100,11 @@
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -8113,12 +8113,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>FBA80116</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>B0HBW4XTRH</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>AH-40 Pro</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -8136,11 +8136,11 @@
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -8149,12 +8149,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FBA80117</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>B0HBW4T618</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>AH-53 Pro</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -8172,11 +8172,11 @@
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>YNT</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -8185,12 +8185,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>FBA80117</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>B0HBW4T618</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>AH-53 Pro</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -8208,11 +8208,11 @@
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -8221,12 +8221,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -8244,11 +8244,11 @@
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="n">
-        <v>504</v>
+        <v>142</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -8257,12 +8257,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -8280,11 +8280,11 @@
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="n">
-        <v>501</v>
+        <v>86</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -8293,12 +8293,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>FBA75687</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>AM-W11</t>
+          <t>AI-04</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -8316,11 +8316,11 @@
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="n">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -8329,12 +8329,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -8352,11 +8352,11 @@
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
-        <v>2000</v>
+        <v>38</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -8365,12 +8365,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA79108</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>AM-W16</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -8388,11 +8388,11 @@
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="n">
-        <v>2000</v>
+        <v>31</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -8401,12 +8401,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -8424,11 +8424,11 @@
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
-        <v>480</v>
+        <v>32</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -8437,12 +8437,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FBA80085</t>
+          <t>FBA79958</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -8460,11 +8460,11 @@
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Blinkit</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -8473,12 +8473,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA80116</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0HBW4XTRH</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AH-40 Pro</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -8496,7 +8496,7 @@
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
-        <v>504</v>
+        <v>100</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -8509,12 +8509,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA80116</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0HBW4XTRH</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AH-40 Pro</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -8532,7 +8532,7 @@
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
-        <v>504</v>
+        <v>100</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -8545,12 +8545,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA80117</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0HBW4T618</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AH-53 Pro</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -8568,11 +8568,11 @@
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
-        <v>504</v>
+        <v>50</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -8581,12 +8581,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA80117</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0HBW4T618</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>AM-C2</t>
+          <t>AH-53 Pro</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -8604,11 +8604,11 @@
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
-        <v>504</v>
+        <v>50</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -8617,12 +8617,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -8640,11 +8640,11 @@
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
-        <v>1000</v>
+        <v>504</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -8653,12 +8653,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>AM-W47 WIRLESS</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -8676,7 +8676,7 @@
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
-        <v>1840</v>
+        <v>501</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -8689,12 +8689,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA75687</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>AM-W47 WIRLESS</t>
+          <t>AM-W11</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -8712,7 +8712,7 @@
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -8725,12 +8725,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>AM-W47 WIRED</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -8761,12 +8761,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>AM-W47 WIRED</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -8797,12 +8797,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -8820,7 +8820,7 @@
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -8833,12 +8833,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>FBA76597</t>
+          <t>FBA80085</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>AA-06</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -8856,11 +8856,11 @@
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -8869,12 +8869,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>FBA76597</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>AA-06</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -8905,12 +8905,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FBA75683</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>AA-03</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -8928,11 +8928,11 @@
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -8941,12 +8941,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>FBA79962</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>BE-4T</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -8964,11 +8964,11 @@
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
-        <v>400</v>
+        <v>504</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -8977,12 +8977,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>FBA79963</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>AM-Pro8</t>
+          <t>AM-C2</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -9000,11 +9000,11 @@
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
-        <v>10</v>
+        <v>504</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -9013,12 +9013,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FBA80114</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>B0HBVYQLS4</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>AH-53</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9036,11 +9036,11 @@
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -9049,12 +9049,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>FBA80114</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>B0HBVYQLS4</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>AH-53</t>
+          <t>AM-W47 WIRLESS</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -9072,11 +9072,11 @@
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="n">
-        <v>100</v>
+        <v>1840</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -9085,12 +9085,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FBA80115</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>B0HBWD8WWW</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>AH-50-DH</t>
+          <t>AM-W47 WIRLESS</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -9108,11 +9108,11 @@
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -9121,12 +9121,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FBA80115</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>B0HBWD8WWW</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>AH-50-DH</t>
+          <t>AM-W47 WIRED</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -9144,11 +9144,11 @@
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -9157,12 +9157,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AM-W47 WIRED</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -9180,7 +9180,7 @@
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -9193,12 +9193,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>FBA80141</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>B0FJS57732</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -9216,7 +9216,7 @@
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -9229,12 +9229,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA76597</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AA-06</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -9252,7 +9252,7 @@
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
-        <v>400</v>
+        <v>504</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -9265,12 +9265,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA75683</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AA-03</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -9301,12 +9301,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FBA79964</t>
+          <t>FBA79962</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>AM-Pro12</t>
+          <t>BE-4T</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -9324,11 +9324,11 @@
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="n">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -9337,12 +9337,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA79963</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AM-Pro8</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -9360,11 +9360,11 @@
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -9373,12 +9373,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA80114</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0HBVYQLS4</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AH-53</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -9396,11 +9396,11 @@
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -9409,12 +9409,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA80114</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0HBVYQLS4</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AH-53</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -9445,10 +9445,14 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FBA80299</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr"/>
+          <t>FBA80115</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>B0HBWD8WWW</t>
+        </is>
+      </c>
       <c r="C251" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9456,7 +9460,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>M8 Speaker</t>
+          <t>AH-50-DH</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -9464,11 +9468,11 @@
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -9477,10 +9481,14 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>FBA80181</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr"/>
+          <t>FBA80115</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>B0HBWD8WWW</t>
+        </is>
+      </c>
       <c r="C252" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9488,7 +9496,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>AI-04 Pro</t>
+          <t>AH-50-DH</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -9496,7 +9504,7 @@
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -9509,12 +9517,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9524,7 +9532,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -9536,7 +9544,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -9545,12 +9553,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA80141</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0FJS57732</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9560,7 +9568,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -9568,7 +9576,7 @@
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -9581,12 +9589,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9596,7 +9604,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -9604,7 +9612,7 @@
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
-        <v>2508</v>
+        <v>400</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -9617,12 +9625,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9632,7 +9640,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -9640,7 +9648,7 @@
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
-        <v>2496</v>
+        <v>500</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -9653,12 +9661,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79964</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9668,7 +9676,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-Pro12</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -9676,7 +9684,7 @@
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="n">
-        <v>2010</v>
+        <v>50</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -9689,12 +9697,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9704,7 +9712,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -9712,11 +9720,11 @@
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -9725,12 +9733,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9740,7 +9748,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -9748,7 +9756,7 @@
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="n">
-        <v>2025</v>
+        <v>200</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -9761,12 +9769,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9776,7 +9784,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -9784,11 +9792,11 @@
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="n">
-        <v>1512</v>
+        <v>100</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -9797,14 +9805,10 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>FBA79983</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>B0GN321RXQ</t>
-        </is>
-      </c>
+          <t>FBA80299</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9812,7 +9816,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>AM-S6</t>
+          <t>M8 Speaker</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -9820,11 +9824,11 @@
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -9833,14 +9837,10 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>FBA79848</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
+          <t>FBA80181</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
       <c r="C262" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AI-04 Pro</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -9856,11 +9856,11 @@
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="n">
-        <v>976</v>
+        <v>1000</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -9869,12 +9869,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -9892,11 +9892,11 @@
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="n">
-        <v>1024</v>
+        <v>1000</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -9905,12 +9905,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -9928,11 +9928,11 @@
       <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="n">
-        <v>888</v>
+        <v>1000</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -9941,12 +9941,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -9964,11 +9964,11 @@
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="n">
-        <v>2000</v>
+        <v>2508</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -9977,12 +9977,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -10000,11 +10000,11 @@
       <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="n">
-        <v>92</v>
+        <v>2496</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -10013,12 +10013,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>FBA79830</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -10036,7 +10036,7 @@
       <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="n">
-        <v>1000</v>
+        <v>2010</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -10049,12 +10049,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA79972</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -10072,11 +10072,11 @@
       <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -10085,12 +10085,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>FBA80109</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>B0H2ZCQFTZ</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -10108,7 +10108,7 @@
       <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="n">
-        <v>50</v>
+        <v>2025</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -10121,12 +10121,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>FBA80122</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>B0HBWGNK1T</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>AM-C56</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -10144,7 +10144,7 @@
       <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -10153,6 +10153,330 @@
       </c>
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>FBA79983</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>B0GN321RXQ</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>AM-S6</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="n">
+        <v>49</v>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>FBA79848</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="n">
+        <v>976</v>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>FBA79848</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>FBA79848</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="n">
+        <v>888</v>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>FBA79848</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>AM-S2</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="n">
+        <v>92</v>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>FBA79830</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>B0FJ8TSQK1</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>GB-03 (AI-12 + AM-C43)</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>FBA79968</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>B0G53M9258</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>AI-14</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="n">
+        <v>100</v>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>FBA80109</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>B0H2ZCQFTZ</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="n">
+        <v>50</v>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>FBA80122</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>B0HBWGNK1T</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>AM-C56</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="n">
+        <v>504</v>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input/Inventory_snapshot_audio_array.xlsx
+++ b/data/input/Inventory_snapshot_audio_array.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L279"/>
+  <dimension ref="A1:L270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -8509,12 +8509,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>FBA80116</t>
+          <t>FBA80117</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>B0HBW4XTRH</t>
+          <t>B0HBW4T618</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>AH-40 Pro</t>
+          <t>AH-53 Pro</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -8532,7 +8532,7 @@
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -8545,12 +8545,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FBA80117</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>B0HBW4T618</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>AH-53 Pro</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -8568,7 +8568,7 @@
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
-        <v>50</v>
+        <v>504</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -8581,12 +8581,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FBA80117</t>
+          <t>FBA75687</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>B0HBW4T618</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>AH-53 Pro</t>
+          <t>AM-W11</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -8604,7 +8604,7 @@
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -8617,12 +8617,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -8640,7 +8640,7 @@
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
-        <v>504</v>
+        <v>2040</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -8653,12 +8653,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -8676,11 +8676,11 @@
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
-        <v>501</v>
+        <v>2000</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -8689,12 +8689,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>FBA75687</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>AM-W11</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -8712,7 +8712,7 @@
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -8725,12 +8725,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA80085</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -8748,11 +8748,11 @@
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -8761,12 +8761,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -8784,11 +8784,11 @@
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
-        <v>2000</v>
+        <v>504</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -8797,12 +8797,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -8820,7 +8820,7 @@
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -8833,12 +8833,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>FBA80085</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -8856,7 +8856,7 @@
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -8869,12 +8869,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AM-C2</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -8905,12 +8905,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -8928,7 +8928,7 @@
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
-        <v>504</v>
+        <v>1000</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -8941,12 +8941,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AM-W47 WIRLESS</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -8964,11 +8964,11 @@
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
-        <v>504</v>
+        <v>1840</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -8977,12 +8977,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>AM-C2</t>
+          <t>AM-W47 WIRLESS</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -9000,11 +9000,11 @@
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
-        <v>504</v>
+        <v>2000</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -9013,12 +9013,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-W47 WIRED</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9036,11 +9036,11 @@
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -9049,12 +9049,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>AM-W47 WIRLESS</t>
+          <t>AM-W47 WIRED</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -9072,11 +9072,11 @@
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="n">
-        <v>1840</v>
+        <v>2000</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -9085,12 +9085,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>AM-W47 WIRLESS</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -9108,7 +9108,7 @@
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -9121,12 +9121,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA76597</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>AM-W47 WIRED</t>
+          <t>AA-06</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -9144,7 +9144,7 @@
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="n">
-        <v>2000</v>
+        <v>504</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -9157,12 +9157,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA75683</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>AM-W47 WIRED</t>
+          <t>AA-03</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -9180,11 +9180,11 @@
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -9193,12 +9193,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA79962</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>BE-4T</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -9216,11 +9216,11 @@
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -9229,12 +9229,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>FBA76597</t>
+          <t>FBA79963</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>AA-06</t>
+          <t>AM-Pro8</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -9252,11 +9252,11 @@
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
-        <v>504</v>
+        <v>10</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -9265,12 +9265,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>FBA75683</t>
+          <t>FBA80114</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0HBVYQLS4</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>AA-03</t>
+          <t>AH-53</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -9288,11 +9288,11 @@
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -9301,12 +9301,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FBA79962</t>
+          <t>FBA80115</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0HBWD8WWW</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>BE-4T</t>
+          <t>AH-50-DH</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -9324,11 +9324,11 @@
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -9337,12 +9337,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>FBA79963</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>AM-Pro8</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -9360,7 +9360,7 @@
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>FBA80114</t>
+          <t>FBA80141</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>B0HBVYQLS4</t>
+          <t>B0FJS57732</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>AH-53</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -9396,11 +9396,11 @@
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
-        <v>100</v>
+        <v>1008</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -9409,12 +9409,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>FBA80114</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>B0HBVYQLS4</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>AH-53</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -9432,7 +9432,7 @@
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -9445,12 +9445,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FBA80115</t>
+          <t>FBA79964</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>B0HBWD8WWW</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>AH-50-DH</t>
+          <t>AM-Pro12</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -9468,11 +9468,11 @@
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -9481,12 +9481,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>FBA80115</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>B0HBWD8WWW</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>AH-50-DH</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -9504,7 +9504,7 @@
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -9517,12 +9517,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -9540,11 +9540,11 @@
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -9553,14 +9553,10 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>FBA80141</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>B0FJS57732</t>
-        </is>
-      </c>
+          <t>FBA80299</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
       <c r="C254" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9568,7 +9564,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>M8 Speaker</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -9576,7 +9572,7 @@
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
-        <v>1008</v>
+        <v>20</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -9589,14 +9585,10 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>FBA80084</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>B0GXP97CZG</t>
-        </is>
-      </c>
+          <t>FBA80181</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9604,7 +9596,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AI-04 Pro</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -9612,11 +9604,11 @@
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -9625,12 +9617,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9640,7 +9632,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -9648,11 +9640,11 @@
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -9661,12 +9653,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>FBA79964</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9676,7 +9668,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>AM-Pro12</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -9684,7 +9676,7 @@
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -9697,12 +9689,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9712,7 +9704,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -9720,7 +9712,7 @@
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="n">
-        <v>100</v>
+        <v>2508</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -9733,12 +9725,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9748,7 +9740,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -9756,7 +9748,7 @@
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="n">
-        <v>200</v>
+        <v>2496</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -9769,12 +9761,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9784,7 +9776,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -9792,11 +9784,11 @@
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="n">
-        <v>100</v>
+        <v>2010</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -9805,10 +9797,14 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>FBA80299</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr"/>
+          <t>FBA79972</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>B0GCP1J2HC</t>
+        </is>
+      </c>
       <c r="C261" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9816,7 +9812,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>M8 Speaker</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -9824,7 +9820,7 @@
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -9837,10 +9833,14 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>FBA80181</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr"/>
+          <t>FBA79838</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>B0FQBX8J17</t>
+        </is>
+      </c>
       <c r="C262" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>AI-04 Pro</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -9856,7 +9856,7 @@
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="n">
-        <v>1000</v>
+        <v>2025</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -9869,12 +9869,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -9892,11 +9892,11 @@
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="n">
-        <v>1000</v>
+        <v>1512</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -9905,12 +9905,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA79983</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0GN321RXQ</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AM-S6</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -9928,11 +9928,11 @@
       <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="n">
-        <v>1000</v>
+        <v>49</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -9941,12 +9941,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -9964,7 +9964,7 @@
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="n">
-        <v>2508</v>
+        <v>976</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -9977,12 +9977,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -10000,7 +10000,7 @@
       <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="n">
-        <v>2496</v>
+        <v>1024</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -10036,11 +10036,11 @@
       <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="n">
-        <v>2010</v>
+        <v>92</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Open Order</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -10049,12 +10049,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79830</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>GB-03 (AI-12 + AM-C43)</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -10072,7 +10072,7 @@
       <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -10085,12 +10085,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA80109</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0H2ZCQFTZ</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -10108,7 +10108,7 @@
       <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="n">
-        <v>2025</v>
+        <v>50</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -10121,12 +10121,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA80122</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0HBWGNK1T</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AM-C56</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -10144,7 +10144,7 @@
       <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="n">
-        <v>1512</v>
+        <v>504</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -10153,330 +10153,6 @@
       </c>
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>FBA79983</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>B0GN321RXQ</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>AM-S6</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="n">
-        <v>49</v>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>FBA79848</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>AM-S2</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="n">
-        <v>976</v>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>FBA79848</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>AM-S2</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
-      <c r="I273" t="n">
-        <v>1024</v>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>FBA79848</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>AM-S2</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr"/>
-      <c r="I274" t="n">
-        <v>888</v>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>FBA79848</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>AM-S2</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
-      <c r="I275" t="n">
-        <v>92</v>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>FBA79830</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>B0FJ8TSQK1</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr"/>
-      <c r="I276" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>FBA79968</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>B0G53M9258</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>AI-14</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="n">
-        <v>100</v>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>FBA80109</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>B0H2ZCQFTZ</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
-      <c r="I278" t="n">
-        <v>50</v>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>FBA80122</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>B0HBWGNK1T</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>AM-C56</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
-      <c r="H279" t="inlineStr"/>
-      <c r="I279" t="n">
-        <v>504</v>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
